--- a/backtest/5日周期交易计划_2026_回测结果.xlsx
+++ b/backtest/5日周期交易计划_2026_回测结果.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="707">
   <si>
     <t>指标</t>
   </si>
@@ -195,90 +195,90 @@
     <t>688787</t>
   </si>
   <si>
+    <t>688031</t>
+  </si>
+  <si>
+    <t>002517</t>
+  </si>
+  <si>
+    <t>601339</t>
+  </si>
+  <si>
+    <t>600783</t>
+  </si>
+  <si>
+    <t>601116</t>
+  </si>
+  <si>
+    <t>603966</t>
+  </si>
+  <si>
     <t>688248</t>
   </si>
   <si>
-    <t>603966</t>
-  </si>
-  <si>
-    <t>601116</t>
-  </si>
-  <si>
     <t>600828</t>
   </si>
   <si>
-    <t>601339</t>
-  </si>
-  <si>
-    <t>002517</t>
-  </si>
-  <si>
-    <t>688031</t>
-  </si>
-  <si>
-    <t>600783</t>
-  </si>
-  <si>
     <t>300986</t>
   </si>
   <si>
+    <t>603163</t>
+  </si>
+  <si>
+    <t>001360</t>
+  </si>
+  <si>
+    <t>605287</t>
+  </si>
+  <si>
+    <t>300835</t>
+  </si>
+  <si>
+    <t>001337</t>
+  </si>
+  <si>
+    <t>688628</t>
+  </si>
+  <si>
+    <t>603949</t>
+  </si>
+  <si>
+    <t>605080</t>
+  </si>
+  <si>
     <t>600686</t>
   </si>
   <si>
-    <t>605080</t>
-  </si>
-  <si>
-    <t>603949</t>
-  </si>
-  <si>
     <t>688084</t>
   </si>
   <si>
-    <t>688628</t>
-  </si>
-  <si>
-    <t>001337</t>
-  </si>
-  <si>
-    <t>300835</t>
-  </si>
-  <si>
-    <t>605287</t>
-  </si>
-  <si>
-    <t>001360</t>
-  </si>
-  <si>
-    <t>603163</t>
-  </si>
-  <si>
     <t>601615</t>
   </si>
   <si>
+    <t>600926</t>
+  </si>
+  <si>
+    <t>002995</t>
+  </si>
+  <si>
+    <t>601225</t>
+  </si>
+  <si>
+    <t>603311</t>
+  </si>
+  <si>
+    <t>000968</t>
+  </si>
+  <si>
     <t>688210</t>
   </si>
   <si>
+    <t>002679</t>
+  </si>
+  <si>
     <t>002658</t>
   </si>
   <si>
-    <t>000968</t>
-  </si>
-  <si>
-    <t>002679</t>
-  </si>
-  <si>
-    <t>601225</t>
-  </si>
-  <si>
-    <t>600926</t>
-  </si>
-  <si>
-    <t>603311</t>
-  </si>
-  <si>
-    <t>002995</t>
-  </si>
-  <si>
     <t>603960</t>
   </si>
   <si>
@@ -294,153 +294,153 @@
     <t>601598</t>
   </si>
   <si>
+    <t>688070</t>
+  </si>
+  <si>
+    <t>603103</t>
+  </si>
+  <si>
+    <t>000599</t>
+  </si>
+  <si>
+    <t>688367</t>
+  </si>
+  <si>
     <t>601702</t>
   </si>
   <si>
-    <t>688070</t>
-  </si>
-  <si>
-    <t>603103</t>
-  </si>
-  <si>
-    <t>000599</t>
-  </si>
-  <si>
-    <t>688367</t>
+    <t>002441</t>
+  </si>
+  <si>
+    <t>603301</t>
+  </si>
+  <si>
+    <t>603232</t>
+  </si>
+  <si>
+    <t>688025</t>
+  </si>
+  <si>
+    <t>603334</t>
+  </si>
+  <si>
+    <t>688312</t>
+  </si>
+  <si>
+    <t>603626</t>
+  </si>
+  <si>
+    <t>603150</t>
   </si>
   <si>
     <t>001326</t>
   </si>
   <si>
-    <t>603150</t>
-  </si>
-  <si>
-    <t>603626</t>
-  </si>
-  <si>
     <t>001335</t>
   </si>
   <si>
-    <t>688312</t>
-  </si>
-  <si>
-    <t>002441</t>
-  </si>
-  <si>
-    <t>688025</t>
-  </si>
-  <si>
-    <t>603232</t>
-  </si>
-  <si>
-    <t>603301</t>
-  </si>
-  <si>
-    <t>603334</t>
+    <t>001896</t>
+  </si>
+  <si>
+    <t>002028</t>
+  </si>
+  <si>
+    <t>603057</t>
+  </si>
+  <si>
+    <t>605289</t>
+  </si>
+  <si>
+    <t>002937</t>
+  </si>
+  <si>
+    <t>601872</t>
+  </si>
+  <si>
+    <t>001309</t>
+  </si>
+  <si>
+    <t>301160</t>
   </si>
   <si>
     <t>300831</t>
   </si>
   <si>
-    <t>301160</t>
-  </si>
-  <si>
-    <t>001309</t>
-  </si>
-  <si>
     <t>002380</t>
   </si>
   <si>
-    <t>601872</t>
-  </si>
-  <si>
-    <t>002937</t>
-  </si>
-  <si>
-    <t>605289</t>
-  </si>
-  <si>
-    <t>603057</t>
-  </si>
-  <si>
-    <t>002028</t>
-  </si>
-  <si>
-    <t>001896</t>
+    <t>300720</t>
+  </si>
+  <si>
+    <t>600649</t>
+  </si>
+  <si>
+    <t>600230</t>
+  </si>
+  <si>
+    <t>600715</t>
+  </si>
+  <si>
+    <t>688668</t>
+  </si>
+  <si>
+    <t>002921</t>
+  </si>
+  <si>
+    <t>003018</t>
+  </si>
+  <si>
+    <t>002545</t>
   </si>
   <si>
     <t>301087</t>
   </si>
   <si>
-    <t>002545</t>
-  </si>
-  <si>
-    <t>003018</t>
-  </si>
-  <si>
-    <t>688668</t>
-  </si>
-  <si>
-    <t>002921</t>
-  </si>
-  <si>
-    <t>600715</t>
-  </si>
-  <si>
-    <t>300720</t>
-  </si>
-  <si>
-    <t>600230</t>
-  </si>
-  <si>
-    <t>600649</t>
+    <t>301536</t>
+  </si>
+  <si>
+    <t>301032</t>
+  </si>
+  <si>
+    <t>601789</t>
+  </si>
+  <si>
+    <t>605268</t>
+  </si>
+  <si>
+    <t>301308</t>
+  </si>
+  <si>
+    <t>300461</t>
   </si>
   <si>
     <t>300257</t>
   </si>
   <si>
-    <t>300461</t>
-  </si>
-  <si>
-    <t>301308</t>
-  </si>
-  <si>
-    <t>605268</t>
-  </si>
-  <si>
-    <t>601789</t>
-  </si>
-  <si>
-    <t>301032</t>
-  </si>
-  <si>
-    <t>301536</t>
+    <t>605222</t>
+  </si>
+  <si>
+    <t>688800</t>
+  </si>
+  <si>
+    <t>002285</t>
+  </si>
+  <si>
+    <t>600433</t>
+  </si>
+  <si>
+    <t>301309</t>
+  </si>
+  <si>
+    <t>688612</t>
   </si>
   <si>
     <t>300085</t>
   </si>
   <si>
-    <t>301309</t>
-  </si>
-  <si>
-    <t>688612</t>
-  </si>
-  <si>
     <t>600610</t>
   </si>
   <si>
-    <t>600433</t>
-  </si>
-  <si>
-    <t>002285</t>
-  </si>
-  <si>
-    <t>605222</t>
-  </si>
-  <si>
-    <t>688800</t>
-  </si>
-  <si>
     <t>301093</t>
   </si>
   <si>
@@ -462,165 +462,177 @@
     <t>688267</t>
   </si>
   <si>
+    <t>603588</t>
+  </si>
+  <si>
+    <t>301015</t>
+  </si>
+  <si>
+    <t>300834</t>
+  </si>
+  <si>
+    <t>301529</t>
+  </si>
+  <si>
+    <t>603585</t>
+  </si>
+  <si>
     <t>300689</t>
   </si>
   <si>
+    <t>002035</t>
+  </si>
+  <si>
+    <t>300440</t>
+  </si>
+  <si>
     <t>002773</t>
   </si>
   <si>
-    <t>300440</t>
-  </si>
-  <si>
-    <t>603585</t>
-  </si>
-  <si>
-    <t>002035</t>
-  </si>
-  <si>
-    <t>300834</t>
-  </si>
-  <si>
-    <t>301529</t>
-  </si>
-  <si>
-    <t>301015</t>
-  </si>
-  <si>
-    <t>603588</t>
+    <t>002386</t>
+  </si>
+  <si>
+    <t>300179</t>
+  </si>
+  <si>
+    <t>002624</t>
+  </si>
+  <si>
+    <t>603988</t>
+  </si>
+  <si>
+    <t>600545</t>
+  </si>
+  <si>
+    <t>301326</t>
+  </si>
+  <si>
+    <t>600654</t>
+  </si>
+  <si>
+    <t>002008</t>
   </si>
   <si>
     <t>300870</t>
   </si>
   <si>
-    <t>002008</t>
-  </si>
-  <si>
-    <t>600654</t>
-  </si>
-  <si>
-    <t>301326</t>
-  </si>
-  <si>
     <t>301310</t>
   </si>
   <si>
-    <t>603988</t>
-  </si>
-  <si>
-    <t>600545</t>
-  </si>
-  <si>
-    <t>002624</t>
-  </si>
-  <si>
-    <t>300179</t>
-  </si>
-  <si>
-    <t>002386</t>
+    <t>600572</t>
+  </si>
+  <si>
+    <t>002667</t>
+  </si>
+  <si>
+    <t>603682</t>
+  </si>
+  <si>
+    <t>300866</t>
+  </si>
+  <si>
+    <t>600749</t>
+  </si>
+  <si>
+    <t>002853</t>
+  </si>
+  <si>
+    <t>002787</t>
   </si>
   <si>
     <t>603171</t>
   </si>
   <si>
-    <t>002787</t>
-  </si>
-  <si>
     <t>603698</t>
   </si>
   <si>
-    <t>002853</t>
-  </si>
-  <si>
-    <t>600749</t>
-  </si>
-  <si>
-    <t>300866</t>
-  </si>
-  <si>
-    <t>603682</t>
-  </si>
-  <si>
-    <t>002667</t>
-  </si>
-  <si>
-    <t>600572</t>
+    <t>301133</t>
+  </si>
+  <si>
+    <t>600156</t>
+  </si>
+  <si>
+    <t>301611</t>
+  </si>
+  <si>
+    <t>000811</t>
+  </si>
+  <si>
+    <t>002803</t>
+  </si>
+  <si>
+    <t>002975</t>
+  </si>
+  <si>
+    <t>600736</t>
   </si>
   <si>
     <t>300687</t>
   </si>
   <si>
-    <t>600736</t>
-  </si>
-  <si>
-    <t>002975</t>
-  </si>
-  <si>
     <t>300539</t>
   </si>
   <si>
-    <t>002803</t>
-  </si>
-  <si>
-    <t>000811</t>
-  </si>
-  <si>
-    <t>301611</t>
-  </si>
-  <si>
-    <t>600156</t>
-  </si>
-  <si>
-    <t>301133</t>
+    <t>002831</t>
+  </si>
+  <si>
+    <t>300905</t>
+  </si>
+  <si>
+    <t>300842</t>
+  </si>
+  <si>
+    <t>002181</t>
+  </si>
+  <si>
+    <t>002631</t>
+  </si>
+  <si>
+    <t>000672</t>
+  </si>
+  <si>
+    <t>603045</t>
   </si>
   <si>
     <t>002484</t>
   </si>
   <si>
-    <t>603045</t>
-  </si>
-  <si>
     <t>603931</t>
   </si>
   <si>
-    <t>000672</t>
-  </si>
-  <si>
-    <t>300842</t>
-  </si>
-  <si>
-    <t>002181</t>
-  </si>
-  <si>
-    <t>300905</t>
-  </si>
-  <si>
-    <t>002631</t>
-  </si>
-  <si>
-    <t>002831</t>
+    <t>603052</t>
+  </si>
+  <si>
+    <t>002965</t>
+  </si>
+  <si>
+    <t>688001</t>
+  </si>
+  <si>
+    <t>300749</t>
   </si>
   <si>
     <t>002782</t>
   </si>
   <si>
-    <t>300749</t>
-  </si>
-  <si>
-    <t>688001</t>
-  </si>
-  <si>
     <t>002303</t>
   </si>
   <si>
-    <t>002965</t>
-  </si>
-  <si>
-    <t>603052</t>
-  </si>
-  <si>
     <t>600381</t>
   </si>
   <si>
+    <t>688130</t>
+  </si>
+  <si>
+    <t>603360</t>
+  </si>
+  <si>
+    <t>003001</t>
+  </si>
+  <si>
+    <t>600626</t>
+  </si>
+  <si>
     <t>600850</t>
   </si>
   <si>
@@ -630,123 +642,111 @@
     <t>002226</t>
   </si>
   <si>
-    <t>600626</t>
-  </si>
-  <si>
-    <t>603360</t>
-  </si>
-  <si>
-    <t>003001</t>
-  </si>
-  <si>
-    <t>688130</t>
+    <t>605066</t>
+  </si>
+  <si>
+    <t>000509</t>
+  </si>
+  <si>
+    <t>600162</t>
+  </si>
+  <si>
+    <t>002993</t>
+  </si>
+  <si>
+    <t>002072</t>
+  </si>
+  <si>
+    <t>603661</t>
+  </si>
+  <si>
+    <t>301588</t>
+  </si>
+  <si>
+    <t>300868</t>
   </si>
   <si>
     <t>002655</t>
   </si>
   <si>
-    <t>000509</t>
-  </si>
-  <si>
-    <t>600162</t>
-  </si>
-  <si>
-    <t>002993</t>
-  </si>
-  <si>
-    <t>002072</t>
-  </si>
-  <si>
-    <t>605066</t>
-  </si>
-  <si>
     <t>002465</t>
   </si>
   <si>
-    <t>603661</t>
-  </si>
-  <si>
-    <t>301588</t>
-  </si>
-  <si>
-    <t>300868</t>
+    <t>002125</t>
+  </si>
+  <si>
+    <t>001226</t>
+  </si>
+  <si>
+    <t>002951</t>
+  </si>
+  <si>
+    <t>002404</t>
+  </si>
+  <si>
+    <t>603330</t>
+  </si>
+  <si>
+    <t>002830</t>
+  </si>
+  <si>
+    <t>300881</t>
   </si>
   <si>
     <t>002096</t>
   </si>
   <si>
-    <t>300881</t>
-  </si>
-  <si>
-    <t>002830</t>
-  </si>
-  <si>
     <t>002314</t>
   </si>
   <si>
-    <t>603330</t>
-  </si>
-  <si>
-    <t>001226</t>
-  </si>
-  <si>
-    <t>002951</t>
-  </si>
-  <si>
-    <t>002125</t>
-  </si>
-  <si>
-    <t>002404</t>
+    <t>002982</t>
+  </si>
+  <si>
+    <t>603938</t>
+  </si>
+  <si>
+    <t>601588</t>
+  </si>
+  <si>
+    <t>000048</t>
+  </si>
+  <si>
+    <t>688056</t>
+  </si>
+  <si>
+    <t>002903</t>
   </si>
   <si>
     <t>300656</t>
   </si>
   <si>
-    <t>002903</t>
-  </si>
-  <si>
-    <t>688056</t>
-  </si>
-  <si>
-    <t>000048</t>
-  </si>
-  <si>
-    <t>601588</t>
-  </si>
-  <si>
-    <t>603938</t>
-  </si>
-  <si>
-    <t>002982</t>
+    <t>603618</t>
+  </si>
+  <si>
+    <t>600110</t>
+  </si>
+  <si>
+    <t>300903</t>
+  </si>
+  <si>
+    <t>600026</t>
+  </si>
+  <si>
+    <t>300769</t>
+  </si>
+  <si>
+    <t>002913</t>
+  </si>
+  <si>
+    <t>002972</t>
+  </si>
+  <si>
+    <t>603738</t>
   </si>
   <si>
     <t>001696</t>
   </si>
   <si>
-    <t>603738</t>
-  </si>
-  <si>
-    <t>002972</t>
-  </si>
-  <si>
-    <t>002913</t>
-  </si>
-  <si>
-    <t>603618</t>
-  </si>
-  <si>
-    <t>600026</t>
-  </si>
-  <si>
-    <t>300903</t>
-  </si>
-  <si>
-    <t>600110</t>
-  </si>
-  <si>
-    <t>300769</t>
-  </si>
-  <si>
     <t>603407</t>
   </si>
   <si>
@@ -759,202 +759,214 @@
     <t>002976</t>
   </si>
   <si>
+    <t>002558</t>
+  </si>
+  <si>
+    <t>301248</t>
+  </si>
+  <si>
     <t>002990</t>
   </si>
   <si>
-    <t>002558</t>
-  </si>
-  <si>
-    <t>301248</t>
+    <t>002342</t>
+  </si>
+  <si>
+    <t>002693</t>
+  </si>
+  <si>
+    <t>002459</t>
+  </si>
+  <si>
+    <t>000810</t>
+  </si>
+  <si>
+    <t>603956</t>
+  </si>
+  <si>
+    <t>603477</t>
+  </si>
+  <si>
+    <t>301382</t>
+  </si>
+  <si>
+    <t>600630</t>
+  </si>
+  <si>
+    <t>002714</t>
   </si>
   <si>
     <t>002779</t>
   </si>
   <si>
-    <t>002693</t>
-  </si>
-  <si>
-    <t>002714</t>
-  </si>
-  <si>
-    <t>301382</t>
-  </si>
-  <si>
-    <t>600630</t>
-  </si>
-  <si>
-    <t>603956</t>
-  </si>
-  <si>
-    <t>002459</t>
-  </si>
-  <si>
-    <t>000810</t>
-  </si>
-  <si>
-    <t>002342</t>
-  </si>
-  <si>
-    <t>603477</t>
+    <t>605118</t>
+  </si>
+  <si>
+    <t>300909</t>
+  </si>
+  <si>
+    <t>603139</t>
+  </si>
+  <si>
+    <t>000977</t>
+  </si>
+  <si>
+    <t>000731</t>
+  </si>
+  <si>
+    <t>002274</t>
+  </si>
+  <si>
+    <t>000779</t>
   </si>
   <si>
     <t>688069</t>
   </si>
   <si>
-    <t>000779</t>
-  </si>
-  <si>
-    <t>002274</t>
-  </si>
-  <si>
-    <t>000731</t>
-  </si>
-  <si>
-    <t>603139</t>
-  </si>
-  <si>
-    <t>300909</t>
-  </si>
-  <si>
-    <t>605118</t>
-  </si>
-  <si>
-    <t>000977</t>
+    <t>600746</t>
+  </si>
+  <si>
+    <t>002900</t>
+  </si>
+  <si>
+    <t>000959</t>
+  </si>
+  <si>
+    <t>605178</t>
+  </si>
+  <si>
+    <t>002677</t>
+  </si>
+  <si>
+    <t>600602</t>
+  </si>
+  <si>
+    <t>688485</t>
+  </si>
+  <si>
+    <t>002379</t>
+  </si>
+  <si>
+    <t>002128</t>
   </si>
   <si>
     <t>300227</t>
   </si>
   <si>
-    <t>002128</t>
-  </si>
-  <si>
-    <t>002379</t>
-  </si>
-  <si>
-    <t>688485</t>
-  </si>
-  <si>
-    <t>000959</t>
-  </si>
-  <si>
-    <t>600746</t>
-  </si>
-  <si>
-    <t>605178</t>
-  </si>
-  <si>
-    <t>002677</t>
-  </si>
-  <si>
-    <t>002900</t>
-  </si>
-  <si>
-    <t>600602</t>
+    <t>600322</t>
+  </si>
+  <si>
+    <t>000862</t>
+  </si>
+  <si>
+    <t>002955</t>
+  </si>
+  <si>
+    <t>001258</t>
+  </si>
+  <si>
+    <t>688078</t>
   </si>
   <si>
     <t>605196</t>
   </si>
   <si>
+    <t>605288</t>
+  </si>
+  <si>
     <t>688618</t>
   </si>
   <si>
-    <t>605288</t>
+    <t>605155</t>
   </si>
   <si>
     <t>002339</t>
   </si>
   <si>
-    <t>605155</t>
-  </si>
-  <si>
-    <t>688078</t>
-  </si>
-  <si>
-    <t>001258</t>
-  </si>
-  <si>
-    <t>002955</t>
-  </si>
-  <si>
-    <t>000862</t>
-  </si>
-  <si>
-    <t>600322</t>
+    <t>301108</t>
+  </si>
+  <si>
+    <t>301228</t>
+  </si>
+  <si>
+    <t>000668</t>
+  </si>
+  <si>
+    <t>300998</t>
+  </si>
+  <si>
+    <t>003030</t>
   </si>
   <si>
     <t>603660</t>
   </si>
   <si>
+    <t>605388</t>
+  </si>
+  <si>
+    <t>300469</t>
+  </si>
+  <si>
     <t>603221</t>
   </si>
   <si>
-    <t>300469</t>
-  </si>
-  <si>
-    <t>605388</t>
-  </si>
-  <si>
-    <t>000668</t>
-  </si>
-  <si>
-    <t>301228</t>
-  </si>
-  <si>
-    <t>301108</t>
-  </si>
-  <si>
-    <t>300998</t>
-  </si>
-  <si>
-    <t>003030</t>
+    <t>601700</t>
+  </si>
+  <si>
+    <t>688661</t>
+  </si>
+  <si>
+    <t>603124</t>
+  </si>
+  <si>
+    <t>001210</t>
+  </si>
+  <si>
+    <t>002963</t>
   </si>
   <si>
     <t>002361</t>
   </si>
   <si>
-    <t>002963</t>
-  </si>
-  <si>
-    <t>001210</t>
-  </si>
-  <si>
     <t>603657</t>
   </si>
   <si>
-    <t>603124</t>
-  </si>
-  <si>
-    <t>688661</t>
-  </si>
-  <si>
-    <t>601700</t>
+    <t>688693</t>
+  </si>
+  <si>
+    <t>002520</t>
+  </si>
+  <si>
+    <t>603883</t>
+  </si>
+  <si>
+    <t>000692</t>
+  </si>
+  <si>
+    <t>301626</t>
+  </si>
+  <si>
+    <t>603758</t>
+  </si>
+  <si>
+    <t>000410</t>
+  </si>
+  <si>
+    <t>688531</t>
   </si>
   <si>
     <t>688052</t>
   </si>
   <si>
-    <t>000410</t>
-  </si>
-  <si>
-    <t>603758</t>
-  </si>
-  <si>
-    <t>688531</t>
-  </si>
-  <si>
-    <t>688693</t>
-  </si>
-  <si>
-    <t>002520</t>
-  </si>
-  <si>
-    <t>000692</t>
-  </si>
-  <si>
-    <t>603883</t>
-  </si>
-  <si>
-    <t>301626</t>
+    <t>002647</t>
+  </si>
+  <si>
+    <t>002742</t>
+  </si>
+  <si>
+    <t>605133</t>
+  </si>
+  <si>
+    <t>300845</t>
   </si>
   <si>
     <t>603071</t>
@@ -963,21 +975,9 @@
     <t>000523</t>
   </si>
   <si>
-    <t>002647</t>
-  </si>
-  <si>
     <t>688611</t>
   </si>
   <si>
-    <t>605133</t>
-  </si>
-  <si>
-    <t>002742</t>
-  </si>
-  <si>
-    <t>300845</t>
-  </si>
-  <si>
     <t>002476</t>
   </si>
   <si>
@@ -1005,90 +1005,90 @@
     <t>海天瑞声</t>
   </si>
   <si>
+    <t>星环科技-U</t>
+  </si>
+  <si>
+    <t>恺英网络</t>
+  </si>
+  <si>
+    <t>百隆东方</t>
+  </si>
+  <si>
+    <t>鲁信创投</t>
+  </si>
+  <si>
+    <t>三江购物</t>
+  </si>
+  <si>
+    <t>法兰泰克</t>
+  </si>
+  <si>
     <t>南网科技</t>
   </si>
   <si>
-    <t>法兰泰克</t>
-  </si>
-  <si>
-    <t>三江购物</t>
-  </si>
-  <si>
     <t>茂业商业</t>
   </si>
   <si>
-    <t>百隆东方</t>
-  </si>
-  <si>
-    <t>恺英网络</t>
-  </si>
-  <si>
-    <t>星环科技-U</t>
-  </si>
-  <si>
-    <t>鲁信创投</t>
-  </si>
-  <si>
     <t>志特新材</t>
   </si>
   <si>
+    <t>圣晖集成</t>
+  </si>
+  <si>
+    <t>南矿集团</t>
+  </si>
+  <si>
+    <t>德才股份</t>
+  </si>
+  <si>
+    <t>龙磁科技</t>
+  </si>
+  <si>
+    <t>四川黄金</t>
+  </si>
+  <si>
+    <t>优利德</t>
+  </si>
+  <si>
+    <t>雪龙集团</t>
+  </si>
+  <si>
+    <t>浙江自然</t>
+  </si>
+  <si>
     <t>金龙汽车</t>
   </si>
   <si>
-    <t>浙江自然</t>
-  </si>
-  <si>
-    <t>雪龙集团</t>
-  </si>
-  <si>
     <t>晶品特装</t>
   </si>
   <si>
-    <t>优利德</t>
-  </si>
-  <si>
-    <t>四川黄金</t>
-  </si>
-  <si>
-    <t>龙磁科技</t>
-  </si>
-  <si>
-    <t>德才股份</t>
-  </si>
-  <si>
-    <t>南矿集团</t>
-  </si>
-  <si>
-    <t>圣晖集成</t>
-  </si>
-  <si>
     <t>明阳智能</t>
   </si>
   <si>
+    <t>杭州银行</t>
+  </si>
+  <si>
+    <t>天地在线</t>
+  </si>
+  <si>
+    <t>陕西煤业</t>
+  </si>
+  <si>
+    <t>金海高科</t>
+  </si>
+  <si>
+    <t>蓝焰控股</t>
+  </si>
+  <si>
     <t>统联精密</t>
   </si>
   <si>
+    <t>福建金森</t>
+  </si>
+  <si>
     <t>雪迪龙</t>
   </si>
   <si>
-    <t>蓝焰控股</t>
-  </si>
-  <si>
-    <t>福建金森</t>
-  </si>
-  <si>
-    <t>陕西煤业</t>
-  </si>
-  <si>
-    <t>杭州银行</t>
-  </si>
-  <si>
-    <t>金海高科</t>
-  </si>
-  <si>
-    <t>天地在线</t>
-  </si>
-  <si>
     <t>克来机电</t>
   </si>
   <si>
@@ -1104,153 +1104,153 @@
     <t>中国外运</t>
   </si>
   <si>
+    <t>纵横股份</t>
+  </si>
+  <si>
+    <t>横店影视</t>
+  </si>
+  <si>
+    <t>青岛双星</t>
+  </si>
+  <si>
+    <t>工大高科</t>
+  </si>
+  <si>
     <t>华峰铝业</t>
   </si>
   <si>
-    <t>纵横股份</t>
-  </si>
-  <si>
-    <t>横店影视</t>
-  </si>
-  <si>
-    <t>青岛双星</t>
-  </si>
-  <si>
-    <t>工大高科</t>
+    <t>众业达</t>
+  </si>
+  <si>
+    <t>振德医疗</t>
+  </si>
+  <si>
+    <t>格尔软件</t>
+  </si>
+  <si>
+    <t>杰普特</t>
+  </si>
+  <si>
+    <t>丰倍生物</t>
+  </si>
+  <si>
+    <t>燕麦科技</t>
+  </si>
+  <si>
+    <t>科森科技</t>
+  </si>
+  <si>
+    <t>万朗磁塑</t>
   </si>
   <si>
     <t>联域股份</t>
   </si>
   <si>
-    <t>万朗磁塑</t>
-  </si>
-  <si>
-    <t>科森科技</t>
-  </si>
-  <si>
     <t>信凯科技</t>
   </si>
   <si>
-    <t>燕麦科技</t>
-  </si>
-  <si>
-    <t>众业达</t>
-  </si>
-  <si>
-    <t>杰普特</t>
-  </si>
-  <si>
-    <t>格尔软件</t>
-  </si>
-  <si>
-    <t>振德医疗</t>
-  </si>
-  <si>
-    <t>丰倍生物</t>
+    <t>豫能控股</t>
+  </si>
+  <si>
+    <t>思源电气</t>
+  </si>
+  <si>
+    <t>紫燕食品</t>
+  </si>
+  <si>
+    <t>罗曼股份</t>
+  </si>
+  <si>
+    <t>兴瑞科技</t>
+  </si>
+  <si>
+    <t>招商轮船</t>
+  </si>
+  <si>
+    <t>德明利</t>
+  </si>
+  <si>
+    <t>翔楼新材</t>
   </si>
   <si>
     <t>派瑞股份</t>
   </si>
   <si>
-    <t>翔楼新材</t>
-  </si>
-  <si>
-    <t>德明利</t>
-  </si>
-  <si>
     <t>科远智慧</t>
   </si>
   <si>
-    <t>招商轮船</t>
-  </si>
-  <si>
-    <t>兴瑞科技</t>
-  </si>
-  <si>
-    <t>罗曼股份</t>
-  </si>
-  <si>
-    <t>紫燕食品</t>
-  </si>
-  <si>
-    <t>思源电气</t>
-  </si>
-  <si>
-    <t>豫能控股</t>
+    <t>海川智能</t>
+  </si>
+  <si>
+    <t>城投控股</t>
+  </si>
+  <si>
+    <t>沧州大化</t>
+  </si>
+  <si>
+    <t>文投控股</t>
+  </si>
+  <si>
+    <t>鼎通科技</t>
+  </si>
+  <si>
+    <t>联诚精密</t>
+  </si>
+  <si>
+    <t>金富科技</t>
+  </si>
+  <si>
+    <t>东方铁塔</t>
   </si>
   <si>
     <t>可孚医疗</t>
   </si>
   <si>
-    <t>东方铁塔</t>
-  </si>
-  <si>
-    <t>金富科技</t>
-  </si>
-  <si>
-    <t>鼎通科技</t>
-  </si>
-  <si>
-    <t>联诚精密</t>
-  </si>
-  <si>
-    <t>文投控股</t>
-  </si>
-  <si>
-    <t>海川智能</t>
-  </si>
-  <si>
-    <t>沧州大化</t>
-  </si>
-  <si>
-    <t>城投控股</t>
+    <t>星宸科技</t>
+  </si>
+  <si>
+    <t>新柴股份</t>
+  </si>
+  <si>
+    <t>宁波建工</t>
+  </si>
+  <si>
+    <t>王力安防</t>
+  </si>
+  <si>
+    <t>江波龙</t>
+  </si>
+  <si>
+    <t>田中精机</t>
   </si>
   <si>
     <t>开山股份</t>
   </si>
   <si>
-    <t>田中精机</t>
-  </si>
-  <si>
-    <t>江波龙</t>
-  </si>
-  <si>
-    <t>王力安防</t>
-  </si>
-  <si>
-    <t>宁波建工</t>
-  </si>
-  <si>
-    <t>新柴股份</t>
-  </si>
-  <si>
-    <t>星宸科技</t>
+    <t>起帆电缆</t>
+  </si>
+  <si>
+    <t>瑞可达</t>
+  </si>
+  <si>
+    <t>世联行</t>
+  </si>
+  <si>
+    <t>冠豪高新</t>
+  </si>
+  <si>
+    <t>万得凯</t>
+  </si>
+  <si>
+    <t>威迈斯</t>
   </si>
   <si>
     <t>银之杰</t>
   </si>
   <si>
-    <t>万得凯</t>
-  </si>
-  <si>
-    <t>威迈斯</t>
-  </si>
-  <si>
     <t>中毅达</t>
   </si>
   <si>
-    <t>冠豪高新</t>
-  </si>
-  <si>
-    <t>世联行</t>
-  </si>
-  <si>
-    <t>起帆电缆</t>
-  </si>
-  <si>
-    <t>瑞可达</t>
-  </si>
-  <si>
     <t>华兰股份</t>
   </si>
   <si>
@@ -1272,165 +1272,177 @@
     <t>中触媒</t>
   </si>
   <si>
+    <t>高能环境</t>
+  </si>
+  <si>
+    <t>百洋医药</t>
+  </si>
+  <si>
+    <t>星辉环材</t>
+  </si>
+  <si>
+    <t>福赛科技</t>
+  </si>
+  <si>
+    <t>苏利股份</t>
+  </si>
+  <si>
     <t>澄天伟业</t>
   </si>
   <si>
+    <t>华帝股份</t>
+  </si>
+  <si>
+    <t>运达科技</t>
+  </si>
+  <si>
     <t>康弘药业</t>
   </si>
   <si>
-    <t>运达科技</t>
-  </si>
-  <si>
-    <t>苏利股份</t>
-  </si>
-  <si>
-    <t>华帝股份</t>
-  </si>
-  <si>
-    <t>星辉环材</t>
-  </si>
-  <si>
-    <t>福赛科技</t>
-  </si>
-  <si>
-    <t>百洋医药</t>
-  </si>
-  <si>
-    <t>高能环境</t>
+    <t>天原股份</t>
+  </si>
+  <si>
+    <t>四方达</t>
+  </si>
+  <si>
+    <t>完美世界</t>
+  </si>
+  <si>
+    <t>中电电机</t>
+  </si>
+  <si>
+    <t>卓郎智能</t>
+  </si>
+  <si>
+    <t>捷邦科技</t>
+  </si>
+  <si>
+    <t>中安科</t>
+  </si>
+  <si>
+    <t>大族激光</t>
   </si>
   <si>
     <t>欧陆通</t>
   </si>
   <si>
-    <t>大族激光</t>
-  </si>
-  <si>
-    <t>中安科</t>
-  </si>
-  <si>
-    <t>捷邦科技</t>
-  </si>
-  <si>
     <t>鑫宏业</t>
   </si>
   <si>
-    <t>中电电机</t>
-  </si>
-  <si>
-    <t>卓郎智能</t>
-  </si>
-  <si>
-    <t>完美世界</t>
-  </si>
-  <si>
-    <t>四方达</t>
-  </si>
-  <si>
-    <t>天原股份</t>
+    <t>康恩贝</t>
+  </si>
+  <si>
+    <t>威领股份</t>
+  </si>
+  <si>
+    <t>锦和商管</t>
+  </si>
+  <si>
+    <t>安克创新</t>
+  </si>
+  <si>
+    <t>西藏旅游</t>
+  </si>
+  <si>
+    <t>皮阿诺</t>
+  </si>
+  <si>
+    <t>华源控股</t>
   </si>
   <si>
     <t>税友股份</t>
   </si>
   <si>
-    <t>华源控股</t>
-  </si>
-  <si>
     <t>航天工程</t>
   </si>
   <si>
-    <t>皮阿诺</t>
-  </si>
-  <si>
-    <t>西藏旅游</t>
-  </si>
-  <si>
-    <t>安克创新</t>
-  </si>
-  <si>
-    <t>锦和商管</t>
-  </si>
-  <si>
-    <t>威领股份</t>
-  </si>
-  <si>
-    <t>康恩贝</t>
+    <t>金钟股份</t>
+  </si>
+  <si>
+    <t>华升股份</t>
+  </si>
+  <si>
+    <t>珂玛科技</t>
+  </si>
+  <si>
+    <t>冰轮环境</t>
+  </si>
+  <si>
+    <t>吉宏股份</t>
+  </si>
+  <si>
+    <t>博杰股份</t>
+  </si>
+  <si>
+    <t>苏州高新</t>
   </si>
   <si>
     <t>赛意信息</t>
   </si>
   <si>
-    <t>苏州高新</t>
-  </si>
-  <si>
-    <t>博杰股份</t>
-  </si>
-  <si>
     <t>横河精密</t>
   </si>
   <si>
-    <t>吉宏股份</t>
-  </si>
-  <si>
-    <t>冰轮环境</t>
-  </si>
-  <si>
-    <t>珂玛科技</t>
-  </si>
-  <si>
-    <t>华升股份</t>
-  </si>
-  <si>
-    <t>金钟股份</t>
+    <t>裕同科技</t>
+  </si>
+  <si>
+    <t>宝丽迪</t>
+  </si>
+  <si>
+    <t>帝科股份</t>
+  </si>
+  <si>
+    <t>粤传媒</t>
+  </si>
+  <si>
+    <t>德尔未来</t>
+  </si>
+  <si>
+    <t>上峰材料</t>
+  </si>
+  <si>
+    <t>福达合金</t>
   </si>
   <si>
     <t>江海股份</t>
   </si>
   <si>
-    <t>福达合金</t>
-  </si>
-  <si>
     <t>格林达</t>
   </si>
   <si>
-    <t>上峰材料</t>
-  </si>
-  <si>
-    <t>帝科股份</t>
-  </si>
-  <si>
-    <t>粤传媒</t>
-  </si>
-  <si>
-    <t>宝丽迪</t>
-  </si>
-  <si>
-    <t>德尔未来</t>
-  </si>
-  <si>
-    <t>裕同科技</t>
+    <t>可川科技</t>
+  </si>
+  <si>
+    <t>祥鑫科技</t>
+  </si>
+  <si>
+    <t>华兴源创</t>
+  </si>
+  <si>
+    <t>顶固集创</t>
   </si>
   <si>
     <t>可立克</t>
   </si>
   <si>
-    <t>顶固集创</t>
-  </si>
-  <si>
-    <t>华兴源创</t>
-  </si>
-  <si>
     <t>美盈森</t>
   </si>
   <si>
-    <t>祥鑫科技</t>
-  </si>
-  <si>
-    <t>可川科技</t>
-  </si>
-  <si>
     <t>*ST春天</t>
   </si>
   <si>
+    <t>晶华微</t>
+  </si>
+  <si>
+    <t>百傲化学</t>
+  </si>
+  <si>
+    <t>中岩大地</t>
+  </si>
+  <si>
+    <t>申达股份</t>
+  </si>
+  <si>
     <t>电科数字</t>
   </si>
   <si>
@@ -1440,123 +1452,111 @@
     <t>江南化工</t>
   </si>
   <si>
-    <t>申达股份</t>
-  </si>
-  <si>
-    <t>百傲化学</t>
-  </si>
-  <si>
-    <t>中岩大地</t>
-  </si>
-  <si>
-    <t>晶华微</t>
+    <t>天正电气</t>
+  </si>
+  <si>
+    <t>华塑控股</t>
+  </si>
+  <si>
+    <t>香江控股</t>
+  </si>
+  <si>
+    <t>奥海科技</t>
+  </si>
+  <si>
+    <t>凯瑞德</t>
+  </si>
+  <si>
+    <t>恒林股份</t>
+  </si>
+  <si>
+    <t>美新科技</t>
+  </si>
+  <si>
+    <t>杰美特</t>
   </si>
   <si>
     <t>共达电声</t>
   </si>
   <si>
-    <t>华塑控股</t>
-  </si>
-  <si>
-    <t>香江控股</t>
-  </si>
-  <si>
-    <t>奥海科技</t>
-  </si>
-  <si>
-    <t>凯瑞德</t>
-  </si>
-  <si>
-    <t>天正电气</t>
-  </si>
-  <si>
     <t>海格通信</t>
   </si>
   <si>
-    <t>恒林股份</t>
-  </si>
-  <si>
-    <t>美新科技</t>
-  </si>
-  <si>
-    <t>杰美特</t>
+    <t>湘潭电化</t>
+  </si>
+  <si>
+    <t>拓山重工</t>
+  </si>
+  <si>
+    <t>金时科技</t>
+  </si>
+  <si>
+    <t>嘉欣丝绸</t>
+  </si>
+  <si>
+    <t>天洋新材</t>
+  </si>
+  <si>
+    <t>名雕股份</t>
+  </si>
+  <si>
+    <t>盛德鑫泰</t>
   </si>
   <si>
     <t>易普力</t>
   </si>
   <si>
-    <t>盛德鑫泰</t>
-  </si>
-  <si>
-    <t>名雕股份</t>
-  </si>
-  <si>
     <t>南山控股</t>
   </si>
   <si>
-    <t>天洋新材</t>
-  </si>
-  <si>
-    <t>拓山重工</t>
-  </si>
-  <si>
-    <t>金时科技</t>
-  </si>
-  <si>
-    <t>湘潭电化</t>
-  </si>
-  <si>
-    <t>嘉欣丝绸</t>
+    <t>湘佳股份</t>
+  </si>
+  <si>
+    <t>三孚股份</t>
+  </si>
+  <si>
+    <t>北辰实业</t>
+  </si>
+  <si>
+    <t>京基智农</t>
+  </si>
+  <si>
+    <t>莱伯泰科</t>
+  </si>
+  <si>
+    <t>宇环数控</t>
   </si>
   <si>
     <t>民德电子</t>
   </si>
   <si>
-    <t>宇环数控</t>
-  </si>
-  <si>
-    <t>莱伯泰科</t>
-  </si>
-  <si>
-    <t>京基智农</t>
-  </si>
-  <si>
-    <t>北辰实业</t>
-  </si>
-  <si>
-    <t>三孚股份</t>
-  </si>
-  <si>
-    <t>湘佳股份</t>
+    <t>杭电股份</t>
+  </si>
+  <si>
+    <t>诺德股份</t>
+  </si>
+  <si>
+    <t>科翔股份</t>
+  </si>
+  <si>
+    <t>中远海能</t>
+  </si>
+  <si>
+    <t>德方纳米</t>
+  </si>
+  <si>
+    <t>奥士康</t>
+  </si>
+  <si>
+    <t>科安达</t>
+  </si>
+  <si>
+    <t>泰晶科技</t>
   </si>
   <si>
     <t>宗申动力</t>
   </si>
   <si>
-    <t>泰晶科技</t>
-  </si>
-  <si>
-    <t>科安达</t>
-  </si>
-  <si>
-    <t>奥士康</t>
-  </si>
-  <si>
-    <t>杭电股份</t>
-  </si>
-  <si>
-    <t>中远海能</t>
-  </si>
-  <si>
-    <t>科翔股份</t>
-  </si>
-  <si>
-    <t>诺德股份</t>
-  </si>
-  <si>
-    <t>德方纳米</t>
-  </si>
-  <si>
     <t>长裕集团</t>
   </si>
   <si>
@@ -1569,202 +1569,214 @@
     <t>瑞玛精密</t>
   </si>
   <si>
+    <t>巨人网络</t>
+  </si>
+  <si>
+    <t>杰创智能</t>
+  </si>
+  <si>
     <t>盛视科技</t>
   </si>
   <si>
-    <t>巨人网络</t>
-  </si>
-  <si>
-    <t>杰创智能</t>
+    <t>巨力索具</t>
+  </si>
+  <si>
+    <t>双成药业</t>
+  </si>
+  <si>
+    <t>晶澳科技</t>
+  </si>
+  <si>
+    <t>创维数字</t>
+  </si>
+  <si>
+    <t>威派格</t>
+  </si>
+  <si>
+    <t>巨星农牧</t>
+  </si>
+  <si>
+    <t>蜂助手</t>
+  </si>
+  <si>
+    <t>龙头股份</t>
+  </si>
+  <si>
+    <t>牧原股份</t>
   </si>
   <si>
     <t>中坚科技</t>
   </si>
   <si>
-    <t>双成药业</t>
-  </si>
-  <si>
-    <t>牧原股份</t>
-  </si>
-  <si>
-    <t>蜂助手</t>
-  </si>
-  <si>
-    <t>龙头股份</t>
-  </si>
-  <si>
-    <t>威派格</t>
-  </si>
-  <si>
-    <t>晶澳科技</t>
-  </si>
-  <si>
-    <t>创维数字</t>
-  </si>
-  <si>
-    <t>巨力索具</t>
-  </si>
-  <si>
-    <t>巨星农牧</t>
+    <t>力鼎光电</t>
+  </si>
+  <si>
+    <t>汇创达</t>
+  </si>
+  <si>
+    <t>康惠股份</t>
+  </si>
+  <si>
+    <t>浪潮信息</t>
+  </si>
+  <si>
+    <t>四川美丰</t>
+  </si>
+  <si>
+    <t>华昌化工</t>
+  </si>
+  <si>
+    <t>甘咨询</t>
   </si>
   <si>
     <t>德林海</t>
   </si>
   <si>
-    <t>甘咨询</t>
-  </si>
-  <si>
-    <t>华昌化工</t>
-  </si>
-  <si>
-    <t>四川美丰</t>
-  </si>
-  <si>
-    <t>康惠股份</t>
-  </si>
-  <si>
-    <t>汇创达</t>
-  </si>
-  <si>
-    <t>力鼎光电</t>
-  </si>
-  <si>
-    <t>浪潮信息</t>
+    <t>江苏索普</t>
+  </si>
+  <si>
+    <t>哈三联</t>
+  </si>
+  <si>
+    <t>首钢股份</t>
+  </si>
+  <si>
+    <t>时空科技</t>
+  </si>
+  <si>
+    <t>浙江美大</t>
+  </si>
+  <si>
+    <t>云赛智联</t>
+  </si>
+  <si>
+    <t>九州一轨</t>
+  </si>
+  <si>
+    <t>宏桥控股</t>
+  </si>
+  <si>
+    <t>电投能源</t>
   </si>
   <si>
     <t>光韵达</t>
   </si>
   <si>
-    <t>电投能源</t>
-  </si>
-  <si>
-    <t>宏桥控股</t>
-  </si>
-  <si>
-    <t>九州一轨</t>
-  </si>
-  <si>
-    <t>首钢股份</t>
-  </si>
-  <si>
-    <t>江苏索普</t>
-  </si>
-  <si>
-    <t>时空科技</t>
-  </si>
-  <si>
-    <t>浙江美大</t>
-  </si>
-  <si>
-    <t>哈三联</t>
-  </si>
-  <si>
-    <t>云赛智联</t>
+    <t>津投城开</t>
+  </si>
+  <si>
+    <t>银星能源</t>
+  </si>
+  <si>
+    <t>鸿合科技</t>
+  </si>
+  <si>
+    <t>立新能源</t>
+  </si>
+  <si>
+    <t>龙软科技</t>
   </si>
   <si>
     <t>华通线缆</t>
   </si>
   <si>
+    <t>凯迪股份</t>
+  </si>
+  <si>
     <t>三旺通信</t>
   </si>
   <si>
-    <t>凯迪股份</t>
+    <t>西大门</t>
   </si>
   <si>
     <t>积成电子</t>
   </si>
   <si>
-    <t>西大门</t>
-  </si>
-  <si>
-    <t>龙软科技</t>
-  </si>
-  <si>
-    <t>立新能源</t>
-  </si>
-  <si>
-    <t>鸿合科技</t>
-  </si>
-  <si>
-    <t>银星能源</t>
-  </si>
-  <si>
-    <t>津投城开</t>
+    <t>洁雅股份</t>
+  </si>
+  <si>
+    <t>实朴检测</t>
+  </si>
+  <si>
+    <t>荣丰控股</t>
+  </si>
+  <si>
+    <t>宁波方正</t>
+  </si>
+  <si>
+    <t>祖名股份</t>
   </si>
   <si>
     <t>苏州科达</t>
   </si>
   <si>
+    <t>均瑶健康</t>
+  </si>
+  <si>
+    <t>信息发展</t>
+  </si>
+  <si>
     <t>爱丽家居</t>
   </si>
   <si>
-    <t>信息发展</t>
-  </si>
-  <si>
-    <t>均瑶健康</t>
-  </si>
-  <si>
-    <t>荣丰控股</t>
-  </si>
-  <si>
-    <t>实朴检测</t>
-  </si>
-  <si>
-    <t>洁雅股份</t>
-  </si>
-  <si>
-    <t>宁波方正</t>
-  </si>
-  <si>
-    <t>祖名股份</t>
+    <t>风范股份</t>
+  </si>
+  <si>
+    <t>和林微纳</t>
+  </si>
+  <si>
+    <t>江南新材</t>
+  </si>
+  <si>
+    <t>金房能源</t>
+  </si>
+  <si>
+    <t>豪尔赛</t>
   </si>
   <si>
     <t>神剑股份</t>
   </si>
   <si>
-    <t>豪尔赛</t>
-  </si>
-  <si>
-    <t>金房能源</t>
-  </si>
-  <si>
     <t>春光科技</t>
   </si>
   <si>
-    <t>江南新材</t>
-  </si>
-  <si>
-    <t>和林微纳</t>
-  </si>
-  <si>
-    <t>风范股份</t>
+    <t>锴威特</t>
+  </si>
+  <si>
+    <t>日发精机</t>
+  </si>
+  <si>
+    <t>老百姓</t>
+  </si>
+  <si>
+    <t>惠天热电</t>
+  </si>
+  <si>
+    <t>苏州天脉</t>
+  </si>
+  <si>
+    <t>秦安股份</t>
+  </si>
+  <si>
+    <t>沈阳机床</t>
+  </si>
+  <si>
+    <t>日联科技</t>
   </si>
   <si>
     <t>纳芯微</t>
   </si>
   <si>
-    <t>沈阳机床</t>
-  </si>
-  <si>
-    <t>秦安股份</t>
-  </si>
-  <si>
-    <t>日联科技</t>
-  </si>
-  <si>
-    <t>锴威特</t>
-  </si>
-  <si>
-    <t>日发精机</t>
-  </si>
-  <si>
-    <t>惠天热电</t>
-  </si>
-  <si>
-    <t>老百姓</t>
-  </si>
-  <si>
-    <t>苏州天脉</t>
+    <t>仁东控股</t>
+  </si>
+  <si>
+    <t>冀衡医药</t>
+  </si>
+  <si>
+    <t>嵘泰股份</t>
+  </si>
+  <si>
+    <t>捷安高科</t>
   </si>
   <si>
     <t>物产环能</t>
@@ -1773,21 +1785,9 @@
     <t>红棉股份</t>
   </si>
   <si>
-    <t>仁东控股</t>
-  </si>
-  <si>
     <t>杭州柯林</t>
   </si>
   <si>
-    <t>嵘泰股份</t>
-  </si>
-  <si>
-    <t>冀衡医药</t>
-  </si>
-  <si>
-    <t>捷安高科</t>
-  </si>
-  <si>
     <t>新叶股份</t>
   </si>
   <si>
@@ -1923,12 +1923,12 @@
     <t>2026-02-24 15:00:00</t>
   </si>
   <si>
+    <t>2026-02-24 09:40:00</t>
+  </si>
+  <si>
     <t>2026-02-11 09:35:00</t>
   </si>
   <si>
-    <t>2026-02-24 09:40:00</t>
-  </si>
-  <si>
     <t>2026-03-03 15:00:00</t>
   </si>
   <si>
@@ -1938,10 +1938,16 @@
     <t>2026-03-10 15:00:00</t>
   </si>
   <si>
+    <t>2026-03-04 09:40:00</t>
+  </si>
+  <si>
     <t>2026-03-10 09:40:00</t>
   </si>
   <si>
-    <t>2026-03-04 09:40:00</t>
+    <t>2026-03-13 09:45:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 10:45:00</t>
   </si>
   <si>
     <t>2026-03-17 15:00:00</t>
@@ -1950,30 +1956,24 @@
     <t>2026-03-16 10:30:00</t>
   </si>
   <si>
-    <t>2026-03-17 10:45:00</t>
-  </si>
-  <si>
-    <t>2026-03-13 09:45:00</t>
+    <t>2026-03-19 10:15:00</t>
+  </si>
+  <si>
+    <t>2026-03-18 09:40:00</t>
   </si>
   <si>
     <t>2026-03-24 15:00:00</t>
   </si>
   <si>
+    <t>2026-03-20 09:55:00</t>
+  </si>
+  <si>
     <t>2026-04-08 15:00:00</t>
   </si>
   <si>
     <t>2026-03-18 10:30:00</t>
   </si>
   <si>
-    <t>2026-03-18 09:40:00</t>
-  </si>
-  <si>
-    <t>2026-03-20 09:55:00</t>
-  </si>
-  <si>
-    <t>2026-03-19 10:15:00</t>
-  </si>
-  <si>
     <t>2026-03-31 14:55:00</t>
   </si>
   <si>
@@ -1986,12 +1986,12 @@
     <t>2026-04-01 09:40:00</t>
   </si>
   <si>
+    <t>2026-04-02 14:00:00</t>
+  </si>
+  <si>
     <t>2026-04-07 14:35:00</t>
   </si>
   <si>
-    <t>2026-04-02 14:00:00</t>
-  </si>
-  <si>
     <t>2026-04-15 15:00:00</t>
   </si>
   <si>
@@ -2019,27 +2019,27 @@
     <t>2026-06-03 15:00:00</t>
   </si>
   <si>
+    <t>2026-06-10 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-04 09:40:00</t>
+  </si>
+  <si>
+    <t>2026-06-10 09:35:00</t>
+  </si>
+  <si>
     <t>2026-06-09 09:35:00</t>
   </si>
   <si>
-    <t>2026-06-04 09:40:00</t>
-  </si>
-  <si>
     <t>2026-06-10 09:45:00</t>
   </si>
   <si>
-    <t>2026-06-10 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-10 09:35:00</t>
+    <t>2026-06-11 09:40:00</t>
   </si>
   <si>
     <t>2026-06-17 15:00:00</t>
   </si>
   <si>
-    <t>2026-06-11 09:40:00</t>
-  </si>
-  <si>
     <t>2026-06-25 15:00:00</t>
   </si>
   <si>
@@ -2058,22 +2058,28 @@
     <t>2026-06-29 10:15:00</t>
   </si>
   <si>
+    <t>2026-07-06 13:05:00</t>
+  </si>
+  <si>
+    <t>2026-07-09 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-07-03 10:25:00</t>
+  </si>
+  <si>
+    <t>2026-07-08 10:40:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 09:35:00</t>
+  </si>
+  <si>
     <t>2026-07-08 09:35:00</t>
   </si>
   <si>
-    <t>2026-07-09 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 09:35:00</t>
-  </si>
-  <si>
-    <t>2026-07-03 10:25:00</t>
-  </si>
-  <si>
-    <t>2026-07-08 10:40:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 13:05:00</t>
+    <t>2026-07-10 10:15:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:50:00</t>
   </si>
   <si>
     <t>2026-07-10 09:40:00</t>
@@ -2082,25 +2088,22 @@
     <t>2026-07-16 15:00:00</t>
   </si>
   <si>
-    <t>2026-07-13 09:50:00</t>
-  </si>
-  <si>
-    <t>2026-07-10 10:15:00</t>
+    <t>2026-07-23 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-07-21 09:55:00</t>
+  </si>
+  <si>
+    <t>2026-07-17 09:50:00</t>
+  </si>
+  <si>
+    <t>2026-07-22 10:45:00</t>
   </si>
   <si>
     <t>2026-07-17 09:40:00</t>
   </si>
   <si>
-    <t>2026-07-23 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-17 09:50:00</t>
-  </si>
-  <si>
-    <t>2026-07-22 10:45:00</t>
-  </si>
-  <si>
-    <t>2026-07-21 09:55:00</t>
+    <t>2026-07-24 09:40:00</t>
   </si>
   <si>
     <t>2026-07-30 15:00:00</t>
@@ -2109,22 +2112,19 @@
     <t>2026-07-24 11:00:00</t>
   </si>
   <si>
-    <t>2026-07-24 09:40:00</t>
-  </si>
-  <si>
     <t>2026-07-24 10:30:00</t>
   </si>
   <si>
+    <t>2026-08-06 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 09:55:00</t>
+  </si>
+  <si>
     <t>2026-07-31 09:40:00</t>
   </si>
   <si>
     <t>2026-08-07 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-06 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 09:55:00</t>
   </si>
   <si>
     <t>2026-08-13 15:00:00</t>
@@ -2510,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>37.28</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2518,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>67.39</v>
+        <v>74.70999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2534,7 +2534,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2542,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>58.06</v>
+        <v>59.38</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3193,6 +3193,26 @@
       </c>
       <c r="F32">
         <v>1.3728</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
+        <v>0.84</v>
+      </c>
+      <c r="C33">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>4.537500000000001</v>
+      </c>
+      <c r="E33">
+        <v>3.8115</v>
+      </c>
+      <c r="F33">
+        <v>1.4251</v>
       </c>
     </row>
   </sheetData>
@@ -3202,7 +3222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G295"/>
+  <dimension ref="A1:G303"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3423,16 +3443,16 @@
         <v>592</v>
       </c>
       <c r="D10">
-        <v>55.02</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
         <v>625</v>
       </c>
       <c r="F10">
-        <v>59.22</v>
+        <v>189.7</v>
       </c>
       <c r="G10">
-        <v>7.63</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3446,16 +3466,16 @@
         <v>592</v>
       </c>
       <c r="D11">
-        <v>13.58</v>
+        <v>26.55</v>
       </c>
       <c r="E11" t="s">
         <v>625</v>
       </c>
       <c r="F11">
-        <v>14.2</v>
+        <v>26.34</v>
       </c>
       <c r="G11">
-        <v>4.57</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3469,16 +3489,16 @@
         <v>592</v>
       </c>
       <c r="D12">
-        <v>18.18</v>
+        <v>6.21</v>
       </c>
       <c r="E12" t="s">
         <v>625</v>
       </c>
       <c r="F12">
-        <v>17.6</v>
+        <v>6.17</v>
       </c>
       <c r="G12">
-        <v>-3.19</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3492,16 +3512,16 @@
         <v>592</v>
       </c>
       <c r="D13">
-        <v>8.16</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>625</v>
       </c>
       <c r="F13">
-        <v>6.92</v>
+        <v>26.01</v>
       </c>
       <c r="G13">
-        <v>-15.2</v>
+        <v>-31.55</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3515,16 +3535,16 @@
         <v>592</v>
       </c>
       <c r="D14">
-        <v>6.21</v>
+        <v>18.18</v>
       </c>
       <c r="E14" t="s">
         <v>625</v>
       </c>
       <c r="F14">
-        <v>6.17</v>
+        <v>17.6</v>
       </c>
       <c r="G14">
-        <v>-0.64</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3538,16 +3558,16 @@
         <v>592</v>
       </c>
       <c r="D15">
-        <v>26.55</v>
+        <v>13.58</v>
       </c>
       <c r="E15" t="s">
         <v>625</v>
       </c>
       <c r="F15">
-        <v>26.34</v>
+        <v>14.2</v>
       </c>
       <c r="G15">
-        <v>-0.79</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3561,16 +3581,16 @@
         <v>592</v>
       </c>
       <c r="D16">
-        <v>192</v>
+        <v>55.02</v>
       </c>
       <c r="E16" t="s">
         <v>625</v>
       </c>
       <c r="F16">
-        <v>189.7</v>
+        <v>59.22</v>
       </c>
       <c r="G16">
-        <v>-1.2</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3584,16 +3604,16 @@
         <v>592</v>
       </c>
       <c r="D17">
-        <v>38</v>
+        <v>8.16</v>
       </c>
       <c r="E17" t="s">
         <v>625</v>
       </c>
       <c r="F17">
-        <v>26.01</v>
+        <v>6.92</v>
       </c>
       <c r="G17">
-        <v>-31.55</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3630,16 +3650,16 @@
         <v>594</v>
       </c>
       <c r="D19">
-        <v>19.5</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
         <v>627</v>
       </c>
       <c r="F19">
-        <v>19.06</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="G19">
-        <v>-2.26</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3653,16 +3673,16 @@
         <v>594</v>
       </c>
       <c r="D20">
-        <v>27.1</v>
+        <v>24.77</v>
       </c>
       <c r="E20" t="s">
         <v>627</v>
       </c>
       <c r="F20">
-        <v>24.91</v>
+        <v>28.9</v>
       </c>
       <c r="G20">
-        <v>-8.08</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3676,16 +3696,16 @@
         <v>594</v>
       </c>
       <c r="D21">
-        <v>21.5</v>
+        <v>39.57</v>
       </c>
       <c r="E21" t="s">
         <v>627</v>
       </c>
       <c r="F21">
-        <v>22.64</v>
+        <v>46.79</v>
       </c>
       <c r="G21">
-        <v>5.3</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3699,16 +3719,16 @@
         <v>594</v>
       </c>
       <c r="D22">
-        <v>103.82</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="E22" t="s">
         <v>627</v>
       </c>
       <c r="F22">
-        <v>93.15000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="G22">
-        <v>-10.28</v>
+        <v>-6.97</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3722,16 +3742,16 @@
         <v>594</v>
       </c>
       <c r="D23">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
         <v>627</v>
       </c>
       <c r="F23">
-        <v>38.82</v>
+        <v>55.25</v>
       </c>
       <c r="G23">
-        <v>3.52</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3745,16 +3765,16 @@
         <v>594</v>
       </c>
       <c r="D24">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="E24" t="s">
         <v>627</v>
       </c>
       <c r="F24">
-        <v>55.25</v>
+        <v>38.82</v>
       </c>
       <c r="G24">
-        <v>41.67</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3768,16 +3788,16 @@
         <v>594</v>
       </c>
       <c r="D25">
-        <v>76.18000000000001</v>
+        <v>21.5</v>
       </c>
       <c r="E25" t="s">
         <v>627</v>
       </c>
       <c r="F25">
-        <v>70.87</v>
+        <v>22.64</v>
       </c>
       <c r="G25">
-        <v>-6.97</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3791,16 +3811,16 @@
         <v>594</v>
       </c>
       <c r="D26">
-        <v>39.57</v>
+        <v>27.1</v>
       </c>
       <c r="E26" t="s">
         <v>627</v>
       </c>
       <c r="F26">
-        <v>46.79</v>
+        <v>24.91</v>
       </c>
       <c r="G26">
-        <v>18.25</v>
+        <v>-8.08</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3814,16 +3834,16 @@
         <v>594</v>
       </c>
       <c r="D27">
-        <v>24.77</v>
+        <v>19.5</v>
       </c>
       <c r="E27" t="s">
         <v>627</v>
       </c>
       <c r="F27">
-        <v>28.9</v>
+        <v>19.06</v>
       </c>
       <c r="G27">
-        <v>16.67</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3837,16 +3857,16 @@
         <v>594</v>
       </c>
       <c r="D28">
-        <v>88</v>
+        <v>103.82</v>
       </c>
       <c r="E28" t="s">
         <v>627</v>
       </c>
       <c r="F28">
-        <v>92.34999999999999</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="G28">
-        <v>4.94</v>
+        <v>-10.28</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3883,16 +3903,16 @@
         <v>596</v>
       </c>
       <c r="D30">
-        <v>53</v>
+        <v>15.58</v>
       </c>
       <c r="E30" t="s">
         <v>629</v>
       </c>
       <c r="F30">
-        <v>54.08</v>
+        <v>15.92</v>
       </c>
       <c r="G30">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3906,16 +3926,16 @@
         <v>596</v>
       </c>
       <c r="D31">
-        <v>10.41</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
         <v>629</v>
       </c>
       <c r="F31">
-        <v>9.369999999999999</v>
+        <v>35.15</v>
       </c>
       <c r="G31">
-        <v>-9.99</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3929,16 +3949,16 @@
         <v>596</v>
       </c>
       <c r="D32">
-        <v>8.08</v>
+        <v>21.8</v>
       </c>
       <c r="E32" t="s">
         <v>629</v>
       </c>
       <c r="F32">
-        <v>7.78</v>
+        <v>20.93</v>
       </c>
       <c r="G32">
-        <v>-3.71</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3952,16 +3972,16 @@
         <v>596</v>
       </c>
       <c r="D33">
-        <v>12.06</v>
+        <v>15.85</v>
       </c>
       <c r="E33" t="s">
         <v>629</v>
       </c>
       <c r="F33">
-        <v>11.26</v>
+        <v>16.03</v>
       </c>
       <c r="G33">
-        <v>-6.63</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3975,16 +3995,16 @@
         <v>596</v>
       </c>
       <c r="D34">
-        <v>21.8</v>
+        <v>8.08</v>
       </c>
       <c r="E34" t="s">
         <v>629</v>
       </c>
       <c r="F34">
-        <v>20.93</v>
+        <v>7.78</v>
       </c>
       <c r="G34">
-        <v>-3.99</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3998,16 +4018,16 @@
         <v>596</v>
       </c>
       <c r="D35">
-        <v>15.58</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
         <v>629</v>
       </c>
       <c r="F35">
-        <v>15.92</v>
+        <v>54.08</v>
       </c>
       <c r="G35">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4021,16 +4041,16 @@
         <v>596</v>
       </c>
       <c r="D36">
-        <v>15.85</v>
+        <v>12.06</v>
       </c>
       <c r="E36" t="s">
         <v>629</v>
       </c>
       <c r="F36">
-        <v>16.03</v>
+        <v>11.26</v>
       </c>
       <c r="G36">
-        <v>1.14</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4044,16 +4064,16 @@
         <v>596</v>
       </c>
       <c r="D37">
-        <v>25</v>
+        <v>10.41</v>
       </c>
       <c r="E37" t="s">
         <v>629</v>
       </c>
       <c r="F37">
-        <v>35.15</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G37">
-        <v>40.6</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4182,16 +4202,16 @@
         <v>597</v>
       </c>
       <c r="D43">
-        <v>26.92</v>
+        <v>63.71</v>
       </c>
       <c r="E43" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F43">
-        <v>23.44</v>
+        <v>59.43</v>
       </c>
       <c r="G43">
-        <v>-12.93</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4205,16 +4225,16 @@
         <v>597</v>
       </c>
       <c r="D44">
-        <v>63.71</v>
+        <v>30.86</v>
       </c>
       <c r="E44" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F44">
-        <v>59.43</v>
+        <v>36.74</v>
       </c>
       <c r="G44">
-        <v>-6.72</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4228,16 +4248,16 @@
         <v>597</v>
       </c>
       <c r="D45">
-        <v>30.86</v>
+        <v>7.2</v>
       </c>
       <c r="E45" t="s">
         <v>630</v>
       </c>
       <c r="F45">
-        <v>36.74</v>
+        <v>6.79</v>
       </c>
       <c r="G45">
-        <v>19.05</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4251,16 +4271,16 @@
         <v>597</v>
       </c>
       <c r="D46">
-        <v>7.2</v>
+        <v>35.45</v>
       </c>
       <c r="E46" t="s">
         <v>630</v>
       </c>
       <c r="F46">
-        <v>6.79</v>
+        <v>38.18</v>
       </c>
       <c r="G46">
-        <v>-5.69</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -4274,16 +4294,16 @@
         <v>597</v>
       </c>
       <c r="D47">
-        <v>35.45</v>
+        <v>26.92</v>
       </c>
       <c r="E47" t="s">
         <v>630</v>
       </c>
       <c r="F47">
-        <v>38.18</v>
+        <v>23.44</v>
       </c>
       <c r="G47">
-        <v>7.7</v>
+        <v>-12.93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -4297,16 +4317,16 @@
         <v>598</v>
       </c>
       <c r="D48">
-        <v>61.93</v>
+        <v>10.9</v>
       </c>
       <c r="E48" t="s">
         <v>634</v>
       </c>
       <c r="F48">
-        <v>60.73</v>
+        <v>11.35</v>
       </c>
       <c r="G48">
-        <v>-1.94</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -4320,16 +4340,16 @@
         <v>598</v>
       </c>
       <c r="D49">
-        <v>54.85</v>
+        <v>84.72</v>
       </c>
       <c r="E49" t="s">
         <v>634</v>
       </c>
       <c r="F49">
-        <v>60.31</v>
+        <v>86.5</v>
       </c>
       <c r="G49">
-        <v>9.949999999999999</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -4343,16 +4363,16 @@
         <v>598</v>
       </c>
       <c r="D50">
-        <v>27.55</v>
+        <v>27.75</v>
       </c>
       <c r="E50" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F50">
-        <v>26.68</v>
+        <v>24.16</v>
       </c>
       <c r="G50">
-        <v>-3.16</v>
+        <v>-12.94</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -4366,16 +4386,16 @@
         <v>598</v>
       </c>
       <c r="D51">
-        <v>56.11</v>
+        <v>215</v>
       </c>
       <c r="E51" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F51">
-        <v>51.34</v>
+        <v>209.71</v>
       </c>
       <c r="G51">
-        <v>-8.5</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -4389,16 +4409,16 @@
         <v>598</v>
       </c>
       <c r="D52">
-        <v>52.31</v>
+        <v>58.75</v>
       </c>
       <c r="E52" t="s">
         <v>634</v>
       </c>
       <c r="F52">
-        <v>50.29</v>
+        <v>55.83</v>
       </c>
       <c r="G52">
-        <v>-3.86</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -4412,16 +4432,16 @@
         <v>598</v>
       </c>
       <c r="D53">
-        <v>10.9</v>
+        <v>52.31</v>
       </c>
       <c r="E53" t="s">
         <v>634</v>
       </c>
       <c r="F53">
-        <v>11.35</v>
+        <v>50.29</v>
       </c>
       <c r="G53">
-        <v>4.13</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4435,16 +4455,16 @@
         <v>598</v>
       </c>
       <c r="D54">
-        <v>215</v>
+        <v>27.55</v>
       </c>
       <c r="E54" t="s">
         <v>634</v>
       </c>
       <c r="F54">
-        <v>209.71</v>
+        <v>26.68</v>
       </c>
       <c r="G54">
-        <v>-2.46</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4458,16 +4478,16 @@
         <v>598</v>
       </c>
       <c r="D55">
-        <v>27.75</v>
+        <v>54.85</v>
       </c>
       <c r="E55" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F55">
-        <v>24.16</v>
+        <v>60.31</v>
       </c>
       <c r="G55">
-        <v>-12.94</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -4481,16 +4501,16 @@
         <v>598</v>
       </c>
       <c r="D56">
-        <v>84.72</v>
+        <v>61.93</v>
       </c>
       <c r="E56" t="s">
         <v>634</v>
       </c>
       <c r="F56">
-        <v>86.5</v>
+        <v>60.73</v>
       </c>
       <c r="G56">
-        <v>2.1</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -4504,16 +4524,16 @@
         <v>598</v>
       </c>
       <c r="D57">
-        <v>58.75</v>
+        <v>56.11</v>
       </c>
       <c r="E57" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F57">
-        <v>55.83</v>
+        <v>51.34</v>
       </c>
       <c r="G57">
-        <v>-4.97</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4527,16 +4547,16 @@
         <v>599</v>
       </c>
       <c r="D58">
-        <v>15.47</v>
+        <v>10.5</v>
       </c>
       <c r="E58" t="s">
         <v>637</v>
       </c>
       <c r="F58">
-        <v>16.27</v>
+        <v>13.28</v>
       </c>
       <c r="G58">
-        <v>5.17</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4550,16 +4570,16 @@
         <v>599</v>
       </c>
       <c r="D59">
-        <v>65.52</v>
+        <v>223</v>
       </c>
       <c r="E59" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F59">
-        <v>65.7</v>
+        <v>219.4</v>
       </c>
       <c r="G59">
-        <v>0.27</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4573,16 +4593,16 @@
         <v>599</v>
       </c>
       <c r="D60">
-        <v>252</v>
+        <v>29.98</v>
       </c>
       <c r="E60" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F60">
-        <v>249.3</v>
+        <v>33.5</v>
       </c>
       <c r="G60">
-        <v>-1.07</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -4596,16 +4616,16 @@
         <v>599</v>
       </c>
       <c r="D61">
-        <v>32</v>
+        <v>100.24</v>
       </c>
       <c r="E61" t="s">
         <v>637</v>
       </c>
       <c r="F61">
-        <v>33.95</v>
+        <v>126.7</v>
       </c>
       <c r="G61">
-        <v>6.09</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -4619,16 +4639,16 @@
         <v>599</v>
       </c>
       <c r="D62">
-        <v>13.99</v>
+        <v>24.93</v>
       </c>
       <c r="E62" t="s">
         <v>637</v>
       </c>
       <c r="F62">
-        <v>19.65</v>
+        <v>26.44</v>
       </c>
       <c r="G62">
-        <v>40.46</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4642,16 +4662,16 @@
         <v>599</v>
       </c>
       <c r="D63">
-        <v>24.93</v>
+        <v>13.99</v>
       </c>
       <c r="E63" t="s">
         <v>637</v>
       </c>
       <c r="F63">
-        <v>26.44</v>
+        <v>19.65</v>
       </c>
       <c r="G63">
-        <v>6.06</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4665,16 +4685,16 @@
         <v>599</v>
       </c>
       <c r="D64">
-        <v>100.24</v>
+        <v>252</v>
       </c>
       <c r="E64" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F64">
-        <v>126.7</v>
+        <v>249.3</v>
       </c>
       <c r="G64">
-        <v>26.4</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4688,16 +4708,16 @@
         <v>599</v>
       </c>
       <c r="D65">
-        <v>29.98</v>
+        <v>65.52</v>
       </c>
       <c r="E65" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F65">
-        <v>33.5</v>
+        <v>65.7</v>
       </c>
       <c r="G65">
-        <v>11.74</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -4711,16 +4731,16 @@
         <v>599</v>
       </c>
       <c r="D66">
-        <v>223</v>
+        <v>15.47</v>
       </c>
       <c r="E66" t="s">
         <v>637</v>
       </c>
       <c r="F66">
-        <v>219.4</v>
+        <v>16.27</v>
       </c>
       <c r="G66">
-        <v>-1.61</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4734,16 +4754,16 @@
         <v>599</v>
       </c>
       <c r="D67">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="E67" t="s">
         <v>637</v>
       </c>
       <c r="F67">
-        <v>13.28</v>
+        <v>33.95</v>
       </c>
       <c r="G67">
-        <v>26.48</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4757,16 +4777,16 @@
         <v>600</v>
       </c>
       <c r="D68">
-        <v>57.94</v>
+        <v>37</v>
       </c>
       <c r="E68" t="s">
         <v>639</v>
       </c>
       <c r="F68">
-        <v>60.04</v>
+        <v>41.69</v>
       </c>
       <c r="G68">
-        <v>3.62</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4780,16 +4800,16 @@
         <v>600</v>
       </c>
       <c r="D69">
-        <v>29.4</v>
+        <v>4.75</v>
       </c>
       <c r="E69" t="s">
         <v>640</v>
       </c>
       <c r="F69">
-        <v>26.82</v>
+        <v>4.81</v>
       </c>
       <c r="G69">
-        <v>-8.779999999999999</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4803,85 +4823,85 @@
         <v>600</v>
       </c>
       <c r="D70">
-        <v>27.3</v>
+        <v>22.81</v>
       </c>
       <c r="E70" t="s">
         <v>639</v>
       </c>
       <c r="F70">
-        <v>26.65</v>
+        <v>23.51</v>
       </c>
       <c r="G70">
-        <v>-2.38</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B71" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C71" t="s">
         <v>600</v>
       </c>
       <c r="D71">
-        <v>140</v>
+        <v>32.52</v>
       </c>
       <c r="E71" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F71">
-        <v>144.31</v>
+        <v>31.9</v>
       </c>
       <c r="G71">
-        <v>3.08</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B72" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C72" t="s">
         <v>600</v>
       </c>
       <c r="D72">
-        <v>26.28</v>
+        <v>2.15</v>
       </c>
       <c r="E72" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F72">
-        <v>26.85</v>
+        <v>2.15</v>
       </c>
       <c r="G72">
-        <v>2.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B73" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C73" t="s">
         <v>600</v>
       </c>
       <c r="D73">
-        <v>32.52</v>
+        <v>140</v>
       </c>
       <c r="E73" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F73">
-        <v>31.9</v>
+        <v>144.31</v>
       </c>
       <c r="G73">
-        <v>-1.91</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4895,16 +4915,16 @@
         <v>600</v>
       </c>
       <c r="D74">
-        <v>2.15</v>
+        <v>26.28</v>
       </c>
       <c r="E74" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F74">
-        <v>2.15</v>
+        <v>26.85</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4918,16 +4938,16 @@
         <v>600</v>
       </c>
       <c r="D75">
-        <v>37</v>
+        <v>27.3</v>
       </c>
       <c r="E75" t="s">
         <v>639</v>
       </c>
       <c r="F75">
-        <v>41.69</v>
+        <v>26.65</v>
       </c>
       <c r="G75">
-        <v>12.68</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4941,16 +4961,16 @@
         <v>600</v>
       </c>
       <c r="D76">
-        <v>22.81</v>
+        <v>29.4</v>
       </c>
       <c r="E76" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F76">
-        <v>23.51</v>
+        <v>26.82</v>
       </c>
       <c r="G76">
-        <v>3.07</v>
+        <v>-8.779999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4964,16 +4984,16 @@
         <v>600</v>
       </c>
       <c r="D77">
-        <v>4.75</v>
+        <v>57.94</v>
       </c>
       <c r="E77" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F77">
-        <v>4.81</v>
+        <v>60.04</v>
       </c>
       <c r="G77">
-        <v>1.26</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4987,62 +5007,62 @@
         <v>601</v>
       </c>
       <c r="D78">
-        <v>35.62</v>
+        <v>80.27</v>
       </c>
       <c r="E78" t="s">
         <v>642</v>
       </c>
       <c r="F78">
-        <v>31.82</v>
+        <v>73.53</v>
       </c>
       <c r="G78">
-        <v>-10.67</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B79" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="C79" t="s">
         <v>601</v>
       </c>
       <c r="D79">
-        <v>61.16</v>
+        <v>14.7</v>
       </c>
       <c r="E79" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F79">
-        <v>58.86</v>
+        <v>13.65</v>
       </c>
       <c r="G79">
-        <v>-3.76</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="B80" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="C80" t="s">
         <v>601</v>
       </c>
       <c r="D80">
-        <v>56.3</v>
+        <v>294.01</v>
       </c>
       <c r="E80" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F80">
-        <v>50.71</v>
+        <v>354</v>
       </c>
       <c r="G80">
-        <v>-9.93</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5056,62 +5076,62 @@
         <v>601</v>
       </c>
       <c r="D81">
-        <v>333</v>
+        <v>6.88</v>
       </c>
       <c r="E81" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F81">
-        <v>331.9</v>
+        <v>6.11</v>
       </c>
       <c r="G81">
-        <v>-0.33</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C82" t="s">
         <v>601</v>
       </c>
       <c r="D82">
-        <v>18.55</v>
+        <v>41.92</v>
       </c>
       <c r="E82" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F82">
-        <v>12.52</v>
+        <v>35.76</v>
       </c>
       <c r="G82">
-        <v>-32.51</v>
+        <v>-14.69</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B83" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C83" t="s">
         <v>601</v>
       </c>
       <c r="D83">
-        <v>41.92</v>
+        <v>18.55</v>
       </c>
       <c r="E83" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F83">
-        <v>35.76</v>
+        <v>12.52</v>
       </c>
       <c r="G83">
-        <v>-14.69</v>
+        <v>-32.51</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -5125,62 +5145,62 @@
         <v>601</v>
       </c>
       <c r="D84">
-        <v>6.88</v>
+        <v>333</v>
       </c>
       <c r="E84" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F84">
-        <v>6.11</v>
+        <v>331.9</v>
       </c>
       <c r="G84">
-        <v>-11.19</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C85" t="s">
         <v>601</v>
       </c>
       <c r="D85">
-        <v>294.01</v>
+        <v>56.3</v>
       </c>
       <c r="E85" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F85">
-        <v>354</v>
+        <v>50.71</v>
       </c>
       <c r="G85">
-        <v>20.4</v>
+        <v>-9.93</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B86" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C86" t="s">
         <v>601</v>
       </c>
       <c r="D86">
-        <v>14.7</v>
+        <v>61.16</v>
       </c>
       <c r="E86" t="s">
         <v>644</v>
       </c>
       <c r="F86">
-        <v>13.65</v>
+        <v>58.86</v>
       </c>
       <c r="G86">
-        <v>-7.14</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -5194,16 +5214,16 @@
         <v>601</v>
       </c>
       <c r="D87">
-        <v>80.27</v>
+        <v>35.62</v>
       </c>
       <c r="E87" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F87">
-        <v>73.53</v>
+        <v>31.82</v>
       </c>
       <c r="G87">
-        <v>-8.4</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5217,16 +5237,16 @@
         <v>602</v>
       </c>
       <c r="D88">
-        <v>42</v>
+        <v>22.39</v>
       </c>
       <c r="E88" t="s">
         <v>646</v>
       </c>
       <c r="F88">
-        <v>46.43</v>
+        <v>21.51</v>
       </c>
       <c r="G88">
-        <v>10.55</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -5240,16 +5260,16 @@
         <v>602</v>
       </c>
       <c r="D89">
-        <v>33.3</v>
+        <v>88</v>
       </c>
       <c r="E89" t="s">
         <v>647</v>
       </c>
       <c r="F89">
-        <v>40.4</v>
+        <v>87</v>
       </c>
       <c r="G89">
-        <v>21.32</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -5263,16 +5283,16 @@
         <v>602</v>
       </c>
       <c r="D90">
-        <v>30.15</v>
+        <v>3.41</v>
       </c>
       <c r="E90" t="s">
         <v>648</v>
       </c>
       <c r="F90">
-        <v>29.64</v>
+        <v>3.14</v>
       </c>
       <c r="G90">
-        <v>-1.69</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -5286,16 +5306,16 @@
         <v>602</v>
       </c>
       <c r="D91">
-        <v>10.99</v>
+        <v>3.67</v>
       </c>
       <c r="E91" t="s">
         <v>649</v>
       </c>
       <c r="F91">
-        <v>10.72</v>
+        <v>3.55</v>
       </c>
       <c r="G91">
-        <v>-2.46</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -5309,16 +5329,16 @@
         <v>602</v>
       </c>
       <c r="D92">
-        <v>3.67</v>
+        <v>33.3</v>
       </c>
       <c r="E92" t="s">
         <v>650</v>
       </c>
       <c r="F92">
-        <v>3.55</v>
+        <v>40.4</v>
       </c>
       <c r="G92">
-        <v>-3.27</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -5332,16 +5352,16 @@
         <v>602</v>
       </c>
       <c r="D93">
-        <v>3.41</v>
+        <v>30.15</v>
       </c>
       <c r="E93" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="F93">
-        <v>3.14</v>
+        <v>29.64</v>
       </c>
       <c r="G93">
-        <v>-7.92</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -5355,16 +5375,16 @@
         <v>602</v>
       </c>
       <c r="D94">
-        <v>22.39</v>
+        <v>42</v>
       </c>
       <c r="E94" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F94">
-        <v>21.51</v>
+        <v>46.43</v>
       </c>
       <c r="G94">
-        <v>-3.93</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -5378,16 +5398,16 @@
         <v>602</v>
       </c>
       <c r="D95">
-        <v>88</v>
+        <v>10.99</v>
       </c>
       <c r="E95" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F95">
-        <v>87</v>
+        <v>10.72</v>
       </c>
       <c r="G95">
-        <v>-1.14</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -5562,200 +5582,200 @@
         <v>604</v>
       </c>
       <c r="D103">
-        <v>47.33</v>
+        <v>15.4</v>
       </c>
       <c r="E103" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="F103">
-        <v>47.25</v>
+        <v>17.3</v>
       </c>
       <c r="G103">
-        <v>-0.17</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>419</v>
+        <v>370</v>
       </c>
       <c r="C104" t="s">
         <v>604</v>
       </c>
       <c r="D104">
-        <v>28.8</v>
+        <v>224</v>
       </c>
       <c r="E104" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="F104">
-        <v>28.57</v>
+        <v>227.03</v>
       </c>
       <c r="G104">
-        <v>-0.8</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B105" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C105" t="s">
         <v>604</v>
       </c>
       <c r="D105">
-        <v>16.1</v>
+        <v>23.97</v>
       </c>
       <c r="E105" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="F105">
-        <v>15.64</v>
+        <v>24.9</v>
       </c>
       <c r="G105">
-        <v>-2.86</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C106" t="s">
         <v>604</v>
       </c>
       <c r="D106">
-        <v>22.2</v>
+        <v>36.23</v>
       </c>
       <c r="E106" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F106">
-        <v>23.35</v>
+        <v>45.02</v>
       </c>
       <c r="G106">
-        <v>5.18</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B107" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C107" t="s">
         <v>604</v>
       </c>
       <c r="D107">
-        <v>6.78</v>
+        <v>117</v>
       </c>
       <c r="E107" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="F107">
-        <v>6.54</v>
+        <v>110.12</v>
       </c>
       <c r="G107">
-        <v>-3.54</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B108" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C108" t="s">
         <v>604</v>
       </c>
       <c r="D108">
-        <v>36.23</v>
+        <v>22.2</v>
       </c>
       <c r="E108" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F108">
-        <v>45.02</v>
+        <v>23.35</v>
       </c>
       <c r="G108">
-        <v>24.26</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B109" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C109" t="s">
         <v>604</v>
       </c>
       <c r="D109">
-        <v>117</v>
+        <v>47.33</v>
       </c>
       <c r="E109" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F109">
-        <v>110.12</v>
+        <v>47.25</v>
       </c>
       <c r="G109">
-        <v>-5.88</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B110" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C110" t="s">
         <v>604</v>
       </c>
       <c r="D110">
-        <v>23.97</v>
+        <v>6.78</v>
       </c>
       <c r="E110" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F110">
-        <v>24.9</v>
+        <v>6.54</v>
       </c>
       <c r="G110">
-        <v>3.88</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="B111" t="s">
-        <v>373</v>
+        <v>425</v>
       </c>
       <c r="C111" t="s">
         <v>604</v>
       </c>
       <c r="D111">
-        <v>224</v>
+        <v>16.1</v>
       </c>
       <c r="E111" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F111">
-        <v>227.03</v>
+        <v>15.64</v>
       </c>
       <c r="G111">
-        <v>1.35</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -5769,16 +5789,16 @@
         <v>604</v>
       </c>
       <c r="D112">
-        <v>15.4</v>
+        <v>28.8</v>
       </c>
       <c r="E112" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F112">
-        <v>17.3</v>
+        <v>28.57</v>
       </c>
       <c r="G112">
-        <v>12.34</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -5792,16 +5812,16 @@
         <v>605</v>
       </c>
       <c r="D113">
-        <v>289</v>
+        <v>6.1</v>
       </c>
       <c r="E113" t="s">
         <v>658</v>
       </c>
       <c r="F113">
-        <v>338</v>
+        <v>6.17</v>
       </c>
       <c r="G113">
-        <v>16.96</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5815,16 +5835,16 @@
         <v>605</v>
       </c>
       <c r="D114">
-        <v>71</v>
+        <v>23.3</v>
       </c>
       <c r="E114" t="s">
         <v>658</v>
       </c>
       <c r="F114">
-        <v>78.79000000000001</v>
+        <v>23.32</v>
       </c>
       <c r="G114">
-        <v>10.97</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5838,16 +5858,16 @@
         <v>605</v>
       </c>
       <c r="D115">
-        <v>4.84</v>
+        <v>20</v>
       </c>
       <c r="E115" t="s">
         <v>658</v>
       </c>
       <c r="F115">
-        <v>4.41</v>
+        <v>19.31</v>
       </c>
       <c r="G115">
-        <v>-8.880000000000001</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5861,16 +5881,16 @@
         <v>605</v>
       </c>
       <c r="D116">
-        <v>145.59</v>
+        <v>27</v>
       </c>
       <c r="E116" t="s">
         <v>658</v>
       </c>
       <c r="F116">
-        <v>159.19</v>
+        <v>26.73</v>
       </c>
       <c r="G116">
-        <v>9.34</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5884,16 +5904,16 @@
         <v>605</v>
       </c>
       <c r="D117">
-        <v>41.79</v>
+        <v>3.92</v>
       </c>
       <c r="E117" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F117">
-        <v>56.27</v>
+        <v>3.9</v>
       </c>
       <c r="G117">
-        <v>34.65</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5907,16 +5927,16 @@
         <v>605</v>
       </c>
       <c r="D118">
-        <v>27</v>
+        <v>145.59</v>
       </c>
       <c r="E118" t="s">
         <v>658</v>
       </c>
       <c r="F118">
-        <v>26.73</v>
+        <v>159.19</v>
       </c>
       <c r="G118">
-        <v>-1</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5930,16 +5950,16 @@
         <v>605</v>
       </c>
       <c r="D119">
-        <v>3.92</v>
+        <v>4.84</v>
       </c>
       <c r="E119" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F119">
-        <v>3.9</v>
+        <v>4.41</v>
       </c>
       <c r="G119">
-        <v>-0.51</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5953,16 +5973,16 @@
         <v>605</v>
       </c>
       <c r="D120">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="E120" t="s">
         <v>658</v>
       </c>
       <c r="F120">
-        <v>19.31</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G120">
-        <v>-3.45</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5976,16 +5996,16 @@
         <v>605</v>
       </c>
       <c r="D121">
-        <v>23.3</v>
+        <v>289</v>
       </c>
       <c r="E121" t="s">
         <v>658</v>
       </c>
       <c r="F121">
-        <v>23.32</v>
+        <v>338</v>
       </c>
       <c r="G121">
-        <v>0.09</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -5999,16 +6019,16 @@
         <v>605</v>
       </c>
       <c r="D122">
-        <v>6.1</v>
+        <v>41.79</v>
       </c>
       <c r="E122" t="s">
         <v>658</v>
       </c>
       <c r="F122">
-        <v>6.17</v>
+        <v>56.27</v>
       </c>
       <c r="G122">
-        <v>1.15</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6022,177 +6042,177 @@
         <v>606</v>
       </c>
       <c r="D123">
-        <v>53.9</v>
+        <v>5.08</v>
       </c>
       <c r="E123" t="s">
         <v>660</v>
       </c>
       <c r="F123">
-        <v>59.81</v>
+        <v>4.6</v>
       </c>
       <c r="G123">
-        <v>10.96</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="B124" t="s">
-        <v>383</v>
+        <v>438</v>
       </c>
       <c r="C124" t="s">
         <v>606</v>
       </c>
       <c r="D124">
-        <v>127</v>
+        <v>28.94</v>
       </c>
       <c r="E124" t="s">
         <v>660</v>
       </c>
       <c r="F124">
-        <v>130.97</v>
+        <v>30.76</v>
       </c>
       <c r="G124">
-        <v>3.13</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B125" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C125" t="s">
         <v>606</v>
       </c>
       <c r="D125">
-        <v>16.73</v>
+        <v>7.01</v>
       </c>
       <c r="E125" t="s">
         <v>660</v>
       </c>
       <c r="F125">
-        <v>17.67</v>
+        <v>7.13</v>
       </c>
       <c r="G125">
-        <v>5.62</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B126" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C126" t="s">
         <v>606</v>
       </c>
       <c r="D126">
-        <v>38.2</v>
+        <v>113</v>
       </c>
       <c r="E126" t="s">
         <v>660</v>
       </c>
       <c r="F126">
-        <v>47</v>
+        <v>118.43</v>
       </c>
       <c r="G126">
-        <v>23.04</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C127" t="s">
         <v>606</v>
       </c>
       <c r="D127">
-        <v>26</v>
+        <v>17.95</v>
       </c>
       <c r="E127" t="s">
         <v>660</v>
       </c>
       <c r="F127">
-        <v>28.88</v>
+        <v>20.77</v>
       </c>
       <c r="G127">
-        <v>11.08</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B128" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C128" t="s">
         <v>606</v>
       </c>
       <c r="D128">
-        <v>17.95</v>
+        <v>26</v>
       </c>
       <c r="E128" t="s">
         <v>660</v>
       </c>
       <c r="F128">
-        <v>20.77</v>
+        <v>28.88</v>
       </c>
       <c r="G128">
-        <v>15.71</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B129" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C129" t="s">
         <v>606</v>
       </c>
       <c r="D129">
-        <v>113</v>
+        <v>16.73</v>
       </c>
       <c r="E129" t="s">
         <v>660</v>
       </c>
       <c r="F129">
-        <v>118.43</v>
+        <v>17.67</v>
       </c>
       <c r="G129">
-        <v>4.81</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="B130" t="s">
-        <v>443</v>
+        <v>380</v>
       </c>
       <c r="C130" t="s">
         <v>606</v>
       </c>
       <c r="D130">
-        <v>7.01</v>
+        <v>127</v>
       </c>
       <c r="E130" t="s">
         <v>660</v>
       </c>
       <c r="F130">
-        <v>7.13</v>
+        <v>130.97</v>
       </c>
       <c r="G130">
-        <v>1.71</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6206,16 +6226,16 @@
         <v>606</v>
       </c>
       <c r="D131">
-        <v>28.94</v>
+        <v>53.9</v>
       </c>
       <c r="E131" t="s">
         <v>660</v>
       </c>
       <c r="F131">
-        <v>30.76</v>
+        <v>59.81</v>
       </c>
       <c r="G131">
-        <v>6.29</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6229,16 +6249,16 @@
         <v>606</v>
       </c>
       <c r="D132">
-        <v>5.08</v>
+        <v>38.2</v>
       </c>
       <c r="E132" t="s">
         <v>660</v>
       </c>
       <c r="F132">
-        <v>4.6</v>
+        <v>47</v>
       </c>
       <c r="G132">
-        <v>-9.449999999999999</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -6252,16 +6272,16 @@
         <v>607</v>
       </c>
       <c r="D133">
-        <v>21.98</v>
+        <v>47.42</v>
       </c>
       <c r="E133" t="s">
         <v>661</v>
       </c>
       <c r="F133">
-        <v>24.98</v>
+        <v>45.6</v>
       </c>
       <c r="G133">
-        <v>13.65</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -6275,154 +6295,154 @@
         <v>607</v>
       </c>
       <c r="D134">
-        <v>8.369999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E134" t="s">
         <v>661</v>
       </c>
       <c r="F134">
-        <v>8.4</v>
+        <v>11.17</v>
       </c>
       <c r="G134">
-        <v>0.36</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B135" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C135" t="s">
         <v>607</v>
       </c>
       <c r="D135">
-        <v>106.8</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E135" t="s">
         <v>661</v>
       </c>
       <c r="F135">
-        <v>110.11</v>
+        <v>61.4</v>
       </c>
       <c r="G135">
-        <v>3.1</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B136" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C136" t="s">
         <v>607</v>
       </c>
       <c r="D136">
-        <v>31.4</v>
+        <v>110</v>
       </c>
       <c r="E136" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F136">
-        <v>28.23</v>
+        <v>105</v>
       </c>
       <c r="G136">
-        <v>-10.1</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B137" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C137" t="s">
         <v>607</v>
       </c>
       <c r="D137">
-        <v>18.8</v>
+        <v>22.83</v>
       </c>
       <c r="E137" t="s">
         <v>661</v>
       </c>
       <c r="F137">
-        <v>19.59</v>
+        <v>24.63</v>
       </c>
       <c r="G137">
-        <v>4.2</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B138" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C138" t="s">
         <v>607</v>
       </c>
       <c r="D138">
-        <v>22.83</v>
+        <v>18.8</v>
       </c>
       <c r="E138" t="s">
         <v>661</v>
       </c>
       <c r="F138">
-        <v>24.63</v>
+        <v>19.59</v>
       </c>
       <c r="G138">
-        <v>7.88</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B139" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C139" t="s">
         <v>607</v>
       </c>
       <c r="D139">
-        <v>110</v>
+        <v>106.8</v>
       </c>
       <c r="E139" t="s">
         <v>661</v>
       </c>
       <c r="F139">
-        <v>105</v>
+        <v>110.11</v>
       </c>
       <c r="G139">
-        <v>-4.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B140" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C140" t="s">
         <v>607</v>
       </c>
       <c r="D140">
-        <v>65.73999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E140" t="s">
         <v>661</v>
       </c>
       <c r="F140">
-        <v>61.4</v>
+        <v>8.4</v>
       </c>
       <c r="G140">
-        <v>-6.6</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -6436,16 +6456,16 @@
         <v>607</v>
       </c>
       <c r="D141">
-        <v>9.4</v>
+        <v>21.98</v>
       </c>
       <c r="E141" t="s">
         <v>661</v>
       </c>
       <c r="F141">
-        <v>11.17</v>
+        <v>24.98</v>
       </c>
       <c r="G141">
-        <v>18.83</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -6459,16 +6479,16 @@
         <v>607</v>
       </c>
       <c r="D142">
-        <v>47.42</v>
+        <v>31.4</v>
       </c>
       <c r="E142" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F142">
-        <v>45.6</v>
+        <v>28.23</v>
       </c>
       <c r="G142">
-        <v>-3.84</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -6482,16 +6502,16 @@
         <v>608</v>
       </c>
       <c r="D143">
-        <v>40.7</v>
+        <v>37.9</v>
       </c>
       <c r="E143" t="s">
         <v>663</v>
       </c>
       <c r="F143">
-        <v>47.29</v>
+        <v>43.45</v>
       </c>
       <c r="G143">
-        <v>16.19</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -6505,16 +6525,16 @@
         <v>608</v>
       </c>
       <c r="D144">
-        <v>56.49</v>
+        <v>65.22</v>
       </c>
       <c r="E144" t="s">
         <v>663</v>
       </c>
       <c r="F144">
-        <v>77.11</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G144">
-        <v>36.5</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -6528,16 +6548,16 @@
         <v>608</v>
       </c>
       <c r="D145">
-        <v>40.07</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E145" t="s">
         <v>663</v>
       </c>
       <c r="F145">
-        <v>45.14</v>
+        <v>95.16</v>
       </c>
       <c r="G145">
-        <v>12.65</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -6551,62 +6571,62 @@
         <v>608</v>
       </c>
       <c r="D146">
-        <v>14.41</v>
+        <v>18.2</v>
       </c>
       <c r="E146" t="s">
         <v>663</v>
       </c>
       <c r="F146">
-        <v>17.22</v>
+        <v>17.9</v>
       </c>
       <c r="G146">
-        <v>19.5</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="C147" t="s">
         <v>608</v>
       </c>
       <c r="D147">
-        <v>181.29</v>
+        <v>8.82</v>
       </c>
       <c r="E147" t="s">
         <v>663</v>
       </c>
       <c r="F147">
-        <v>191.66</v>
+        <v>8.27</v>
       </c>
       <c r="G147">
-        <v>5.72</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="B148" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="C148" t="s">
         <v>608</v>
       </c>
       <c r="D148">
-        <v>95.09999999999999</v>
+        <v>181.29</v>
       </c>
       <c r="E148" t="s">
         <v>663</v>
       </c>
       <c r="F148">
-        <v>95.16</v>
+        <v>191.66</v>
       </c>
       <c r="G148">
-        <v>0.06</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -6620,16 +6640,16 @@
         <v>608</v>
       </c>
       <c r="D149">
-        <v>18.2</v>
+        <v>14.41</v>
       </c>
       <c r="E149" t="s">
         <v>663</v>
       </c>
       <c r="F149">
-        <v>17.9</v>
+        <v>17.22</v>
       </c>
       <c r="G149">
-        <v>-1.65</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -6643,16 +6663,16 @@
         <v>608</v>
       </c>
       <c r="D150">
-        <v>65.22</v>
+        <v>56.49</v>
       </c>
       <c r="E150" t="s">
         <v>663</v>
       </c>
       <c r="F150">
-        <v>76.09999999999999</v>
+        <v>77.11</v>
       </c>
       <c r="G150">
-        <v>16.68</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -6666,16 +6686,16 @@
         <v>608</v>
       </c>
       <c r="D151">
-        <v>8.82</v>
+        <v>40.7</v>
       </c>
       <c r="E151" t="s">
         <v>663</v>
       </c>
       <c r="F151">
-        <v>8.27</v>
+        <v>47.29</v>
       </c>
       <c r="G151">
-        <v>-6.24</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -6689,16 +6709,16 @@
         <v>608</v>
       </c>
       <c r="D152">
-        <v>37.9</v>
+        <v>40.07</v>
       </c>
       <c r="E152" t="s">
         <v>663</v>
       </c>
       <c r="F152">
-        <v>43.45</v>
+        <v>45.14</v>
       </c>
       <c r="G152">
-        <v>14.64</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -6712,39 +6732,39 @@
         <v>609</v>
       </c>
       <c r="D153">
-        <v>25</v>
+        <v>115.38</v>
       </c>
       <c r="E153" t="s">
         <v>664</v>
       </c>
       <c r="F153">
-        <v>30.35</v>
+        <v>102.39</v>
       </c>
       <c r="G153">
-        <v>21.4</v>
+        <v>-11.26</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="B154" t="s">
-        <v>396</v>
+        <v>447</v>
       </c>
       <c r="C154" t="s">
         <v>609</v>
       </c>
       <c r="D154">
-        <v>37.87</v>
+        <v>14.19</v>
       </c>
       <c r="E154" t="s">
         <v>664</v>
       </c>
       <c r="F154">
-        <v>32.38</v>
+        <v>11.85</v>
       </c>
       <c r="G154">
-        <v>-14.5</v>
+        <v>-16.49</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -6758,16 +6778,16 @@
         <v>609</v>
       </c>
       <c r="D155">
-        <v>24.4</v>
+        <v>35.6</v>
       </c>
       <c r="E155" t="s">
         <v>664</v>
       </c>
       <c r="F155">
-        <v>24.68</v>
+        <v>36.29</v>
       </c>
       <c r="G155">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -6804,62 +6824,62 @@
         <v>609</v>
       </c>
       <c r="D157">
-        <v>3.65</v>
+        <v>24.4</v>
       </c>
       <c r="E157" t="s">
         <v>664</v>
       </c>
       <c r="F157">
-        <v>3.5</v>
+        <v>24.68</v>
       </c>
       <c r="G157">
-        <v>-4.11</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="B158" t="s">
-        <v>468</v>
+        <v>402</v>
       </c>
       <c r="C158" t="s">
         <v>609</v>
       </c>
       <c r="D158">
-        <v>35.6</v>
+        <v>37.87</v>
       </c>
       <c r="E158" t="s">
         <v>664</v>
       </c>
       <c r="F158">
-        <v>36.29</v>
+        <v>32.38</v>
       </c>
       <c r="G158">
-        <v>1.94</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B159" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="C159" t="s">
         <v>609</v>
       </c>
       <c r="D159">
-        <v>14.19</v>
+        <v>25</v>
       </c>
       <c r="E159" t="s">
         <v>664</v>
       </c>
       <c r="F159">
-        <v>11.85</v>
+        <v>30.35</v>
       </c>
       <c r="G159">
-        <v>-16.49</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -6873,16 +6893,16 @@
         <v>609</v>
       </c>
       <c r="D160">
-        <v>115.38</v>
+        <v>3.65</v>
       </c>
       <c r="E160" t="s">
         <v>664</v>
       </c>
       <c r="F160">
-        <v>102.39</v>
+        <v>3.5</v>
       </c>
       <c r="G160">
-        <v>-11.26</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -6919,16 +6939,16 @@
         <v>610</v>
       </c>
       <c r="D162">
-        <v>21.91</v>
+        <v>30.7</v>
       </c>
       <c r="E162" t="s">
         <v>665</v>
       </c>
       <c r="F162">
-        <v>22.75</v>
+        <v>27.77</v>
       </c>
       <c r="G162">
-        <v>3.83</v>
+        <v>-9.539999999999999</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6942,16 +6962,16 @@
         <v>610</v>
       </c>
       <c r="D163">
-        <v>4.12</v>
+        <v>24.58</v>
       </c>
       <c r="E163" t="s">
         <v>665</v>
       </c>
       <c r="F163">
-        <v>3.72</v>
+        <v>24.44</v>
       </c>
       <c r="G163">
-        <v>-9.710000000000001</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -6965,16 +6985,16 @@
         <v>610</v>
       </c>
       <c r="D164">
-        <v>6.31</v>
+        <v>22.66</v>
       </c>
       <c r="E164" t="s">
         <v>665</v>
       </c>
       <c r="F164">
-        <v>5.31</v>
+        <v>19.38</v>
       </c>
       <c r="G164">
-        <v>-15.85</v>
+        <v>-14.47</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7011,16 +7031,16 @@
         <v>610</v>
       </c>
       <c r="D166">
-        <v>24.58</v>
+        <v>21.91</v>
       </c>
       <c r="E166" t="s">
         <v>665</v>
       </c>
       <c r="F166">
-        <v>24.44</v>
+        <v>22.75</v>
       </c>
       <c r="G166">
-        <v>-0.57</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7034,16 +7054,16 @@
         <v>610</v>
       </c>
       <c r="D167">
-        <v>22.66</v>
+        <v>4.12</v>
       </c>
       <c r="E167" t="s">
         <v>665</v>
       </c>
       <c r="F167">
-        <v>19.38</v>
+        <v>3.72</v>
       </c>
       <c r="G167">
-        <v>-14.47</v>
+        <v>-9.710000000000001</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7057,16 +7077,16 @@
         <v>610</v>
       </c>
       <c r="D168">
-        <v>30.7</v>
+        <v>6.31</v>
       </c>
       <c r="E168" t="s">
         <v>665</v>
       </c>
       <c r="F168">
-        <v>27.77</v>
+        <v>5.31</v>
       </c>
       <c r="G168">
-        <v>-9.539999999999999</v>
+        <v>-15.85</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7080,16 +7100,16 @@
         <v>611</v>
       </c>
       <c r="D169">
-        <v>38.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E169" t="s">
         <v>666</v>
       </c>
       <c r="F169">
-        <v>38.27</v>
+        <v>7.21</v>
       </c>
       <c r="G169">
-        <v>-0.6</v>
+        <v>-13.03</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7195,16 +7215,16 @@
         <v>611</v>
       </c>
       <c r="D174">
-        <v>8.289999999999999</v>
+        <v>30.77</v>
       </c>
       <c r="E174" t="s">
         <v>666</v>
       </c>
       <c r="F174">
-        <v>7.21</v>
+        <v>34.09</v>
       </c>
       <c r="G174">
-        <v>-13.03</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7218,16 +7238,16 @@
         <v>611</v>
       </c>
       <c r="D175">
-        <v>17.63</v>
+        <v>41.29</v>
       </c>
       <c r="E175" t="s">
         <v>666</v>
       </c>
       <c r="F175">
-        <v>15.36</v>
+        <v>36.77</v>
       </c>
       <c r="G175">
-        <v>-12.88</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7241,16 +7261,16 @@
         <v>611</v>
       </c>
       <c r="D176">
-        <v>30.77</v>
+        <v>114</v>
       </c>
       <c r="E176" t="s">
         <v>666</v>
       </c>
       <c r="F176">
-        <v>34.09</v>
+        <v>114.39</v>
       </c>
       <c r="G176">
-        <v>10.79</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7264,16 +7284,16 @@
         <v>611</v>
       </c>
       <c r="D177">
-        <v>41.29</v>
+        <v>38.5</v>
       </c>
       <c r="E177" t="s">
         <v>666</v>
       </c>
       <c r="F177">
-        <v>36.77</v>
+        <v>38.27</v>
       </c>
       <c r="G177">
-        <v>-10.95</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7287,223 +7307,223 @@
         <v>611</v>
       </c>
       <c r="D178">
-        <v>114</v>
+        <v>17.63</v>
       </c>
       <c r="E178" t="s">
         <v>666</v>
       </c>
       <c r="F178">
-        <v>114.39</v>
+        <v>15.36</v>
       </c>
       <c r="G178">
-        <v>0.34</v>
+        <v>-12.88</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>218</v>
+        <v>173</v>
       </c>
       <c r="B179" t="s">
-        <v>488</v>
+        <v>443</v>
       </c>
       <c r="C179" t="s">
         <v>612</v>
       </c>
       <c r="D179">
-        <v>11.7</v>
+        <v>27.37</v>
       </c>
       <c r="E179" t="s">
         <v>667</v>
       </c>
       <c r="F179">
-        <v>10.31</v>
+        <v>27.15</v>
       </c>
       <c r="G179">
-        <v>-11.88</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B180" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C180" t="s">
         <v>612</v>
       </c>
       <c r="D180">
-        <v>46.93</v>
+        <v>17</v>
       </c>
       <c r="E180" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F180">
-        <v>46.24</v>
+        <v>18.78</v>
       </c>
       <c r="G180">
-        <v>-1.47</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B181" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C181" t="s">
         <v>612</v>
       </c>
       <c r="D181">
-        <v>15.78</v>
+        <v>50.33</v>
       </c>
       <c r="E181" t="s">
         <v>668</v>
       </c>
       <c r="F181">
-        <v>15.97</v>
+        <v>50.4</v>
       </c>
       <c r="G181">
-        <v>1.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B182" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C182" t="s">
         <v>612</v>
       </c>
       <c r="D182">
-        <v>2.45</v>
+        <v>21.41</v>
       </c>
       <c r="E182" t="s">
         <v>669</v>
       </c>
       <c r="F182">
-        <v>2.36</v>
+        <v>16.91</v>
       </c>
       <c r="G182">
-        <v>-3.67</v>
+        <v>-21.02</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B183" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C183" t="s">
         <v>612</v>
       </c>
       <c r="D183">
-        <v>8.550000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="E183" t="s">
         <v>670</v>
       </c>
       <c r="F183">
-        <v>9</v>
+        <v>6.48</v>
       </c>
       <c r="G183">
-        <v>5.26</v>
+        <v>-11.84</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B184" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C184" t="s">
         <v>612</v>
       </c>
       <c r="D184">
-        <v>50.33</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E184" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F184">
-        <v>50.4</v>
+        <v>9</v>
       </c>
       <c r="G184">
-        <v>0.14</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B185" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C185" t="s">
         <v>612</v>
       </c>
       <c r="D185">
-        <v>21.41</v>
+        <v>15.78</v>
       </c>
       <c r="E185" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F185">
-        <v>16.91</v>
+        <v>15.97</v>
       </c>
       <c r="G185">
-        <v>-21.02</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B186" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C186" t="s">
         <v>612</v>
       </c>
       <c r="D186">
-        <v>17</v>
+        <v>46.93</v>
       </c>
       <c r="E186" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F186">
-        <v>18.78</v>
+        <v>46.24</v>
       </c>
       <c r="G186">
-        <v>10.47</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="B187" t="s">
-        <v>438</v>
+        <v>495</v>
       </c>
       <c r="C187" t="s">
         <v>612</v>
       </c>
       <c r="D187">
-        <v>27.37</v>
+        <v>11.7</v>
       </c>
       <c r="E187" t="s">
         <v>670</v>
       </c>
       <c r="F187">
-        <v>27.15</v>
+        <v>10.31</v>
       </c>
       <c r="G187">
-        <v>-0.8</v>
+        <v>-11.88</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7517,16 +7537,16 @@
         <v>612</v>
       </c>
       <c r="D188">
-        <v>7.35</v>
+        <v>2.45</v>
       </c>
       <c r="E188" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="F188">
-        <v>6.48</v>
+        <v>2.36</v>
       </c>
       <c r="G188">
-        <v>-11.84</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7540,223 +7560,223 @@
         <v>613</v>
       </c>
       <c r="D189">
-        <v>37.38</v>
+        <v>12.8</v>
       </c>
       <c r="E189" t="s">
         <v>672</v>
       </c>
       <c r="F189">
-        <v>39.12</v>
+        <v>12.81</v>
       </c>
       <c r="G189">
-        <v>4.65</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="B190" t="s">
-        <v>382</v>
+        <v>498</v>
       </c>
       <c r="C190" t="s">
         <v>613</v>
       </c>
       <c r="D190">
-        <v>35.11</v>
+        <v>62.85</v>
       </c>
       <c r="E190" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F190">
-        <v>40.71</v>
+        <v>55.44</v>
       </c>
       <c r="G190">
-        <v>15.95</v>
+        <v>-11.79</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B191" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C191" t="s">
         <v>613</v>
       </c>
       <c r="D191">
-        <v>44.15</v>
+        <v>1.94</v>
       </c>
       <c r="E191" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F191">
-        <v>44.75</v>
+        <v>1.91</v>
       </c>
       <c r="G191">
-        <v>1.36</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>56</v>
+        <v>219</v>
       </c>
       <c r="B192" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="C192" t="s">
         <v>613</v>
       </c>
       <c r="D192">
-        <v>43.8</v>
+        <v>52.48</v>
       </c>
       <c r="E192" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F192">
-        <v>43.36</v>
+        <v>50.93</v>
       </c>
       <c r="G192">
-        <v>-1</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B193" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C193" t="s">
         <v>613</v>
       </c>
       <c r="D193">
-        <v>57.43</v>
+        <v>18.95</v>
       </c>
       <c r="E193" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F193">
-        <v>66.40000000000001</v>
+        <v>19.13</v>
       </c>
       <c r="G193">
-        <v>15.62</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B194" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C194" t="s">
         <v>613</v>
       </c>
       <c r="D194">
-        <v>52.48</v>
+        <v>57.43</v>
       </c>
       <c r="E194" t="s">
         <v>673</v>
       </c>
       <c r="F194">
-        <v>50.93</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G194">
-        <v>-2.95</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B195" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C195" t="s">
         <v>613</v>
       </c>
       <c r="D195">
-        <v>18.95</v>
+        <v>44.15</v>
       </c>
       <c r="E195" t="s">
         <v>672</v>
       </c>
       <c r="F195">
-        <v>19.13</v>
+        <v>44.75</v>
       </c>
       <c r="G195">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="B196" t="s">
-        <v>501</v>
+        <v>381</v>
       </c>
       <c r="C196" t="s">
         <v>613</v>
       </c>
       <c r="D196">
-        <v>1.94</v>
+        <v>35.11</v>
       </c>
       <c r="E196" t="s">
         <v>673</v>
       </c>
       <c r="F196">
-        <v>1.91</v>
+        <v>40.71</v>
       </c>
       <c r="G196">
-        <v>-1.55</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B197" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C197" t="s">
         <v>613</v>
       </c>
       <c r="D197">
-        <v>62.85</v>
+        <v>37.38</v>
       </c>
       <c r="E197" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F197">
-        <v>55.44</v>
+        <v>39.12</v>
       </c>
       <c r="G197">
-        <v>-11.79</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="B198" t="s">
-        <v>503</v>
+        <v>326</v>
       </c>
       <c r="C198" t="s">
         <v>613</v>
       </c>
       <c r="D198">
-        <v>12.8</v>
+        <v>43.8</v>
       </c>
       <c r="E198" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F198">
-        <v>12.81</v>
+        <v>43.36</v>
       </c>
       <c r="G198">
-        <v>0.08</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -7770,16 +7790,16 @@
         <v>614</v>
       </c>
       <c r="D199">
-        <v>24.22</v>
+        <v>51</v>
       </c>
       <c r="E199" t="s">
         <v>674</v>
       </c>
       <c r="F199">
-        <v>25.26</v>
+        <v>57.19</v>
       </c>
       <c r="G199">
-        <v>4.29</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -7793,16 +7813,16 @@
         <v>614</v>
       </c>
       <c r="D200">
-        <v>59</v>
+        <v>17.5</v>
       </c>
       <c r="E200" t="s">
         <v>674</v>
       </c>
       <c r="F200">
-        <v>64.76000000000001</v>
+        <v>15.77</v>
       </c>
       <c r="G200">
-        <v>9.76</v>
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -7816,16 +7836,16 @@
         <v>614</v>
       </c>
       <c r="D201">
-        <v>16.51</v>
+        <v>99.92</v>
       </c>
       <c r="E201" t="s">
         <v>674</v>
       </c>
       <c r="F201">
-        <v>17.32</v>
+        <v>112.71</v>
       </c>
       <c r="G201">
-        <v>4.91</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -7839,62 +7859,62 @@
         <v>614</v>
       </c>
       <c r="D202">
-        <v>67.47</v>
+        <v>19.9</v>
       </c>
       <c r="E202" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F202">
-        <v>66.65000000000001</v>
+        <v>19.08</v>
       </c>
       <c r="G202">
-        <v>-1.22</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="B203" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="C203" t="s">
         <v>614</v>
       </c>
       <c r="D203">
-        <v>3.78</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E203" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F203">
-        <v>4.25</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="G203">
-        <v>12.43</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="B204" t="s">
-        <v>508</v>
+        <v>469</v>
       </c>
       <c r="C204" t="s">
         <v>614</v>
       </c>
       <c r="D204">
-        <v>51</v>
+        <v>3.78</v>
       </c>
       <c r="E204" t="s">
         <v>674</v>
       </c>
       <c r="F204">
-        <v>57.19</v>
+        <v>4.25</v>
       </c>
       <c r="G204">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -7908,16 +7928,16 @@
         <v>614</v>
       </c>
       <c r="D205">
-        <v>19.9</v>
+        <v>67.47</v>
       </c>
       <c r="E205" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F205">
-        <v>19.08</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="G205">
-        <v>-4.12</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -7931,16 +7951,16 @@
         <v>614</v>
       </c>
       <c r="D206">
-        <v>99.92</v>
+        <v>16.51</v>
       </c>
       <c r="E206" t="s">
         <v>674</v>
       </c>
       <c r="F206">
-        <v>112.71</v>
+        <v>17.32</v>
       </c>
       <c r="G206">
-        <v>12.8</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -7954,16 +7974,16 @@
         <v>614</v>
       </c>
       <c r="D207">
-        <v>17.5</v>
+        <v>59</v>
       </c>
       <c r="E207" t="s">
         <v>674</v>
       </c>
       <c r="F207">
-        <v>15.77</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="G207">
-        <v>-9.890000000000001</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -7977,39 +7997,39 @@
         <v>614</v>
       </c>
       <c r="D208">
-        <v>67.65000000000001</v>
+        <v>24.22</v>
       </c>
       <c r="E208" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F208">
-        <v>66.01000000000001</v>
+        <v>25.26</v>
       </c>
       <c r="G208">
-        <v>-2.42</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B209" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C209" t="s">
         <v>615</v>
       </c>
       <c r="D209">
-        <v>39.5</v>
+        <v>54.48</v>
       </c>
       <c r="E209" t="s">
         <v>677</v>
       </c>
       <c r="F209">
-        <v>41.43</v>
+        <v>50.89</v>
       </c>
       <c r="G209">
-        <v>4.89</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -8083,117 +8103,117 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="C213" t="s">
         <v>615</v>
       </c>
       <c r="D213">
-        <v>54.48</v>
+        <v>38.39</v>
       </c>
       <c r="E213" t="s">
         <v>677</v>
       </c>
       <c r="F213">
-        <v>50.89</v>
+        <v>39.68</v>
       </c>
       <c r="G213">
-        <v>-6.59</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="B214" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="C214" t="s">
         <v>615</v>
       </c>
       <c r="D214">
-        <v>38.39</v>
+        <v>27.59</v>
       </c>
       <c r="E214" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F214">
-        <v>39.68</v>
+        <v>28.41</v>
       </c>
       <c r="G214">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B215" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C215" t="s">
         <v>615</v>
       </c>
       <c r="D215">
-        <v>27.59</v>
+        <v>28.29</v>
       </c>
       <c r="E215" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F215">
-        <v>28.41</v>
+        <v>27.71</v>
       </c>
       <c r="G215">
-        <v>2.97</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B216" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C216" t="s">
         <v>615</v>
       </c>
       <c r="D216">
-        <v>72.27</v>
+        <v>85</v>
       </c>
       <c r="E216" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F216">
-        <v>71.89</v>
+        <v>72.3</v>
       </c>
       <c r="G216">
-        <v>-0.53</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>248</v>
+        <v>175</v>
       </c>
       <c r="B217" t="s">
-        <v>518</v>
+        <v>445</v>
       </c>
       <c r="C217" t="s">
         <v>615</v>
       </c>
       <c r="D217">
-        <v>28.29</v>
+        <v>39.5</v>
       </c>
       <c r="E217" t="s">
         <v>677</v>
       </c>
       <c r="F217">
-        <v>27.71</v>
+        <v>41.43</v>
       </c>
       <c r="G217">
-        <v>-2.05</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -8207,16 +8227,16 @@
         <v>615</v>
       </c>
       <c r="D218">
-        <v>85</v>
+        <v>72.27</v>
       </c>
       <c r="E218" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F218">
-        <v>72.3</v>
+        <v>71.89</v>
       </c>
       <c r="G218">
-        <v>-14.94</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -8230,16 +8250,16 @@
         <v>616</v>
       </c>
       <c r="D219">
-        <v>81.34999999999999</v>
+        <v>11.57</v>
       </c>
       <c r="E219" t="s">
         <v>680</v>
       </c>
       <c r="F219">
-        <v>77.02</v>
+        <v>10.3</v>
       </c>
       <c r="G219">
-        <v>-5.32</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -8276,16 +8296,16 @@
         <v>616</v>
       </c>
       <c r="D221">
-        <v>37.25</v>
+        <v>9</v>
       </c>
       <c r="E221" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F221">
-        <v>37.11</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G221">
-        <v>-0.38</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -8299,16 +8319,16 @@
         <v>616</v>
       </c>
       <c r="D222">
-        <v>46</v>
+        <v>13.3</v>
       </c>
       <c r="E222" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="F222">
-        <v>42.38</v>
+        <v>11.65</v>
       </c>
       <c r="G222">
-        <v>-7.87</v>
+        <v>-12.41</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -8322,16 +8342,16 @@
         <v>616</v>
       </c>
       <c r="D223">
-        <v>10.52</v>
+        <v>5.87</v>
       </c>
       <c r="E223" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F223">
-        <v>8.66</v>
+        <v>5.85</v>
       </c>
       <c r="G223">
-        <v>-17.68</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -8345,16 +8365,16 @@
         <v>616</v>
       </c>
       <c r="D224">
-        <v>5.87</v>
+        <v>14.85</v>
       </c>
       <c r="E224" t="s">
         <v>681</v>
       </c>
       <c r="F224">
-        <v>5.85</v>
+        <v>15.38</v>
       </c>
       <c r="G224">
-        <v>-0.34</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -8368,16 +8388,16 @@
         <v>616</v>
       </c>
       <c r="D225">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E225" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F225">
-        <v>8.380000000000001</v>
+        <v>42.38</v>
       </c>
       <c r="G225">
-        <v>-6.89</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -8391,16 +8411,16 @@
         <v>616</v>
       </c>
       <c r="D226">
-        <v>13.3</v>
+        <v>10.52</v>
       </c>
       <c r="E226" t="s">
         <v>684</v>
       </c>
       <c r="F226">
-        <v>11.65</v>
+        <v>8.66</v>
       </c>
       <c r="G226">
-        <v>-12.41</v>
+        <v>-17.68</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -8414,16 +8434,16 @@
         <v>616</v>
       </c>
       <c r="D227">
-        <v>11.57</v>
+        <v>37.25</v>
       </c>
       <c r="E227" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F227">
-        <v>10.3</v>
+        <v>37.11</v>
       </c>
       <c r="G227">
-        <v>-10.98</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -8437,16 +8457,16 @@
         <v>616</v>
       </c>
       <c r="D228">
-        <v>14.85</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="E228" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="F228">
-        <v>15.38</v>
+        <v>77.02</v>
       </c>
       <c r="G228">
-        <v>3.57</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -8466,10 +8486,10 @@
         <v>686</v>
       </c>
       <c r="F229">
-        <v>36.11</v>
+        <v>33.87</v>
       </c>
       <c r="G229">
-        <v>1.72</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -8483,16 +8503,16 @@
         <v>617</v>
       </c>
       <c r="D230">
-        <v>9.630000000000001</v>
+        <v>56.01</v>
       </c>
       <c r="E230" t="s">
         <v>687</v>
       </c>
       <c r="F230">
-        <v>11.12</v>
+        <v>53.66</v>
       </c>
       <c r="G230">
-        <v>15.47</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -8506,16 +8526,16 @@
         <v>617</v>
       </c>
       <c r="D231">
-        <v>5.4</v>
+        <v>40.12</v>
       </c>
       <c r="E231" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F231">
-        <v>5.42</v>
+        <v>40.5</v>
       </c>
       <c r="G231">
-        <v>0.37</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -8529,16 +8549,16 @@
         <v>617</v>
       </c>
       <c r="D232">
-        <v>5.77</v>
+        <v>92</v>
       </c>
       <c r="E232" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F232">
-        <v>5.89</v>
+        <v>85</v>
       </c>
       <c r="G232">
-        <v>2.08</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -8552,16 +8572,16 @@
         <v>617</v>
       </c>
       <c r="D233">
-        <v>40.12</v>
+        <v>5.77</v>
       </c>
       <c r="E233" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F233">
-        <v>40.5</v>
+        <v>5.89</v>
       </c>
       <c r="G233">
-        <v>0.95</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -8575,16 +8595,16 @@
         <v>617</v>
       </c>
       <c r="D234">
-        <v>56.01</v>
+        <v>5.4</v>
       </c>
       <c r="E234" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F234">
-        <v>53.66</v>
+        <v>5.42</v>
       </c>
       <c r="G234">
-        <v>-4.2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -8598,16 +8618,16 @@
         <v>617</v>
       </c>
       <c r="D235">
-        <v>35.5</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E235" t="s">
         <v>689</v>
       </c>
       <c r="F235">
-        <v>33.87</v>
+        <v>11.12</v>
       </c>
       <c r="G235">
-        <v>-4.59</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -8621,16 +8641,16 @@
         <v>617</v>
       </c>
       <c r="D236">
-        <v>92</v>
+        <v>35.5</v>
       </c>
       <c r="E236" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F236">
-        <v>85</v>
+        <v>36.11</v>
       </c>
       <c r="G236">
-        <v>-7.61</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -8644,16 +8664,16 @@
         <v>618</v>
       </c>
       <c r="D237">
-        <v>9.84</v>
+        <v>6.12</v>
       </c>
       <c r="E237" t="s">
         <v>690</v>
       </c>
       <c r="F237">
-        <v>9.390000000000001</v>
+        <v>6.48</v>
       </c>
       <c r="G237">
-        <v>-4.57</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -8667,177 +8687,177 @@
         <v>618</v>
       </c>
       <c r="D238">
-        <v>25.95</v>
+        <v>11.31</v>
       </c>
       <c r="E238" t="s">
         <v>691</v>
       </c>
       <c r="F238">
-        <v>27.59</v>
+        <v>9.74</v>
       </c>
       <c r="G238">
-        <v>6.32</v>
+        <v>-13.88</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="B239" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="C239" t="s">
         <v>618</v>
       </c>
       <c r="D239">
-        <v>19.56</v>
+        <v>3.71</v>
       </c>
       <c r="E239" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F239">
-        <v>18.54</v>
+        <v>3.84</v>
       </c>
       <c r="G239">
-        <v>-5.21</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B240" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C240" t="s">
         <v>618</v>
       </c>
       <c r="D240">
-        <v>18.37</v>
+        <v>98.52</v>
       </c>
       <c r="E240" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F240">
-        <v>20.45</v>
+        <v>92.31</v>
       </c>
       <c r="G240">
-        <v>11.32</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B241" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C241" t="s">
         <v>618</v>
       </c>
       <c r="D241">
-        <v>53.58</v>
+        <v>7.95</v>
       </c>
       <c r="E241" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F241">
-        <v>52.65</v>
+        <v>6.13</v>
       </c>
       <c r="G241">
-        <v>-1.74</v>
+        <v>-22.89</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B242" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C242" t="s">
         <v>618</v>
       </c>
       <c r="D242">
-        <v>3.71</v>
+        <v>18.37</v>
       </c>
       <c r="E242" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F242">
-        <v>3.84</v>
+        <v>19.04</v>
       </c>
       <c r="G242">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C243" t="s">
         <v>618</v>
       </c>
       <c r="D243">
-        <v>6.12</v>
+        <v>53.58</v>
       </c>
       <c r="E243" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F243">
-        <v>6.48</v>
+        <v>52.65</v>
       </c>
       <c r="G243">
-        <v>5.88</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B244" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C244" t="s">
         <v>618</v>
       </c>
       <c r="D244">
-        <v>98.52</v>
+        <v>18.37</v>
       </c>
       <c r="E244" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F244">
-        <v>92.31</v>
+        <v>20.45</v>
       </c>
       <c r="G244">
-        <v>-6.3</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="B245" t="s">
-        <v>545</v>
+        <v>473</v>
       </c>
       <c r="C245" t="s">
         <v>618</v>
       </c>
       <c r="D245">
-        <v>7.95</v>
+        <v>19.56</v>
       </c>
       <c r="E245" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="F245">
-        <v>6.13</v>
+        <v>18.54</v>
       </c>
       <c r="G245">
-        <v>-22.89</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -8851,16 +8871,16 @@
         <v>618</v>
       </c>
       <c r="D246">
-        <v>11.31</v>
+        <v>25.95</v>
       </c>
       <c r="E246" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="F246">
-        <v>9.74</v>
+        <v>27.59</v>
       </c>
       <c r="G246">
-        <v>-13.88</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -8874,16 +8894,16 @@
         <v>618</v>
       </c>
       <c r="D247">
-        <v>18.37</v>
+        <v>9.84</v>
       </c>
       <c r="E247" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F247">
-        <v>19.04</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G247">
-        <v>3.65</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -8897,16 +8917,16 @@
         <v>619</v>
       </c>
       <c r="D248">
-        <v>28.95</v>
+        <v>2.53</v>
       </c>
       <c r="E248" t="s">
         <v>695</v>
       </c>
       <c r="F248">
-        <v>31.66</v>
+        <v>2.52</v>
       </c>
       <c r="G248">
-        <v>9.359999999999999</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -8920,16 +8940,16 @@
         <v>619</v>
       </c>
       <c r="D249">
-        <v>28.9</v>
+        <v>5.8</v>
       </c>
       <c r="E249" t="s">
         <v>696</v>
       </c>
       <c r="F249">
-        <v>28</v>
+        <v>5.51</v>
       </c>
       <c r="G249">
-        <v>-3.11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -8943,16 +8963,16 @@
         <v>619</v>
       </c>
       <c r="D250">
-        <v>66.33</v>
+        <v>30.42</v>
       </c>
       <c r="E250" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F250">
-        <v>69</v>
+        <v>31.31</v>
       </c>
       <c r="G250">
-        <v>4.03</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -8966,16 +8986,16 @@
         <v>619</v>
       </c>
       <c r="D251">
-        <v>7.15</v>
+        <v>12.99</v>
       </c>
       <c r="E251" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F251">
-        <v>7.06</v>
+        <v>12.35</v>
       </c>
       <c r="G251">
-        <v>-1.26</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -8989,16 +9009,16 @@
         <v>619</v>
       </c>
       <c r="D252">
-        <v>12.98</v>
+        <v>20.13</v>
       </c>
       <c r="E252" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F252">
-        <v>12.48</v>
+        <v>20.42</v>
       </c>
       <c r="G252">
-        <v>-3.85</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -9012,16 +9032,16 @@
         <v>619</v>
       </c>
       <c r="D253">
-        <v>20.13</v>
+        <v>28.95</v>
       </c>
       <c r="E253" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F253">
-        <v>20.42</v>
+        <v>31.66</v>
       </c>
       <c r="G253">
-        <v>1.44</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -9035,16 +9055,16 @@
         <v>619</v>
       </c>
       <c r="D254">
-        <v>12.99</v>
+        <v>66.33</v>
       </c>
       <c r="E254" t="s">
         <v>695</v>
       </c>
       <c r="F254">
-        <v>12.35</v>
+        <v>69</v>
       </c>
       <c r="G254">
-        <v>-4.93</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -9058,16 +9078,16 @@
         <v>619</v>
       </c>
       <c r="D255">
-        <v>30.42</v>
+        <v>28.9</v>
       </c>
       <c r="E255" t="s">
         <v>697</v>
       </c>
       <c r="F255">
-        <v>31.31</v>
+        <v>28</v>
       </c>
       <c r="G255">
-        <v>2.93</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -9081,16 +9101,16 @@
         <v>619</v>
       </c>
       <c r="D256">
-        <v>5.8</v>
+        <v>12.98</v>
       </c>
       <c r="E256" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F256">
-        <v>5.51</v>
+        <v>12.48</v>
       </c>
       <c r="G256">
-        <v>-5</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -9104,16 +9124,16 @@
         <v>619</v>
       </c>
       <c r="D257">
-        <v>2.53</v>
+        <v>7.15</v>
       </c>
       <c r="E257" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F257">
-        <v>2.52</v>
+        <v>7.06</v>
       </c>
       <c r="G257">
-        <v>-0.4</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -9127,16 +9147,16 @@
         <v>620</v>
       </c>
       <c r="D258">
-        <v>8.83</v>
+        <v>33.6</v>
       </c>
       <c r="E258" t="s">
         <v>699</v>
       </c>
       <c r="F258">
-        <v>8.779999999999999</v>
+        <v>36.82</v>
       </c>
       <c r="G258">
-        <v>-0.57</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -9150,16 +9170,16 @@
         <v>620</v>
       </c>
       <c r="D259">
-        <v>22.54</v>
+        <v>65</v>
       </c>
       <c r="E259" t="s">
         <v>700</v>
       </c>
       <c r="F259">
-        <v>24.82</v>
+        <v>63.89</v>
       </c>
       <c r="G259">
-        <v>10.12</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -9173,85 +9193,85 @@
         <v>620</v>
       </c>
       <c r="D260">
-        <v>53.4</v>
+        <v>19.3</v>
       </c>
       <c r="E260" t="s">
         <v>701</v>
       </c>
       <c r="F260">
-        <v>59.38</v>
+        <v>19.19</v>
       </c>
       <c r="G260">
-        <v>11.2</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="B261" t="s">
-        <v>497</v>
+        <v>561</v>
       </c>
       <c r="C261" t="s">
         <v>620</v>
       </c>
       <c r="D261">
-        <v>23.6</v>
+        <v>22.21</v>
       </c>
       <c r="E261" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F261">
-        <v>23.77</v>
+        <v>22.99</v>
       </c>
       <c r="G261">
-        <v>0.72</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B262" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C262" t="s">
         <v>620</v>
       </c>
       <c r="D262">
-        <v>5.77</v>
+        <v>20.33</v>
       </c>
       <c r="E262" t="s">
         <v>701</v>
       </c>
       <c r="F262">
-        <v>5.88</v>
+        <v>20.96</v>
       </c>
       <c r="G262">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>292</v>
+        <v>233</v>
       </c>
       <c r="B263" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="C263" t="s">
         <v>620</v>
       </c>
       <c r="D263">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="E263" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F263">
-        <v>19.19</v>
+        <v>23.77</v>
       </c>
       <c r="G263">
-        <v>-0.57</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -9265,16 +9285,16 @@
         <v>620</v>
       </c>
       <c r="D264">
-        <v>65</v>
+        <v>8.83</v>
       </c>
       <c r="E264" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F264">
-        <v>63.89</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G264">
-        <v>-1.71</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -9288,16 +9308,16 @@
         <v>620</v>
       </c>
       <c r="D265">
-        <v>33.6</v>
+        <v>5.77</v>
       </c>
       <c r="E265" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F265">
-        <v>36.82</v>
+        <v>5.88</v>
       </c>
       <c r="G265">
-        <v>9.58</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -9311,16 +9331,16 @@
         <v>620</v>
       </c>
       <c r="D266">
-        <v>22.21</v>
+        <v>53.4</v>
       </c>
       <c r="E266" t="s">
         <v>699</v>
       </c>
       <c r="F266">
-        <v>22.99</v>
+        <v>59.38</v>
       </c>
       <c r="G266">
-        <v>3.51</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -9334,16 +9354,16 @@
         <v>620</v>
       </c>
       <c r="D267">
-        <v>20.33</v>
+        <v>22.54</v>
       </c>
       <c r="E267" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F267">
-        <v>20.96</v>
+        <v>24.82</v>
       </c>
       <c r="G267">
-        <v>3.1</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -9357,62 +9377,62 @@
         <v>621</v>
       </c>
       <c r="D268">
-        <v>11.6</v>
+        <v>6.87</v>
       </c>
       <c r="E268" t="s">
         <v>703</v>
       </c>
       <c r="F268">
-        <v>11.89</v>
+        <v>7.1</v>
       </c>
       <c r="G268">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="B269" t="s">
-        <v>515</v>
+        <v>568</v>
       </c>
       <c r="C269" t="s">
         <v>621</v>
       </c>
       <c r="D269">
-        <v>206.01</v>
+        <v>104</v>
       </c>
       <c r="E269" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F269">
-        <v>242.63</v>
+        <v>100.61</v>
       </c>
       <c r="G269">
-        <v>17.78</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="B270" t="s">
-        <v>568</v>
+        <v>511</v>
       </c>
       <c r="C270" t="s">
         <v>621</v>
       </c>
       <c r="D270">
-        <v>20.66</v>
+        <v>36.47</v>
       </c>
       <c r="E270" t="s">
         <v>703</v>
       </c>
       <c r="F270">
-        <v>18.1</v>
+        <v>36.13</v>
       </c>
       <c r="G270">
-        <v>-12.39</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -9426,16 +9446,16 @@
         <v>621</v>
       </c>
       <c r="D271">
-        <v>21.59</v>
+        <v>128.8</v>
       </c>
       <c r="E271" t="s">
         <v>703</v>
       </c>
       <c r="F271">
-        <v>23.13</v>
+        <v>138.99</v>
       </c>
       <c r="G271">
-        <v>7.13</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -9449,16 +9469,16 @@
         <v>621</v>
       </c>
       <c r="D272">
-        <v>28.03</v>
+        <v>21.59</v>
       </c>
       <c r="E272" t="s">
         <v>703</v>
       </c>
       <c r="F272">
-        <v>26.98</v>
+        <v>23.13</v>
       </c>
       <c r="G272">
-        <v>-3.75</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -9472,39 +9492,39 @@
         <v>621</v>
       </c>
       <c r="D273">
-        <v>128.8</v>
+        <v>20.66</v>
       </c>
       <c r="E273" t="s">
         <v>703</v>
       </c>
       <c r="F273">
-        <v>138.99</v>
+        <v>18.1</v>
       </c>
       <c r="G273">
-        <v>7.91</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B274" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="C274" t="s">
         <v>621</v>
       </c>
       <c r="D274">
-        <v>36.47</v>
+        <v>206.01</v>
       </c>
       <c r="E274" t="s">
         <v>703</v>
       </c>
       <c r="F274">
-        <v>36.13</v>
+        <v>242.63</v>
       </c>
       <c r="G274">
-        <v>-0.93</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -9518,62 +9538,62 @@
         <v>621</v>
       </c>
       <c r="D275">
-        <v>104</v>
+        <v>11.6</v>
       </c>
       <c r="E275" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F275">
-        <v>100.61</v>
+        <v>11.89</v>
       </c>
       <c r="G275">
-        <v>-3.26</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>303</v>
+        <v>117</v>
       </c>
       <c r="B276" t="s">
-        <v>573</v>
+        <v>387</v>
       </c>
       <c r="C276" t="s">
         <v>621</v>
       </c>
       <c r="D276">
-        <v>6.87</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E276" t="s">
         <v>703</v>
       </c>
       <c r="F276">
-        <v>7.1</v>
+        <v>86.3</v>
       </c>
       <c r="G276">
-        <v>3.35</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="B277" t="s">
-        <v>393</v>
+        <v>573</v>
       </c>
       <c r="C277" t="s">
         <v>621</v>
       </c>
       <c r="D277">
-        <v>73.98999999999999</v>
+        <v>28.03</v>
       </c>
       <c r="E277" t="s">
         <v>703</v>
       </c>
       <c r="F277">
-        <v>86.3</v>
+        <v>26.98</v>
       </c>
       <c r="G277">
-        <v>16.64</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -9587,16 +9607,16 @@
         <v>622</v>
       </c>
       <c r="D278">
-        <v>233</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="E278" t="s">
         <v>705</v>
       </c>
       <c r="F278">
-        <v>245.3</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="G278">
-        <v>5.28</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -9610,16 +9630,16 @@
         <v>622</v>
       </c>
       <c r="D279">
-        <v>5.55</v>
+        <v>6.39</v>
       </c>
       <c r="E279" t="s">
         <v>705</v>
       </c>
       <c r="F279">
-        <v>5.03</v>
+        <v>5.99</v>
       </c>
       <c r="G279">
-        <v>-9.369999999999999</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -9633,16 +9653,16 @@
         <v>622</v>
       </c>
       <c r="D280">
-        <v>15</v>
+        <v>13.44</v>
       </c>
       <c r="E280" t="s">
         <v>705</v>
       </c>
       <c r="F280">
-        <v>10.69</v>
+        <v>13.27</v>
       </c>
       <c r="G280">
-        <v>-28.73</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -9656,154 +9676,154 @@
         <v>622</v>
       </c>
       <c r="D281">
-        <v>141.34</v>
+        <v>5.12</v>
       </c>
       <c r="E281" t="s">
         <v>705</v>
       </c>
       <c r="F281">
-        <v>133.73</v>
+        <v>4.13</v>
       </c>
       <c r="G281">
-        <v>-5.38</v>
+        <v>-19.34</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>113</v>
+        <v>308</v>
       </c>
       <c r="B282" t="s">
-        <v>383</v>
+        <v>578</v>
       </c>
       <c r="C282" t="s">
         <v>622</v>
       </c>
       <c r="D282">
-        <v>107.92</v>
+        <v>246.4</v>
       </c>
       <c r="E282" t="s">
         <v>705</v>
       </c>
       <c r="F282">
-        <v>107.21</v>
+        <v>259.59</v>
       </c>
       <c r="G282">
-        <v>-0.66</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B283" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C283" t="s">
         <v>622</v>
       </c>
       <c r="D283">
-        <v>88.81999999999999</v>
+        <v>15</v>
       </c>
       <c r="E283" t="s">
         <v>705</v>
       </c>
       <c r="F283">
-        <v>77.26000000000001</v>
+        <v>10.69</v>
       </c>
       <c r="G283">
-        <v>-13.02</v>
+        <v>-28.73</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B284" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C284" t="s">
         <v>622</v>
       </c>
       <c r="D284">
-        <v>6.39</v>
+        <v>5.55</v>
       </c>
       <c r="E284" t="s">
         <v>705</v>
       </c>
       <c r="F284">
-        <v>5.99</v>
+        <v>5.03</v>
       </c>
       <c r="G284">
-        <v>-6.26</v>
+        <v>-9.369999999999999</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B285" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C285" t="s">
         <v>622</v>
       </c>
       <c r="D285">
-        <v>5.12</v>
+        <v>141.34</v>
       </c>
       <c r="E285" t="s">
         <v>705</v>
       </c>
       <c r="F285">
-        <v>4.13</v>
+        <v>133.73</v>
       </c>
       <c r="G285">
-        <v>-19.34</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B286" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C286" t="s">
         <v>622</v>
       </c>
       <c r="D286">
-        <v>13.44</v>
+        <v>233</v>
       </c>
       <c r="E286" t="s">
         <v>705</v>
       </c>
       <c r="F286">
-        <v>13.27</v>
+        <v>245.3</v>
       </c>
       <c r="G286">
-        <v>-1.26</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>312</v>
+        <v>110</v>
       </c>
       <c r="B287" t="s">
-        <v>582</v>
+        <v>380</v>
       </c>
       <c r="C287" t="s">
         <v>622</v>
       </c>
       <c r="D287">
-        <v>246.4</v>
+        <v>107.92</v>
       </c>
       <c r="E287" t="s">
         <v>705</v>
       </c>
       <c r="F287">
-        <v>259.59</v>
+        <v>107.21</v>
       </c>
       <c r="G287">
-        <v>5.35</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -9817,16 +9837,16 @@
         <v>623</v>
       </c>
       <c r="D288">
-        <v>12.35</v>
+        <v>12.4</v>
       </c>
       <c r="E288" t="s">
         <v>706</v>
       </c>
       <c r="F288">
-        <v>12.66</v>
+        <v>11.98</v>
       </c>
       <c r="G288">
-        <v>2.51</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -9840,16 +9860,16 @@
         <v>623</v>
       </c>
       <c r="D289">
-        <v>3.53</v>
+        <v>4.15</v>
       </c>
       <c r="E289" t="s">
         <v>706</v>
       </c>
       <c r="F289">
-        <v>3.42</v>
+        <v>5.67</v>
       </c>
       <c r="G289">
-        <v>-3.12</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -9863,16 +9883,16 @@
         <v>623</v>
       </c>
       <c r="D290">
-        <v>12.4</v>
+        <v>27.84</v>
       </c>
       <c r="E290" t="s">
         <v>706</v>
       </c>
       <c r="F290">
-        <v>11.98</v>
+        <v>27.5</v>
       </c>
       <c r="G290">
-        <v>-3.39</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -9886,107 +9906,291 @@
         <v>623</v>
       </c>
       <c r="D291">
-        <v>64.66</v>
+        <v>12.1</v>
       </c>
       <c r="E291" t="s">
         <v>706</v>
       </c>
       <c r="F291">
-        <v>61.77</v>
+        <v>12.81</v>
       </c>
       <c r="G291">
-        <v>-4.47</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B292" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C292" t="s">
         <v>623</v>
       </c>
       <c r="D292">
-        <v>27.84</v>
+        <v>12.4</v>
       </c>
       <c r="E292" t="s">
         <v>706</v>
       </c>
       <c r="F292">
-        <v>27.5</v>
+        <v>11.98</v>
       </c>
       <c r="G292">
-        <v>-1.22</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B293" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C293" t="s">
         <v>623</v>
       </c>
       <c r="D293">
-        <v>4.15</v>
+        <v>12.35</v>
       </c>
       <c r="E293" t="s">
         <v>706</v>
       </c>
       <c r="F293">
-        <v>5.67</v>
+        <v>12.66</v>
       </c>
       <c r="G293">
-        <v>36.63</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B294" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C294" t="s">
         <v>623</v>
       </c>
       <c r="D294">
-        <v>12.1</v>
+        <v>3.53</v>
       </c>
       <c r="E294" t="s">
         <v>706</v>
       </c>
       <c r="F294">
-        <v>12.81</v>
+        <v>3.42</v>
       </c>
       <c r="G294">
-        <v>5.87</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B295" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C295" t="s">
         <v>623</v>
       </c>
       <c r="D295">
-        <v>4.87</v>
+        <v>3.53</v>
       </c>
       <c r="E295" t="s">
         <v>706</v>
       </c>
       <c r="F295">
+        <v>3.42</v>
+      </c>
+      <c r="G295">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>317</v>
+      </c>
+      <c r="B296" t="s">
+        <v>587</v>
+      </c>
+      <c r="C296" t="s">
+        <v>623</v>
+      </c>
+      <c r="D296">
+        <v>12.35</v>
+      </c>
+      <c r="E296" t="s">
+        <v>706</v>
+      </c>
+      <c r="F296">
+        <v>12.66</v>
+      </c>
+      <c r="G296">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>319</v>
+      </c>
+      <c r="B297" t="s">
+        <v>589</v>
+      </c>
+      <c r="C297" t="s">
+        <v>623</v>
+      </c>
+      <c r="D297">
+        <v>64.66</v>
+      </c>
+      <c r="E297" t="s">
+        <v>706</v>
+      </c>
+      <c r="F297">
+        <v>61.77</v>
+      </c>
+      <c r="G297">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>316</v>
+      </c>
+      <c r="B298" t="s">
+        <v>586</v>
+      </c>
+      <c r="C298" t="s">
+        <v>623</v>
+      </c>
+      <c r="D298">
+        <v>12.1</v>
+      </c>
+      <c r="E298" t="s">
+        <v>706</v>
+      </c>
+      <c r="F298">
+        <v>12.81</v>
+      </c>
+      <c r="G298">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" t="s">
+        <v>314</v>
+      </c>
+      <c r="B299" t="s">
+        <v>584</v>
+      </c>
+      <c r="C299" t="s">
+        <v>623</v>
+      </c>
+      <c r="D299">
+        <v>4.15</v>
+      </c>
+      <c r="E299" t="s">
+        <v>706</v>
+      </c>
+      <c r="F299">
+        <v>5.67</v>
+      </c>
+      <c r="G299">
+        <v>36.63</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>315</v>
+      </c>
+      <c r="B300" t="s">
+        <v>585</v>
+      </c>
+      <c r="C300" t="s">
+        <v>623</v>
+      </c>
+      <c r="D300">
+        <v>27.84</v>
+      </c>
+      <c r="E300" t="s">
+        <v>706</v>
+      </c>
+      <c r="F300">
+        <v>27.5</v>
+      </c>
+      <c r="G300">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" t="s">
+        <v>319</v>
+      </c>
+      <c r="B301" t="s">
+        <v>589</v>
+      </c>
+      <c r="C301" t="s">
+        <v>623</v>
+      </c>
+      <c r="D301">
+        <v>64.66</v>
+      </c>
+      <c r="E301" t="s">
+        <v>706</v>
+      </c>
+      <c r="F301">
+        <v>61.77</v>
+      </c>
+      <c r="G301">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" t="s">
+        <v>320</v>
+      </c>
+      <c r="B302" t="s">
+        <v>590</v>
+      </c>
+      <c r="C302" t="s">
+        <v>623</v>
+      </c>
+      <c r="D302">
+        <v>4.87</v>
+      </c>
+      <c r="E302" t="s">
+        <v>706</v>
+      </c>
+      <c r="F302">
         <v>5.04</v>
       </c>
-      <c r="G295">
+      <c r="G302">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" t="s">
+        <v>320</v>
+      </c>
+      <c r="B303" t="s">
+        <v>590</v>
+      </c>
+      <c r="C303" t="s">
+        <v>623</v>
+      </c>
+      <c r="D303">
+        <v>4.87</v>
+      </c>
+      <c r="E303" t="s">
+        <v>706</v>
+      </c>
+      <c r="F303">
+        <v>5.04</v>
+      </c>
+      <c r="G303">
         <v>3.49</v>
       </c>
     </row>

--- a/backtest/5日周期交易计划_2026_回测结果.xlsx
+++ b/backtest/5日周期交易计划_2026_回测结果.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="707">
   <si>
     <t>指标</t>
   </si>
@@ -195,88 +195,94 @@
     <t>688787</t>
   </si>
   <si>
+    <t>600828</t>
+  </si>
+  <si>
+    <t>688248</t>
+  </si>
+  <si>
+    <t>603966</t>
+  </si>
+  <si>
+    <t>601116</t>
+  </si>
+  <si>
+    <t>002517</t>
+  </si>
+  <si>
     <t>688031</t>
   </si>
   <si>
-    <t>002517</t>
+    <t>600783</t>
   </si>
   <si>
     <t>601339</t>
   </si>
   <si>
-    <t>600783</t>
-  </si>
-  <si>
-    <t>601116</t>
-  </si>
-  <si>
-    <t>603966</t>
-  </si>
-  <si>
-    <t>688248</t>
-  </si>
-  <si>
-    <t>600828</t>
-  </si>
-  <si>
     <t>300986</t>
   </si>
   <si>
+    <t>603949</t>
+  </si>
+  <si>
+    <t>688628</t>
+  </si>
+  <si>
+    <t>600686</t>
+  </si>
+  <si>
+    <t>605080</t>
+  </si>
+  <si>
+    <t>688084</t>
+  </si>
+  <si>
+    <t>605287</t>
+  </si>
+  <si>
+    <t>001360</t>
+  </si>
+  <si>
     <t>603163</t>
   </si>
   <si>
-    <t>001360</t>
-  </si>
-  <si>
-    <t>605287</t>
-  </si>
-  <si>
     <t>300835</t>
   </si>
   <si>
     <t>001337</t>
   </si>
   <si>
-    <t>688628</t>
-  </si>
-  <si>
-    <t>603949</t>
-  </si>
-  <si>
-    <t>605080</t>
-  </si>
-  <si>
-    <t>600686</t>
-  </si>
-  <si>
-    <t>688084</t>
-  </si>
-  <si>
     <t>601615</t>
   </si>
   <si>
+    <t>000968</t>
+  </si>
+  <si>
+    <t>002679</t>
+  </si>
+  <si>
+    <t>688210</t>
+  </si>
+  <si>
+    <t>002658</t>
+  </si>
+  <si>
+    <t>601225</t>
+  </si>
+  <si>
     <t>600926</t>
   </si>
   <si>
+    <t>603311</t>
+  </si>
+  <si>
     <t>002995</t>
   </si>
   <si>
-    <t>601225</t>
-  </si>
-  <si>
-    <t>603311</t>
-  </si>
-  <si>
-    <t>000968</t>
-  </si>
-  <si>
-    <t>688210</t>
-  </si>
-  <si>
-    <t>002679</t>
-  </si>
-  <si>
-    <t>002658</t>
+    <t>000089</t>
+  </si>
+  <si>
+    <t>002457</t>
   </si>
   <si>
     <t>603960</t>
@@ -285,136 +291,148 @@
     <t>600133</t>
   </si>
   <si>
-    <t>000089</t>
-  </si>
-  <si>
-    <t>002457</t>
-  </si>
-  <si>
     <t>601598</t>
   </si>
   <si>
+    <t>601702</t>
+  </si>
+  <si>
+    <t>000599</t>
+  </si>
+  <si>
+    <t>688367</t>
+  </si>
+  <si>
     <t>688070</t>
   </si>
   <si>
     <t>603103</t>
   </si>
   <si>
-    <t>000599</t>
-  </si>
-  <si>
-    <t>688367</t>
-  </si>
-  <si>
-    <t>601702</t>
+    <t>001326</t>
+  </si>
+  <si>
+    <t>603150</t>
+  </si>
+  <si>
+    <t>603626</t>
+  </si>
+  <si>
+    <t>001335</t>
+  </si>
+  <si>
+    <t>688312</t>
   </si>
   <si>
     <t>002441</t>
   </si>
   <si>
+    <t>688025</t>
+  </si>
+  <si>
+    <t>603232</t>
+  </si>
+  <si>
     <t>603301</t>
   </si>
   <si>
-    <t>603232</t>
-  </si>
-  <si>
-    <t>688025</t>
-  </si>
-  <si>
     <t>603334</t>
   </si>
   <si>
-    <t>688312</t>
-  </si>
-  <si>
-    <t>603626</t>
-  </si>
-  <si>
-    <t>603150</t>
-  </si>
-  <si>
-    <t>001326</t>
-  </si>
-  <si>
-    <t>001335</t>
+    <t>601872</t>
+  </si>
+  <si>
+    <t>300831</t>
+  </si>
+  <si>
+    <t>301160</t>
+  </si>
+  <si>
+    <t>001309</t>
+  </si>
+  <si>
+    <t>002380</t>
+  </si>
+  <si>
+    <t>605289</t>
+  </si>
+  <si>
+    <t>603057</t>
+  </si>
+  <si>
+    <t>002028</t>
   </si>
   <si>
     <t>001896</t>
   </si>
   <si>
-    <t>002028</t>
-  </si>
-  <si>
-    <t>603057</t>
-  </si>
-  <si>
-    <t>605289</t>
-  </si>
-  <si>
     <t>002937</t>
   </si>
   <si>
-    <t>601872</t>
-  </si>
-  <si>
-    <t>001309</t>
-  </si>
-  <si>
-    <t>301160</t>
-  </si>
-  <si>
-    <t>300831</t>
-  </si>
-  <si>
-    <t>002380</t>
+    <t>688668</t>
+  </si>
+  <si>
+    <t>002921</t>
+  </si>
+  <si>
+    <t>301087</t>
+  </si>
+  <si>
+    <t>002545</t>
+  </si>
+  <si>
+    <t>003018</t>
+  </si>
+  <si>
+    <t>600715</t>
   </si>
   <si>
     <t>300720</t>
   </si>
   <si>
+    <t>600230</t>
+  </si>
+  <si>
     <t>600649</t>
   </si>
   <si>
-    <t>600230</t>
-  </si>
-  <si>
-    <t>600715</t>
-  </si>
-  <si>
-    <t>688668</t>
-  </si>
-  <si>
-    <t>002921</t>
-  </si>
-  <si>
-    <t>003018</t>
-  </si>
-  <si>
-    <t>002545</t>
-  </si>
-  <si>
-    <t>301087</t>
+    <t>300461</t>
+  </si>
+  <si>
+    <t>301308</t>
+  </si>
+  <si>
+    <t>300257</t>
+  </si>
+  <si>
+    <t>605268</t>
+  </si>
+  <si>
+    <t>601789</t>
+  </si>
+  <si>
+    <t>301032</t>
   </si>
   <si>
     <t>301536</t>
   </si>
   <si>
-    <t>301032</t>
-  </si>
-  <si>
-    <t>601789</t>
-  </si>
-  <si>
-    <t>605268</t>
-  </si>
-  <si>
-    <t>301308</t>
-  </si>
-  <si>
-    <t>300461</t>
-  </si>
-  <si>
-    <t>300257</t>
+    <t>300085</t>
+  </si>
+  <si>
+    <t>301309</t>
+  </si>
+  <si>
+    <t>688612</t>
+  </si>
+  <si>
+    <t>600610</t>
+  </si>
+  <si>
+    <t>600433</t>
+  </si>
+  <si>
+    <t>002285</t>
   </si>
   <si>
     <t>605222</t>
@@ -423,463 +441,460 @@
     <t>688800</t>
   </si>
   <si>
-    <t>002285</t>
-  </si>
-  <si>
-    <t>600433</t>
-  </si>
-  <si>
-    <t>301309</t>
-  </si>
-  <si>
-    <t>688612</t>
-  </si>
-  <si>
-    <t>300085</t>
-  </si>
-  <si>
-    <t>600610</t>
+    <t>001333</t>
   </si>
   <si>
     <t>301093</t>
   </si>
   <si>
+    <t>601128</t>
+  </si>
+  <si>
     <t>603165</t>
   </si>
   <si>
-    <t>001333</t>
+    <t>605077</t>
+  </si>
+  <si>
+    <t>688267</t>
   </si>
   <si>
     <t>603833</t>
   </si>
   <si>
-    <t>601128</t>
-  </si>
-  <si>
-    <t>605077</t>
-  </si>
-  <si>
-    <t>688267</t>
+    <t>002035</t>
+  </si>
+  <si>
+    <t>300834</t>
+  </si>
+  <si>
+    <t>300689</t>
+  </si>
+  <si>
+    <t>002773</t>
+  </si>
+  <si>
+    <t>300440</t>
+  </si>
+  <si>
+    <t>603585</t>
+  </si>
+  <si>
+    <t>301529</t>
+  </si>
+  <si>
+    <t>301015</t>
   </si>
   <si>
     <t>603588</t>
   </si>
   <si>
-    <t>301015</t>
-  </si>
-  <si>
-    <t>300834</t>
-  </si>
-  <si>
-    <t>301529</t>
-  </si>
-  <si>
-    <t>603585</t>
-  </si>
-  <si>
-    <t>300689</t>
-  </si>
-  <si>
-    <t>002035</t>
-  </si>
-  <si>
-    <t>300440</t>
-  </si>
-  <si>
-    <t>002773</t>
+    <t>002008</t>
+  </si>
+  <si>
+    <t>300870</t>
+  </si>
+  <si>
+    <t>600654</t>
+  </si>
+  <si>
+    <t>301326</t>
+  </si>
+  <si>
+    <t>301310</t>
+  </si>
+  <si>
+    <t>603988</t>
   </si>
   <si>
     <t>002386</t>
   </si>
   <si>
+    <t>002624</t>
+  </si>
+  <si>
     <t>300179</t>
   </si>
   <si>
-    <t>002624</t>
-  </si>
-  <si>
-    <t>603988</t>
-  </si>
-  <si>
     <t>600545</t>
   </si>
   <si>
-    <t>301326</t>
-  </si>
-  <si>
-    <t>600654</t>
-  </si>
-  <si>
-    <t>002008</t>
-  </si>
-  <si>
-    <t>300870</t>
-  </si>
-  <si>
-    <t>301310</t>
+    <t>002853</t>
+  </si>
+  <si>
+    <t>603171</t>
+  </si>
+  <si>
+    <t>603698</t>
+  </si>
+  <si>
+    <t>002787</t>
+  </si>
+  <si>
+    <t>600749</t>
+  </si>
+  <si>
+    <t>603682</t>
+  </si>
+  <si>
+    <t>002667</t>
   </si>
   <si>
     <t>600572</t>
   </si>
   <si>
-    <t>002667</t>
-  </si>
-  <si>
-    <t>603682</t>
-  </si>
-  <si>
     <t>300866</t>
   </si>
   <si>
-    <t>600749</t>
-  </si>
-  <si>
-    <t>002853</t>
-  </si>
-  <si>
-    <t>002787</t>
-  </si>
-  <si>
-    <t>603171</t>
-  </si>
-  <si>
-    <t>603698</t>
+    <t>300539</t>
+  </si>
+  <si>
+    <t>300687</t>
+  </si>
+  <si>
+    <t>600736</t>
+  </si>
+  <si>
+    <t>002975</t>
+  </si>
+  <si>
+    <t>002803</t>
+  </si>
+  <si>
+    <t>000811</t>
+  </si>
+  <si>
+    <t>600156</t>
   </si>
   <si>
     <t>301133</t>
   </si>
   <si>
-    <t>600156</t>
-  </si>
-  <si>
     <t>301611</t>
   </si>
   <si>
-    <t>000811</t>
-  </si>
-  <si>
-    <t>002803</t>
-  </si>
-  <si>
-    <t>002975</t>
-  </si>
-  <si>
-    <t>600736</t>
-  </si>
-  <si>
-    <t>300687</t>
-  </si>
-  <si>
-    <t>300539</t>
+    <t>000672</t>
+  </si>
+  <si>
+    <t>603931</t>
+  </si>
+  <si>
+    <t>002484</t>
+  </si>
+  <si>
+    <t>603045</t>
+  </si>
+  <si>
+    <t>002181</t>
+  </si>
+  <si>
+    <t>300842</t>
+  </si>
+  <si>
+    <t>300905</t>
+  </si>
+  <si>
+    <t>002631</t>
   </si>
   <si>
     <t>002831</t>
   </si>
   <si>
-    <t>300905</t>
-  </si>
-  <si>
-    <t>300842</t>
-  </si>
-  <si>
-    <t>002181</t>
-  </si>
-  <si>
-    <t>002631</t>
-  </si>
-  <si>
-    <t>000672</t>
-  </si>
-  <si>
-    <t>603045</t>
-  </si>
-  <si>
-    <t>002484</t>
-  </si>
-  <si>
-    <t>603931</t>
+    <t>002965</t>
   </si>
   <si>
     <t>603052</t>
   </si>
   <si>
-    <t>002965</t>
-  </si>
-  <si>
     <t>688001</t>
   </si>
   <si>
     <t>300749</t>
   </si>
   <si>
+    <t>600381</t>
+  </si>
+  <si>
     <t>002782</t>
   </si>
   <si>
     <t>002303</t>
   </si>
   <si>
-    <t>600381</t>
+    <t>002489</t>
+  </si>
+  <si>
+    <t>600850</t>
+  </si>
+  <si>
+    <t>002226</t>
+  </si>
+  <si>
+    <t>600626</t>
+  </si>
+  <si>
+    <t>603360</t>
+  </si>
+  <si>
+    <t>003001</t>
   </si>
   <si>
     <t>688130</t>
   </si>
   <si>
-    <t>603360</t>
-  </si>
-  <si>
-    <t>003001</t>
-  </si>
-  <si>
-    <t>600626</t>
-  </si>
-  <si>
-    <t>600850</t>
-  </si>
-  <si>
-    <t>002489</t>
-  </si>
-  <si>
-    <t>002226</t>
+    <t>002465</t>
+  </si>
+  <si>
+    <t>002655</t>
+  </si>
+  <si>
+    <t>300868</t>
+  </si>
+  <si>
+    <t>603661</t>
+  </si>
+  <si>
+    <t>301588</t>
+  </si>
+  <si>
+    <t>002072</t>
+  </si>
+  <si>
+    <t>600162</t>
+  </si>
+  <si>
+    <t>000509</t>
   </si>
   <si>
     <t>605066</t>
   </si>
   <si>
-    <t>000509</t>
-  </si>
-  <si>
-    <t>600162</t>
-  </si>
-  <si>
     <t>002993</t>
   </si>
   <si>
-    <t>002072</t>
-  </si>
-  <si>
-    <t>603661</t>
-  </si>
-  <si>
-    <t>301588</t>
-  </si>
-  <si>
-    <t>300868</t>
-  </si>
-  <si>
-    <t>002655</t>
-  </si>
-  <si>
-    <t>002465</t>
+    <t>603330</t>
+  </si>
+  <si>
+    <t>002830</t>
+  </si>
+  <si>
+    <t>002314</t>
+  </si>
+  <si>
+    <t>002096</t>
+  </si>
+  <si>
+    <t>300881</t>
+  </si>
+  <si>
+    <t>002951</t>
+  </si>
+  <si>
+    <t>001226</t>
   </si>
   <si>
     <t>002125</t>
   </si>
   <si>
-    <t>001226</t>
-  </si>
-  <si>
-    <t>002951</t>
-  </si>
-  <si>
     <t>002404</t>
   </si>
   <si>
-    <t>603330</t>
-  </si>
-  <si>
-    <t>002830</t>
-  </si>
-  <si>
-    <t>300881</t>
-  </si>
-  <si>
-    <t>002096</t>
-  </si>
-  <si>
-    <t>002314</t>
+    <t>688056</t>
+  </si>
+  <si>
+    <t>300656</t>
+  </si>
+  <si>
+    <t>002903</t>
   </si>
   <si>
     <t>002982</t>
   </si>
   <si>
+    <t>601588</t>
+  </si>
+  <si>
     <t>603938</t>
   </si>
   <si>
-    <t>601588</t>
-  </si>
-  <si>
     <t>000048</t>
   </si>
   <si>
-    <t>688056</t>
-  </si>
-  <si>
-    <t>002903</t>
-  </si>
-  <si>
-    <t>300656</t>
+    <t>603738</t>
+  </si>
+  <si>
+    <t>002972</t>
+  </si>
+  <si>
+    <t>002913</t>
+  </si>
+  <si>
+    <t>001696</t>
+  </si>
+  <si>
+    <t>300769</t>
+  </si>
+  <si>
+    <t>600026</t>
+  </si>
+  <si>
+    <t>300903</t>
+  </si>
+  <si>
+    <t>600110</t>
   </si>
   <si>
     <t>603618</t>
   </si>
   <si>
-    <t>600110</t>
-  </si>
-  <si>
-    <t>300903</t>
-  </si>
-  <si>
-    <t>600026</t>
-  </si>
-  <si>
-    <t>300769</t>
-  </si>
-  <si>
-    <t>002913</t>
-  </si>
-  <si>
-    <t>002972</t>
-  </si>
-  <si>
-    <t>603738</t>
-  </si>
-  <si>
-    <t>001696</t>
+    <t>002990</t>
+  </si>
+  <si>
+    <t>301248</t>
+  </si>
+  <si>
+    <t>002558</t>
+  </si>
+  <si>
+    <t>002976</t>
+  </si>
+  <si>
+    <t>002440</t>
   </si>
   <si>
     <t>603407</t>
   </si>
   <si>
-    <t>002440</t>
-  </si>
-  <si>
     <t>300489</t>
   </si>
   <si>
-    <t>002976</t>
-  </si>
-  <si>
-    <t>002558</t>
-  </si>
-  <si>
-    <t>301248</t>
-  </si>
-  <si>
-    <t>002990</t>
+    <t>002714</t>
+  </si>
+  <si>
+    <t>301382</t>
+  </si>
+  <si>
+    <t>002779</t>
+  </si>
+  <si>
+    <t>603477</t>
+  </si>
+  <si>
+    <t>600630</t>
+  </si>
+  <si>
+    <t>000810</t>
+  </si>
+  <si>
+    <t>002459</t>
+  </si>
+  <si>
+    <t>002693</t>
+  </si>
+  <si>
+    <t>603956</t>
   </si>
   <si>
     <t>002342</t>
   </si>
   <si>
-    <t>002693</t>
-  </si>
-  <si>
-    <t>002459</t>
-  </si>
-  <si>
-    <t>000810</t>
-  </si>
-  <si>
-    <t>603956</t>
-  </si>
-  <si>
-    <t>603477</t>
-  </si>
-  <si>
-    <t>301382</t>
-  </si>
-  <si>
-    <t>600630</t>
-  </si>
-  <si>
-    <t>002714</t>
-  </si>
-  <si>
-    <t>002779</t>
+    <t>000977</t>
   </si>
   <si>
     <t>605118</t>
   </si>
   <si>
+    <t>603139</t>
+  </si>
+  <si>
     <t>300909</t>
   </si>
   <si>
-    <t>603139</t>
-  </si>
-  <si>
-    <t>000977</t>
-  </si>
-  <si>
     <t>000731</t>
   </si>
   <si>
+    <t>000779</t>
+  </si>
+  <si>
+    <t>688069</t>
+  </si>
+  <si>
     <t>002274</t>
   </si>
   <si>
-    <t>000779</t>
-  </si>
-  <si>
-    <t>688069</t>
+    <t>002128</t>
+  </si>
+  <si>
+    <t>002379</t>
+  </si>
+  <si>
+    <t>688485</t>
   </si>
   <si>
     <t>600746</t>
   </si>
   <si>
+    <t>300227</t>
+  </si>
+  <si>
+    <t>605178</t>
+  </si>
+  <si>
+    <t>002677</t>
+  </si>
+  <si>
+    <t>000959</t>
+  </si>
+  <si>
     <t>002900</t>
   </si>
   <si>
-    <t>000959</t>
-  </si>
-  <si>
-    <t>605178</t>
-  </si>
-  <si>
-    <t>002677</t>
-  </si>
-  <si>
     <t>600602</t>
   </si>
   <si>
-    <t>688485</t>
-  </si>
-  <si>
-    <t>002379</t>
-  </si>
-  <si>
-    <t>002128</t>
-  </si>
-  <si>
-    <t>300227</t>
+    <t>605196</t>
+  </si>
+  <si>
+    <t>605155</t>
+  </si>
+  <si>
+    <t>688618</t>
+  </si>
+  <si>
+    <t>605288</t>
+  </si>
+  <si>
+    <t>002339</t>
+  </si>
+  <si>
+    <t>688078</t>
+  </si>
+  <si>
+    <t>002955</t>
+  </si>
+  <si>
+    <t>000862</t>
   </si>
   <si>
     <t>600322</t>
   </si>
   <si>
-    <t>000862</t>
-  </si>
-  <si>
-    <t>002955</t>
-  </si>
-  <si>
     <t>001258</t>
   </si>
   <si>
-    <t>688078</t>
-  </si>
-  <si>
-    <t>605196</t>
-  </si>
-  <si>
-    <t>605288</t>
-  </si>
-  <si>
-    <t>688618</t>
-  </si>
-  <si>
-    <t>605155</t>
-  </si>
-  <si>
-    <t>002339</t>
+    <t>300469</t>
+  </si>
+  <si>
+    <t>603660</t>
+  </si>
+  <si>
+    <t>605388</t>
+  </si>
+  <si>
+    <t>603221</t>
+  </si>
+  <si>
+    <t>003030</t>
   </si>
   <si>
     <t>301108</t>
@@ -888,27 +903,12 @@
     <t>301228</t>
   </si>
   <si>
+    <t>300998</t>
+  </si>
+  <si>
     <t>000668</t>
   </si>
   <si>
-    <t>300998</t>
-  </si>
-  <si>
-    <t>003030</t>
-  </si>
-  <si>
-    <t>603660</t>
-  </si>
-  <si>
-    <t>605388</t>
-  </si>
-  <si>
-    <t>300469</t>
-  </si>
-  <si>
-    <t>603221</t>
-  </si>
-  <si>
     <t>601700</t>
   </si>
   <si>
@@ -918,6 +918,9 @@
     <t>603124</t>
   </si>
   <si>
+    <t>603657</t>
+  </si>
+  <si>
     <t>001210</t>
   </si>
   <si>
@@ -927,7 +930,16 @@
     <t>002361</t>
   </si>
   <si>
-    <t>603657</t>
+    <t>688052</t>
+  </si>
+  <si>
+    <t>688531</t>
+  </si>
+  <si>
+    <t>603758</t>
+  </si>
+  <si>
+    <t>000410</t>
   </si>
   <si>
     <t>688693</t>
@@ -936,48 +948,36 @@
     <t>002520</t>
   </si>
   <si>
+    <t>000692</t>
+  </si>
+  <si>
     <t>603883</t>
   </si>
   <si>
-    <t>000692</t>
-  </si>
-  <si>
     <t>301626</t>
   </si>
   <si>
-    <t>603758</t>
-  </si>
-  <si>
-    <t>000410</t>
-  </si>
-  <si>
-    <t>688531</t>
-  </si>
-  <si>
-    <t>688052</t>
-  </si>
-  <si>
     <t>002647</t>
   </si>
   <si>
+    <t>605133</t>
+  </si>
+  <si>
     <t>002742</t>
   </si>
   <si>
-    <t>605133</t>
-  </si>
-  <si>
     <t>300845</t>
   </si>
   <si>
+    <t>688611</t>
+  </si>
+  <si>
     <t>603071</t>
   </si>
   <si>
     <t>000523</t>
   </si>
   <si>
-    <t>688611</t>
-  </si>
-  <si>
     <t>002476</t>
   </si>
   <si>
@@ -1005,88 +1005,94 @@
     <t>海天瑞声</t>
   </si>
   <si>
+    <t>茂业商业</t>
+  </si>
+  <si>
+    <t>南网科技</t>
+  </si>
+  <si>
+    <t>法兰泰克</t>
+  </si>
+  <si>
+    <t>三江购物</t>
+  </si>
+  <si>
+    <t>恺英网络</t>
+  </si>
+  <si>
     <t>星环科技-U</t>
   </si>
   <si>
-    <t>恺英网络</t>
+    <t>鲁信创投</t>
   </si>
   <si>
     <t>百隆东方</t>
   </si>
   <si>
-    <t>鲁信创投</t>
-  </si>
-  <si>
-    <t>三江购物</t>
-  </si>
-  <si>
-    <t>法兰泰克</t>
-  </si>
-  <si>
-    <t>南网科技</t>
-  </si>
-  <si>
-    <t>茂业商业</t>
-  </si>
-  <si>
     <t>志特新材</t>
   </si>
   <si>
+    <t>雪龙集团</t>
+  </si>
+  <si>
+    <t>优利德</t>
+  </si>
+  <si>
+    <t>金龙汽车</t>
+  </si>
+  <si>
+    <t>浙江自然</t>
+  </si>
+  <si>
+    <t>晶品特装</t>
+  </si>
+  <si>
+    <t>德才股份</t>
+  </si>
+  <si>
+    <t>南矿集团</t>
+  </si>
+  <si>
     <t>圣晖集成</t>
   </si>
   <si>
-    <t>南矿集团</t>
-  </si>
-  <si>
-    <t>德才股份</t>
-  </si>
-  <si>
     <t>龙磁科技</t>
   </si>
   <si>
     <t>四川黄金</t>
   </si>
   <si>
-    <t>优利德</t>
-  </si>
-  <si>
-    <t>雪龙集团</t>
-  </si>
-  <si>
-    <t>浙江自然</t>
-  </si>
-  <si>
-    <t>金龙汽车</t>
-  </si>
-  <si>
-    <t>晶品特装</t>
-  </si>
-  <si>
     <t>明阳智能</t>
   </si>
   <si>
+    <t>蓝焰控股</t>
+  </si>
+  <si>
+    <t>福建金森</t>
+  </si>
+  <si>
+    <t>统联精密</t>
+  </si>
+  <si>
+    <t>雪迪龙</t>
+  </si>
+  <si>
+    <t>陕西煤业</t>
+  </si>
+  <si>
     <t>杭州银行</t>
   </si>
   <si>
+    <t>金海高科</t>
+  </si>
+  <si>
     <t>天地在线</t>
   </si>
   <si>
-    <t>陕西煤业</t>
-  </si>
-  <si>
-    <t>金海高科</t>
-  </si>
-  <si>
-    <t>蓝焰控股</t>
-  </si>
-  <si>
-    <t>统联精密</t>
-  </si>
-  <si>
-    <t>福建金森</t>
-  </si>
-  <si>
-    <t>雪迪龙</t>
+    <t>深圳机场</t>
+  </si>
+  <si>
+    <t>青龙管业</t>
   </si>
   <si>
     <t>克来机电</t>
@@ -1095,136 +1101,148 @@
     <t>东湖高新</t>
   </si>
   <si>
-    <t>深圳机场</t>
-  </si>
-  <si>
-    <t>青龙管业</t>
-  </si>
-  <si>
     <t>中国外运</t>
   </si>
   <si>
+    <t>华峰铝业</t>
+  </si>
+  <si>
+    <t>青岛双星</t>
+  </si>
+  <si>
+    <t>工大高科</t>
+  </si>
+  <si>
     <t>纵横股份</t>
   </si>
   <si>
     <t>横店影视</t>
   </si>
   <si>
-    <t>青岛双星</t>
-  </si>
-  <si>
-    <t>工大高科</t>
-  </si>
-  <si>
-    <t>华峰铝业</t>
+    <t>联域股份</t>
+  </si>
+  <si>
+    <t>万朗磁塑</t>
+  </si>
+  <si>
+    <t>科森科技</t>
+  </si>
+  <si>
+    <t>信凯科技</t>
+  </si>
+  <si>
+    <t>燕麦科技</t>
   </si>
   <si>
     <t>众业达</t>
   </si>
   <si>
+    <t>杰普特</t>
+  </si>
+  <si>
+    <t>格尔软件</t>
+  </si>
+  <si>
     <t>振德医疗</t>
   </si>
   <si>
-    <t>格尔软件</t>
-  </si>
-  <si>
-    <t>杰普特</t>
-  </si>
-  <si>
     <t>丰倍生物</t>
   </si>
   <si>
-    <t>燕麦科技</t>
-  </si>
-  <si>
-    <t>科森科技</t>
-  </si>
-  <si>
-    <t>万朗磁塑</t>
-  </si>
-  <si>
-    <t>联域股份</t>
-  </si>
-  <si>
-    <t>信凯科技</t>
+    <t>招商轮船</t>
+  </si>
+  <si>
+    <t>派瑞股份</t>
+  </si>
+  <si>
+    <t>翔楼新材</t>
+  </si>
+  <si>
+    <t>德明利</t>
+  </si>
+  <si>
+    <t>科远智慧</t>
+  </si>
+  <si>
+    <t>罗曼股份</t>
+  </si>
+  <si>
+    <t>紫燕食品</t>
+  </si>
+  <si>
+    <t>思源电气</t>
   </si>
   <si>
     <t>豫能控股</t>
   </si>
   <si>
-    <t>思源电气</t>
-  </si>
-  <si>
-    <t>紫燕食品</t>
-  </si>
-  <si>
-    <t>罗曼股份</t>
-  </si>
-  <si>
     <t>兴瑞科技</t>
   </si>
   <si>
-    <t>招商轮船</t>
-  </si>
-  <si>
-    <t>德明利</t>
-  </si>
-  <si>
-    <t>翔楼新材</t>
-  </si>
-  <si>
-    <t>派瑞股份</t>
-  </si>
-  <si>
-    <t>科远智慧</t>
+    <t>鼎通科技</t>
+  </si>
+  <si>
+    <t>联诚精密</t>
+  </si>
+  <si>
+    <t>可孚医疗</t>
+  </si>
+  <si>
+    <t>东方铁塔</t>
+  </si>
+  <si>
+    <t>金富科技</t>
+  </si>
+  <si>
+    <t>文投控股</t>
   </si>
   <si>
     <t>海川智能</t>
   </si>
   <si>
+    <t>沧州大化</t>
+  </si>
+  <si>
     <t>城投控股</t>
   </si>
   <si>
-    <t>沧州大化</t>
-  </si>
-  <si>
-    <t>文投控股</t>
-  </si>
-  <si>
-    <t>鼎通科技</t>
-  </si>
-  <si>
-    <t>联诚精密</t>
-  </si>
-  <si>
-    <t>金富科技</t>
-  </si>
-  <si>
-    <t>东方铁塔</t>
-  </si>
-  <si>
-    <t>可孚医疗</t>
+    <t>田中精机</t>
+  </si>
+  <si>
+    <t>江波龙</t>
+  </si>
+  <si>
+    <t>开山股份</t>
+  </si>
+  <si>
+    <t>王力安防</t>
+  </si>
+  <si>
+    <t>宁波建工</t>
+  </si>
+  <si>
+    <t>新柴股份</t>
   </si>
   <si>
     <t>星宸科技</t>
   </si>
   <si>
-    <t>新柴股份</t>
-  </si>
-  <si>
-    <t>宁波建工</t>
-  </si>
-  <si>
-    <t>王力安防</t>
-  </si>
-  <si>
-    <t>江波龙</t>
-  </si>
-  <si>
-    <t>田中精机</t>
-  </si>
-  <si>
-    <t>开山股份</t>
+    <t>银之杰</t>
+  </si>
+  <si>
+    <t>万得凯</t>
+  </si>
+  <si>
+    <t>威迈斯</t>
+  </si>
+  <si>
+    <t>中毅达</t>
+  </si>
+  <si>
+    <t>冠豪高新</t>
+  </si>
+  <si>
+    <t>世联行</t>
   </si>
   <si>
     <t>起帆电缆</t>
@@ -1233,463 +1251,460 @@
     <t>瑞可达</t>
   </si>
   <si>
-    <t>世联行</t>
-  </si>
-  <si>
-    <t>冠豪高新</t>
-  </si>
-  <si>
-    <t>万得凯</t>
-  </si>
-  <si>
-    <t>威迈斯</t>
-  </si>
-  <si>
-    <t>银之杰</t>
-  </si>
-  <si>
-    <t>中毅达</t>
+    <t>光华股份</t>
   </si>
   <si>
     <t>华兰股份</t>
   </si>
   <si>
+    <t>常熟银行</t>
+  </si>
+  <si>
     <t>荣晟环保</t>
   </si>
   <si>
-    <t>光华股份</t>
+    <t>华康股份</t>
+  </si>
+  <si>
+    <t>中触媒</t>
   </si>
   <si>
     <t>欧派家居</t>
   </si>
   <si>
-    <t>常熟银行</t>
-  </si>
-  <si>
-    <t>华康股份</t>
-  </si>
-  <si>
-    <t>中触媒</t>
+    <t>华帝股份</t>
+  </si>
+  <si>
+    <t>星辉环材</t>
+  </si>
+  <si>
+    <t>澄天伟业</t>
+  </si>
+  <si>
+    <t>康弘药业</t>
+  </si>
+  <si>
+    <t>运达科技</t>
+  </si>
+  <si>
+    <t>苏利股份</t>
+  </si>
+  <si>
+    <t>福赛科技</t>
+  </si>
+  <si>
+    <t>百洋医药</t>
   </si>
   <si>
     <t>高能环境</t>
   </si>
   <si>
-    <t>百洋医药</t>
-  </si>
-  <si>
-    <t>星辉环材</t>
-  </si>
-  <si>
-    <t>福赛科技</t>
-  </si>
-  <si>
-    <t>苏利股份</t>
-  </si>
-  <si>
-    <t>澄天伟业</t>
-  </si>
-  <si>
-    <t>华帝股份</t>
-  </si>
-  <si>
-    <t>运达科技</t>
-  </si>
-  <si>
-    <t>康弘药业</t>
+    <t>大族激光</t>
+  </si>
+  <si>
+    <t>欧陆通</t>
+  </si>
+  <si>
+    <t>中安科</t>
+  </si>
+  <si>
+    <t>捷邦科技</t>
+  </si>
+  <si>
+    <t>鑫宏业</t>
+  </si>
+  <si>
+    <t>中电电机</t>
   </si>
   <si>
     <t>天原股份</t>
   </si>
   <si>
+    <t>完美世界</t>
+  </si>
+  <si>
     <t>四方达</t>
   </si>
   <si>
-    <t>完美世界</t>
-  </si>
-  <si>
-    <t>中电电机</t>
-  </si>
-  <si>
     <t>卓郎智能</t>
   </si>
   <si>
-    <t>捷邦科技</t>
-  </si>
-  <si>
-    <t>中安科</t>
-  </si>
-  <si>
-    <t>大族激光</t>
-  </si>
-  <si>
-    <t>欧陆通</t>
-  </si>
-  <si>
-    <t>鑫宏业</t>
+    <t>皮阿诺</t>
+  </si>
+  <si>
+    <t>税友股份</t>
+  </si>
+  <si>
+    <t>航天工程</t>
+  </si>
+  <si>
+    <t>华源控股</t>
+  </si>
+  <si>
+    <t>西藏旅游</t>
+  </si>
+  <si>
+    <t>锦和商管</t>
+  </si>
+  <si>
+    <t>威领股份</t>
   </si>
   <si>
     <t>康恩贝</t>
   </si>
   <si>
-    <t>威领股份</t>
-  </si>
-  <si>
-    <t>锦和商管</t>
-  </si>
-  <si>
     <t>安克创新</t>
   </si>
   <si>
-    <t>西藏旅游</t>
-  </si>
-  <si>
-    <t>皮阿诺</t>
-  </si>
-  <si>
-    <t>华源控股</t>
-  </si>
-  <si>
-    <t>税友股份</t>
-  </si>
-  <si>
-    <t>航天工程</t>
+    <t>横河精密</t>
+  </si>
+  <si>
+    <t>赛意信息</t>
+  </si>
+  <si>
+    <t>苏州高新</t>
+  </si>
+  <si>
+    <t>博杰股份</t>
+  </si>
+  <si>
+    <t>吉宏股份</t>
+  </si>
+  <si>
+    <t>冰轮环境</t>
+  </si>
+  <si>
+    <t>华升股份</t>
   </si>
   <si>
     <t>金钟股份</t>
   </si>
   <si>
-    <t>华升股份</t>
-  </si>
-  <si>
     <t>珂玛科技</t>
   </si>
   <si>
-    <t>冰轮环境</t>
-  </si>
-  <si>
-    <t>吉宏股份</t>
-  </si>
-  <si>
-    <t>博杰股份</t>
-  </si>
-  <si>
-    <t>苏州高新</t>
-  </si>
-  <si>
-    <t>赛意信息</t>
-  </si>
-  <si>
-    <t>横河精密</t>
+    <t>上峰材料</t>
+  </si>
+  <si>
+    <t>格林达</t>
+  </si>
+  <si>
+    <t>江海股份</t>
+  </si>
+  <si>
+    <t>福达合金</t>
+  </si>
+  <si>
+    <t>粤传媒</t>
+  </si>
+  <si>
+    <t>帝科股份</t>
+  </si>
+  <si>
+    <t>宝丽迪</t>
+  </si>
+  <si>
+    <t>德尔未来</t>
   </si>
   <si>
     <t>裕同科技</t>
   </si>
   <si>
-    <t>宝丽迪</t>
-  </si>
-  <si>
-    <t>帝科股份</t>
-  </si>
-  <si>
-    <t>粤传媒</t>
-  </si>
-  <si>
-    <t>德尔未来</t>
-  </si>
-  <si>
-    <t>上峰材料</t>
-  </si>
-  <si>
-    <t>福达合金</t>
-  </si>
-  <si>
-    <t>江海股份</t>
-  </si>
-  <si>
-    <t>格林达</t>
+    <t>祥鑫科技</t>
   </si>
   <si>
     <t>可川科技</t>
   </si>
   <si>
-    <t>祥鑫科技</t>
-  </si>
-  <si>
     <t>华兴源创</t>
   </si>
   <si>
     <t>顶固集创</t>
   </si>
   <si>
+    <t>*ST春天</t>
+  </si>
+  <si>
     <t>可立克</t>
   </si>
   <si>
     <t>美盈森</t>
   </si>
   <si>
-    <t>*ST春天</t>
+    <t>浙江永强</t>
+  </si>
+  <si>
+    <t>电科数字</t>
+  </si>
+  <si>
+    <t>江南化工</t>
+  </si>
+  <si>
+    <t>申达股份</t>
+  </si>
+  <si>
+    <t>百傲化学</t>
+  </si>
+  <si>
+    <t>中岩大地</t>
   </si>
   <si>
     <t>晶华微</t>
   </si>
   <si>
-    <t>百傲化学</t>
-  </si>
-  <si>
-    <t>中岩大地</t>
-  </si>
-  <si>
-    <t>申达股份</t>
-  </si>
-  <si>
-    <t>电科数字</t>
-  </si>
-  <si>
-    <t>浙江永强</t>
-  </si>
-  <si>
-    <t>江南化工</t>
+    <t>海格通信</t>
+  </si>
+  <si>
+    <t>共达电声</t>
+  </si>
+  <si>
+    <t>杰美特</t>
+  </si>
+  <si>
+    <t>恒林股份</t>
+  </si>
+  <si>
+    <t>美新科技</t>
+  </si>
+  <si>
+    <t>凯瑞德</t>
+  </si>
+  <si>
+    <t>香江控股</t>
+  </si>
+  <si>
+    <t>华塑控股</t>
   </si>
   <si>
     <t>天正电气</t>
   </si>
   <si>
-    <t>华塑控股</t>
-  </si>
-  <si>
-    <t>香江控股</t>
-  </si>
-  <si>
     <t>奥海科技</t>
   </si>
   <si>
-    <t>凯瑞德</t>
-  </si>
-  <si>
-    <t>恒林股份</t>
-  </si>
-  <si>
-    <t>美新科技</t>
-  </si>
-  <si>
-    <t>杰美特</t>
-  </si>
-  <si>
-    <t>共达电声</t>
-  </si>
-  <si>
-    <t>海格通信</t>
+    <t>天洋新材</t>
+  </si>
+  <si>
+    <t>名雕股份</t>
+  </si>
+  <si>
+    <t>南山控股</t>
+  </si>
+  <si>
+    <t>易普力</t>
+  </si>
+  <si>
+    <t>盛德鑫泰</t>
+  </si>
+  <si>
+    <t>金时科技</t>
+  </si>
+  <si>
+    <t>拓山重工</t>
   </si>
   <si>
     <t>湘潭电化</t>
   </si>
   <si>
-    <t>拓山重工</t>
-  </si>
-  <si>
-    <t>金时科技</t>
-  </si>
-  <si>
     <t>嘉欣丝绸</t>
   </si>
   <si>
-    <t>天洋新材</t>
-  </si>
-  <si>
-    <t>名雕股份</t>
-  </si>
-  <si>
-    <t>盛德鑫泰</t>
-  </si>
-  <si>
-    <t>易普力</t>
-  </si>
-  <si>
-    <t>南山控股</t>
+    <t>莱伯泰科</t>
+  </si>
+  <si>
+    <t>民德电子</t>
+  </si>
+  <si>
+    <t>宇环数控</t>
   </si>
   <si>
     <t>湘佳股份</t>
   </si>
   <si>
+    <t>北辰实业</t>
+  </si>
+  <si>
     <t>三孚股份</t>
   </si>
   <si>
-    <t>北辰实业</t>
-  </si>
-  <si>
     <t>京基智农</t>
   </si>
   <si>
-    <t>莱伯泰科</t>
-  </si>
-  <si>
-    <t>宇环数控</t>
-  </si>
-  <si>
-    <t>民德电子</t>
+    <t>泰晶科技</t>
+  </si>
+  <si>
+    <t>科安达</t>
+  </si>
+  <si>
+    <t>奥士康</t>
+  </si>
+  <si>
+    <t>宗申动力</t>
+  </si>
+  <si>
+    <t>德方纳米</t>
+  </si>
+  <si>
+    <t>中远海能</t>
+  </si>
+  <si>
+    <t>科翔股份</t>
+  </si>
+  <si>
+    <t>诺德股份</t>
   </si>
   <si>
     <t>杭电股份</t>
   </si>
   <si>
-    <t>诺德股份</t>
-  </si>
-  <si>
-    <t>科翔股份</t>
-  </si>
-  <si>
-    <t>中远海能</t>
-  </si>
-  <si>
-    <t>德方纳米</t>
-  </si>
-  <si>
-    <t>奥士康</t>
-  </si>
-  <si>
-    <t>科安达</t>
-  </si>
-  <si>
-    <t>泰晶科技</t>
-  </si>
-  <si>
-    <t>宗申动力</t>
+    <t>盛视科技</t>
+  </si>
+  <si>
+    <t>杰创智能</t>
+  </si>
+  <si>
+    <t>巨人网络</t>
+  </si>
+  <si>
+    <t>瑞玛精密</t>
+  </si>
+  <si>
+    <t>闰土股份</t>
   </si>
   <si>
     <t>长裕集团</t>
   </si>
   <si>
-    <t>闰土股份</t>
-  </si>
-  <si>
     <t>光智科技</t>
   </si>
   <si>
-    <t>瑞玛精密</t>
-  </si>
-  <si>
-    <t>巨人网络</t>
-  </si>
-  <si>
-    <t>杰创智能</t>
-  </si>
-  <si>
-    <t>盛视科技</t>
+    <t>牧原股份</t>
+  </si>
+  <si>
+    <t>蜂助手</t>
+  </si>
+  <si>
+    <t>中坚科技</t>
+  </si>
+  <si>
+    <t>巨星农牧</t>
+  </si>
+  <si>
+    <t>龙头股份</t>
+  </si>
+  <si>
+    <t>创维数字</t>
+  </si>
+  <si>
+    <t>晶澳科技</t>
+  </si>
+  <si>
+    <t>双成药业</t>
+  </si>
+  <si>
+    <t>威派格</t>
   </si>
   <si>
     <t>巨力索具</t>
   </si>
   <si>
-    <t>双成药业</t>
-  </si>
-  <si>
-    <t>晶澳科技</t>
-  </si>
-  <si>
-    <t>创维数字</t>
-  </si>
-  <si>
-    <t>威派格</t>
-  </si>
-  <si>
-    <t>巨星农牧</t>
-  </si>
-  <si>
-    <t>蜂助手</t>
-  </si>
-  <si>
-    <t>龙头股份</t>
-  </si>
-  <si>
-    <t>牧原股份</t>
-  </si>
-  <si>
-    <t>中坚科技</t>
+    <t>浪潮信息</t>
   </si>
   <si>
     <t>力鼎光电</t>
   </si>
   <si>
+    <t>康惠股份</t>
+  </si>
+  <si>
     <t>汇创达</t>
   </si>
   <si>
-    <t>康惠股份</t>
-  </si>
-  <si>
-    <t>浪潮信息</t>
-  </si>
-  <si>
     <t>四川美丰</t>
   </si>
   <si>
+    <t>甘咨询</t>
+  </si>
+  <si>
+    <t>德林海</t>
+  </si>
+  <si>
     <t>华昌化工</t>
   </si>
   <si>
-    <t>甘咨询</t>
-  </si>
-  <si>
-    <t>德林海</t>
+    <t>电投能源</t>
+  </si>
+  <si>
+    <t>宏桥控股</t>
+  </si>
+  <si>
+    <t>九州一轨</t>
   </si>
   <si>
     <t>江苏索普</t>
   </si>
   <si>
+    <t>光韵达</t>
+  </si>
+  <si>
+    <t>时空科技</t>
+  </si>
+  <si>
+    <t>浙江美大</t>
+  </si>
+  <si>
+    <t>首钢股份</t>
+  </si>
+  <si>
     <t>哈三联</t>
   </si>
   <si>
-    <t>首钢股份</t>
-  </si>
-  <si>
-    <t>时空科技</t>
-  </si>
-  <si>
-    <t>浙江美大</t>
-  </si>
-  <si>
     <t>云赛智联</t>
   </si>
   <si>
-    <t>九州一轨</t>
-  </si>
-  <si>
-    <t>宏桥控股</t>
-  </si>
-  <si>
-    <t>电投能源</t>
-  </si>
-  <si>
-    <t>光韵达</t>
+    <t>华通线缆</t>
+  </si>
+  <si>
+    <t>西大门</t>
+  </si>
+  <si>
+    <t>三旺通信</t>
+  </si>
+  <si>
+    <t>凯迪股份</t>
+  </si>
+  <si>
+    <t>积成电子</t>
+  </si>
+  <si>
+    <t>龙软科技</t>
+  </si>
+  <si>
+    <t>鸿合科技</t>
+  </si>
+  <si>
+    <t>银星能源</t>
   </si>
   <si>
     <t>津投城开</t>
   </si>
   <si>
-    <t>银星能源</t>
-  </si>
-  <si>
-    <t>鸿合科技</t>
-  </si>
-  <si>
     <t>立新能源</t>
   </si>
   <si>
-    <t>龙软科技</t>
-  </si>
-  <si>
-    <t>华通线缆</t>
-  </si>
-  <si>
-    <t>凯迪股份</t>
-  </si>
-  <si>
-    <t>三旺通信</t>
-  </si>
-  <si>
-    <t>西大门</t>
-  </si>
-  <si>
-    <t>积成电子</t>
+    <t>信息发展</t>
+  </si>
+  <si>
+    <t>苏州科达</t>
+  </si>
+  <si>
+    <t>均瑶健康</t>
+  </si>
+  <si>
+    <t>爱丽家居</t>
+  </si>
+  <si>
+    <t>祖名股份</t>
   </si>
   <si>
     <t>洁雅股份</t>
@@ -1698,27 +1713,12 @@
     <t>实朴检测</t>
   </si>
   <si>
+    <t>宁波方正</t>
+  </si>
+  <si>
     <t>荣丰控股</t>
   </si>
   <si>
-    <t>宁波方正</t>
-  </si>
-  <si>
-    <t>祖名股份</t>
-  </si>
-  <si>
-    <t>苏州科达</t>
-  </si>
-  <si>
-    <t>均瑶健康</t>
-  </si>
-  <si>
-    <t>信息发展</t>
-  </si>
-  <si>
-    <t>爱丽家居</t>
-  </si>
-  <si>
     <t>风范股份</t>
   </si>
   <si>
@@ -1728,6 +1728,9 @@
     <t>江南新材</t>
   </si>
   <si>
+    <t>春光科技</t>
+  </si>
+  <si>
     <t>金房能源</t>
   </si>
   <si>
@@ -1737,7 +1740,16 @@
     <t>神剑股份</t>
   </si>
   <si>
-    <t>春光科技</t>
+    <t>纳芯微</t>
+  </si>
+  <si>
+    <t>日联科技</t>
+  </si>
+  <si>
+    <t>秦安股份</t>
+  </si>
+  <si>
+    <t>沈阳机床</t>
   </si>
   <si>
     <t>锴威特</t>
@@ -1746,48 +1758,36 @@
     <t>日发精机</t>
   </si>
   <si>
+    <t>惠天热电</t>
+  </si>
+  <si>
     <t>老百姓</t>
   </si>
   <si>
-    <t>惠天热电</t>
-  </si>
-  <si>
     <t>苏州天脉</t>
   </si>
   <si>
-    <t>秦安股份</t>
-  </si>
-  <si>
-    <t>沈阳机床</t>
-  </si>
-  <si>
-    <t>日联科技</t>
-  </si>
-  <si>
-    <t>纳芯微</t>
-  </si>
-  <si>
     <t>仁东控股</t>
   </si>
   <si>
+    <t>嵘泰股份</t>
+  </si>
+  <si>
     <t>冀衡医药</t>
   </si>
   <si>
-    <t>嵘泰股份</t>
-  </si>
-  <si>
     <t>捷安高科</t>
   </si>
   <si>
+    <t>杭州柯林</t>
+  </si>
+  <si>
     <t>物产环能</t>
   </si>
   <si>
     <t>红棉股份</t>
   </si>
   <si>
-    <t>杭州柯林</t>
-  </si>
-  <si>
     <t>新叶股份</t>
   </si>
   <si>
@@ -1923,55 +1923,58 @@
     <t>2026-02-24 15:00:00</t>
   </si>
   <si>
+    <t>2026-02-11 09:35:00</t>
+  </si>
+  <si>
     <t>2026-02-24 09:40:00</t>
   </si>
   <si>
-    <t>2026-02-11 09:35:00</t>
-  </si>
-  <si>
     <t>2026-03-03 15:00:00</t>
   </si>
   <si>
     <t>2026-02-25 09:40:00</t>
   </si>
   <si>
+    <t>2026-03-04 09:40:00</t>
+  </si>
+  <si>
     <t>2026-03-10 15:00:00</t>
   </si>
   <si>
-    <t>2026-03-04 09:40:00</t>
-  </si>
-  <si>
     <t>2026-03-10 09:40:00</t>
   </si>
   <si>
+    <t>2026-03-16 10:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 10:45:00</t>
+  </si>
+  <si>
     <t>2026-03-13 09:45:00</t>
   </si>
   <si>
-    <t>2026-03-17 10:45:00</t>
-  </si>
-  <si>
-    <t>2026-03-17 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-16 10:30:00</t>
+    <t>2026-03-24 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-04-08 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-18 10:30:00</t>
+  </si>
+  <si>
+    <t>2026-03-18 09:40:00</t>
+  </si>
+  <si>
+    <t>2026-03-20 09:55:00</t>
   </si>
   <si>
     <t>2026-03-19 10:15:00</t>
   </si>
   <si>
-    <t>2026-03-18 09:40:00</t>
-  </si>
-  <si>
-    <t>2026-03-24 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-20 09:55:00</t>
-  </si>
-  <si>
-    <t>2026-04-08 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-18 10:30:00</t>
+    <t>2026-03-25 09:40:00</t>
   </si>
   <si>
     <t>2026-03-31 14:55:00</t>
@@ -1980,18 +1983,15 @@
     <t>2026-03-31 15:00:00</t>
   </si>
   <si>
-    <t>2026-03-25 09:40:00</t>
-  </si>
-  <si>
     <t>2026-04-01 09:40:00</t>
   </si>
   <si>
+    <t>2026-04-07 14:35:00</t>
+  </si>
+  <si>
     <t>2026-04-02 14:00:00</t>
   </si>
   <si>
-    <t>2026-04-07 14:35:00</t>
-  </si>
-  <si>
     <t>2026-04-15 15:00:00</t>
   </si>
   <si>
@@ -2001,12 +2001,12 @@
     <t>2026-04-22 15:00:00</t>
   </si>
   <si>
+    <t>2026-04-28 13:40:00</t>
+  </si>
+  <si>
     <t>2026-04-29 15:00:00</t>
   </si>
   <si>
-    <t>2026-04-28 13:40:00</t>
-  </si>
-  <si>
     <t>2026-05-13 15:00:00</t>
   </si>
   <si>
@@ -2025,106 +2025,106 @@
     <t>2026-06-04 09:40:00</t>
   </si>
   <si>
+    <t>2026-06-10 09:45:00</t>
+  </si>
+  <si>
+    <t>2026-06-09 09:35:00</t>
+  </si>
+  <si>
     <t>2026-06-10 09:35:00</t>
   </si>
   <si>
-    <t>2026-06-09 09:35:00</t>
-  </si>
-  <si>
-    <t>2026-06-10 09:45:00</t>
+    <t>2026-06-17 15:00:00</t>
   </si>
   <si>
     <t>2026-06-11 09:40:00</t>
   </si>
   <si>
-    <t>2026-06-17 15:00:00</t>
-  </si>
-  <si>
     <t>2026-06-25 15:00:00</t>
   </si>
   <si>
+    <t>2026-06-18 11:30:00</t>
+  </si>
+  <si>
     <t>2026-06-18 10:35:00</t>
   </si>
   <si>
-    <t>2026-06-18 11:30:00</t>
-  </si>
-  <si>
     <t>2026-07-02 15:00:00</t>
   </si>
   <si>
+    <t>2026-06-29 10:15:00</t>
+  </si>
+  <si>
     <t>2026-06-26 09:40:00</t>
   </si>
   <si>
-    <t>2026-06-29 10:15:00</t>
+    <t>2026-07-09 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-07-08 09:35:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 09:35:00</t>
+  </si>
+  <si>
+    <t>2026-07-08 10:40:00</t>
+  </si>
+  <si>
+    <t>2026-07-03 10:25:00</t>
   </si>
   <si>
     <t>2026-07-06 13:05:00</t>
   </si>
   <si>
-    <t>2026-07-09 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-03 10:25:00</t>
-  </si>
-  <si>
-    <t>2026-07-08 10:40:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 09:35:00</t>
-  </si>
-  <si>
-    <t>2026-07-08 09:35:00</t>
+    <t>2026-07-16 15:00:00</t>
   </si>
   <si>
     <t>2026-07-10 10:15:00</t>
   </si>
   <si>
+    <t>2026-07-10 09:40:00</t>
+  </si>
+  <si>
     <t>2026-07-13 09:50:00</t>
   </si>
   <si>
-    <t>2026-07-10 09:40:00</t>
-  </si>
-  <si>
-    <t>2026-07-16 15:00:00</t>
-  </si>
-  <si>
     <t>2026-07-23 15:00:00</t>
   </si>
   <si>
+    <t>2026-07-17 09:40:00</t>
+  </si>
+  <si>
+    <t>2026-07-17 09:50:00</t>
+  </si>
+  <si>
+    <t>2026-07-22 10:45:00</t>
+  </si>
+  <si>
     <t>2026-07-21 09:55:00</t>
   </si>
   <si>
-    <t>2026-07-17 09:50:00</t>
-  </si>
-  <si>
-    <t>2026-07-22 10:45:00</t>
-  </si>
-  <si>
-    <t>2026-07-17 09:40:00</t>
+    <t>2026-07-30 15:00:00</t>
+  </si>
+  <si>
+    <t>2026-07-24 10:30:00</t>
+  </si>
+  <si>
+    <t>2026-07-24 11:00:00</t>
   </si>
   <si>
     <t>2026-07-24 09:40:00</t>
   </si>
   <si>
-    <t>2026-07-30 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-24 11:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-24 10:30:00</t>
-  </si>
-  <si>
     <t>2026-08-06 15:00:00</t>
   </si>
   <si>
+    <t>2026-07-31 09:40:00</t>
+  </si>
+  <si>
+    <t>2026-08-07 15:00:00</t>
+  </si>
+  <si>
     <t>2026-08-03 09:55:00</t>
-  </si>
-  <si>
-    <t>2026-07-31 09:40:00</t>
-  </si>
-  <si>
-    <t>2026-08-07 15:00:00</t>
   </si>
   <si>
     <t>2026-08-13 15:00:00</t>
@@ -2510,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>42.51</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2518,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>74.70999999999999</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2534,7 +2534,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2542,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>59.38</v>
+        <v>60.61</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3213,6 +3213,26 @@
       </c>
       <c r="F33">
         <v>1.4251</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
+        <v>0.84</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>4.537500000000001</v>
+      </c>
+      <c r="E34">
+        <v>3.8115</v>
+      </c>
+      <c r="F34">
+        <v>1.4795</v>
       </c>
     </row>
   </sheetData>
@@ -3222,7 +3242,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G311"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3443,16 +3463,16 @@
         <v>592</v>
       </c>
       <c r="D10">
-        <v>192</v>
+        <v>8.16</v>
       </c>
       <c r="E10" t="s">
         <v>625</v>
       </c>
       <c r="F10">
-        <v>189.7</v>
+        <v>6.92</v>
       </c>
       <c r="G10">
-        <v>-1.2</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3466,16 +3486,16 @@
         <v>592</v>
       </c>
       <c r="D11">
-        <v>26.55</v>
+        <v>55.02</v>
       </c>
       <c r="E11" t="s">
         <v>625</v>
       </c>
       <c r="F11">
-        <v>26.34</v>
+        <v>59.22</v>
       </c>
       <c r="G11">
-        <v>-0.79</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3489,16 +3509,16 @@
         <v>592</v>
       </c>
       <c r="D12">
-        <v>6.21</v>
+        <v>13.58</v>
       </c>
       <c r="E12" t="s">
         <v>625</v>
       </c>
       <c r="F12">
-        <v>6.17</v>
+        <v>14.2</v>
       </c>
       <c r="G12">
-        <v>-0.64</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3512,16 +3532,16 @@
         <v>592</v>
       </c>
       <c r="D13">
-        <v>38</v>
+        <v>18.18</v>
       </c>
       <c r="E13" t="s">
         <v>625</v>
       </c>
       <c r="F13">
-        <v>26.01</v>
+        <v>17.6</v>
       </c>
       <c r="G13">
-        <v>-31.55</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3535,16 +3555,16 @@
         <v>592</v>
       </c>
       <c r="D14">
-        <v>18.18</v>
+        <v>26.55</v>
       </c>
       <c r="E14" t="s">
         <v>625</v>
       </c>
       <c r="F14">
-        <v>17.6</v>
+        <v>26.34</v>
       </c>
       <c r="G14">
-        <v>-3.19</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3558,16 +3578,16 @@
         <v>592</v>
       </c>
       <c r="D15">
-        <v>13.58</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
         <v>625</v>
       </c>
       <c r="F15">
-        <v>14.2</v>
+        <v>189.7</v>
       </c>
       <c r="G15">
-        <v>4.57</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3581,16 +3601,16 @@
         <v>592</v>
       </c>
       <c r="D16">
-        <v>55.02</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
         <v>625</v>
       </c>
       <c r="F16">
-        <v>59.22</v>
+        <v>26.01</v>
       </c>
       <c r="G16">
-        <v>7.63</v>
+        <v>-31.55</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3604,16 +3624,16 @@
         <v>592</v>
       </c>
       <c r="D17">
-        <v>8.16</v>
+        <v>6.21</v>
       </c>
       <c r="E17" t="s">
         <v>625</v>
       </c>
       <c r="F17">
-        <v>6.92</v>
+        <v>6.17</v>
       </c>
       <c r="G17">
-        <v>-15.2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3650,16 +3670,16 @@
         <v>594</v>
       </c>
       <c r="D19">
-        <v>88</v>
+        <v>21.5</v>
       </c>
       <c r="E19" t="s">
         <v>627</v>
       </c>
       <c r="F19">
-        <v>92.34999999999999</v>
+        <v>22.64</v>
       </c>
       <c r="G19">
-        <v>4.94</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3673,16 +3693,16 @@
         <v>594</v>
       </c>
       <c r="D20">
-        <v>24.77</v>
+        <v>37.5</v>
       </c>
       <c r="E20" t="s">
         <v>627</v>
       </c>
       <c r="F20">
-        <v>28.9</v>
+        <v>38.82</v>
       </c>
       <c r="G20">
-        <v>16.67</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3696,16 +3716,16 @@
         <v>594</v>
       </c>
       <c r="D21">
-        <v>39.57</v>
+        <v>19.5</v>
       </c>
       <c r="E21" t="s">
         <v>627</v>
       </c>
       <c r="F21">
-        <v>46.79</v>
+        <v>19.06</v>
       </c>
       <c r="G21">
-        <v>18.25</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3719,16 +3739,16 @@
         <v>594</v>
       </c>
       <c r="D22">
-        <v>76.18000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="E22" t="s">
         <v>627</v>
       </c>
       <c r="F22">
-        <v>70.87</v>
+        <v>24.91</v>
       </c>
       <c r="G22">
-        <v>-6.97</v>
+        <v>-8.08</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3742,16 +3762,16 @@
         <v>594</v>
       </c>
       <c r="D23">
-        <v>39</v>
+        <v>103.82</v>
       </c>
       <c r="E23" t="s">
         <v>627</v>
       </c>
       <c r="F23">
-        <v>55.25</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="G23">
-        <v>41.67</v>
+        <v>-10.28</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3765,16 +3785,16 @@
         <v>594</v>
       </c>
       <c r="D24">
-        <v>37.5</v>
+        <v>39.57</v>
       </c>
       <c r="E24" t="s">
         <v>627</v>
       </c>
       <c r="F24">
-        <v>38.82</v>
+        <v>46.79</v>
       </c>
       <c r="G24">
-        <v>3.52</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3788,16 +3808,16 @@
         <v>594</v>
       </c>
       <c r="D25">
-        <v>21.5</v>
+        <v>24.77</v>
       </c>
       <c r="E25" t="s">
         <v>627</v>
       </c>
       <c r="F25">
-        <v>22.64</v>
+        <v>28.9</v>
       </c>
       <c r="G25">
-        <v>5.3</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3811,16 +3831,16 @@
         <v>594</v>
       </c>
       <c r="D26">
-        <v>27.1</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
         <v>627</v>
       </c>
       <c r="F26">
-        <v>24.91</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="G26">
-        <v>-8.08</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3834,16 +3854,16 @@
         <v>594</v>
       </c>
       <c r="D27">
-        <v>19.5</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="E27" t="s">
         <v>627</v>
       </c>
       <c r="F27">
-        <v>19.06</v>
+        <v>70.87</v>
       </c>
       <c r="G27">
-        <v>-2.26</v>
+        <v>-6.97</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3857,16 +3877,16 @@
         <v>594</v>
       </c>
       <c r="D28">
-        <v>103.82</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s">
         <v>627</v>
       </c>
       <c r="F28">
-        <v>93.15000000000001</v>
+        <v>55.25</v>
       </c>
       <c r="G28">
-        <v>-10.28</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3903,16 +3923,16 @@
         <v>596</v>
       </c>
       <c r="D30">
-        <v>15.58</v>
+        <v>8.08</v>
       </c>
       <c r="E30" t="s">
         <v>629</v>
       </c>
       <c r="F30">
-        <v>15.92</v>
+        <v>7.78</v>
       </c>
       <c r="G30">
-        <v>2.18</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3926,16 +3946,16 @@
         <v>596</v>
       </c>
       <c r="D31">
-        <v>25</v>
+        <v>12.06</v>
       </c>
       <c r="E31" t="s">
         <v>629</v>
       </c>
       <c r="F31">
-        <v>35.15</v>
+        <v>11.26</v>
       </c>
       <c r="G31">
-        <v>40.6</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3949,16 +3969,16 @@
         <v>596</v>
       </c>
       <c r="D32">
-        <v>21.8</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
         <v>629</v>
       </c>
       <c r="F32">
-        <v>20.93</v>
+        <v>54.08</v>
       </c>
       <c r="G32">
-        <v>-3.99</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3972,16 +3992,16 @@
         <v>596</v>
       </c>
       <c r="D33">
-        <v>15.85</v>
+        <v>10.41</v>
       </c>
       <c r="E33" t="s">
         <v>629</v>
       </c>
       <c r="F33">
-        <v>16.03</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G33">
-        <v>1.14</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3995,16 +4015,16 @@
         <v>596</v>
       </c>
       <c r="D34">
-        <v>8.08</v>
+        <v>21.8</v>
       </c>
       <c r="E34" t="s">
         <v>629</v>
       </c>
       <c r="F34">
-        <v>7.78</v>
+        <v>20.93</v>
       </c>
       <c r="G34">
-        <v>-3.71</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -4018,16 +4038,16 @@
         <v>596</v>
       </c>
       <c r="D35">
-        <v>53</v>
+        <v>15.58</v>
       </c>
       <c r="E35" t="s">
         <v>629</v>
       </c>
       <c r="F35">
-        <v>54.08</v>
+        <v>15.92</v>
       </c>
       <c r="G35">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4041,16 +4061,16 @@
         <v>596</v>
       </c>
       <c r="D36">
-        <v>12.06</v>
+        <v>15.85</v>
       </c>
       <c r="E36" t="s">
         <v>629</v>
       </c>
       <c r="F36">
-        <v>11.26</v>
+        <v>16.03</v>
       </c>
       <c r="G36">
-        <v>-6.63</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4064,16 +4084,16 @@
         <v>596</v>
       </c>
       <c r="D37">
-        <v>10.41</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
         <v>629</v>
       </c>
       <c r="F37">
-        <v>9.369999999999999</v>
+        <v>35.15</v>
       </c>
       <c r="G37">
-        <v>-9.99</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4087,16 +4107,16 @@
         <v>597</v>
       </c>
       <c r="D38">
-        <v>21.61</v>
+        <v>7.27</v>
       </c>
       <c r="E38" t="s">
         <v>630</v>
       </c>
       <c r="F38">
-        <v>22.32</v>
+        <v>7.23</v>
       </c>
       <c r="G38">
-        <v>3.29</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4110,16 +4130,16 @@
         <v>597</v>
       </c>
       <c r="D39">
-        <v>10.95</v>
+        <v>12.48</v>
       </c>
       <c r="E39" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F39">
-        <v>10.3</v>
+        <v>13.07</v>
       </c>
       <c r="G39">
-        <v>-5.94</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4133,16 +4153,16 @@
         <v>597</v>
       </c>
       <c r="D40">
-        <v>7.27</v>
+        <v>21.61</v>
       </c>
       <c r="E40" t="s">
         <v>630</v>
       </c>
       <c r="F40">
-        <v>7.23</v>
+        <v>22.32</v>
       </c>
       <c r="G40">
-        <v>-0.55</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4156,16 +4176,16 @@
         <v>597</v>
       </c>
       <c r="D41">
-        <v>12.48</v>
+        <v>10.95</v>
       </c>
       <c r="E41" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F41">
-        <v>13.07</v>
+        <v>10.3</v>
       </c>
       <c r="G41">
-        <v>4.73</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4202,16 +4222,16 @@
         <v>597</v>
       </c>
       <c r="D43">
-        <v>63.71</v>
+        <v>26.92</v>
       </c>
       <c r="E43" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F43">
-        <v>59.43</v>
+        <v>23.44</v>
       </c>
       <c r="G43">
-        <v>-6.72</v>
+        <v>-12.93</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4225,16 +4245,16 @@
         <v>597</v>
       </c>
       <c r="D44">
-        <v>30.86</v>
+        <v>7.2</v>
       </c>
       <c r="E44" t="s">
         <v>630</v>
       </c>
       <c r="F44">
-        <v>36.74</v>
+        <v>6.79</v>
       </c>
       <c r="G44">
-        <v>19.05</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4248,16 +4268,16 @@
         <v>597</v>
       </c>
       <c r="D45">
-        <v>7.2</v>
+        <v>35.45</v>
       </c>
       <c r="E45" t="s">
         <v>630</v>
       </c>
       <c r="F45">
-        <v>6.79</v>
+        <v>38.18</v>
       </c>
       <c r="G45">
-        <v>-5.69</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4271,16 +4291,16 @@
         <v>597</v>
       </c>
       <c r="D46">
-        <v>35.45</v>
+        <v>63.71</v>
       </c>
       <c r="E46" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F46">
-        <v>38.18</v>
+        <v>59.43</v>
       </c>
       <c r="G46">
-        <v>7.7</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -4294,16 +4314,16 @@
         <v>597</v>
       </c>
       <c r="D47">
-        <v>26.92</v>
+        <v>30.86</v>
       </c>
       <c r="E47" t="s">
         <v>630</v>
       </c>
       <c r="F47">
-        <v>23.44</v>
+        <v>36.74</v>
       </c>
       <c r="G47">
-        <v>-12.93</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -4317,16 +4337,16 @@
         <v>598</v>
       </c>
       <c r="D48">
-        <v>10.9</v>
+        <v>61.93</v>
       </c>
       <c r="E48" t="s">
         <v>634</v>
       </c>
       <c r="F48">
-        <v>11.35</v>
+        <v>60.73</v>
       </c>
       <c r="G48">
-        <v>4.13</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -4340,16 +4360,16 @@
         <v>598</v>
       </c>
       <c r="D49">
-        <v>84.72</v>
+        <v>54.85</v>
       </c>
       <c r="E49" t="s">
         <v>634</v>
       </c>
       <c r="F49">
-        <v>86.5</v>
+        <v>60.31</v>
       </c>
       <c r="G49">
-        <v>2.1</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -4363,16 +4383,16 @@
         <v>598</v>
       </c>
       <c r="D50">
-        <v>27.75</v>
+        <v>27.55</v>
       </c>
       <c r="E50" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F50">
-        <v>24.16</v>
+        <v>26.68</v>
       </c>
       <c r="G50">
-        <v>-12.94</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -4386,16 +4406,16 @@
         <v>598</v>
       </c>
       <c r="D51">
-        <v>215</v>
+        <v>56.11</v>
       </c>
       <c r="E51" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F51">
-        <v>209.71</v>
+        <v>51.34</v>
       </c>
       <c r="G51">
-        <v>-2.46</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -4409,16 +4429,16 @@
         <v>598</v>
       </c>
       <c r="D52">
-        <v>58.75</v>
+        <v>52.31</v>
       </c>
       <c r="E52" t="s">
         <v>634</v>
       </c>
       <c r="F52">
-        <v>55.83</v>
+        <v>50.29</v>
       </c>
       <c r="G52">
-        <v>-4.97</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -4432,16 +4452,16 @@
         <v>598</v>
       </c>
       <c r="D53">
-        <v>52.31</v>
+        <v>10.9</v>
       </c>
       <c r="E53" t="s">
         <v>634</v>
       </c>
       <c r="F53">
-        <v>50.29</v>
+        <v>11.35</v>
       </c>
       <c r="G53">
-        <v>-3.86</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4455,16 +4475,16 @@
         <v>598</v>
       </c>
       <c r="D54">
-        <v>27.55</v>
+        <v>215</v>
       </c>
       <c r="E54" t="s">
         <v>634</v>
       </c>
       <c r="F54">
-        <v>26.68</v>
+        <v>209.71</v>
       </c>
       <c r="G54">
-        <v>-3.16</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4478,16 +4498,16 @@
         <v>598</v>
       </c>
       <c r="D55">
-        <v>54.85</v>
+        <v>27.75</v>
       </c>
       <c r="E55" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F55">
-        <v>60.31</v>
+        <v>24.16</v>
       </c>
       <c r="G55">
-        <v>9.949999999999999</v>
+        <v>-12.94</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -4501,16 +4521,16 @@
         <v>598</v>
       </c>
       <c r="D56">
-        <v>61.93</v>
+        <v>84.72</v>
       </c>
       <c r="E56" t="s">
         <v>634</v>
       </c>
       <c r="F56">
-        <v>60.73</v>
+        <v>86.5</v>
       </c>
       <c r="G56">
-        <v>-1.94</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -4524,16 +4544,16 @@
         <v>598</v>
       </c>
       <c r="D57">
-        <v>56.11</v>
+        <v>58.75</v>
       </c>
       <c r="E57" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F57">
-        <v>51.34</v>
+        <v>55.83</v>
       </c>
       <c r="G57">
-        <v>-8.5</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4547,16 +4567,16 @@
         <v>599</v>
       </c>
       <c r="D58">
-        <v>10.5</v>
+        <v>13.99</v>
       </c>
       <c r="E58" t="s">
         <v>637</v>
       </c>
       <c r="F58">
-        <v>13.28</v>
+        <v>19.65</v>
       </c>
       <c r="G58">
-        <v>26.48</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4570,16 +4590,16 @@
         <v>599</v>
       </c>
       <c r="D59">
-        <v>223</v>
+        <v>15.47</v>
       </c>
       <c r="E59" t="s">
         <v>637</v>
       </c>
       <c r="F59">
-        <v>219.4</v>
+        <v>16.27</v>
       </c>
       <c r="G59">
-        <v>-1.61</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4593,16 +4613,16 @@
         <v>599</v>
       </c>
       <c r="D60">
-        <v>29.98</v>
+        <v>65.52</v>
       </c>
       <c r="E60" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F60">
-        <v>33.5</v>
+        <v>65.7</v>
       </c>
       <c r="G60">
-        <v>11.74</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -4616,16 +4636,16 @@
         <v>599</v>
       </c>
       <c r="D61">
-        <v>100.24</v>
+        <v>252</v>
       </c>
       <c r="E61" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F61">
-        <v>126.7</v>
+        <v>249.3</v>
       </c>
       <c r="G61">
-        <v>26.4</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -4639,16 +4659,16 @@
         <v>599</v>
       </c>
       <c r="D62">
-        <v>24.93</v>
+        <v>32</v>
       </c>
       <c r="E62" t="s">
         <v>637</v>
       </c>
       <c r="F62">
-        <v>26.44</v>
+        <v>33.95</v>
       </c>
       <c r="G62">
-        <v>6.06</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4662,16 +4682,16 @@
         <v>599</v>
       </c>
       <c r="D63">
-        <v>13.99</v>
+        <v>100.24</v>
       </c>
       <c r="E63" t="s">
         <v>637</v>
       </c>
       <c r="F63">
-        <v>19.65</v>
+        <v>126.7</v>
       </c>
       <c r="G63">
-        <v>40.46</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4685,16 +4705,16 @@
         <v>599</v>
       </c>
       <c r="D64">
-        <v>252</v>
+        <v>29.98</v>
       </c>
       <c r="E64" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F64">
-        <v>249.3</v>
+        <v>33.5</v>
       </c>
       <c r="G64">
-        <v>-1.07</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4708,16 +4728,16 @@
         <v>599</v>
       </c>
       <c r="D65">
-        <v>65.52</v>
+        <v>223</v>
       </c>
       <c r="E65" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F65">
-        <v>65.7</v>
+        <v>219.4</v>
       </c>
       <c r="G65">
-        <v>0.27</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -4731,16 +4751,16 @@
         <v>599</v>
       </c>
       <c r="D66">
-        <v>15.47</v>
+        <v>10.5</v>
       </c>
       <c r="E66" t="s">
         <v>637</v>
       </c>
       <c r="F66">
-        <v>16.27</v>
+        <v>13.28</v>
       </c>
       <c r="G66">
-        <v>5.17</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4754,16 +4774,16 @@
         <v>599</v>
       </c>
       <c r="D67">
-        <v>32</v>
+        <v>24.93</v>
       </c>
       <c r="E67" t="s">
         <v>637</v>
       </c>
       <c r="F67">
-        <v>33.95</v>
+        <v>26.44</v>
       </c>
       <c r="G67">
-        <v>6.09</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4777,16 +4797,16 @@
         <v>600</v>
       </c>
       <c r="D68">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
         <v>639</v>
       </c>
       <c r="F68">
-        <v>41.69</v>
+        <v>144.31</v>
       </c>
       <c r="G68">
-        <v>12.68</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4800,16 +4820,16 @@
         <v>600</v>
       </c>
       <c r="D69">
-        <v>4.75</v>
+        <v>26.28</v>
       </c>
       <c r="E69" t="s">
         <v>640</v>
       </c>
       <c r="F69">
-        <v>4.81</v>
+        <v>26.85</v>
       </c>
       <c r="G69">
-        <v>1.26</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4823,85 +4843,85 @@
         <v>600</v>
       </c>
       <c r="D70">
-        <v>22.81</v>
+        <v>57.94</v>
       </c>
       <c r="E70" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F70">
-        <v>23.51</v>
+        <v>60.04</v>
       </c>
       <c r="G70">
-        <v>3.07</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B71" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C71" t="s">
         <v>600</v>
       </c>
       <c r="D71">
-        <v>32.52</v>
+        <v>29.4</v>
       </c>
       <c r="E71" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F71">
-        <v>31.9</v>
+        <v>26.82</v>
       </c>
       <c r="G71">
-        <v>-1.91</v>
+        <v>-8.779999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B72" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C72" t="s">
         <v>600</v>
       </c>
       <c r="D72">
-        <v>2.15</v>
+        <v>27.3</v>
       </c>
       <c r="E72" t="s">
         <v>640</v>
       </c>
       <c r="F72">
-        <v>2.15</v>
+        <v>26.65</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B73" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C73" t="s">
         <v>600</v>
       </c>
       <c r="D73">
-        <v>140</v>
+        <v>32.52</v>
       </c>
       <c r="E73" t="s">
         <v>640</v>
       </c>
       <c r="F73">
-        <v>144.31</v>
+        <v>31.9</v>
       </c>
       <c r="G73">
-        <v>3.08</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4915,16 +4935,16 @@
         <v>600</v>
       </c>
       <c r="D74">
-        <v>26.28</v>
+        <v>2.15</v>
       </c>
       <c r="E74" t="s">
         <v>639</v>
       </c>
       <c r="F74">
-        <v>26.85</v>
+        <v>2.15</v>
       </c>
       <c r="G74">
-        <v>2.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4938,16 +4958,16 @@
         <v>600</v>
       </c>
       <c r="D75">
-        <v>27.3</v>
+        <v>37</v>
       </c>
       <c r="E75" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F75">
-        <v>26.65</v>
+        <v>41.69</v>
       </c>
       <c r="G75">
-        <v>-2.38</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4961,16 +4981,16 @@
         <v>600</v>
       </c>
       <c r="D76">
-        <v>29.4</v>
+        <v>22.81</v>
       </c>
       <c r="E76" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F76">
-        <v>26.82</v>
+        <v>23.51</v>
       </c>
       <c r="G76">
-        <v>-8.779999999999999</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4984,16 +5004,16 @@
         <v>600</v>
       </c>
       <c r="D77">
-        <v>57.94</v>
+        <v>4.75</v>
       </c>
       <c r="E77" t="s">
         <v>639</v>
       </c>
       <c r="F77">
-        <v>60.04</v>
+        <v>4.81</v>
       </c>
       <c r="G77">
-        <v>3.62</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5007,16 +5027,16 @@
         <v>601</v>
       </c>
       <c r="D78">
-        <v>80.27</v>
+        <v>56.3</v>
       </c>
       <c r="E78" t="s">
         <v>642</v>
       </c>
       <c r="F78">
-        <v>73.53</v>
+        <v>50.71</v>
       </c>
       <c r="G78">
-        <v>-8.4</v>
+        <v>-9.93</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5030,200 +5050,200 @@
         <v>601</v>
       </c>
       <c r="D79">
-        <v>14.7</v>
+        <v>333</v>
       </c>
       <c r="E79" t="s">
         <v>643</v>
       </c>
       <c r="F79">
-        <v>13.65</v>
+        <v>331.9</v>
       </c>
       <c r="G79">
-        <v>-7.14</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="B80" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C80" t="s">
         <v>601</v>
       </c>
       <c r="D80">
-        <v>294.01</v>
+        <v>35.62</v>
       </c>
       <c r="E80" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F80">
-        <v>354</v>
+        <v>31.82</v>
       </c>
       <c r="G80">
-        <v>20.4</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B81" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C81" t="s">
         <v>601</v>
       </c>
       <c r="D81">
-        <v>6.88</v>
+        <v>18.55</v>
       </c>
       <c r="E81" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F81">
-        <v>6.11</v>
+        <v>12.52</v>
       </c>
       <c r="G81">
-        <v>-11.19</v>
+        <v>-32.51</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B82" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C82" t="s">
         <v>601</v>
       </c>
       <c r="D82">
-        <v>41.92</v>
+        <v>61.16</v>
       </c>
       <c r="E82" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F82">
-        <v>35.76</v>
+        <v>58.86</v>
       </c>
       <c r="G82">
-        <v>-14.69</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B83" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C83" t="s">
         <v>601</v>
       </c>
       <c r="D83">
-        <v>18.55</v>
+        <v>6.88</v>
       </c>
       <c r="E83" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F83">
-        <v>12.52</v>
+        <v>6.11</v>
       </c>
       <c r="G83">
-        <v>-32.51</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B84" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C84" t="s">
         <v>601</v>
       </c>
       <c r="D84">
-        <v>333</v>
+        <v>14.7</v>
       </c>
       <c r="E84" t="s">
         <v>644</v>
       </c>
       <c r="F84">
-        <v>331.9</v>
+        <v>13.65</v>
       </c>
       <c r="G84">
-        <v>-0.33</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B85" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C85" t="s">
         <v>601</v>
       </c>
       <c r="D85">
-        <v>56.3</v>
+        <v>80.27</v>
       </c>
       <c r="E85" t="s">
         <v>645</v>
       </c>
       <c r="F85">
-        <v>50.71</v>
+        <v>73.53</v>
       </c>
       <c r="G85">
-        <v>-9.93</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B86" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="C86" t="s">
         <v>601</v>
       </c>
       <c r="D86">
-        <v>61.16</v>
+        <v>41.92</v>
       </c>
       <c r="E86" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F86">
-        <v>58.86</v>
+        <v>35.76</v>
       </c>
       <c r="G86">
-        <v>-3.76</v>
+        <v>-14.69</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B87" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="C87" t="s">
         <v>601</v>
       </c>
       <c r="D87">
-        <v>35.62</v>
+        <v>294.01</v>
       </c>
       <c r="E87" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F87">
-        <v>31.82</v>
+        <v>354</v>
       </c>
       <c r="G87">
-        <v>-10.67</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5237,16 +5257,16 @@
         <v>602</v>
       </c>
       <c r="D88">
-        <v>22.39</v>
+        <v>42</v>
       </c>
       <c r="E88" t="s">
         <v>646</v>
       </c>
       <c r="F88">
-        <v>21.51</v>
+        <v>46.43</v>
       </c>
       <c r="G88">
-        <v>-3.93</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -5260,16 +5280,16 @@
         <v>602</v>
       </c>
       <c r="D89">
-        <v>88</v>
+        <v>33.3</v>
       </c>
       <c r="E89" t="s">
         <v>647</v>
       </c>
       <c r="F89">
-        <v>87</v>
+        <v>40.4</v>
       </c>
       <c r="G89">
-        <v>-1.14</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -5283,16 +5303,16 @@
         <v>602</v>
       </c>
       <c r="D90">
-        <v>3.41</v>
+        <v>30.15</v>
       </c>
       <c r="E90" t="s">
         <v>648</v>
       </c>
       <c r="F90">
-        <v>3.14</v>
+        <v>29.64</v>
       </c>
       <c r="G90">
-        <v>-7.92</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -5306,16 +5326,16 @@
         <v>602</v>
       </c>
       <c r="D91">
-        <v>3.67</v>
+        <v>10.99</v>
       </c>
       <c r="E91" t="s">
         <v>649</v>
       </c>
       <c r="F91">
-        <v>3.55</v>
+        <v>10.72</v>
       </c>
       <c r="G91">
-        <v>-3.27</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -5329,16 +5349,16 @@
         <v>602</v>
       </c>
       <c r="D92">
-        <v>33.3</v>
+        <v>3.67</v>
       </c>
       <c r="E92" t="s">
         <v>650</v>
       </c>
       <c r="F92">
-        <v>40.4</v>
+        <v>3.55</v>
       </c>
       <c r="G92">
-        <v>21.32</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -5352,16 +5372,16 @@
         <v>602</v>
       </c>
       <c r="D93">
-        <v>30.15</v>
+        <v>3.41</v>
       </c>
       <c r="E93" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="F93">
-        <v>29.64</v>
+        <v>3.14</v>
       </c>
       <c r="G93">
-        <v>-1.69</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -5375,16 +5395,16 @@
         <v>602</v>
       </c>
       <c r="D94">
-        <v>42</v>
+        <v>22.39</v>
       </c>
       <c r="E94" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="F94">
-        <v>46.43</v>
+        <v>21.51</v>
       </c>
       <c r="G94">
-        <v>10.55</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -5398,16 +5418,16 @@
         <v>602</v>
       </c>
       <c r="D95">
-        <v>10.99</v>
+        <v>88</v>
       </c>
       <c r="E95" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F95">
-        <v>10.72</v>
+        <v>87</v>
       </c>
       <c r="G95">
-        <v>-2.46</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -5421,16 +5441,16 @@
         <v>603</v>
       </c>
       <c r="D96">
-        <v>84.98</v>
+        <v>24.6</v>
       </c>
       <c r="E96" t="s">
         <v>652</v>
       </c>
       <c r="F96">
-        <v>83.27</v>
+        <v>24.97</v>
       </c>
       <c r="G96">
-        <v>-2.01</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -5444,16 +5464,16 @@
         <v>603</v>
       </c>
       <c r="D97">
-        <v>15.52</v>
+        <v>84.98</v>
       </c>
       <c r="E97" t="s">
         <v>653</v>
       </c>
       <c r="F97">
-        <v>15.46</v>
+        <v>83.27</v>
       </c>
       <c r="G97">
-        <v>-0.39</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -5467,16 +5487,16 @@
         <v>603</v>
       </c>
       <c r="D98">
-        <v>24.6</v>
+        <v>7.05</v>
       </c>
       <c r="E98" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F98">
-        <v>24.97</v>
+        <v>7.01</v>
       </c>
       <c r="G98">
-        <v>1.5</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -5490,16 +5510,16 @@
         <v>603</v>
       </c>
       <c r="D99">
-        <v>54.38</v>
+        <v>15.52</v>
       </c>
       <c r="E99" t="s">
         <v>654</v>
       </c>
       <c r="F99">
-        <v>54.25</v>
+        <v>15.46</v>
       </c>
       <c r="G99">
-        <v>-0.24</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -5513,16 +5533,16 @@
         <v>603</v>
       </c>
       <c r="D100">
-        <v>7.05</v>
+        <v>14.45</v>
       </c>
       <c r="E100" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F100">
-        <v>7.01</v>
+        <v>14.48</v>
       </c>
       <c r="G100">
-        <v>-0.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -5536,16 +5556,16 @@
         <v>603</v>
       </c>
       <c r="D101">
-        <v>14.45</v>
+        <v>27.88</v>
       </c>
       <c r="E101" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F101">
-        <v>14.48</v>
+        <v>28.49</v>
       </c>
       <c r="G101">
-        <v>0.21</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -5559,16 +5579,16 @@
         <v>603</v>
       </c>
       <c r="D102">
-        <v>27.88</v>
+        <v>54.38</v>
       </c>
       <c r="E102" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F102">
-        <v>28.49</v>
+        <v>54.25</v>
       </c>
       <c r="G102">
-        <v>2.19</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -5582,116 +5602,116 @@
         <v>604</v>
       </c>
       <c r="D103">
-        <v>15.4</v>
+        <v>6.78</v>
       </c>
       <c r="E103" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F103">
-        <v>17.3</v>
+        <v>6.54</v>
       </c>
       <c r="G103">
-        <v>12.34</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="B104" t="s">
-        <v>370</v>
+        <v>419</v>
       </c>
       <c r="C104" t="s">
         <v>604</v>
       </c>
       <c r="D104">
-        <v>224</v>
+        <v>36.23</v>
       </c>
       <c r="E104" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="F104">
-        <v>227.03</v>
+        <v>45.02</v>
       </c>
       <c r="G104">
-        <v>1.35</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B105" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C105" t="s">
         <v>604</v>
       </c>
       <c r="D105">
-        <v>23.97</v>
+        <v>47.33</v>
       </c>
       <c r="E105" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="F105">
-        <v>24.9</v>
+        <v>47.25</v>
       </c>
       <c r="G105">
-        <v>3.88</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B106" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C106" t="s">
         <v>604</v>
       </c>
       <c r="D106">
-        <v>36.23</v>
+        <v>28.8</v>
       </c>
       <c r="E106" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F106">
-        <v>45.02</v>
+        <v>28.57</v>
       </c>
       <c r="G106">
-        <v>24.26</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B107" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C107" t="s">
         <v>604</v>
       </c>
       <c r="D107">
-        <v>117</v>
+        <v>16.1</v>
       </c>
       <c r="E107" t="s">
         <v>656</v>
       </c>
       <c r="F107">
-        <v>110.12</v>
+        <v>15.64</v>
       </c>
       <c r="G107">
-        <v>-5.88</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B108" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C108" t="s">
         <v>604</v>
@@ -5700,7 +5720,7 @@
         <v>22.2</v>
       </c>
       <c r="E108" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F108">
         <v>23.35</v>
@@ -5711,71 +5731,71 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B109" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C109" t="s">
         <v>604</v>
       </c>
       <c r="D109">
-        <v>47.33</v>
+        <v>117</v>
       </c>
       <c r="E109" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F109">
-        <v>47.25</v>
+        <v>110.12</v>
       </c>
       <c r="G109">
-        <v>-0.17</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B110" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C110" t="s">
         <v>604</v>
       </c>
       <c r="D110">
-        <v>6.78</v>
+        <v>23.97</v>
       </c>
       <c r="E110" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F110">
-        <v>6.54</v>
+        <v>24.9</v>
       </c>
       <c r="G110">
-        <v>-3.54</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="C111" t="s">
         <v>604</v>
       </c>
       <c r="D111">
-        <v>16.1</v>
+        <v>224</v>
       </c>
       <c r="E111" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F111">
-        <v>15.64</v>
+        <v>227.03</v>
       </c>
       <c r="G111">
-        <v>-2.86</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -5789,16 +5809,16 @@
         <v>604</v>
       </c>
       <c r="D112">
-        <v>28.8</v>
+        <v>15.4</v>
       </c>
       <c r="E112" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F112">
-        <v>28.57</v>
+        <v>17.3</v>
       </c>
       <c r="G112">
-        <v>-0.8</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -5812,16 +5832,16 @@
         <v>605</v>
       </c>
       <c r="D113">
-        <v>6.1</v>
+        <v>71</v>
       </c>
       <c r="E113" t="s">
         <v>658</v>
       </c>
       <c r="F113">
-        <v>6.17</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G113">
-        <v>1.15</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5835,16 +5855,16 @@
         <v>605</v>
       </c>
       <c r="D114">
-        <v>23.3</v>
+        <v>289</v>
       </c>
       <c r="E114" t="s">
         <v>658</v>
       </c>
       <c r="F114">
-        <v>23.32</v>
+        <v>338</v>
       </c>
       <c r="G114">
-        <v>0.09</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5858,16 +5878,16 @@
         <v>605</v>
       </c>
       <c r="D115">
-        <v>20</v>
+        <v>4.84</v>
       </c>
       <c r="E115" t="s">
         <v>658</v>
       </c>
       <c r="F115">
-        <v>19.31</v>
+        <v>4.41</v>
       </c>
       <c r="G115">
-        <v>-3.45</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5881,16 +5901,16 @@
         <v>605</v>
       </c>
       <c r="D116">
-        <v>27</v>
+        <v>145.59</v>
       </c>
       <c r="E116" t="s">
         <v>658</v>
       </c>
       <c r="F116">
-        <v>26.73</v>
+        <v>159.19</v>
       </c>
       <c r="G116">
-        <v>-1</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5904,16 +5924,16 @@
         <v>605</v>
       </c>
       <c r="D117">
-        <v>3.92</v>
+        <v>41.79</v>
       </c>
       <c r="E117" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F117">
-        <v>3.9</v>
+        <v>56.27</v>
       </c>
       <c r="G117">
-        <v>-0.51</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5927,16 +5947,16 @@
         <v>605</v>
       </c>
       <c r="D118">
-        <v>145.59</v>
+        <v>27</v>
       </c>
       <c r="E118" t="s">
         <v>658</v>
       </c>
       <c r="F118">
-        <v>159.19</v>
+        <v>26.73</v>
       </c>
       <c r="G118">
-        <v>9.34</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5950,16 +5970,16 @@
         <v>605</v>
       </c>
       <c r="D119">
-        <v>4.84</v>
+        <v>6.1</v>
       </c>
       <c r="E119" t="s">
         <v>658</v>
       </c>
       <c r="F119">
-        <v>4.41</v>
+        <v>6.17</v>
       </c>
       <c r="G119">
-        <v>-8.880000000000001</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5973,16 +5993,16 @@
         <v>605</v>
       </c>
       <c r="D120">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="E120" t="s">
         <v>658</v>
       </c>
       <c r="F120">
-        <v>78.79000000000001</v>
+        <v>19.31</v>
       </c>
       <c r="G120">
-        <v>10.97</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5996,16 +6016,16 @@
         <v>605</v>
       </c>
       <c r="D121">
-        <v>289</v>
+        <v>23.3</v>
       </c>
       <c r="E121" t="s">
         <v>658</v>
       </c>
       <c r="F121">
-        <v>338</v>
+        <v>23.32</v>
       </c>
       <c r="G121">
-        <v>16.96</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6019,16 +6039,16 @@
         <v>605</v>
       </c>
       <c r="D122">
-        <v>41.79</v>
+        <v>3.92</v>
       </c>
       <c r="E122" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F122">
-        <v>56.27</v>
+        <v>3.9</v>
       </c>
       <c r="G122">
-        <v>34.65</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6042,16 +6062,16 @@
         <v>606</v>
       </c>
       <c r="D123">
-        <v>5.08</v>
+        <v>26</v>
       </c>
       <c r="E123" t="s">
         <v>660</v>
       </c>
       <c r="F123">
-        <v>4.6</v>
+        <v>28.88</v>
       </c>
       <c r="G123">
-        <v>-9.449999999999999</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6065,154 +6085,154 @@
         <v>606</v>
       </c>
       <c r="D124">
-        <v>28.94</v>
+        <v>53.9</v>
       </c>
       <c r="E124" t="s">
         <v>660</v>
       </c>
       <c r="F124">
-        <v>30.76</v>
+        <v>59.81</v>
       </c>
       <c r="G124">
-        <v>6.29</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="B125" t="s">
-        <v>439</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
         <v>606</v>
       </c>
       <c r="D125">
-        <v>7.01</v>
+        <v>127</v>
       </c>
       <c r="E125" t="s">
         <v>660</v>
       </c>
       <c r="F125">
-        <v>7.13</v>
+        <v>130.97</v>
       </c>
       <c r="G125">
-        <v>1.71</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B126" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C126" t="s">
         <v>606</v>
       </c>
       <c r="D126">
-        <v>113</v>
+        <v>38.2</v>
       </c>
       <c r="E126" t="s">
         <v>660</v>
       </c>
       <c r="F126">
-        <v>118.43</v>
+        <v>47</v>
       </c>
       <c r="G126">
-        <v>4.81</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B127" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C127" t="s">
         <v>606</v>
       </c>
       <c r="D127">
-        <v>17.95</v>
+        <v>16.73</v>
       </c>
       <c r="E127" t="s">
         <v>660</v>
       </c>
       <c r="F127">
-        <v>20.77</v>
+        <v>17.67</v>
       </c>
       <c r="G127">
-        <v>15.71</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B128" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C128" t="s">
         <v>606</v>
       </c>
       <c r="D128">
-        <v>26</v>
+        <v>17.95</v>
       </c>
       <c r="E128" t="s">
         <v>660</v>
       </c>
       <c r="F128">
-        <v>28.88</v>
+        <v>20.77</v>
       </c>
       <c r="G128">
-        <v>11.08</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B129" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C129" t="s">
         <v>606</v>
       </c>
       <c r="D129">
-        <v>16.73</v>
+        <v>7.01</v>
       </c>
       <c r="E129" t="s">
         <v>660</v>
       </c>
       <c r="F129">
-        <v>17.67</v>
+        <v>7.13</v>
       </c>
       <c r="G129">
-        <v>5.62</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="B130" t="s">
-        <v>380</v>
+        <v>443</v>
       </c>
       <c r="C130" t="s">
         <v>606</v>
       </c>
       <c r="D130">
-        <v>127</v>
+        <v>28.94</v>
       </c>
       <c r="E130" t="s">
         <v>660</v>
       </c>
       <c r="F130">
-        <v>130.97</v>
+        <v>30.76</v>
       </c>
       <c r="G130">
-        <v>3.13</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6226,16 +6246,16 @@
         <v>606</v>
       </c>
       <c r="D131">
-        <v>53.9</v>
+        <v>5.08</v>
       </c>
       <c r="E131" t="s">
         <v>660</v>
       </c>
       <c r="F131">
-        <v>59.81</v>
+        <v>4.6</v>
       </c>
       <c r="G131">
-        <v>10.96</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6249,16 +6269,16 @@
         <v>606</v>
       </c>
       <c r="D132">
-        <v>38.2</v>
+        <v>113</v>
       </c>
       <c r="E132" t="s">
         <v>660</v>
       </c>
       <c r="F132">
-        <v>47</v>
+        <v>118.43</v>
       </c>
       <c r="G132">
-        <v>23.04</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -6272,16 +6292,16 @@
         <v>607</v>
       </c>
       <c r="D133">
-        <v>47.42</v>
+        <v>31.4</v>
       </c>
       <c r="E133" t="s">
         <v>661</v>
       </c>
       <c r="F133">
-        <v>45.6</v>
+        <v>28.23</v>
       </c>
       <c r="G133">
-        <v>-3.84</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -6295,131 +6315,131 @@
         <v>607</v>
       </c>
       <c r="D134">
-        <v>9.4</v>
+        <v>21.98</v>
       </c>
       <c r="E134" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F134">
-        <v>11.17</v>
+        <v>24.98</v>
       </c>
       <c r="G134">
-        <v>18.83</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B135" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C135" t="s">
         <v>607</v>
       </c>
       <c r="D135">
-        <v>65.73999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E135" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F135">
-        <v>61.4</v>
+        <v>8.4</v>
       </c>
       <c r="G135">
-        <v>-6.6</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B136" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C136" t="s">
         <v>607</v>
       </c>
       <c r="D136">
-        <v>110</v>
+        <v>106.8</v>
       </c>
       <c r="E136" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F136">
-        <v>105</v>
+        <v>110.11</v>
       </c>
       <c r="G136">
-        <v>-4.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B137" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C137" t="s">
         <v>607</v>
       </c>
       <c r="D137">
-        <v>22.83</v>
+        <v>18.8</v>
       </c>
       <c r="E137" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F137">
-        <v>24.63</v>
+        <v>19.59</v>
       </c>
       <c r="G137">
-        <v>7.88</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B138" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C138" t="s">
         <v>607</v>
       </c>
       <c r="D138">
-        <v>18.8</v>
+        <v>22.83</v>
       </c>
       <c r="E138" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F138">
-        <v>19.59</v>
+        <v>24.63</v>
       </c>
       <c r="G138">
-        <v>4.2</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B139" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C139" t="s">
         <v>607</v>
       </c>
       <c r="D139">
-        <v>106.8</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E139" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F139">
-        <v>110.11</v>
+        <v>61.4</v>
       </c>
       <c r="G139">
-        <v>3.1</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -6433,16 +6453,16 @@
         <v>607</v>
       </c>
       <c r="D140">
-        <v>8.369999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E140" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F140">
-        <v>8.4</v>
+        <v>11.17</v>
       </c>
       <c r="G140">
-        <v>0.36</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -6456,16 +6476,16 @@
         <v>607</v>
       </c>
       <c r="D141">
-        <v>21.98</v>
+        <v>47.42</v>
       </c>
       <c r="E141" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F141">
-        <v>24.98</v>
+        <v>45.6</v>
       </c>
       <c r="G141">
-        <v>13.65</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -6479,154 +6499,154 @@
         <v>607</v>
       </c>
       <c r="D142">
-        <v>31.4</v>
+        <v>110</v>
       </c>
       <c r="E142" t="s">
         <v>662</v>
       </c>
       <c r="F142">
-        <v>28.23</v>
+        <v>105</v>
       </c>
       <c r="G142">
-        <v>-10.1</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="B143" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="C143" t="s">
         <v>608</v>
       </c>
       <c r="D143">
-        <v>37.9</v>
+        <v>181.29</v>
       </c>
       <c r="E143" t="s">
         <v>663</v>
       </c>
       <c r="F143">
-        <v>43.45</v>
+        <v>191.66</v>
       </c>
       <c r="G143">
-        <v>14.64</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B144" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C144" t="s">
         <v>608</v>
       </c>
       <c r="D144">
-        <v>65.22</v>
+        <v>14.41</v>
       </c>
       <c r="E144" t="s">
         <v>663</v>
       </c>
       <c r="F144">
-        <v>76.09999999999999</v>
+        <v>17.22</v>
       </c>
       <c r="G144">
-        <v>16.68</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B145" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C145" t="s">
         <v>608</v>
       </c>
       <c r="D145">
-        <v>95.09999999999999</v>
+        <v>40.07</v>
       </c>
       <c r="E145" t="s">
         <v>663</v>
       </c>
       <c r="F145">
-        <v>95.16</v>
+        <v>45.14</v>
       </c>
       <c r="G145">
-        <v>0.06</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B146" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C146" t="s">
         <v>608</v>
       </c>
       <c r="D146">
-        <v>18.2</v>
+        <v>40.7</v>
       </c>
       <c r="E146" t="s">
         <v>663</v>
       </c>
       <c r="F146">
-        <v>17.9</v>
+        <v>47.29</v>
       </c>
       <c r="G146">
-        <v>-1.65</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B147" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C147" t="s">
         <v>608</v>
       </c>
       <c r="D147">
-        <v>8.82</v>
+        <v>56.49</v>
       </c>
       <c r="E147" t="s">
         <v>663</v>
       </c>
       <c r="F147">
-        <v>8.27</v>
+        <v>77.11</v>
       </c>
       <c r="G147">
-        <v>-6.24</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="B148" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="C148" t="s">
         <v>608</v>
       </c>
       <c r="D148">
-        <v>181.29</v>
+        <v>18.2</v>
       </c>
       <c r="E148" t="s">
         <v>663</v>
       </c>
       <c r="F148">
-        <v>191.66</v>
+        <v>17.9</v>
       </c>
       <c r="G148">
-        <v>5.72</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -6640,16 +6660,16 @@
         <v>608</v>
       </c>
       <c r="D149">
-        <v>14.41</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E149" t="s">
         <v>663</v>
       </c>
       <c r="F149">
-        <v>17.22</v>
+        <v>95.16</v>
       </c>
       <c r="G149">
-        <v>19.5</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -6663,16 +6683,16 @@
         <v>608</v>
       </c>
       <c r="D150">
-        <v>56.49</v>
+        <v>65.22</v>
       </c>
       <c r="E150" t="s">
         <v>663</v>
       </c>
       <c r="F150">
-        <v>77.11</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G150">
-        <v>36.5</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -6686,16 +6706,16 @@
         <v>608</v>
       </c>
       <c r="D151">
-        <v>40.7</v>
+        <v>8.82</v>
       </c>
       <c r="E151" t="s">
         <v>663</v>
       </c>
       <c r="F151">
-        <v>47.29</v>
+        <v>8.27</v>
       </c>
       <c r="G151">
-        <v>16.19</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -6709,16 +6729,16 @@
         <v>608</v>
       </c>
       <c r="D152">
-        <v>40.07</v>
+        <v>37.9</v>
       </c>
       <c r="E152" t="s">
         <v>663</v>
       </c>
       <c r="F152">
-        <v>45.14</v>
+        <v>43.45</v>
       </c>
       <c r="G152">
-        <v>12.65</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -6732,62 +6752,62 @@
         <v>609</v>
       </c>
       <c r="D153">
-        <v>115.38</v>
+        <v>35.6</v>
       </c>
       <c r="E153" t="s">
         <v>664</v>
       </c>
       <c r="F153">
-        <v>102.39</v>
+        <v>36.29</v>
       </c>
       <c r="G153">
-        <v>-11.26</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B154" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="C154" t="s">
         <v>609</v>
       </c>
       <c r="D154">
-        <v>14.19</v>
+        <v>115.38</v>
       </c>
       <c r="E154" t="s">
         <v>664</v>
       </c>
       <c r="F154">
-        <v>11.85</v>
+        <v>102.39</v>
       </c>
       <c r="G154">
-        <v>-16.49</v>
+        <v>-11.26</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B155" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C155" t="s">
         <v>609</v>
       </c>
       <c r="D155">
-        <v>35.6</v>
+        <v>14.19</v>
       </c>
       <c r="E155" t="s">
         <v>664</v>
       </c>
       <c r="F155">
-        <v>36.29</v>
+        <v>11.85</v>
       </c>
       <c r="G155">
-        <v>1.94</v>
+        <v>-16.49</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -6838,33 +6858,33 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="B158" t="s">
-        <v>402</v>
+        <v>468</v>
       </c>
       <c r="C158" t="s">
         <v>609</v>
       </c>
       <c r="D158">
-        <v>37.87</v>
+        <v>5.06</v>
       </c>
       <c r="E158" t="s">
         <v>664</v>
       </c>
       <c r="F158">
-        <v>32.38</v>
+        <v>4.85</v>
       </c>
       <c r="G158">
-        <v>-14.5</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B159" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C159" t="s">
         <v>609</v>
@@ -6884,10 +6904,10 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B160" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C160" t="s">
         <v>609</v>
@@ -6907,25 +6927,25 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="B161" t="s">
-        <v>470</v>
+        <v>398</v>
       </c>
       <c r="C161" t="s">
         <v>609</v>
       </c>
       <c r="D161">
-        <v>5.06</v>
+        <v>37.87</v>
       </c>
       <c r="E161" t="s">
         <v>664</v>
       </c>
       <c r="F161">
-        <v>4.85</v>
+        <v>32.38</v>
       </c>
       <c r="G161">
-        <v>-4.15</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -6939,16 +6959,16 @@
         <v>610</v>
       </c>
       <c r="D162">
-        <v>30.7</v>
+        <v>4.12</v>
       </c>
       <c r="E162" t="s">
         <v>665</v>
       </c>
       <c r="F162">
-        <v>27.77</v>
+        <v>3.72</v>
       </c>
       <c r="G162">
-        <v>-9.539999999999999</v>
+        <v>-9.710000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6962,16 +6982,16 @@
         <v>610</v>
       </c>
       <c r="D163">
-        <v>24.58</v>
+        <v>21.91</v>
       </c>
       <c r="E163" t="s">
         <v>665</v>
       </c>
       <c r="F163">
-        <v>24.44</v>
+        <v>22.75</v>
       </c>
       <c r="G163">
-        <v>-0.57</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -6985,16 +7005,16 @@
         <v>610</v>
       </c>
       <c r="D164">
-        <v>22.66</v>
+        <v>6.31</v>
       </c>
       <c r="E164" t="s">
         <v>665</v>
       </c>
       <c r="F164">
-        <v>19.38</v>
+        <v>5.31</v>
       </c>
       <c r="G164">
-        <v>-14.47</v>
+        <v>-15.85</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7031,16 +7051,16 @@
         <v>610</v>
       </c>
       <c r="D166">
-        <v>21.91</v>
+        <v>24.58</v>
       </c>
       <c r="E166" t="s">
         <v>665</v>
       </c>
       <c r="F166">
-        <v>22.75</v>
+        <v>24.44</v>
       </c>
       <c r="G166">
-        <v>3.83</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7054,16 +7074,16 @@
         <v>610</v>
       </c>
       <c r="D167">
-        <v>4.12</v>
+        <v>22.66</v>
       </c>
       <c r="E167" t="s">
         <v>665</v>
       </c>
       <c r="F167">
-        <v>3.72</v>
+        <v>19.38</v>
       </c>
       <c r="G167">
-        <v>-9.710000000000001</v>
+        <v>-14.47</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7077,16 +7097,16 @@
         <v>610</v>
       </c>
       <c r="D168">
-        <v>6.31</v>
+        <v>30.7</v>
       </c>
       <c r="E168" t="s">
         <v>665</v>
       </c>
       <c r="F168">
-        <v>5.31</v>
+        <v>27.77</v>
       </c>
       <c r="G168">
-        <v>-15.85</v>
+        <v>-9.539999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7100,16 +7120,16 @@
         <v>611</v>
       </c>
       <c r="D169">
-        <v>8.289999999999999</v>
+        <v>17.63</v>
       </c>
       <c r="E169" t="s">
         <v>666</v>
       </c>
       <c r="F169">
-        <v>7.21</v>
+        <v>15.36</v>
       </c>
       <c r="G169">
-        <v>-13.03</v>
+        <v>-12.88</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7123,16 +7143,16 @@
         <v>611</v>
       </c>
       <c r="D170">
-        <v>5.72</v>
+        <v>38.5</v>
       </c>
       <c r="E170" t="s">
         <v>666</v>
       </c>
       <c r="F170">
-        <v>4.89</v>
+        <v>38.27</v>
       </c>
       <c r="G170">
-        <v>-14.51</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7146,16 +7166,16 @@
         <v>611</v>
       </c>
       <c r="D171">
-        <v>2.47</v>
+        <v>114</v>
       </c>
       <c r="E171" t="s">
         <v>666</v>
       </c>
       <c r="F171">
-        <v>3.35</v>
+        <v>114.39</v>
       </c>
       <c r="G171">
-        <v>35.63</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7169,16 +7189,16 @@
         <v>611</v>
       </c>
       <c r="D172">
-        <v>66.28</v>
+        <v>30.77</v>
       </c>
       <c r="E172" t="s">
         <v>666</v>
       </c>
       <c r="F172">
-        <v>61.01</v>
+        <v>34.09</v>
       </c>
       <c r="G172">
-        <v>-7.95</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7192,16 +7212,16 @@
         <v>611</v>
       </c>
       <c r="D173">
-        <v>8.43</v>
+        <v>41.29</v>
       </c>
       <c r="E173" t="s">
         <v>666</v>
       </c>
       <c r="F173">
-        <v>8.17</v>
+        <v>36.77</v>
       </c>
       <c r="G173">
-        <v>-3.08</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7215,16 +7235,16 @@
         <v>611</v>
       </c>
       <c r="D174">
-        <v>30.77</v>
+        <v>8.43</v>
       </c>
       <c r="E174" t="s">
         <v>666</v>
       </c>
       <c r="F174">
-        <v>34.09</v>
+        <v>8.17</v>
       </c>
       <c r="G174">
-        <v>10.79</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7238,16 +7258,16 @@
         <v>611</v>
       </c>
       <c r="D175">
-        <v>41.29</v>
+        <v>2.47</v>
       </c>
       <c r="E175" t="s">
         <v>666</v>
       </c>
       <c r="F175">
-        <v>36.77</v>
+        <v>3.35</v>
       </c>
       <c r="G175">
-        <v>-10.95</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7261,16 +7281,16 @@
         <v>611</v>
       </c>
       <c r="D176">
-        <v>114</v>
+        <v>5.72</v>
       </c>
       <c r="E176" t="s">
         <v>666</v>
       </c>
       <c r="F176">
-        <v>114.39</v>
+        <v>4.89</v>
       </c>
       <c r="G176">
-        <v>0.34</v>
+        <v>-14.51</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7284,16 +7304,16 @@
         <v>611</v>
       </c>
       <c r="D177">
-        <v>38.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E177" t="s">
         <v>666</v>
       </c>
       <c r="F177">
-        <v>38.27</v>
+        <v>7.21</v>
       </c>
       <c r="G177">
-        <v>-0.6</v>
+        <v>-13.03</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7307,223 +7327,223 @@
         <v>611</v>
       </c>
       <c r="D178">
-        <v>17.63</v>
+        <v>66.28</v>
       </c>
       <c r="E178" t="s">
         <v>666</v>
       </c>
       <c r="F178">
-        <v>15.36</v>
+        <v>61.01</v>
       </c>
       <c r="G178">
-        <v>-12.88</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
       <c r="B179" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="C179" t="s">
         <v>612</v>
       </c>
       <c r="D179">
-        <v>27.37</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E179" t="s">
         <v>667</v>
       </c>
       <c r="F179">
-        <v>27.15</v>
+        <v>9</v>
       </c>
       <c r="G179">
-        <v>-0.8</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B180" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C180" t="s">
         <v>612</v>
       </c>
       <c r="D180">
-        <v>17</v>
+        <v>15.78</v>
       </c>
       <c r="E180" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F180">
-        <v>18.78</v>
+        <v>15.97</v>
       </c>
       <c r="G180">
-        <v>10.47</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B181" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C181" t="s">
         <v>612</v>
       </c>
       <c r="D181">
-        <v>50.33</v>
+        <v>2.45</v>
       </c>
       <c r="E181" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F181">
-        <v>50.4</v>
+        <v>2.36</v>
       </c>
       <c r="G181">
-        <v>0.14</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B182" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C182" t="s">
         <v>612</v>
       </c>
       <c r="D182">
-        <v>21.41</v>
+        <v>11.7</v>
       </c>
       <c r="E182" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F182">
-        <v>16.91</v>
+        <v>10.31</v>
       </c>
       <c r="G182">
-        <v>-21.02</v>
+        <v>-11.88</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B183" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C183" t="s">
         <v>612</v>
       </c>
       <c r="D183">
-        <v>7.35</v>
+        <v>46.93</v>
       </c>
       <c r="E183" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F183">
-        <v>6.48</v>
+        <v>46.24</v>
       </c>
       <c r="G183">
-        <v>-11.84</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B184" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C184" t="s">
         <v>612</v>
       </c>
       <c r="D184">
-        <v>8.550000000000001</v>
+        <v>21.41</v>
       </c>
       <c r="E184" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="F184">
-        <v>9</v>
+        <v>16.91</v>
       </c>
       <c r="G184">
-        <v>5.26</v>
+        <v>-21.02</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B185" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C185" t="s">
         <v>612</v>
       </c>
       <c r="D185">
-        <v>15.78</v>
+        <v>50.33</v>
       </c>
       <c r="E185" t="s">
         <v>668</v>
       </c>
       <c r="F185">
-        <v>15.97</v>
+        <v>50.4</v>
       </c>
       <c r="G185">
-        <v>1.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B186" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C186" t="s">
         <v>612</v>
       </c>
       <c r="D186">
-        <v>46.93</v>
+        <v>17</v>
       </c>
       <c r="E186" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F186">
-        <v>46.24</v>
+        <v>18.78</v>
       </c>
       <c r="G186">
-        <v>-1.47</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="B187" t="s">
-        <v>495</v>
+        <v>440</v>
       </c>
       <c r="C187" t="s">
         <v>612</v>
       </c>
       <c r="D187">
-        <v>11.7</v>
+        <v>27.37</v>
       </c>
       <c r="E187" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F187">
-        <v>10.31</v>
+        <v>27.15</v>
       </c>
       <c r="G187">
-        <v>-11.88</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7537,16 +7557,16 @@
         <v>612</v>
       </c>
       <c r="D188">
-        <v>2.45</v>
+        <v>7.35</v>
       </c>
       <c r="E188" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F188">
-        <v>2.36</v>
+        <v>6.48</v>
       </c>
       <c r="G188">
-        <v>-3.67</v>
+        <v>-11.84</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7560,16 +7580,16 @@
         <v>613</v>
       </c>
       <c r="D189">
-        <v>12.8</v>
+        <v>57.43</v>
       </c>
       <c r="E189" t="s">
         <v>672</v>
       </c>
       <c r="F189">
-        <v>12.81</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G189">
-        <v>0.08</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -7583,200 +7603,200 @@
         <v>613</v>
       </c>
       <c r="D190">
-        <v>62.85</v>
+        <v>37.38</v>
       </c>
       <c r="E190" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F190">
-        <v>55.44</v>
+        <v>39.12</v>
       </c>
       <c r="G190">
-        <v>-11.79</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>229</v>
+        <v>56</v>
       </c>
       <c r="B191" t="s">
-        <v>499</v>
+        <v>326</v>
       </c>
       <c r="C191" t="s">
         <v>613</v>
       </c>
       <c r="D191">
-        <v>1.94</v>
+        <v>43.8</v>
       </c>
       <c r="E191" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F191">
-        <v>1.91</v>
+        <v>43.36</v>
       </c>
       <c r="G191">
-        <v>-1.55</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B192" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C192" t="s">
         <v>613</v>
       </c>
       <c r="D192">
-        <v>52.48</v>
+        <v>44.15</v>
       </c>
       <c r="E192" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F192">
-        <v>50.93</v>
+        <v>44.75</v>
       </c>
       <c r="G192">
-        <v>-2.95</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>230</v>
+        <v>116</v>
       </c>
       <c r="B193" t="s">
-        <v>500</v>
+        <v>386</v>
       </c>
       <c r="C193" t="s">
         <v>613</v>
       </c>
       <c r="D193">
-        <v>18.95</v>
+        <v>35.11</v>
       </c>
       <c r="E193" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F193">
-        <v>19.13</v>
+        <v>40.71</v>
       </c>
       <c r="G193">
-        <v>0.95</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B194" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C194" t="s">
         <v>613</v>
       </c>
       <c r="D194">
-        <v>57.43</v>
+        <v>12.8</v>
       </c>
       <c r="E194" t="s">
         <v>673</v>
       </c>
       <c r="F194">
-        <v>66.40000000000001</v>
+        <v>12.81</v>
       </c>
       <c r="G194">
-        <v>15.62</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B195" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C195" t="s">
         <v>613</v>
       </c>
       <c r="D195">
-        <v>44.15</v>
+        <v>1.94</v>
       </c>
       <c r="E195" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F195">
-        <v>44.75</v>
+        <v>1.91</v>
       </c>
       <c r="G195">
-        <v>1.36</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="B196" t="s">
-        <v>381</v>
+        <v>502</v>
       </c>
       <c r="C196" t="s">
         <v>613</v>
       </c>
       <c r="D196">
-        <v>35.11</v>
+        <v>62.85</v>
       </c>
       <c r="E196" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F196">
-        <v>40.71</v>
+        <v>55.44</v>
       </c>
       <c r="G196">
-        <v>15.95</v>
+        <v>-11.79</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B197" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C197" t="s">
         <v>613</v>
       </c>
       <c r="D197">
-        <v>37.38</v>
+        <v>52.48</v>
       </c>
       <c r="E197" t="s">
         <v>673</v>
       </c>
       <c r="F197">
-        <v>39.12</v>
+        <v>50.93</v>
       </c>
       <c r="G197">
-        <v>4.65</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="B198" t="s">
-        <v>326</v>
+        <v>503</v>
       </c>
       <c r="C198" t="s">
         <v>613</v>
       </c>
       <c r="D198">
-        <v>43.8</v>
+        <v>18.95</v>
       </c>
       <c r="E198" t="s">
         <v>672</v>
       </c>
       <c r="F198">
-        <v>43.36</v>
+        <v>19.13</v>
       </c>
       <c r="G198">
-        <v>-1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -7790,16 +7810,16 @@
         <v>614</v>
       </c>
       <c r="D199">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E199" t="s">
         <v>674</v>
       </c>
       <c r="F199">
-        <v>57.19</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="G199">
-        <v>12.14</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -7813,16 +7833,16 @@
         <v>614</v>
       </c>
       <c r="D200">
-        <v>17.5</v>
+        <v>16.51</v>
       </c>
       <c r="E200" t="s">
         <v>674</v>
       </c>
       <c r="F200">
-        <v>15.77</v>
+        <v>17.32</v>
       </c>
       <c r="G200">
-        <v>-9.890000000000001</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -7836,16 +7856,16 @@
         <v>614</v>
       </c>
       <c r="D201">
-        <v>99.92</v>
+        <v>67.47</v>
       </c>
       <c r="E201" t="s">
         <v>674</v>
       </c>
       <c r="F201">
-        <v>112.71</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="G201">
-        <v>12.8</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -7859,62 +7879,62 @@
         <v>614</v>
       </c>
       <c r="D202">
-        <v>19.9</v>
+        <v>24.22</v>
       </c>
       <c r="E202" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F202">
-        <v>19.08</v>
+        <v>25.26</v>
       </c>
       <c r="G202">
-        <v>-4.12</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="B203" t="s">
-        <v>508</v>
+        <v>470</v>
       </c>
       <c r="C203" t="s">
         <v>614</v>
       </c>
       <c r="D203">
-        <v>67.65000000000001</v>
+        <v>3.78</v>
       </c>
       <c r="E203" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F203">
-        <v>66.01000000000001</v>
+        <v>4.25</v>
       </c>
       <c r="G203">
-        <v>-2.42</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="B204" t="s">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="C204" t="s">
         <v>614</v>
       </c>
       <c r="D204">
-        <v>3.78</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E204" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F204">
-        <v>4.25</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="G204">
-        <v>12.43</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -7928,16 +7948,16 @@
         <v>614</v>
       </c>
       <c r="D205">
-        <v>67.47</v>
+        <v>19.9</v>
       </c>
       <c r="E205" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F205">
-        <v>66.65000000000001</v>
+        <v>19.08</v>
       </c>
       <c r="G205">
-        <v>-1.22</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -7951,16 +7971,16 @@
         <v>614</v>
       </c>
       <c r="D206">
-        <v>16.51</v>
+        <v>99.92</v>
       </c>
       <c r="E206" t="s">
         <v>674</v>
       </c>
       <c r="F206">
-        <v>17.32</v>
+        <v>112.71</v>
       </c>
       <c r="G206">
-        <v>4.91</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -7974,16 +7994,16 @@
         <v>614</v>
       </c>
       <c r="D207">
-        <v>59</v>
+        <v>17.5</v>
       </c>
       <c r="E207" t="s">
         <v>674</v>
       </c>
       <c r="F207">
-        <v>64.76000000000001</v>
+        <v>15.77</v>
       </c>
       <c r="G207">
-        <v>9.76</v>
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -7997,62 +8017,62 @@
         <v>614</v>
       </c>
       <c r="D208">
-        <v>24.22</v>
+        <v>51</v>
       </c>
       <c r="E208" t="s">
         <v>674</v>
       </c>
       <c r="F208">
-        <v>25.26</v>
+        <v>57.19</v>
       </c>
       <c r="G208">
-        <v>4.29</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="B209" t="s">
-        <v>449</v>
+        <v>513</v>
       </c>
       <c r="C209" t="s">
         <v>615</v>
       </c>
       <c r="D209">
-        <v>54.48</v>
+        <v>72.27</v>
       </c>
       <c r="E209" t="s">
         <v>677</v>
       </c>
       <c r="F209">
-        <v>50.89</v>
+        <v>71.89</v>
       </c>
       <c r="G209">
-        <v>-6.59</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="B210" t="s">
-        <v>513</v>
+        <v>439</v>
       </c>
       <c r="C210" t="s">
         <v>615</v>
       </c>
       <c r="D210">
-        <v>92.05</v>
+        <v>39.5</v>
       </c>
       <c r="E210" t="s">
         <v>677</v>
       </c>
       <c r="F210">
-        <v>100.71</v>
+        <v>41.43</v>
       </c>
       <c r="G210">
-        <v>9.41</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -8066,16 +8086,16 @@
         <v>615</v>
       </c>
       <c r="D211">
-        <v>11.42</v>
+        <v>85</v>
       </c>
       <c r="E211" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F211">
-        <v>11.01</v>
+        <v>72.3</v>
       </c>
       <c r="G211">
-        <v>-3.59</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -8089,62 +8109,62 @@
         <v>615</v>
       </c>
       <c r="D212">
-        <v>283.11</v>
+        <v>28.29</v>
       </c>
       <c r="E212" t="s">
         <v>677</v>
       </c>
       <c r="F212">
-        <v>289</v>
+        <v>27.71</v>
       </c>
       <c r="G212">
-        <v>2.08</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="B213" t="s">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="C213" t="s">
         <v>615</v>
       </c>
       <c r="D213">
-        <v>38.39</v>
+        <v>27.59</v>
       </c>
       <c r="E213" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F213">
-        <v>39.68</v>
+        <v>28.41</v>
       </c>
       <c r="G213">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="B214" t="s">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="C214" t="s">
         <v>615</v>
       </c>
       <c r="D214">
-        <v>27.59</v>
+        <v>38.39</v>
       </c>
       <c r="E214" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F214">
-        <v>28.41</v>
+        <v>39.68</v>
       </c>
       <c r="G214">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -8158,16 +8178,16 @@
         <v>615</v>
       </c>
       <c r="D215">
-        <v>28.29</v>
+        <v>11.42</v>
       </c>
       <c r="E215" t="s">
         <v>677</v>
       </c>
       <c r="F215">
-        <v>27.71</v>
+        <v>11.01</v>
       </c>
       <c r="G215">
-        <v>-2.05</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -8181,39 +8201,39 @@
         <v>615</v>
       </c>
       <c r="D216">
-        <v>85</v>
+        <v>92.05</v>
       </c>
       <c r="E216" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F216">
-        <v>72.3</v>
+        <v>100.71</v>
       </c>
       <c r="G216">
-        <v>-14.94</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B217" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C217" t="s">
         <v>615</v>
       </c>
       <c r="D217">
-        <v>39.5</v>
+        <v>54.48</v>
       </c>
       <c r="E217" t="s">
         <v>677</v>
       </c>
       <c r="F217">
-        <v>41.43</v>
+        <v>50.89</v>
       </c>
       <c r="G217">
-        <v>4.89</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -8227,16 +8247,16 @@
         <v>615</v>
       </c>
       <c r="D218">
-        <v>72.27</v>
+        <v>283.11</v>
       </c>
       <c r="E218" t="s">
         <v>677</v>
       </c>
       <c r="F218">
-        <v>71.89</v>
+        <v>289</v>
       </c>
       <c r="G218">
-        <v>-0.53</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -8250,16 +8270,16 @@
         <v>616</v>
       </c>
       <c r="D219">
-        <v>11.57</v>
+        <v>37.25</v>
       </c>
       <c r="E219" t="s">
         <v>680</v>
       </c>
       <c r="F219">
-        <v>10.3</v>
+        <v>37.11</v>
       </c>
       <c r="G219">
-        <v>-10.98</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -8273,16 +8293,16 @@
         <v>616</v>
       </c>
       <c r="D220">
-        <v>10.51</v>
+        <v>46</v>
       </c>
       <c r="E220" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F220">
-        <v>9.5</v>
+        <v>42.38</v>
       </c>
       <c r="G220">
-        <v>-9.609999999999999</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -8296,16 +8316,16 @@
         <v>616</v>
       </c>
       <c r="D221">
-        <v>9</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="E221" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F221">
-        <v>8.380000000000001</v>
+        <v>77.02</v>
       </c>
       <c r="G221">
-        <v>-6.89</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -8319,16 +8339,16 @@
         <v>616</v>
       </c>
       <c r="D222">
-        <v>13.3</v>
+        <v>14.85</v>
       </c>
       <c r="E222" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="F222">
-        <v>11.65</v>
+        <v>15.38</v>
       </c>
       <c r="G222">
-        <v>-12.41</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -8342,16 +8362,16 @@
         <v>616</v>
       </c>
       <c r="D223">
-        <v>5.87</v>
+        <v>10.52</v>
       </c>
       <c r="E223" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F223">
-        <v>5.85</v>
+        <v>8.66</v>
       </c>
       <c r="G223">
-        <v>-0.34</v>
+        <v>-17.68</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -8365,16 +8385,16 @@
         <v>616</v>
       </c>
       <c r="D224">
-        <v>14.85</v>
+        <v>13.3</v>
       </c>
       <c r="E224" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="F224">
-        <v>15.38</v>
+        <v>11.65</v>
       </c>
       <c r="G224">
-        <v>3.57</v>
+        <v>-12.41</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -8388,16 +8408,16 @@
         <v>616</v>
       </c>
       <c r="D225">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="E225" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F225">
-        <v>42.38</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G225">
-        <v>-7.87</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -8411,16 +8431,16 @@
         <v>616</v>
       </c>
       <c r="D226">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
       <c r="E226" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F226">
-        <v>8.66</v>
+        <v>9.5</v>
       </c>
       <c r="G226">
-        <v>-17.68</v>
+        <v>-9.609999999999999</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -8434,16 +8454,16 @@
         <v>616</v>
       </c>
       <c r="D227">
-        <v>37.25</v>
+        <v>5.87</v>
       </c>
       <c r="E227" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F227">
-        <v>37.11</v>
+        <v>5.85</v>
       </c>
       <c r="G227">
-        <v>-0.38</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -8457,16 +8477,16 @@
         <v>616</v>
       </c>
       <c r="D228">
-        <v>81.34999999999999</v>
+        <v>11.57</v>
       </c>
       <c r="E228" t="s">
         <v>685</v>
       </c>
       <c r="F228">
-        <v>77.02</v>
+        <v>10.3</v>
       </c>
       <c r="G228">
-        <v>-5.32</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -8480,16 +8500,16 @@
         <v>617</v>
       </c>
       <c r="D229">
-        <v>35.5</v>
+        <v>92</v>
       </c>
       <c r="E229" t="s">
         <v>686</v>
       </c>
       <c r="F229">
-        <v>33.87</v>
+        <v>85</v>
       </c>
       <c r="G229">
-        <v>-4.59</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -8503,16 +8523,16 @@
         <v>617</v>
       </c>
       <c r="D230">
-        <v>56.01</v>
+        <v>35.5</v>
       </c>
       <c r="E230" t="s">
         <v>687</v>
       </c>
       <c r="F230">
-        <v>53.66</v>
+        <v>33.87</v>
       </c>
       <c r="G230">
-        <v>-4.2</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -8549,16 +8569,16 @@
         <v>617</v>
       </c>
       <c r="D232">
-        <v>92</v>
+        <v>56.01</v>
       </c>
       <c r="E232" t="s">
         <v>689</v>
       </c>
       <c r="F232">
-        <v>85</v>
+        <v>53.66</v>
       </c>
       <c r="G232">
-        <v>-7.61</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -8575,7 +8595,7 @@
         <v>5.77</v>
       </c>
       <c r="E233" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F233">
         <v>5.89</v>
@@ -8595,16 +8615,16 @@
         <v>617</v>
       </c>
       <c r="D234">
-        <v>5.4</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E234" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F234">
-        <v>5.42</v>
+        <v>11.12</v>
       </c>
       <c r="G234">
-        <v>0.37</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -8618,16 +8638,16 @@
         <v>617</v>
       </c>
       <c r="D235">
-        <v>9.630000000000001</v>
+        <v>35.5</v>
       </c>
       <c r="E235" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F235">
-        <v>11.12</v>
+        <v>36.11</v>
       </c>
       <c r="G235">
-        <v>15.47</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -8641,16 +8661,16 @@
         <v>617</v>
       </c>
       <c r="D236">
-        <v>35.5</v>
+        <v>5.4</v>
       </c>
       <c r="E236" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F236">
-        <v>36.11</v>
+        <v>5.42</v>
       </c>
       <c r="G236">
-        <v>1.72</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -8664,200 +8684,200 @@
         <v>618</v>
       </c>
       <c r="D237">
-        <v>6.12</v>
+        <v>25.95</v>
       </c>
       <c r="E237" t="s">
         <v>690</v>
       </c>
       <c r="F237">
-        <v>6.48</v>
+        <v>27.59</v>
       </c>
       <c r="G237">
-        <v>5.88</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>269</v>
+        <v>206</v>
       </c>
       <c r="B238" t="s">
-        <v>539</v>
+        <v>476</v>
       </c>
       <c r="C238" t="s">
         <v>618</v>
       </c>
       <c r="D238">
-        <v>11.31</v>
+        <v>19.56</v>
       </c>
       <c r="E238" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F238">
-        <v>9.74</v>
+        <v>18.54</v>
       </c>
       <c r="G238">
-        <v>-13.88</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B239" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C239" t="s">
         <v>618</v>
       </c>
       <c r="D239">
-        <v>3.71</v>
+        <v>18.37</v>
       </c>
       <c r="E239" t="s">
         <v>690</v>
       </c>
       <c r="F239">
-        <v>3.84</v>
+        <v>20.45</v>
       </c>
       <c r="G239">
-        <v>3.5</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B240" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C240" t="s">
         <v>618</v>
       </c>
       <c r="D240">
-        <v>98.52</v>
+        <v>53.58</v>
       </c>
       <c r="E240" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F240">
-        <v>92.31</v>
+        <v>52.65</v>
       </c>
       <c r="G240">
-        <v>-6.3</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B241" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C241" t="s">
         <v>618</v>
       </c>
       <c r="D241">
-        <v>7.95</v>
+        <v>6.12</v>
       </c>
       <c r="E241" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="F241">
-        <v>6.13</v>
+        <v>6.48</v>
       </c>
       <c r="G241">
-        <v>-22.89</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B242" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C242" t="s">
         <v>618</v>
       </c>
       <c r="D242">
-        <v>18.37</v>
+        <v>9.84</v>
       </c>
       <c r="E242" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F242">
-        <v>19.04</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G242">
-        <v>3.65</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B243" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C243" t="s">
         <v>618</v>
       </c>
       <c r="D243">
-        <v>53.58</v>
+        <v>98.52</v>
       </c>
       <c r="E243" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F243">
-        <v>52.65</v>
+        <v>92.31</v>
       </c>
       <c r="G243">
-        <v>-1.74</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B244" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C244" t="s">
         <v>618</v>
       </c>
       <c r="D244">
-        <v>18.37</v>
+        <v>7.95</v>
       </c>
       <c r="E244" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F244">
-        <v>20.45</v>
+        <v>6.13</v>
       </c>
       <c r="G244">
-        <v>11.32</v>
+        <v>-22.89</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="B245" t="s">
-        <v>473</v>
+        <v>545</v>
       </c>
       <c r="C245" t="s">
         <v>618</v>
       </c>
       <c r="D245">
-        <v>19.56</v>
+        <v>3.71</v>
       </c>
       <c r="E245" t="s">
         <v>690</v>
       </c>
       <c r="F245">
-        <v>18.54</v>
+        <v>3.84</v>
       </c>
       <c r="G245">
-        <v>-5.21</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -8871,16 +8891,16 @@
         <v>618</v>
       </c>
       <c r="D246">
-        <v>25.95</v>
+        <v>11.31</v>
       </c>
       <c r="E246" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="F246">
-        <v>27.59</v>
+        <v>9.74</v>
       </c>
       <c r="G246">
-        <v>6.32</v>
+        <v>-13.88</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -8894,16 +8914,16 @@
         <v>618</v>
       </c>
       <c r="D247">
-        <v>9.84</v>
+        <v>18.37</v>
       </c>
       <c r="E247" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="F247">
-        <v>9.390000000000001</v>
+        <v>19.04</v>
       </c>
       <c r="G247">
-        <v>-4.57</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -8917,16 +8937,16 @@
         <v>619</v>
       </c>
       <c r="D248">
-        <v>2.53</v>
+        <v>28.95</v>
       </c>
       <c r="E248" t="s">
         <v>695</v>
       </c>
       <c r="F248">
-        <v>2.52</v>
+        <v>31.66</v>
       </c>
       <c r="G248">
-        <v>-0.4</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -8940,16 +8960,16 @@
         <v>619</v>
       </c>
       <c r="D249">
-        <v>5.8</v>
+        <v>12.98</v>
       </c>
       <c r="E249" t="s">
         <v>696</v>
       </c>
       <c r="F249">
-        <v>5.51</v>
+        <v>12.48</v>
       </c>
       <c r="G249">
-        <v>-5</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -8963,16 +8983,16 @@
         <v>619</v>
       </c>
       <c r="D250">
-        <v>30.42</v>
+        <v>28.9</v>
       </c>
       <c r="E250" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F250">
-        <v>31.31</v>
+        <v>28</v>
       </c>
       <c r="G250">
-        <v>2.93</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -8986,16 +9006,16 @@
         <v>619</v>
       </c>
       <c r="D251">
-        <v>12.99</v>
+        <v>66.33</v>
       </c>
       <c r="E251" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F251">
-        <v>12.35</v>
+        <v>69</v>
       </c>
       <c r="G251">
-        <v>-4.93</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -9009,16 +9029,16 @@
         <v>619</v>
       </c>
       <c r="D252">
-        <v>20.13</v>
+        <v>7.15</v>
       </c>
       <c r="E252" t="s">
         <v>695</v>
       </c>
       <c r="F252">
-        <v>20.42</v>
+        <v>7.06</v>
       </c>
       <c r="G252">
-        <v>1.44</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -9032,16 +9052,16 @@
         <v>619</v>
       </c>
       <c r="D253">
-        <v>28.95</v>
+        <v>20.13</v>
       </c>
       <c r="E253" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F253">
-        <v>31.66</v>
+        <v>20.42</v>
       </c>
       <c r="G253">
-        <v>9.359999999999999</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -9055,16 +9075,16 @@
         <v>619</v>
       </c>
       <c r="D254">
-        <v>66.33</v>
+        <v>30.42</v>
       </c>
       <c r="E254" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F254">
-        <v>69</v>
+        <v>31.31</v>
       </c>
       <c r="G254">
-        <v>4.03</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -9078,16 +9098,16 @@
         <v>619</v>
       </c>
       <c r="D255">
-        <v>28.9</v>
+        <v>5.8</v>
       </c>
       <c r="E255" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F255">
-        <v>28</v>
+        <v>5.51</v>
       </c>
       <c r="G255">
-        <v>-3.11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -9101,16 +9121,16 @@
         <v>619</v>
       </c>
       <c r="D256">
-        <v>12.98</v>
+        <v>2.53</v>
       </c>
       <c r="E256" t="s">
         <v>698</v>
       </c>
       <c r="F256">
-        <v>12.48</v>
+        <v>2.52</v>
       </c>
       <c r="G256">
-        <v>-3.85</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -9124,16 +9144,16 @@
         <v>619</v>
       </c>
       <c r="D257">
-        <v>7.15</v>
+        <v>12.99</v>
       </c>
       <c r="E257" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F257">
-        <v>7.06</v>
+        <v>12.35</v>
       </c>
       <c r="G257">
-        <v>-1.26</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -9147,16 +9167,16 @@
         <v>620</v>
       </c>
       <c r="D258">
-        <v>33.6</v>
+        <v>53.4</v>
       </c>
       <c r="E258" t="s">
         <v>699</v>
       </c>
       <c r="F258">
-        <v>36.82</v>
+        <v>59.38</v>
       </c>
       <c r="G258">
-        <v>9.58</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -9170,16 +9190,16 @@
         <v>620</v>
       </c>
       <c r="D259">
-        <v>65</v>
+        <v>8.83</v>
       </c>
       <c r="E259" t="s">
         <v>700</v>
       </c>
       <c r="F259">
-        <v>63.89</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G259">
-        <v>-1.71</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -9193,85 +9213,85 @@
         <v>620</v>
       </c>
       <c r="D260">
-        <v>19.3</v>
+        <v>5.77</v>
       </c>
       <c r="E260" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F260">
-        <v>19.19</v>
+        <v>5.88</v>
       </c>
       <c r="G260">
-        <v>-0.57</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>291</v>
+        <v>228</v>
       </c>
       <c r="B261" t="s">
-        <v>561</v>
+        <v>498</v>
       </c>
       <c r="C261" t="s">
         <v>620</v>
       </c>
       <c r="D261">
-        <v>22.21</v>
+        <v>23.6</v>
       </c>
       <c r="E261" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F261">
-        <v>22.99</v>
+        <v>23.77</v>
       </c>
       <c r="G261">
-        <v>3.51</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B262" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C262" t="s">
         <v>620</v>
       </c>
       <c r="D262">
-        <v>20.33</v>
+        <v>22.54</v>
       </c>
       <c r="E262" t="s">
         <v>701</v>
       </c>
       <c r="F262">
-        <v>20.96</v>
+        <v>24.82</v>
       </c>
       <c r="G262">
-        <v>3.1</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="B263" t="s">
-        <v>503</v>
+        <v>562</v>
       </c>
       <c r="C263" t="s">
         <v>620</v>
       </c>
       <c r="D263">
-        <v>23.6</v>
+        <v>20.33</v>
       </c>
       <c r="E263" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F263">
-        <v>23.77</v>
+        <v>20.96</v>
       </c>
       <c r="G263">
-        <v>0.72</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -9285,16 +9305,16 @@
         <v>620</v>
       </c>
       <c r="D264">
-        <v>8.83</v>
+        <v>33.6</v>
       </c>
       <c r="E264" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F264">
-        <v>8.779999999999999</v>
+        <v>36.82</v>
       </c>
       <c r="G264">
-        <v>-0.57</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -9308,16 +9328,16 @@
         <v>620</v>
       </c>
       <c r="D265">
-        <v>5.77</v>
+        <v>65</v>
       </c>
       <c r="E265" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F265">
-        <v>5.88</v>
+        <v>63.89</v>
       </c>
       <c r="G265">
-        <v>1.91</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -9331,16 +9351,16 @@
         <v>620</v>
       </c>
       <c r="D266">
-        <v>53.4</v>
+        <v>22.21</v>
       </c>
       <c r="E266" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F266">
-        <v>59.38</v>
+        <v>22.99</v>
       </c>
       <c r="G266">
-        <v>11.2</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -9354,16 +9374,16 @@
         <v>620</v>
       </c>
       <c r="D267">
-        <v>22.54</v>
+        <v>19.3</v>
       </c>
       <c r="E267" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F267">
-        <v>24.82</v>
+        <v>19.19</v>
       </c>
       <c r="G267">
-        <v>10.12</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -9414,10 +9434,10 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B270" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C270" t="s">
         <v>621</v>
@@ -9469,16 +9489,16 @@
         <v>621</v>
       </c>
       <c r="D272">
-        <v>21.59</v>
+        <v>28.03</v>
       </c>
       <c r="E272" t="s">
         <v>703</v>
       </c>
       <c r="F272">
-        <v>23.13</v>
+        <v>26.98</v>
       </c>
       <c r="G272">
-        <v>7.13</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -9492,108 +9512,108 @@
         <v>621</v>
       </c>
       <c r="D273">
-        <v>20.66</v>
+        <v>21.59</v>
       </c>
       <c r="E273" t="s">
         <v>703</v>
       </c>
       <c r="F273">
-        <v>18.1</v>
+        <v>23.13</v>
       </c>
       <c r="G273">
-        <v>-12.39</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="B274" t="s">
-        <v>515</v>
+        <v>572</v>
       </c>
       <c r="C274" t="s">
         <v>621</v>
       </c>
       <c r="D274">
-        <v>206.01</v>
+        <v>20.66</v>
       </c>
       <c r="E274" t="s">
         <v>703</v>
       </c>
       <c r="F274">
-        <v>242.63</v>
+        <v>18.1</v>
       </c>
       <c r="G274">
-        <v>17.78</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="B275" t="s">
-        <v>572</v>
+        <v>519</v>
       </c>
       <c r="C275" t="s">
         <v>621</v>
       </c>
       <c r="D275">
-        <v>11.6</v>
+        <v>206.01</v>
       </c>
       <c r="E275" t="s">
         <v>703</v>
       </c>
       <c r="F275">
-        <v>11.89</v>
+        <v>242.63</v>
       </c>
       <c r="G275">
-        <v>2.5</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>117</v>
+        <v>303</v>
       </c>
       <c r="B276" t="s">
-        <v>387</v>
+        <v>573</v>
       </c>
       <c r="C276" t="s">
         <v>621</v>
       </c>
       <c r="D276">
-        <v>73.98999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="E276" t="s">
         <v>703</v>
       </c>
       <c r="F276">
-        <v>86.3</v>
+        <v>11.89</v>
       </c>
       <c r="G276">
-        <v>16.64</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>303</v>
+        <v>123</v>
       </c>
       <c r="B277" t="s">
-        <v>573</v>
+        <v>393</v>
       </c>
       <c r="C277" t="s">
         <v>621</v>
       </c>
       <c r="D277">
-        <v>28.03</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E277" t="s">
         <v>703</v>
       </c>
       <c r="F277">
-        <v>26.98</v>
+        <v>86.3</v>
       </c>
       <c r="G277">
-        <v>-3.75</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -9607,16 +9627,16 @@
         <v>622</v>
       </c>
       <c r="D278">
-        <v>88.81999999999999</v>
+        <v>233</v>
       </c>
       <c r="E278" t="s">
         <v>705</v>
       </c>
       <c r="F278">
-        <v>77.26000000000001</v>
+        <v>245.3</v>
       </c>
       <c r="G278">
-        <v>-13.02</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -9630,200 +9650,200 @@
         <v>622</v>
       </c>
       <c r="D279">
-        <v>6.39</v>
+        <v>141.34</v>
       </c>
       <c r="E279" t="s">
         <v>705</v>
       </c>
       <c r="F279">
-        <v>5.99</v>
+        <v>133.73</v>
       </c>
       <c r="G279">
-        <v>-6.26</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="B280" t="s">
-        <v>576</v>
+        <v>382</v>
       </c>
       <c r="C280" t="s">
         <v>622</v>
       </c>
       <c r="D280">
-        <v>13.44</v>
+        <v>107.92</v>
       </c>
       <c r="E280" t="s">
         <v>705</v>
       </c>
       <c r="F280">
-        <v>13.27</v>
+        <v>107.21</v>
       </c>
       <c r="G280">
-        <v>-1.26</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B281" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C281" t="s">
         <v>622</v>
       </c>
       <c r="D281">
-        <v>5.12</v>
+        <v>15</v>
       </c>
       <c r="E281" t="s">
         <v>705</v>
       </c>
       <c r="F281">
-        <v>4.13</v>
+        <v>10.69</v>
       </c>
       <c r="G281">
-        <v>-19.34</v>
+        <v>-28.73</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B282" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C282" t="s">
         <v>622</v>
       </c>
       <c r="D282">
-        <v>246.4</v>
+        <v>5.55</v>
       </c>
       <c r="E282" t="s">
         <v>705</v>
       </c>
       <c r="F282">
-        <v>259.59</v>
+        <v>5.03</v>
       </c>
       <c r="G282">
-        <v>5.35</v>
+        <v>-9.369999999999999</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B283" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C283" t="s">
         <v>622</v>
       </c>
       <c r="D283">
-        <v>15</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="E283" t="s">
         <v>705</v>
       </c>
       <c r="F283">
-        <v>10.69</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="G283">
-        <v>-28.73</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B284" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C284" t="s">
         <v>622</v>
       </c>
       <c r="D284">
-        <v>5.55</v>
+        <v>6.39</v>
       </c>
       <c r="E284" t="s">
         <v>705</v>
       </c>
       <c r="F284">
-        <v>5.03</v>
+        <v>5.99</v>
       </c>
       <c r="G284">
-        <v>-9.369999999999999</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B285" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C285" t="s">
         <v>622</v>
       </c>
       <c r="D285">
-        <v>141.34</v>
+        <v>5.12</v>
       </c>
       <c r="E285" t="s">
         <v>705</v>
       </c>
       <c r="F285">
-        <v>133.73</v>
+        <v>4.13</v>
       </c>
       <c r="G285">
-        <v>-5.38</v>
+        <v>-19.34</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B286" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C286" t="s">
         <v>622</v>
       </c>
       <c r="D286">
-        <v>233</v>
+        <v>13.44</v>
       </c>
       <c r="E286" t="s">
         <v>705</v>
       </c>
       <c r="F286">
-        <v>245.3</v>
+        <v>13.27</v>
       </c>
       <c r="G286">
-        <v>5.28</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>110</v>
+        <v>312</v>
       </c>
       <c r="B287" t="s">
-        <v>380</v>
+        <v>582</v>
       </c>
       <c r="C287" t="s">
         <v>622</v>
       </c>
       <c r="D287">
-        <v>107.92</v>
+        <v>246.4</v>
       </c>
       <c r="E287" t="s">
         <v>705</v>
       </c>
       <c r="F287">
-        <v>107.21</v>
+        <v>259.59</v>
       </c>
       <c r="G287">
-        <v>-0.66</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -9860,16 +9880,16 @@
         <v>623</v>
       </c>
       <c r="D289">
-        <v>4.15</v>
+        <v>27.84</v>
       </c>
       <c r="E289" t="s">
         <v>706</v>
       </c>
       <c r="F289">
-        <v>5.67</v>
+        <v>27.5</v>
       </c>
       <c r="G289">
-        <v>36.63</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -9883,16 +9903,16 @@
         <v>623</v>
       </c>
       <c r="D290">
-        <v>27.84</v>
+        <v>4.15</v>
       </c>
       <c r="E290" t="s">
         <v>706</v>
       </c>
       <c r="F290">
-        <v>27.5</v>
+        <v>5.67</v>
       </c>
       <c r="G290">
-        <v>-1.22</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -9920,33 +9940,33 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B292" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C292" t="s">
         <v>623</v>
       </c>
       <c r="D292">
-        <v>12.4</v>
+        <v>64.66</v>
       </c>
       <c r="E292" t="s">
         <v>706</v>
       </c>
       <c r="F292">
-        <v>11.98</v>
+        <v>61.77</v>
       </c>
       <c r="G292">
-        <v>-3.39</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B293" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C293" t="s">
         <v>623</v>
@@ -9966,10 +9986,10 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B294" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C294" t="s">
         <v>623</v>
@@ -9989,148 +10009,148 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B295" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C295" t="s">
         <v>623</v>
       </c>
       <c r="D295">
-        <v>3.53</v>
+        <v>4.87</v>
       </c>
       <c r="E295" t="s">
         <v>706</v>
       </c>
       <c r="F295">
-        <v>3.42</v>
+        <v>5.04</v>
       </c>
       <c r="G295">
-        <v>-3.12</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B296" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C296" t="s">
         <v>623</v>
       </c>
       <c r="D296">
-        <v>12.35</v>
+        <v>3.53</v>
       </c>
       <c r="E296" t="s">
         <v>706</v>
       </c>
       <c r="F296">
-        <v>12.66</v>
+        <v>3.42</v>
       </c>
       <c r="G296">
-        <v>2.51</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B297" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C297" t="s">
         <v>623</v>
       </c>
       <c r="D297">
-        <v>64.66</v>
+        <v>12.35</v>
       </c>
       <c r="E297" t="s">
         <v>706</v>
       </c>
       <c r="F297">
-        <v>61.77</v>
+        <v>12.66</v>
       </c>
       <c r="G297">
-        <v>-4.47</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B298" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C298" t="s">
         <v>623</v>
       </c>
       <c r="D298">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="E298" t="s">
         <v>706</v>
       </c>
       <c r="F298">
-        <v>12.81</v>
+        <v>11.98</v>
       </c>
       <c r="G298">
-        <v>5.87</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B299" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C299" t="s">
         <v>623</v>
       </c>
       <c r="D299">
-        <v>4.15</v>
+        <v>12.1</v>
       </c>
       <c r="E299" t="s">
         <v>706</v>
       </c>
       <c r="F299">
-        <v>5.67</v>
+        <v>12.81</v>
       </c>
       <c r="G299">
-        <v>36.63</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B300" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C300" t="s">
         <v>623</v>
       </c>
       <c r="D300">
-        <v>27.84</v>
+        <v>12.4</v>
       </c>
       <c r="E300" t="s">
         <v>706</v>
       </c>
       <c r="F300">
-        <v>27.5</v>
+        <v>11.98</v>
       </c>
       <c r="G300">
-        <v>-1.22</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B301" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C301" t="s">
         <v>623</v>
@@ -10173,24 +10193,208 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B303" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C303" t="s">
         <v>623</v>
       </c>
       <c r="D303">
-        <v>4.87</v>
+        <v>3.53</v>
       </c>
       <c r="E303" t="s">
         <v>706</v>
       </c>
       <c r="F303">
+        <v>3.42</v>
+      </c>
+      <c r="G303">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" t="s">
+        <v>318</v>
+      </c>
+      <c r="B304" t="s">
+        <v>588</v>
+      </c>
+      <c r="C304" t="s">
+        <v>623</v>
+      </c>
+      <c r="D304">
+        <v>12.35</v>
+      </c>
+      <c r="E304" t="s">
+        <v>706</v>
+      </c>
+      <c r="F304">
+        <v>12.66</v>
+      </c>
+      <c r="G304">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" t="s">
+        <v>317</v>
+      </c>
+      <c r="B305" t="s">
+        <v>587</v>
+      </c>
+      <c r="C305" t="s">
+        <v>623</v>
+      </c>
+      <c r="D305">
+        <v>64.66</v>
+      </c>
+      <c r="E305" t="s">
+        <v>706</v>
+      </c>
+      <c r="F305">
+        <v>61.77</v>
+      </c>
+      <c r="G305">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" t="s">
+        <v>316</v>
+      </c>
+      <c r="B306" t="s">
+        <v>586</v>
+      </c>
+      <c r="C306" t="s">
+        <v>623</v>
+      </c>
+      <c r="D306">
+        <v>12.1</v>
+      </c>
+      <c r="E306" t="s">
+        <v>706</v>
+      </c>
+      <c r="F306">
+        <v>12.81</v>
+      </c>
+      <c r="G306">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" t="s">
+        <v>315</v>
+      </c>
+      <c r="B307" t="s">
+        <v>585</v>
+      </c>
+      <c r="C307" t="s">
+        <v>623</v>
+      </c>
+      <c r="D307">
+        <v>4.15</v>
+      </c>
+      <c r="E307" t="s">
+        <v>706</v>
+      </c>
+      <c r="F307">
+        <v>5.67</v>
+      </c>
+      <c r="G307">
+        <v>36.63</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" t="s">
+        <v>314</v>
+      </c>
+      <c r="B308" t="s">
+        <v>584</v>
+      </c>
+      <c r="C308" t="s">
+        <v>623</v>
+      </c>
+      <c r="D308">
+        <v>27.84</v>
+      </c>
+      <c r="E308" t="s">
+        <v>706</v>
+      </c>
+      <c r="F308">
+        <v>27.5</v>
+      </c>
+      <c r="G308">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" t="s">
+        <v>315</v>
+      </c>
+      <c r="B309" t="s">
+        <v>585</v>
+      </c>
+      <c r="C309" t="s">
+        <v>623</v>
+      </c>
+      <c r="D309">
+        <v>4.15</v>
+      </c>
+      <c r="E309" t="s">
+        <v>706</v>
+      </c>
+      <c r="F309">
+        <v>5.67</v>
+      </c>
+      <c r="G309">
+        <v>36.63</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" t="s">
+        <v>314</v>
+      </c>
+      <c r="B310" t="s">
+        <v>584</v>
+      </c>
+      <c r="C310" t="s">
+        <v>623</v>
+      </c>
+      <c r="D310">
+        <v>27.84</v>
+      </c>
+      <c r="E310" t="s">
+        <v>706</v>
+      </c>
+      <c r="F310">
+        <v>27.5</v>
+      </c>
+      <c r="G310">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" t="s">
+        <v>320</v>
+      </c>
+      <c r="B311" t="s">
+        <v>590</v>
+      </c>
+      <c r="C311" t="s">
+        <v>623</v>
+      </c>
+      <c r="D311">
+        <v>4.87</v>
+      </c>
+      <c r="E311" t="s">
+        <v>706</v>
+      </c>
+      <c r="F311">
         <v>5.04</v>
       </c>
-      <c r="G303">
+      <c r="G311">
         <v>3.49</v>
       </c>
     </row>

--- a/backtest/5日周期交易计划_2026_回测结果.xlsx
+++ b/backtest/5日周期交易计划_2026_回测结果.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="707">
   <si>
     <t>指标</t>
   </si>
@@ -195,66 +195,69 @@
     <t>688787</t>
   </si>
   <si>
+    <t>601339</t>
+  </si>
+  <si>
+    <t>600783</t>
+  </si>
+  <si>
+    <t>688031</t>
+  </si>
+  <si>
+    <t>002517</t>
+  </si>
+  <si>
+    <t>603966</t>
+  </si>
+  <si>
+    <t>688248</t>
+  </si>
+  <si>
     <t>600828</t>
   </si>
   <si>
-    <t>688248</t>
-  </si>
-  <si>
-    <t>603966</t>
-  </si>
-  <si>
     <t>601116</t>
   </si>
   <si>
-    <t>002517</t>
-  </si>
-  <si>
-    <t>688031</t>
-  </si>
-  <si>
-    <t>600783</t>
-  </si>
-  <si>
-    <t>601339</t>
-  </si>
-  <si>
     <t>300986</t>
   </si>
   <si>
+    <t>001360</t>
+  </si>
+  <si>
+    <t>001337</t>
+  </si>
+  <si>
+    <t>300835</t>
+  </si>
+  <si>
+    <t>603163</t>
+  </si>
+  <si>
+    <t>605287</t>
+  </si>
+  <si>
+    <t>605080</t>
+  </si>
+  <si>
+    <t>600686</t>
+  </si>
+  <si>
+    <t>688628</t>
+  </si>
+  <si>
     <t>603949</t>
   </si>
   <si>
-    <t>688628</t>
-  </si>
-  <si>
-    <t>600686</t>
-  </si>
-  <si>
-    <t>605080</t>
-  </si>
-  <si>
     <t>688084</t>
   </si>
   <si>
-    <t>605287</t>
-  </si>
-  <si>
-    <t>001360</t>
-  </si>
-  <si>
-    <t>603163</t>
-  </si>
-  <si>
-    <t>300835</t>
-  </si>
-  <si>
-    <t>001337</t>
-  </si>
-  <si>
     <t>601615</t>
   </si>
   <si>
+    <t>002658</t>
+  </si>
+  <si>
     <t>000968</t>
   </si>
   <si>
@@ -264,9 +267,6 @@
     <t>688210</t>
   </si>
   <si>
-    <t>002658</t>
-  </si>
-  <si>
     <t>601225</t>
   </si>
   <si>
@@ -279,94 +279,97 @@
     <t>002995</t>
   </si>
   <si>
+    <t>688367</t>
+  </si>
+  <si>
+    <t>000599</t>
+  </si>
+  <si>
+    <t>603103</t>
+  </si>
+  <si>
+    <t>688070</t>
+  </si>
+  <si>
+    <t>601702</t>
+  </si>
+  <si>
+    <t>601598</t>
+  </si>
+  <si>
+    <t>600133</t>
+  </si>
+  <si>
+    <t>603960</t>
+  </si>
+  <si>
+    <t>002457</t>
+  </si>
+  <si>
     <t>000089</t>
   </si>
   <si>
-    <t>002457</t>
-  </si>
-  <si>
-    <t>603960</t>
-  </si>
-  <si>
-    <t>600133</t>
-  </si>
-  <si>
-    <t>601598</t>
-  </si>
-  <si>
-    <t>601702</t>
-  </si>
-  <si>
-    <t>000599</t>
-  </si>
-  <si>
-    <t>688367</t>
-  </si>
-  <si>
-    <t>688070</t>
-  </si>
-  <si>
-    <t>603103</t>
+    <t>603334</t>
+  </si>
+  <si>
+    <t>603301</t>
+  </si>
+  <si>
+    <t>603232</t>
+  </si>
+  <si>
+    <t>688025</t>
+  </si>
+  <si>
+    <t>002441</t>
+  </si>
+  <si>
+    <t>688312</t>
+  </si>
+  <si>
+    <t>001335</t>
+  </si>
+  <si>
+    <t>603626</t>
+  </si>
+  <si>
+    <t>603150</t>
   </si>
   <si>
     <t>001326</t>
   </si>
   <si>
-    <t>603150</t>
-  </si>
-  <si>
-    <t>603626</t>
-  </si>
-  <si>
-    <t>001335</t>
-  </si>
-  <si>
-    <t>688312</t>
-  </si>
-  <si>
-    <t>002441</t>
-  </si>
-  <si>
-    <t>688025</t>
-  </si>
-  <si>
-    <t>603232</t>
-  </si>
-  <si>
-    <t>603301</t>
-  </si>
-  <si>
-    <t>603334</t>
+    <t>002937</t>
+  </si>
+  <si>
+    <t>001896</t>
+  </si>
+  <si>
+    <t>002028</t>
+  </si>
+  <si>
+    <t>603057</t>
+  </si>
+  <si>
+    <t>605289</t>
+  </si>
+  <si>
+    <t>001309</t>
+  </si>
+  <si>
+    <t>301160</t>
+  </si>
+  <si>
+    <t>300831</t>
   </si>
   <si>
     <t>601872</t>
   </si>
   <si>
-    <t>300831</t>
-  </si>
-  <si>
-    <t>301160</t>
-  </si>
-  <si>
-    <t>001309</t>
-  </si>
-  <si>
     <t>002380</t>
   </si>
   <si>
-    <t>605289</t>
-  </si>
-  <si>
-    <t>603057</t>
-  </si>
-  <si>
-    <t>002028</t>
-  </si>
-  <si>
-    <t>001896</t>
-  </si>
-  <si>
-    <t>002937</t>
+    <t>003018</t>
   </si>
   <si>
     <t>688668</t>
@@ -381,9 +384,6 @@
     <t>002545</t>
   </si>
   <si>
-    <t>003018</t>
-  </si>
-  <si>
     <t>600715</t>
   </si>
   <si>
@@ -396,27 +396,27 @@
     <t>600649</t>
   </si>
   <si>
+    <t>301536</t>
+  </si>
+  <si>
+    <t>301032</t>
+  </si>
+  <si>
+    <t>601789</t>
+  </si>
+  <si>
+    <t>301308</t>
+  </si>
+  <si>
+    <t>605268</t>
+  </si>
+  <si>
+    <t>300257</t>
+  </si>
+  <si>
     <t>300461</t>
   </si>
   <si>
-    <t>301308</t>
-  </si>
-  <si>
-    <t>300257</t>
-  </si>
-  <si>
-    <t>605268</t>
-  </si>
-  <si>
-    <t>601789</t>
-  </si>
-  <si>
-    <t>301032</t>
-  </si>
-  <si>
-    <t>301536</t>
-  </si>
-  <si>
     <t>300085</t>
   </si>
   <si>
@@ -441,25 +441,28 @@
     <t>688800</t>
   </si>
   <si>
+    <t>603833</t>
+  </si>
+  <si>
+    <t>688267</t>
+  </si>
+  <si>
+    <t>603165</t>
+  </si>
+  <si>
+    <t>605077</t>
+  </si>
+  <si>
+    <t>301093</t>
+  </si>
+  <si>
     <t>001333</t>
   </si>
   <si>
-    <t>301093</t>
-  </si>
-  <si>
     <t>601128</t>
   </si>
   <si>
-    <t>603165</t>
-  </si>
-  <si>
-    <t>605077</t>
-  </si>
-  <si>
-    <t>688267</t>
-  </si>
-  <si>
-    <t>603833</t>
+    <t>603585</t>
   </si>
   <si>
     <t>002035</t>
@@ -477,9 +480,6 @@
     <t>300440</t>
   </si>
   <si>
-    <t>603585</t>
-  </si>
-  <si>
     <t>301529</t>
   </si>
   <si>
@@ -489,115 +489,124 @@
     <t>603588</t>
   </si>
   <si>
+    <t>600545</t>
+  </si>
+  <si>
+    <t>002386</t>
+  </si>
+  <si>
+    <t>300179</t>
+  </si>
+  <si>
+    <t>603988</t>
+  </si>
+  <si>
+    <t>002624</t>
+  </si>
+  <si>
+    <t>301326</t>
+  </si>
+  <si>
     <t>002008</t>
   </si>
   <si>
+    <t>301310</t>
+  </si>
+  <si>
+    <t>600654</t>
+  </si>
+  <si>
     <t>300870</t>
   </si>
   <si>
-    <t>600654</t>
-  </si>
-  <si>
-    <t>301326</t>
-  </si>
-  <si>
-    <t>301310</t>
-  </si>
-  <si>
-    <t>603988</t>
-  </si>
-  <si>
-    <t>002386</t>
-  </si>
-  <si>
-    <t>002624</t>
-  </si>
-  <si>
-    <t>300179</t>
-  </si>
-  <si>
-    <t>600545</t>
+    <t>300866</t>
+  </si>
+  <si>
+    <t>600572</t>
+  </si>
+  <si>
+    <t>002667</t>
+  </si>
+  <si>
+    <t>600749</t>
+  </si>
+  <si>
+    <t>603682</t>
+  </si>
+  <si>
+    <t>603698</t>
+  </si>
+  <si>
+    <t>603171</t>
   </si>
   <si>
     <t>002853</t>
   </si>
   <si>
-    <t>603171</t>
-  </si>
-  <si>
-    <t>603698</t>
-  </si>
-  <si>
     <t>002787</t>
   </si>
   <si>
-    <t>600749</t>
-  </si>
-  <si>
-    <t>603682</t>
-  </si>
-  <si>
-    <t>002667</t>
-  </si>
-  <si>
-    <t>600572</t>
-  </si>
-  <si>
-    <t>300866</t>
+    <t>301611</t>
+  </si>
+  <si>
+    <t>301133</t>
+  </si>
+  <si>
+    <t>600156</t>
+  </si>
+  <si>
+    <t>000811</t>
+  </si>
+  <si>
+    <t>002803</t>
+  </si>
+  <si>
+    <t>600736</t>
+  </si>
+  <si>
+    <t>300687</t>
   </si>
   <si>
     <t>300539</t>
   </si>
   <si>
-    <t>300687</t>
-  </si>
-  <si>
-    <t>600736</t>
-  </si>
-  <si>
     <t>002975</t>
   </si>
   <si>
-    <t>002803</t>
-  </si>
-  <si>
-    <t>000811</t>
-  </si>
-  <si>
-    <t>600156</t>
-  </si>
-  <si>
-    <t>301133</t>
-  </si>
-  <si>
-    <t>301611</t>
+    <t>002831</t>
+  </si>
+  <si>
+    <t>002631</t>
+  </si>
+  <si>
+    <t>300905</t>
+  </si>
+  <si>
+    <t>300842</t>
+  </si>
+  <si>
+    <t>002181</t>
+  </si>
+  <si>
+    <t>603045</t>
+  </si>
+  <si>
+    <t>603931</t>
   </si>
   <si>
     <t>000672</t>
   </si>
   <si>
-    <t>603931</t>
-  </si>
-  <si>
     <t>002484</t>
   </si>
   <si>
-    <t>603045</t>
-  </si>
-  <si>
-    <t>002181</t>
-  </si>
-  <si>
-    <t>300842</t>
-  </si>
-  <si>
-    <t>300905</t>
-  </si>
-  <si>
-    <t>002631</t>
-  </si>
-  <si>
-    <t>002831</t>
+    <t>002782</t>
+  </si>
+  <si>
+    <t>002303</t>
+  </si>
+  <si>
+    <t>300749</t>
   </si>
   <si>
     <t>002965</t>
@@ -606,21 +615,12 @@
     <t>603052</t>
   </si>
   <si>
+    <t>600381</t>
+  </si>
+  <si>
     <t>688001</t>
   </si>
   <si>
-    <t>300749</t>
-  </si>
-  <si>
-    <t>600381</t>
-  </si>
-  <si>
-    <t>002782</t>
-  </si>
-  <si>
-    <t>002303</t>
-  </si>
-  <si>
     <t>002489</t>
   </si>
   <si>
@@ -642,130 +642,145 @@
     <t>688130</t>
   </si>
   <si>
+    <t>002993</t>
+  </si>
+  <si>
+    <t>605066</t>
+  </si>
+  <si>
+    <t>600162</t>
+  </si>
+  <si>
+    <t>002072</t>
+  </si>
+  <si>
+    <t>000509</t>
+  </si>
+  <si>
+    <t>002655</t>
+  </si>
+  <si>
+    <t>301588</t>
+  </si>
+  <si>
+    <t>300868</t>
+  </si>
+  <si>
     <t>002465</t>
   </si>
   <si>
-    <t>002655</t>
-  </si>
-  <si>
-    <t>300868</t>
-  </si>
-  <si>
     <t>603661</t>
   </si>
   <si>
-    <t>301588</t>
-  </si>
-  <si>
-    <t>002072</t>
-  </si>
-  <si>
-    <t>600162</t>
-  </si>
-  <si>
-    <t>000509</t>
-  </si>
-  <si>
-    <t>605066</t>
-  </si>
-  <si>
-    <t>002993</t>
+    <t>002404</t>
+  </si>
+  <si>
+    <t>002951</t>
+  </si>
+  <si>
+    <t>001226</t>
+  </si>
+  <si>
+    <t>002125</t>
   </si>
   <si>
     <t>603330</t>
   </si>
   <si>
+    <t>002314</t>
+  </si>
+  <si>
     <t>002830</t>
   </si>
   <si>
-    <t>002314</t>
-  </si>
-  <si>
     <t>002096</t>
   </si>
   <si>
     <t>300881</t>
   </si>
   <si>
-    <t>002951</t>
-  </si>
-  <si>
-    <t>001226</t>
-  </si>
-  <si>
-    <t>002125</t>
-  </si>
-  <si>
-    <t>002404</t>
+    <t>000048</t>
+  </si>
+  <si>
+    <t>002982</t>
+  </si>
+  <si>
+    <t>603938</t>
+  </si>
+  <si>
+    <t>601588</t>
   </si>
   <si>
     <t>688056</t>
   </si>
   <si>
+    <t>002903</t>
+  </si>
+  <si>
     <t>300656</t>
   </si>
   <si>
-    <t>002903</t>
-  </si>
-  <si>
-    <t>002982</t>
-  </si>
-  <si>
-    <t>601588</t>
-  </si>
-  <si>
-    <t>603938</t>
-  </si>
-  <si>
-    <t>000048</t>
+    <t>300769</t>
+  </si>
+  <si>
+    <t>600026</t>
+  </si>
+  <si>
+    <t>603618</t>
+  </si>
+  <si>
+    <t>300903</t>
+  </si>
+  <si>
+    <t>600110</t>
+  </si>
+  <si>
+    <t>002913</t>
+  </si>
+  <si>
+    <t>002972</t>
+  </si>
+  <si>
+    <t>001696</t>
   </si>
   <si>
     <t>603738</t>
   </si>
   <si>
-    <t>002972</t>
-  </si>
-  <si>
-    <t>002913</t>
-  </si>
-  <si>
-    <t>001696</t>
-  </si>
-  <si>
-    <t>300769</t>
-  </si>
-  <si>
-    <t>600026</t>
-  </si>
-  <si>
-    <t>300903</t>
-  </si>
-  <si>
-    <t>600110</t>
-  </si>
-  <si>
-    <t>603618</t>
+    <t>603407</t>
+  </si>
+  <si>
+    <t>002440</t>
+  </si>
+  <si>
+    <t>300489</t>
+  </si>
+  <si>
+    <t>301248</t>
   </si>
   <si>
     <t>002990</t>
   </si>
   <si>
-    <t>301248</t>
+    <t>002976</t>
   </si>
   <si>
     <t>002558</t>
   </si>
   <si>
-    <t>002976</t>
-  </si>
-  <si>
-    <t>002440</t>
-  </si>
-  <si>
-    <t>603407</t>
-  </si>
-  <si>
-    <t>300489</t>
+    <t>000810</t>
+  </si>
+  <si>
+    <t>002342</t>
+  </si>
+  <si>
+    <t>603956</t>
+  </si>
+  <si>
+    <t>002693</t>
+  </si>
+  <si>
+    <t>002459</t>
   </si>
   <si>
     <t>002714</t>
@@ -774,213 +789,198 @@
     <t>301382</t>
   </si>
   <si>
+    <t>603477</t>
+  </si>
+  <si>
+    <t>600630</t>
+  </si>
+  <si>
     <t>002779</t>
   </si>
   <si>
-    <t>603477</t>
-  </si>
-  <si>
-    <t>600630</t>
-  </si>
-  <si>
-    <t>000810</t>
-  </si>
-  <si>
-    <t>002459</t>
-  </si>
-  <si>
-    <t>002693</t>
-  </si>
-  <si>
-    <t>603956</t>
-  </si>
-  <si>
-    <t>002342</t>
+    <t>002274</t>
+  </si>
+  <si>
+    <t>688069</t>
+  </si>
+  <si>
+    <t>000779</t>
+  </si>
+  <si>
+    <t>000731</t>
+  </si>
+  <si>
+    <t>300909</t>
+  </si>
+  <si>
+    <t>605118</t>
   </si>
   <si>
     <t>000977</t>
   </si>
   <si>
-    <t>605118</t>
-  </si>
-  <si>
     <t>603139</t>
   </si>
   <si>
-    <t>300909</t>
-  </si>
-  <si>
-    <t>000731</t>
-  </si>
-  <si>
-    <t>000779</t>
-  </si>
-  <si>
-    <t>688069</t>
-  </si>
-  <si>
-    <t>002274</t>
+    <t>002900</t>
+  </si>
+  <si>
+    <t>605178</t>
+  </si>
+  <si>
+    <t>002677</t>
+  </si>
+  <si>
+    <t>600746</t>
+  </si>
+  <si>
+    <t>600602</t>
   </si>
   <si>
     <t>002128</t>
   </si>
   <si>
+    <t>688485</t>
+  </si>
+  <si>
     <t>002379</t>
   </si>
   <si>
-    <t>688485</t>
-  </si>
-  <si>
-    <t>600746</t>
+    <t>000959</t>
   </si>
   <si>
     <t>300227</t>
   </si>
   <si>
-    <t>605178</t>
-  </si>
-  <si>
-    <t>002677</t>
-  </si>
-  <si>
-    <t>000959</t>
-  </si>
-  <si>
-    <t>002900</t>
-  </si>
-  <si>
-    <t>600602</t>
+    <t>688078</t>
+  </si>
+  <si>
+    <t>600322</t>
+  </si>
+  <si>
+    <t>000862</t>
+  </si>
+  <si>
+    <t>001258</t>
+  </si>
+  <si>
+    <t>002955</t>
+  </si>
+  <si>
+    <t>002339</t>
+  </si>
+  <si>
+    <t>688618</t>
+  </si>
+  <si>
+    <t>605155</t>
   </si>
   <si>
     <t>605196</t>
   </si>
   <si>
-    <t>605155</t>
-  </si>
-  <si>
-    <t>688618</t>
-  </si>
-  <si>
     <t>605288</t>
   </si>
   <si>
-    <t>002339</t>
-  </si>
-  <si>
-    <t>688078</t>
-  </si>
-  <si>
-    <t>002955</t>
-  </si>
-  <si>
-    <t>000862</t>
-  </si>
-  <si>
-    <t>600322</t>
-  </si>
-  <si>
-    <t>001258</t>
+    <t>003030</t>
+  </si>
+  <si>
+    <t>300998</t>
+  </si>
+  <si>
+    <t>301228</t>
+  </si>
+  <si>
+    <t>301108</t>
+  </si>
+  <si>
+    <t>000668</t>
+  </si>
+  <si>
+    <t>603221</t>
+  </si>
+  <si>
+    <t>603660</t>
+  </si>
+  <si>
+    <t>605388</t>
   </si>
   <si>
     <t>300469</t>
   </si>
   <si>
-    <t>603660</t>
-  </si>
-  <si>
-    <t>605388</t>
-  </si>
-  <si>
-    <t>603221</t>
-  </si>
-  <si>
-    <t>003030</t>
-  </si>
-  <si>
-    <t>301108</t>
-  </si>
-  <si>
-    <t>301228</t>
-  </si>
-  <si>
-    <t>300998</t>
-  </si>
-  <si>
-    <t>000668</t>
+    <t>001210</t>
+  </si>
+  <si>
+    <t>002361</t>
+  </si>
+  <si>
+    <t>002963</t>
+  </si>
+  <si>
+    <t>603124</t>
+  </si>
+  <si>
+    <t>688661</t>
   </si>
   <si>
     <t>601700</t>
   </si>
   <si>
-    <t>688661</t>
-  </si>
-  <si>
-    <t>603124</t>
-  </si>
-  <si>
     <t>603657</t>
   </si>
   <si>
-    <t>001210</t>
-  </si>
-  <si>
-    <t>002963</t>
-  </si>
-  <si>
-    <t>002361</t>
+    <t>301626</t>
+  </si>
+  <si>
+    <t>603883</t>
+  </si>
+  <si>
+    <t>000692</t>
+  </si>
+  <si>
+    <t>688693</t>
+  </si>
+  <si>
+    <t>002520</t>
+  </si>
+  <si>
+    <t>603758</t>
+  </si>
+  <si>
+    <t>688531</t>
   </si>
   <si>
     <t>688052</t>
   </si>
   <si>
-    <t>688531</t>
-  </si>
-  <si>
-    <t>603758</t>
-  </si>
-  <si>
     <t>000410</t>
   </si>
   <si>
-    <t>688693</t>
-  </si>
-  <si>
-    <t>002520</t>
-  </si>
-  <si>
-    <t>000692</t>
-  </si>
-  <si>
-    <t>603883</t>
-  </si>
-  <si>
-    <t>301626</t>
-  </si>
-  <si>
     <t>002647</t>
   </si>
   <si>
     <t>605133</t>
   </si>
   <si>
+    <t>688611</t>
+  </si>
+  <si>
+    <t>002476</t>
+  </si>
+  <si>
+    <t>603071</t>
+  </si>
+  <si>
+    <t>300845</t>
+  </si>
+  <si>
     <t>002742</t>
   </si>
   <si>
-    <t>300845</t>
-  </si>
-  <si>
-    <t>688611</t>
-  </si>
-  <si>
-    <t>603071</t>
-  </si>
-  <si>
     <t>000523</t>
   </si>
   <si>
-    <t>002476</t>
-  </si>
-  <si>
     <t>日辰股份</t>
   </si>
   <si>
@@ -1005,66 +1005,69 @@
     <t>海天瑞声</t>
   </si>
   <si>
+    <t>百隆东方</t>
+  </si>
+  <si>
+    <t>鲁信创投</t>
+  </si>
+  <si>
+    <t>星环科技-U</t>
+  </si>
+  <si>
+    <t>恺英网络</t>
+  </si>
+  <si>
+    <t>法兰泰克</t>
+  </si>
+  <si>
+    <t>南网科技</t>
+  </si>
+  <si>
     <t>茂业商业</t>
   </si>
   <si>
-    <t>南网科技</t>
-  </si>
-  <si>
-    <t>法兰泰克</t>
-  </si>
-  <si>
     <t>三江购物</t>
   </si>
   <si>
-    <t>恺英网络</t>
-  </si>
-  <si>
-    <t>星环科技-U</t>
-  </si>
-  <si>
-    <t>鲁信创投</t>
-  </si>
-  <si>
-    <t>百隆东方</t>
-  </si>
-  <si>
     <t>志特新材</t>
   </si>
   <si>
+    <t>南矿集团</t>
+  </si>
+  <si>
+    <t>四川黄金</t>
+  </si>
+  <si>
+    <t>龙磁科技</t>
+  </si>
+  <si>
+    <t>圣晖集成</t>
+  </si>
+  <si>
+    <t>德才股份</t>
+  </si>
+  <si>
+    <t>浙江自然</t>
+  </si>
+  <si>
+    <t>金龙汽车</t>
+  </si>
+  <si>
+    <t>优利德</t>
+  </si>
+  <si>
     <t>雪龙集团</t>
   </si>
   <si>
-    <t>优利德</t>
-  </si>
-  <si>
-    <t>金龙汽车</t>
-  </si>
-  <si>
-    <t>浙江自然</t>
-  </si>
-  <si>
     <t>晶品特装</t>
   </si>
   <si>
-    <t>德才股份</t>
-  </si>
-  <si>
-    <t>南矿集团</t>
-  </si>
-  <si>
-    <t>圣晖集成</t>
-  </si>
-  <si>
-    <t>龙磁科技</t>
-  </si>
-  <si>
-    <t>四川黄金</t>
-  </si>
-  <si>
     <t>明阳智能</t>
   </si>
   <si>
+    <t>雪迪龙</t>
+  </si>
+  <si>
     <t>蓝焰控股</t>
   </si>
   <si>
@@ -1074,9 +1077,6 @@
     <t>统联精密</t>
   </si>
   <si>
-    <t>雪迪龙</t>
-  </si>
-  <si>
     <t>陕西煤业</t>
   </si>
   <si>
@@ -1089,94 +1089,97 @@
     <t>天地在线</t>
   </si>
   <si>
+    <t>工大高科</t>
+  </si>
+  <si>
+    <t>青岛双星</t>
+  </si>
+  <si>
+    <t>横店影视</t>
+  </si>
+  <si>
+    <t>纵横股份</t>
+  </si>
+  <si>
+    <t>华峰铝业</t>
+  </si>
+  <si>
+    <t>中国外运</t>
+  </si>
+  <si>
+    <t>东湖高新</t>
+  </si>
+  <si>
+    <t>克来机电</t>
+  </si>
+  <si>
+    <t>青龙管业</t>
+  </si>
+  <si>
     <t>深圳机场</t>
   </si>
   <si>
-    <t>青龙管业</t>
-  </si>
-  <si>
-    <t>克来机电</t>
-  </si>
-  <si>
-    <t>东湖高新</t>
-  </si>
-  <si>
-    <t>中国外运</t>
-  </si>
-  <si>
-    <t>华峰铝业</t>
-  </si>
-  <si>
-    <t>青岛双星</t>
-  </si>
-  <si>
-    <t>工大高科</t>
-  </si>
-  <si>
-    <t>纵横股份</t>
-  </si>
-  <si>
-    <t>横店影视</t>
+    <t>丰倍生物</t>
+  </si>
+  <si>
+    <t>振德医疗</t>
+  </si>
+  <si>
+    <t>格尔软件</t>
+  </si>
+  <si>
+    <t>杰普特</t>
+  </si>
+  <si>
+    <t>众业达</t>
+  </si>
+  <si>
+    <t>燕麦科技</t>
+  </si>
+  <si>
+    <t>信凯科技</t>
+  </si>
+  <si>
+    <t>科森科技</t>
+  </si>
+  <si>
+    <t>万朗磁塑</t>
   </si>
   <si>
     <t>联域股份</t>
   </si>
   <si>
-    <t>万朗磁塑</t>
-  </si>
-  <si>
-    <t>科森科技</t>
-  </si>
-  <si>
-    <t>信凯科技</t>
-  </si>
-  <si>
-    <t>燕麦科技</t>
-  </si>
-  <si>
-    <t>众业达</t>
-  </si>
-  <si>
-    <t>杰普特</t>
-  </si>
-  <si>
-    <t>格尔软件</t>
-  </si>
-  <si>
-    <t>振德医疗</t>
-  </si>
-  <si>
-    <t>丰倍生物</t>
+    <t>兴瑞科技</t>
+  </si>
+  <si>
+    <t>豫能控股</t>
+  </si>
+  <si>
+    <t>思源电气</t>
+  </si>
+  <si>
+    <t>紫燕食品</t>
+  </si>
+  <si>
+    <t>罗曼股份</t>
+  </si>
+  <si>
+    <t>德明利</t>
+  </si>
+  <si>
+    <t>翔楼新材</t>
+  </si>
+  <si>
+    <t>派瑞股份</t>
   </si>
   <si>
     <t>招商轮船</t>
   </si>
   <si>
-    <t>派瑞股份</t>
-  </si>
-  <si>
-    <t>翔楼新材</t>
-  </si>
-  <si>
-    <t>德明利</t>
-  </si>
-  <si>
     <t>科远智慧</t>
   </si>
   <si>
-    <t>罗曼股份</t>
-  </si>
-  <si>
-    <t>紫燕食品</t>
-  </si>
-  <si>
-    <t>思源电气</t>
-  </si>
-  <si>
-    <t>豫能控股</t>
-  </si>
-  <si>
-    <t>兴瑞科技</t>
+    <t>金富科技</t>
   </si>
   <si>
     <t>鼎通科技</t>
@@ -1191,9 +1194,6 @@
     <t>东方铁塔</t>
   </si>
   <si>
-    <t>金富科技</t>
-  </si>
-  <si>
     <t>文投控股</t>
   </si>
   <si>
@@ -1206,27 +1206,27 @@
     <t>城投控股</t>
   </si>
   <si>
+    <t>星宸科技</t>
+  </si>
+  <si>
+    <t>新柴股份</t>
+  </si>
+  <si>
+    <t>宁波建工</t>
+  </si>
+  <si>
+    <t>江波龙</t>
+  </si>
+  <si>
+    <t>王力安防</t>
+  </si>
+  <si>
+    <t>开山股份</t>
+  </si>
+  <si>
     <t>田中精机</t>
   </si>
   <si>
-    <t>江波龙</t>
-  </si>
-  <si>
-    <t>开山股份</t>
-  </si>
-  <si>
-    <t>王力安防</t>
-  </si>
-  <si>
-    <t>宁波建工</t>
-  </si>
-  <si>
-    <t>新柴股份</t>
-  </si>
-  <si>
-    <t>星宸科技</t>
-  </si>
-  <si>
     <t>银之杰</t>
   </si>
   <si>
@@ -1251,25 +1251,28 @@
     <t>瑞可达</t>
   </si>
   <si>
+    <t>欧派家居</t>
+  </si>
+  <si>
+    <t>中触媒</t>
+  </si>
+  <si>
+    <t>荣晟环保</t>
+  </si>
+  <si>
+    <t>华康股份</t>
+  </si>
+  <si>
+    <t>华兰股份</t>
+  </si>
+  <si>
     <t>光华股份</t>
   </si>
   <si>
-    <t>华兰股份</t>
-  </si>
-  <si>
     <t>常熟银行</t>
   </si>
   <si>
-    <t>荣晟环保</t>
-  </si>
-  <si>
-    <t>华康股份</t>
-  </si>
-  <si>
-    <t>中触媒</t>
-  </si>
-  <si>
-    <t>欧派家居</t>
+    <t>苏利股份</t>
   </si>
   <si>
     <t>华帝股份</t>
@@ -1287,9 +1290,6 @@
     <t>运达科技</t>
   </si>
   <si>
-    <t>苏利股份</t>
-  </si>
-  <si>
     <t>福赛科技</t>
   </si>
   <si>
@@ -1299,115 +1299,124 @@
     <t>高能环境</t>
   </si>
   <si>
+    <t>卓郎智能</t>
+  </si>
+  <si>
+    <t>天原股份</t>
+  </si>
+  <si>
+    <t>四方达</t>
+  </si>
+  <si>
+    <t>中电电机</t>
+  </si>
+  <si>
+    <t>完美世界</t>
+  </si>
+  <si>
+    <t>捷邦科技</t>
+  </si>
+  <si>
     <t>大族激光</t>
   </si>
   <si>
+    <t>鑫宏业</t>
+  </si>
+  <si>
+    <t>中安科</t>
+  </si>
+  <si>
     <t>欧陆通</t>
   </si>
   <si>
-    <t>中安科</t>
-  </si>
-  <si>
-    <t>捷邦科技</t>
-  </si>
-  <si>
-    <t>鑫宏业</t>
-  </si>
-  <si>
-    <t>中电电机</t>
-  </si>
-  <si>
-    <t>天原股份</t>
-  </si>
-  <si>
-    <t>完美世界</t>
-  </si>
-  <si>
-    <t>四方达</t>
-  </si>
-  <si>
-    <t>卓郎智能</t>
+    <t>安克创新</t>
+  </si>
+  <si>
+    <t>康恩贝</t>
+  </si>
+  <si>
+    <t>威领股份</t>
+  </si>
+  <si>
+    <t>西藏旅游</t>
+  </si>
+  <si>
+    <t>锦和商管</t>
+  </si>
+  <si>
+    <t>航天工程</t>
+  </si>
+  <si>
+    <t>税友股份</t>
   </si>
   <si>
     <t>皮阿诺</t>
   </si>
   <si>
-    <t>税友股份</t>
-  </si>
-  <si>
-    <t>航天工程</t>
-  </si>
-  <si>
     <t>华源控股</t>
   </si>
   <si>
-    <t>西藏旅游</t>
-  </si>
-  <si>
-    <t>锦和商管</t>
-  </si>
-  <si>
-    <t>威领股份</t>
-  </si>
-  <si>
-    <t>康恩贝</t>
-  </si>
-  <si>
-    <t>安克创新</t>
+    <t>珂玛科技</t>
+  </si>
+  <si>
+    <t>金钟股份</t>
+  </si>
+  <si>
+    <t>华升股份</t>
+  </si>
+  <si>
+    <t>冰轮环境</t>
+  </si>
+  <si>
+    <t>吉宏股份</t>
+  </si>
+  <si>
+    <t>苏州高新</t>
+  </si>
+  <si>
+    <t>赛意信息</t>
   </si>
   <si>
     <t>横河精密</t>
   </si>
   <si>
-    <t>赛意信息</t>
-  </si>
-  <si>
-    <t>苏州高新</t>
-  </si>
-  <si>
     <t>博杰股份</t>
   </si>
   <si>
-    <t>吉宏股份</t>
-  </si>
-  <si>
-    <t>冰轮环境</t>
-  </si>
-  <si>
-    <t>华升股份</t>
-  </si>
-  <si>
-    <t>金钟股份</t>
-  </si>
-  <si>
-    <t>珂玛科技</t>
+    <t>裕同科技</t>
+  </si>
+  <si>
+    <t>德尔未来</t>
+  </si>
+  <si>
+    <t>宝丽迪</t>
+  </si>
+  <si>
+    <t>帝科股份</t>
+  </si>
+  <si>
+    <t>粤传媒</t>
+  </si>
+  <si>
+    <t>福达合金</t>
+  </si>
+  <si>
+    <t>格林达</t>
   </si>
   <si>
     <t>上峰材料</t>
   </si>
   <si>
-    <t>格林达</t>
-  </si>
-  <si>
     <t>江海股份</t>
   </si>
   <si>
-    <t>福达合金</t>
-  </si>
-  <si>
-    <t>粤传媒</t>
-  </si>
-  <si>
-    <t>帝科股份</t>
-  </si>
-  <si>
-    <t>宝丽迪</t>
-  </si>
-  <si>
-    <t>德尔未来</t>
-  </si>
-  <si>
-    <t>裕同科技</t>
+    <t>可立克</t>
+  </si>
+  <si>
+    <t>美盈森</t>
+  </si>
+  <si>
+    <t>顶固集创</t>
   </si>
   <si>
     <t>祥鑫科技</t>
@@ -1416,21 +1425,12 @@
     <t>可川科技</t>
   </si>
   <si>
+    <t>*ST春天</t>
+  </si>
+  <si>
     <t>华兴源创</t>
   </si>
   <si>
-    <t>顶固集创</t>
-  </si>
-  <si>
-    <t>*ST春天</t>
-  </si>
-  <si>
-    <t>可立克</t>
-  </si>
-  <si>
-    <t>美盈森</t>
-  </si>
-  <si>
     <t>浙江永强</t>
   </si>
   <si>
@@ -1452,130 +1452,145 @@
     <t>晶华微</t>
   </si>
   <si>
+    <t>奥海科技</t>
+  </si>
+  <si>
+    <t>天正电气</t>
+  </si>
+  <si>
+    <t>香江控股</t>
+  </si>
+  <si>
+    <t>凯瑞德</t>
+  </si>
+  <si>
+    <t>华塑控股</t>
+  </si>
+  <si>
+    <t>共达电声</t>
+  </si>
+  <si>
+    <t>美新科技</t>
+  </si>
+  <si>
+    <t>杰美特</t>
+  </si>
+  <si>
     <t>海格通信</t>
   </si>
   <si>
-    <t>共达电声</t>
-  </si>
-  <si>
-    <t>杰美特</t>
-  </si>
-  <si>
     <t>恒林股份</t>
   </si>
   <si>
-    <t>美新科技</t>
-  </si>
-  <si>
-    <t>凯瑞德</t>
-  </si>
-  <si>
-    <t>香江控股</t>
-  </si>
-  <si>
-    <t>华塑控股</t>
-  </si>
-  <si>
-    <t>天正电气</t>
-  </si>
-  <si>
-    <t>奥海科技</t>
+    <t>嘉欣丝绸</t>
+  </si>
+  <si>
+    <t>金时科技</t>
+  </si>
+  <si>
+    <t>拓山重工</t>
+  </si>
+  <si>
+    <t>湘潭电化</t>
   </si>
   <si>
     <t>天洋新材</t>
   </si>
   <si>
+    <t>南山控股</t>
+  </si>
+  <si>
     <t>名雕股份</t>
   </si>
   <si>
-    <t>南山控股</t>
-  </si>
-  <si>
     <t>易普力</t>
   </si>
   <si>
     <t>盛德鑫泰</t>
   </si>
   <si>
-    <t>金时科技</t>
-  </si>
-  <si>
-    <t>拓山重工</t>
-  </si>
-  <si>
-    <t>湘潭电化</t>
-  </si>
-  <si>
-    <t>嘉欣丝绸</t>
+    <t>京基智农</t>
+  </si>
+  <si>
+    <t>湘佳股份</t>
+  </si>
+  <si>
+    <t>三孚股份</t>
+  </si>
+  <si>
+    <t>北辰实业</t>
   </si>
   <si>
     <t>莱伯泰科</t>
   </si>
   <si>
+    <t>宇环数控</t>
+  </si>
+  <si>
     <t>民德电子</t>
   </si>
   <si>
-    <t>宇环数控</t>
-  </si>
-  <si>
-    <t>湘佳股份</t>
-  </si>
-  <si>
-    <t>北辰实业</t>
-  </si>
-  <si>
-    <t>三孚股份</t>
-  </si>
-  <si>
-    <t>京基智农</t>
+    <t>德方纳米</t>
+  </si>
+  <si>
+    <t>中远海能</t>
+  </si>
+  <si>
+    <t>杭电股份</t>
+  </si>
+  <si>
+    <t>科翔股份</t>
+  </si>
+  <si>
+    <t>诺德股份</t>
+  </si>
+  <si>
+    <t>奥士康</t>
+  </si>
+  <si>
+    <t>科安达</t>
+  </si>
+  <si>
+    <t>宗申动力</t>
   </si>
   <si>
     <t>泰晶科技</t>
   </si>
   <si>
-    <t>科安达</t>
-  </si>
-  <si>
-    <t>奥士康</t>
-  </si>
-  <si>
-    <t>宗申动力</t>
-  </si>
-  <si>
-    <t>德方纳米</t>
-  </si>
-  <si>
-    <t>中远海能</t>
-  </si>
-  <si>
-    <t>科翔股份</t>
-  </si>
-  <si>
-    <t>诺德股份</t>
-  </si>
-  <si>
-    <t>杭电股份</t>
+    <t>长裕集团</t>
+  </si>
+  <si>
+    <t>闰土股份</t>
+  </si>
+  <si>
+    <t>光智科技</t>
+  </si>
+  <si>
+    <t>杰创智能</t>
   </si>
   <si>
     <t>盛视科技</t>
   </si>
   <si>
-    <t>杰创智能</t>
+    <t>瑞玛精密</t>
   </si>
   <si>
     <t>巨人网络</t>
   </si>
   <si>
-    <t>瑞玛精密</t>
-  </si>
-  <si>
-    <t>闰土股份</t>
-  </si>
-  <si>
-    <t>长裕集团</t>
-  </si>
-  <si>
-    <t>光智科技</t>
+    <t>创维数字</t>
+  </si>
+  <si>
+    <t>巨力索具</t>
+  </si>
+  <si>
+    <t>威派格</t>
+  </si>
+  <si>
+    <t>双成药业</t>
+  </si>
+  <si>
+    <t>晶澳科技</t>
   </si>
   <si>
     <t>牧原股份</t>
@@ -1584,213 +1599,198 @@
     <t>蜂助手</t>
   </si>
   <si>
+    <t>巨星农牧</t>
+  </si>
+  <si>
+    <t>龙头股份</t>
+  </si>
+  <si>
     <t>中坚科技</t>
   </si>
   <si>
-    <t>巨星农牧</t>
-  </si>
-  <si>
-    <t>龙头股份</t>
-  </si>
-  <si>
-    <t>创维数字</t>
-  </si>
-  <si>
-    <t>晶澳科技</t>
-  </si>
-  <si>
-    <t>双成药业</t>
-  </si>
-  <si>
-    <t>威派格</t>
-  </si>
-  <si>
-    <t>巨力索具</t>
+    <t>华昌化工</t>
+  </si>
+  <si>
+    <t>德林海</t>
+  </si>
+  <si>
+    <t>甘咨询</t>
+  </si>
+  <si>
+    <t>四川美丰</t>
+  </si>
+  <si>
+    <t>汇创达</t>
+  </si>
+  <si>
+    <t>力鼎光电</t>
   </si>
   <si>
     <t>浪潮信息</t>
   </si>
   <si>
-    <t>力鼎光电</t>
-  </si>
-  <si>
     <t>康惠股份</t>
   </si>
   <si>
-    <t>汇创达</t>
-  </si>
-  <si>
-    <t>四川美丰</t>
-  </si>
-  <si>
-    <t>甘咨询</t>
-  </si>
-  <si>
-    <t>德林海</t>
-  </si>
-  <si>
-    <t>华昌化工</t>
+    <t>哈三联</t>
+  </si>
+  <si>
+    <t>时空科技</t>
+  </si>
+  <si>
+    <t>浙江美大</t>
+  </si>
+  <si>
+    <t>江苏索普</t>
+  </si>
+  <si>
+    <t>云赛智联</t>
   </si>
   <si>
     <t>电投能源</t>
   </si>
   <si>
+    <t>九州一轨</t>
+  </si>
+  <si>
     <t>宏桥控股</t>
   </si>
   <si>
-    <t>九州一轨</t>
-  </si>
-  <si>
-    <t>江苏索普</t>
+    <t>首钢股份</t>
   </si>
   <si>
     <t>光韵达</t>
   </si>
   <si>
-    <t>时空科技</t>
-  </si>
-  <si>
-    <t>浙江美大</t>
-  </si>
-  <si>
-    <t>首钢股份</t>
-  </si>
-  <si>
-    <t>哈三联</t>
-  </si>
-  <si>
-    <t>云赛智联</t>
+    <t>龙软科技</t>
+  </si>
+  <si>
+    <t>津投城开</t>
+  </si>
+  <si>
+    <t>银星能源</t>
+  </si>
+  <si>
+    <t>立新能源</t>
+  </si>
+  <si>
+    <t>鸿合科技</t>
+  </si>
+  <si>
+    <t>积成电子</t>
+  </si>
+  <si>
+    <t>三旺通信</t>
+  </si>
+  <si>
+    <t>西大门</t>
   </si>
   <si>
     <t>华通线缆</t>
   </si>
   <si>
-    <t>西大门</t>
-  </si>
-  <si>
-    <t>三旺通信</t>
-  </si>
-  <si>
     <t>凯迪股份</t>
   </si>
   <si>
-    <t>积成电子</t>
-  </si>
-  <si>
-    <t>龙软科技</t>
-  </si>
-  <si>
-    <t>鸿合科技</t>
-  </si>
-  <si>
-    <t>银星能源</t>
-  </si>
-  <si>
-    <t>津投城开</t>
-  </si>
-  <si>
-    <t>立新能源</t>
+    <t>祖名股份</t>
+  </si>
+  <si>
+    <t>宁波方正</t>
+  </si>
+  <si>
+    <t>实朴检测</t>
+  </si>
+  <si>
+    <t>洁雅股份</t>
+  </si>
+  <si>
+    <t>荣丰控股</t>
+  </si>
+  <si>
+    <t>爱丽家居</t>
+  </si>
+  <si>
+    <t>苏州科达</t>
+  </si>
+  <si>
+    <t>均瑶健康</t>
   </si>
   <si>
     <t>信息发展</t>
   </si>
   <si>
-    <t>苏州科达</t>
-  </si>
-  <si>
-    <t>均瑶健康</t>
-  </si>
-  <si>
-    <t>爱丽家居</t>
-  </si>
-  <si>
-    <t>祖名股份</t>
-  </si>
-  <si>
-    <t>洁雅股份</t>
-  </si>
-  <si>
-    <t>实朴检测</t>
-  </si>
-  <si>
-    <t>宁波方正</t>
-  </si>
-  <si>
-    <t>荣丰控股</t>
+    <t>金房能源</t>
+  </si>
+  <si>
+    <t>神剑股份</t>
+  </si>
+  <si>
+    <t>豪尔赛</t>
+  </si>
+  <si>
+    <t>江南新材</t>
+  </si>
+  <si>
+    <t>和林微纳</t>
   </si>
   <si>
     <t>风范股份</t>
   </si>
   <si>
-    <t>和林微纳</t>
-  </si>
-  <si>
-    <t>江南新材</t>
-  </si>
-  <si>
     <t>春光科技</t>
   </si>
   <si>
-    <t>金房能源</t>
-  </si>
-  <si>
-    <t>豪尔赛</t>
-  </si>
-  <si>
-    <t>神剑股份</t>
+    <t>苏州天脉</t>
+  </si>
+  <si>
+    <t>老百姓</t>
+  </si>
+  <si>
+    <t>惠天热电</t>
+  </si>
+  <si>
+    <t>锴威特</t>
+  </si>
+  <si>
+    <t>日发精机</t>
+  </si>
+  <si>
+    <t>秦安股份</t>
+  </si>
+  <si>
+    <t>日联科技</t>
   </si>
   <si>
     <t>纳芯微</t>
   </si>
   <si>
-    <t>日联科技</t>
-  </si>
-  <si>
-    <t>秦安股份</t>
-  </si>
-  <si>
     <t>沈阳机床</t>
   </si>
   <si>
-    <t>锴威特</t>
-  </si>
-  <si>
-    <t>日发精机</t>
-  </si>
-  <si>
-    <t>惠天热电</t>
-  </si>
-  <si>
-    <t>老百姓</t>
-  </si>
-  <si>
-    <t>苏州天脉</t>
-  </si>
-  <si>
     <t>仁东控股</t>
   </si>
   <si>
     <t>嵘泰股份</t>
   </si>
   <si>
+    <t>杭州柯林</t>
+  </si>
+  <si>
+    <t>新叶股份</t>
+  </si>
+  <si>
+    <t>物产环能</t>
+  </si>
+  <si>
+    <t>捷安高科</t>
+  </si>
+  <si>
     <t>冀衡医药</t>
   </si>
   <si>
-    <t>捷安高科</t>
-  </si>
-  <si>
-    <t>杭州柯林</t>
-  </si>
-  <si>
-    <t>物产环能</t>
-  </si>
-  <si>
     <t>红棉股份</t>
   </si>
   <si>
-    <t>新叶股份</t>
-  </si>
-  <si>
     <t>2026-01-06 09:35:00</t>
   </si>
   <si>
@@ -1911,51 +1911,51 @@
     <t>2026-02-09 15:00:00</t>
   </si>
   <si>
+    <t>2026-02-04 13:05:00</t>
+  </si>
+  <si>
+    <t>2026-02-03 09:40:00</t>
+  </si>
+  <si>
     <t>2026-02-05 13:05:00</t>
   </si>
   <si>
-    <t>2026-02-03 09:40:00</t>
-  </si>
-  <si>
-    <t>2026-02-04 13:05:00</t>
-  </si>
-  <si>
     <t>2026-02-24 15:00:00</t>
   </si>
   <si>
+    <t>2026-02-24 09:40:00</t>
+  </si>
+  <si>
     <t>2026-02-11 09:35:00</t>
   </si>
   <si>
-    <t>2026-02-24 09:40:00</t>
-  </si>
-  <si>
     <t>2026-03-03 15:00:00</t>
   </si>
   <si>
     <t>2026-02-25 09:40:00</t>
   </si>
   <si>
+    <t>2026-03-10 15:00:00</t>
+  </si>
+  <si>
     <t>2026-03-04 09:40:00</t>
   </si>
   <si>
-    <t>2026-03-10 15:00:00</t>
-  </si>
-  <si>
     <t>2026-03-10 09:40:00</t>
   </si>
   <si>
+    <t>2026-03-13 09:45:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 10:45:00</t>
+  </si>
+  <si>
+    <t>2026-03-17 15:00:00</t>
+  </si>
+  <si>
     <t>2026-03-16 10:30:00</t>
   </si>
   <si>
-    <t>2026-03-17 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-03-17 10:45:00</t>
-  </si>
-  <si>
-    <t>2026-03-13 09:45:00</t>
-  </si>
-  <si>
     <t>2026-03-24 15:00:00</t>
   </si>
   <si>
@@ -1977,12 +1977,12 @@
     <t>2026-03-25 09:40:00</t>
   </si>
   <si>
+    <t>2026-03-31 15:00:00</t>
+  </si>
+  <si>
     <t>2026-03-31 14:55:00</t>
   </si>
   <si>
-    <t>2026-03-31 15:00:00</t>
-  </si>
-  <si>
     <t>2026-04-01 09:40:00</t>
   </si>
   <si>
@@ -1992,21 +1992,21 @@
     <t>2026-04-02 14:00:00</t>
   </si>
   <si>
+    <t>2026-04-09 09:40:00</t>
+  </si>
+  <si>
     <t>2026-04-15 15:00:00</t>
   </si>
   <si>
-    <t>2026-04-09 09:40:00</t>
-  </si>
-  <si>
     <t>2026-04-22 15:00:00</t>
   </si>
   <si>
+    <t>2026-04-29 15:00:00</t>
+  </si>
+  <si>
     <t>2026-04-28 13:40:00</t>
   </si>
   <si>
-    <t>2026-04-29 15:00:00</t>
-  </si>
-  <si>
     <t>2026-05-13 15:00:00</t>
   </si>
   <si>
@@ -2019,6 +2019,12 @@
     <t>2026-06-03 15:00:00</t>
   </si>
   <si>
+    <t>2026-06-09 09:35:00</t>
+  </si>
+  <si>
+    <t>2026-06-10 09:35:00</t>
+  </si>
+  <si>
     <t>2026-06-10 15:00:00</t>
   </si>
   <si>
@@ -2028,27 +2034,21 @@
     <t>2026-06-10 09:45:00</t>
   </si>
   <si>
-    <t>2026-06-09 09:35:00</t>
-  </si>
-  <si>
-    <t>2026-06-10 09:35:00</t>
+    <t>2026-06-11 09:40:00</t>
   </si>
   <si>
     <t>2026-06-17 15:00:00</t>
   </si>
   <si>
-    <t>2026-06-11 09:40:00</t>
+    <t>2026-06-18 11:30:00</t>
+  </si>
+  <si>
+    <t>2026-06-18 10:35:00</t>
   </si>
   <si>
     <t>2026-06-25 15:00:00</t>
   </si>
   <si>
-    <t>2026-06-18 11:30:00</t>
-  </si>
-  <si>
-    <t>2026-06-18 10:35:00</t>
-  </si>
-  <si>
     <t>2026-07-02 15:00:00</t>
   </si>
   <si>
@@ -2058,34 +2058,43 @@
     <t>2026-06-26 09:40:00</t>
   </si>
   <si>
+    <t>2026-07-08 10:40:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 13:05:00</t>
+  </si>
+  <si>
     <t>2026-07-09 15:00:00</t>
   </si>
   <si>
+    <t>2026-07-03 10:25:00</t>
+  </si>
+  <si>
+    <t>2026-07-06 09:35:00</t>
+  </si>
+  <si>
     <t>2026-07-08 09:35:00</t>
   </si>
   <si>
-    <t>2026-07-06 09:35:00</t>
-  </si>
-  <si>
-    <t>2026-07-08 10:40:00</t>
-  </si>
-  <si>
-    <t>2026-07-03 10:25:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 13:05:00</t>
-  </si>
-  <si>
     <t>2026-07-16 15:00:00</t>
   </si>
   <si>
+    <t>2026-07-10 09:40:00</t>
+  </si>
+  <si>
+    <t>2026-07-13 09:50:00</t>
+  </si>
+  <si>
     <t>2026-07-10 10:15:00</t>
   </si>
   <si>
-    <t>2026-07-10 09:40:00</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:50:00</t>
+    <t>2026-07-21 09:55:00</t>
+  </si>
+  <si>
+    <t>2026-07-17 09:50:00</t>
+  </si>
+  <si>
+    <t>2026-07-22 10:45:00</t>
   </si>
   <si>
     <t>2026-07-23 15:00:00</t>
@@ -2094,37 +2103,28 @@
     <t>2026-07-17 09:40:00</t>
   </si>
   <si>
-    <t>2026-07-17 09:50:00</t>
-  </si>
-  <si>
-    <t>2026-07-22 10:45:00</t>
-  </si>
-  <si>
-    <t>2026-07-21 09:55:00</t>
+    <t>2026-07-24 09:40:00</t>
   </si>
   <si>
     <t>2026-07-30 15:00:00</t>
   </si>
   <si>
+    <t>2026-07-24 11:00:00</t>
+  </si>
+  <si>
     <t>2026-07-24 10:30:00</t>
   </si>
   <si>
-    <t>2026-07-24 11:00:00</t>
-  </si>
-  <si>
-    <t>2026-07-24 09:40:00</t>
+    <t>2026-07-31 09:40:00</t>
+  </si>
+  <si>
+    <t>2026-08-03 09:55:00</t>
   </si>
   <si>
     <t>2026-08-06 15:00:00</t>
   </si>
   <si>
-    <t>2026-07-31 09:40:00</t>
-  </si>
-  <si>
     <t>2026-08-07 15:00:00</t>
-  </si>
-  <si>
-    <t>2026-08-03 09:55:00</t>
   </si>
   <si>
     <t>2026-08-13 15:00:00</t>
@@ -2510,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>47.95</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2518,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>81.88</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2534,7 +2534,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2542,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>60.61</v>
+        <v>61.76</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3233,6 +3233,26 @@
       </c>
       <c r="F34">
         <v>1.4795</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35">
+        <v>0.84</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>4.537500000000001</v>
+      </c>
+      <c r="E35">
+        <v>3.8115</v>
+      </c>
+      <c r="F35">
+        <v>1.5358</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3262,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G311"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3463,16 +3483,16 @@
         <v>592</v>
       </c>
       <c r="D10">
-        <v>8.16</v>
+        <v>6.21</v>
       </c>
       <c r="E10" t="s">
         <v>625</v>
       </c>
       <c r="F10">
-        <v>6.92</v>
+        <v>6.17</v>
       </c>
       <c r="G10">
-        <v>-15.2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3486,16 +3506,16 @@
         <v>592</v>
       </c>
       <c r="D11">
-        <v>55.02</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
         <v>625</v>
       </c>
       <c r="F11">
-        <v>59.22</v>
+        <v>26.01</v>
       </c>
       <c r="G11">
-        <v>7.63</v>
+        <v>-31.55</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3509,16 +3529,16 @@
         <v>592</v>
       </c>
       <c r="D12">
-        <v>13.58</v>
+        <v>192</v>
       </c>
       <c r="E12" t="s">
         <v>625</v>
       </c>
       <c r="F12">
-        <v>14.2</v>
+        <v>189.7</v>
       </c>
       <c r="G12">
-        <v>4.57</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3532,16 +3552,16 @@
         <v>592</v>
       </c>
       <c r="D13">
-        <v>18.18</v>
+        <v>26.55</v>
       </c>
       <c r="E13" t="s">
         <v>625</v>
       </c>
       <c r="F13">
-        <v>17.6</v>
+        <v>26.34</v>
       </c>
       <c r="G13">
-        <v>-3.19</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3555,16 +3575,16 @@
         <v>592</v>
       </c>
       <c r="D14">
-        <v>26.55</v>
+        <v>13.58</v>
       </c>
       <c r="E14" t="s">
         <v>625</v>
       </c>
       <c r="F14">
-        <v>26.34</v>
+        <v>14.2</v>
       </c>
       <c r="G14">
-        <v>-0.79</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3578,16 +3598,16 @@
         <v>592</v>
       </c>
       <c r="D15">
-        <v>192</v>
+        <v>55.02</v>
       </c>
       <c r="E15" t="s">
         <v>625</v>
       </c>
       <c r="F15">
-        <v>189.7</v>
+        <v>59.22</v>
       </c>
       <c r="G15">
-        <v>-1.2</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3601,16 +3621,16 @@
         <v>592</v>
       </c>
       <c r="D16">
-        <v>38</v>
+        <v>8.16</v>
       </c>
       <c r="E16" t="s">
         <v>625</v>
       </c>
       <c r="F16">
-        <v>26.01</v>
+        <v>6.92</v>
       </c>
       <c r="G16">
-        <v>-31.55</v>
+        <v>-15.2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3624,16 +3644,16 @@
         <v>592</v>
       </c>
       <c r="D17">
-        <v>6.21</v>
+        <v>18.18</v>
       </c>
       <c r="E17" t="s">
         <v>625</v>
       </c>
       <c r="F17">
-        <v>6.17</v>
+        <v>17.6</v>
       </c>
       <c r="G17">
-        <v>-0.64</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3670,16 +3690,16 @@
         <v>594</v>
       </c>
       <c r="D19">
-        <v>21.5</v>
+        <v>24.77</v>
       </c>
       <c r="E19" t="s">
         <v>627</v>
       </c>
       <c r="F19">
-        <v>22.64</v>
+        <v>28.9</v>
       </c>
       <c r="G19">
-        <v>5.3</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3693,16 +3713,16 @@
         <v>594</v>
       </c>
       <c r="D20">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
         <v>627</v>
       </c>
       <c r="F20">
-        <v>38.82</v>
+        <v>55.25</v>
       </c>
       <c r="G20">
-        <v>3.52</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3716,16 +3736,16 @@
         <v>594</v>
       </c>
       <c r="D21">
-        <v>19.5</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="E21" t="s">
         <v>627</v>
       </c>
       <c r="F21">
-        <v>19.06</v>
+        <v>70.87</v>
       </c>
       <c r="G21">
-        <v>-2.26</v>
+        <v>-6.97</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3739,16 +3759,16 @@
         <v>594</v>
       </c>
       <c r="D22">
-        <v>27.1</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
         <v>627</v>
       </c>
       <c r="F22">
-        <v>24.91</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="G22">
-        <v>-8.08</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3762,16 +3782,16 @@
         <v>594</v>
       </c>
       <c r="D23">
-        <v>103.82</v>
+        <v>39.57</v>
       </c>
       <c r="E23" t="s">
         <v>627</v>
       </c>
       <c r="F23">
-        <v>93.15000000000001</v>
+        <v>46.79</v>
       </c>
       <c r="G23">
-        <v>-10.28</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3785,16 +3805,16 @@
         <v>594</v>
       </c>
       <c r="D24">
-        <v>39.57</v>
+        <v>27.1</v>
       </c>
       <c r="E24" t="s">
         <v>627</v>
       </c>
       <c r="F24">
-        <v>46.79</v>
+        <v>24.91</v>
       </c>
       <c r="G24">
-        <v>18.25</v>
+        <v>-8.08</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3808,16 +3828,16 @@
         <v>594</v>
       </c>
       <c r="D25">
-        <v>24.77</v>
+        <v>19.5</v>
       </c>
       <c r="E25" t="s">
         <v>627</v>
       </c>
       <c r="F25">
-        <v>28.9</v>
+        <v>19.06</v>
       </c>
       <c r="G25">
-        <v>16.67</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3831,16 +3851,16 @@
         <v>594</v>
       </c>
       <c r="D26">
-        <v>88</v>
+        <v>37.5</v>
       </c>
       <c r="E26" t="s">
         <v>627</v>
       </c>
       <c r="F26">
-        <v>92.34999999999999</v>
+        <v>38.82</v>
       </c>
       <c r="G26">
-        <v>4.94</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3854,16 +3874,16 @@
         <v>594</v>
       </c>
       <c r="D27">
-        <v>76.18000000000001</v>
+        <v>21.5</v>
       </c>
       <c r="E27" t="s">
         <v>627</v>
       </c>
       <c r="F27">
-        <v>70.87</v>
+        <v>22.64</v>
       </c>
       <c r="G27">
-        <v>-6.97</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3877,16 +3897,16 @@
         <v>594</v>
       </c>
       <c r="D28">
-        <v>39</v>
+        <v>103.82</v>
       </c>
       <c r="E28" t="s">
         <v>627</v>
       </c>
       <c r="F28">
-        <v>55.25</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="G28">
-        <v>41.67</v>
+        <v>-10.28</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3923,16 +3943,16 @@
         <v>596</v>
       </c>
       <c r="D30">
-        <v>8.08</v>
+        <v>10.41</v>
       </c>
       <c r="E30" t="s">
         <v>629</v>
       </c>
       <c r="F30">
-        <v>7.78</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G30">
-        <v>-3.71</v>
+        <v>-9.99</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3946,16 +3966,16 @@
         <v>596</v>
       </c>
       <c r="D31">
-        <v>12.06</v>
+        <v>8.08</v>
       </c>
       <c r="E31" t="s">
         <v>629</v>
       </c>
       <c r="F31">
-        <v>11.26</v>
+        <v>7.78</v>
       </c>
       <c r="G31">
-        <v>-6.63</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3969,16 +3989,16 @@
         <v>596</v>
       </c>
       <c r="D32">
-        <v>53</v>
+        <v>12.06</v>
       </c>
       <c r="E32" t="s">
         <v>629</v>
       </c>
       <c r="F32">
-        <v>54.08</v>
+        <v>11.26</v>
       </c>
       <c r="G32">
-        <v>2.04</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3992,16 +4012,16 @@
         <v>596</v>
       </c>
       <c r="D33">
-        <v>10.41</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
         <v>629</v>
       </c>
       <c r="F33">
-        <v>9.369999999999999</v>
+        <v>54.08</v>
       </c>
       <c r="G33">
-        <v>-9.99</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4107,16 +4127,16 @@
         <v>597</v>
       </c>
       <c r="D38">
-        <v>7.27</v>
+        <v>35.45</v>
       </c>
       <c r="E38" t="s">
         <v>630</v>
       </c>
       <c r="F38">
-        <v>7.23</v>
+        <v>38.18</v>
       </c>
       <c r="G38">
-        <v>-0.55</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4130,16 +4150,16 @@
         <v>597</v>
       </c>
       <c r="D39">
-        <v>12.48</v>
+        <v>7.2</v>
       </c>
       <c r="E39" t="s">
         <v>630</v>
       </c>
       <c r="F39">
-        <v>13.07</v>
+        <v>6.79</v>
       </c>
       <c r="G39">
-        <v>4.73</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4153,16 +4173,16 @@
         <v>597</v>
       </c>
       <c r="D40">
-        <v>21.61</v>
+        <v>30.86</v>
       </c>
       <c r="E40" t="s">
         <v>630</v>
       </c>
       <c r="F40">
-        <v>22.32</v>
+        <v>36.74</v>
       </c>
       <c r="G40">
-        <v>3.29</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4176,16 +4196,16 @@
         <v>597</v>
       </c>
       <c r="D41">
-        <v>10.95</v>
+        <v>63.71</v>
       </c>
       <c r="E41" t="s">
         <v>631</v>
       </c>
       <c r="F41">
-        <v>10.3</v>
+        <v>59.43</v>
       </c>
       <c r="G41">
-        <v>-5.94</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4199,16 +4219,16 @@
         <v>597</v>
       </c>
       <c r="D42">
-        <v>5.6</v>
+        <v>26.92</v>
       </c>
       <c r="E42" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F42">
-        <v>5.63</v>
+        <v>23.44</v>
       </c>
       <c r="G42">
-        <v>0.54</v>
+        <v>-12.93</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4222,16 +4242,16 @@
         <v>597</v>
       </c>
       <c r="D43">
-        <v>26.92</v>
+        <v>5.6</v>
       </c>
       <c r="E43" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F43">
-        <v>23.44</v>
+        <v>5.63</v>
       </c>
       <c r="G43">
-        <v>-12.93</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4245,16 +4265,16 @@
         <v>597</v>
       </c>
       <c r="D44">
-        <v>7.2</v>
+        <v>10.95</v>
       </c>
       <c r="E44" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F44">
-        <v>6.79</v>
+        <v>10.3</v>
       </c>
       <c r="G44">
-        <v>-5.69</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4268,16 +4288,16 @@
         <v>597</v>
       </c>
       <c r="D45">
-        <v>35.45</v>
+        <v>21.61</v>
       </c>
       <c r="E45" t="s">
         <v>630</v>
       </c>
       <c r="F45">
-        <v>38.18</v>
+        <v>22.32</v>
       </c>
       <c r="G45">
-        <v>7.7</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4291,16 +4311,16 @@
         <v>597</v>
       </c>
       <c r="D46">
-        <v>63.71</v>
+        <v>12.48</v>
       </c>
       <c r="E46" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F46">
-        <v>59.43</v>
+        <v>13.07</v>
       </c>
       <c r="G46">
-        <v>-6.72</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -4314,16 +4334,16 @@
         <v>597</v>
       </c>
       <c r="D47">
-        <v>30.86</v>
+        <v>7.27</v>
       </c>
       <c r="E47" t="s">
         <v>630</v>
       </c>
       <c r="F47">
-        <v>36.74</v>
+        <v>7.23</v>
       </c>
       <c r="G47">
-        <v>19.05</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -4337,16 +4357,16 @@
         <v>598</v>
       </c>
       <c r="D48">
-        <v>61.93</v>
+        <v>58.75</v>
       </c>
       <c r="E48" t="s">
         <v>634</v>
       </c>
       <c r="F48">
-        <v>60.73</v>
+        <v>55.83</v>
       </c>
       <c r="G48">
-        <v>-1.94</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -4360,16 +4380,16 @@
         <v>598</v>
       </c>
       <c r="D49">
-        <v>54.85</v>
+        <v>84.72</v>
       </c>
       <c r="E49" t="s">
         <v>634</v>
       </c>
       <c r="F49">
-        <v>60.31</v>
+        <v>86.5</v>
       </c>
       <c r="G49">
-        <v>9.949999999999999</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -4383,16 +4403,16 @@
         <v>598</v>
       </c>
       <c r="D50">
-        <v>27.55</v>
+        <v>27.75</v>
       </c>
       <c r="E50" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F50">
-        <v>26.68</v>
+        <v>24.16</v>
       </c>
       <c r="G50">
-        <v>-3.16</v>
+        <v>-12.94</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -4406,16 +4426,16 @@
         <v>598</v>
       </c>
       <c r="D51">
-        <v>56.11</v>
+        <v>215</v>
       </c>
       <c r="E51" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F51">
-        <v>51.34</v>
+        <v>209.71</v>
       </c>
       <c r="G51">
-        <v>-8.5</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -4429,16 +4449,16 @@
         <v>598</v>
       </c>
       <c r="D52">
-        <v>52.31</v>
+        <v>10.9</v>
       </c>
       <c r="E52" t="s">
         <v>634</v>
       </c>
       <c r="F52">
-        <v>50.29</v>
+        <v>11.35</v>
       </c>
       <c r="G52">
-        <v>-3.86</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -4452,16 +4472,16 @@
         <v>598</v>
       </c>
       <c r="D53">
-        <v>10.9</v>
+        <v>52.31</v>
       </c>
       <c r="E53" t="s">
         <v>634</v>
       </c>
       <c r="F53">
-        <v>11.35</v>
+        <v>50.29</v>
       </c>
       <c r="G53">
-        <v>4.13</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4475,16 +4495,16 @@
         <v>598</v>
       </c>
       <c r="D54">
-        <v>215</v>
+        <v>56.11</v>
       </c>
       <c r="E54" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F54">
-        <v>209.71</v>
+        <v>51.34</v>
       </c>
       <c r="G54">
-        <v>-2.46</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4498,16 +4518,16 @@
         <v>598</v>
       </c>
       <c r="D55">
-        <v>27.75</v>
+        <v>27.55</v>
       </c>
       <c r="E55" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F55">
-        <v>24.16</v>
+        <v>26.68</v>
       </c>
       <c r="G55">
-        <v>-12.94</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -4521,16 +4541,16 @@
         <v>598</v>
       </c>
       <c r="D56">
-        <v>84.72</v>
+        <v>54.85</v>
       </c>
       <c r="E56" t="s">
         <v>634</v>
       </c>
       <c r="F56">
-        <v>86.5</v>
+        <v>60.31</v>
       </c>
       <c r="G56">
-        <v>2.1</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -4544,16 +4564,16 @@
         <v>598</v>
       </c>
       <c r="D57">
-        <v>58.75</v>
+        <v>61.93</v>
       </c>
       <c r="E57" t="s">
         <v>634</v>
       </c>
       <c r="F57">
-        <v>55.83</v>
+        <v>60.73</v>
       </c>
       <c r="G57">
-        <v>-4.97</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4567,16 +4587,16 @@
         <v>599</v>
       </c>
       <c r="D58">
-        <v>13.99</v>
+        <v>24.93</v>
       </c>
       <c r="E58" t="s">
         <v>637</v>
       </c>
       <c r="F58">
-        <v>19.65</v>
+        <v>26.44</v>
       </c>
       <c r="G58">
-        <v>40.46</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4590,16 +4610,16 @@
         <v>599</v>
       </c>
       <c r="D59">
-        <v>15.47</v>
+        <v>10.5</v>
       </c>
       <c r="E59" t="s">
         <v>637</v>
       </c>
       <c r="F59">
-        <v>16.27</v>
+        <v>13.28</v>
       </c>
       <c r="G59">
-        <v>5.17</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4613,16 +4633,16 @@
         <v>599</v>
       </c>
       <c r="D60">
-        <v>65.52</v>
+        <v>223</v>
       </c>
       <c r="E60" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F60">
-        <v>65.7</v>
+        <v>219.4</v>
       </c>
       <c r="G60">
-        <v>0.27</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -4636,16 +4656,16 @@
         <v>599</v>
       </c>
       <c r="D61">
-        <v>252</v>
+        <v>29.98</v>
       </c>
       <c r="E61" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F61">
-        <v>249.3</v>
+        <v>33.5</v>
       </c>
       <c r="G61">
-        <v>-1.07</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -4659,16 +4679,16 @@
         <v>599</v>
       </c>
       <c r="D62">
-        <v>32</v>
+        <v>100.24</v>
       </c>
       <c r="E62" t="s">
         <v>637</v>
       </c>
       <c r="F62">
-        <v>33.95</v>
+        <v>126.7</v>
       </c>
       <c r="G62">
-        <v>6.09</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4682,16 +4702,16 @@
         <v>599</v>
       </c>
       <c r="D63">
-        <v>100.24</v>
+        <v>252</v>
       </c>
       <c r="E63" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F63">
-        <v>126.7</v>
+        <v>249.3</v>
       </c>
       <c r="G63">
-        <v>26.4</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4705,16 +4725,16 @@
         <v>599</v>
       </c>
       <c r="D64">
-        <v>29.98</v>
+        <v>65.52</v>
       </c>
       <c r="E64" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F64">
-        <v>33.5</v>
+        <v>65.7</v>
       </c>
       <c r="G64">
-        <v>11.74</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4728,16 +4748,16 @@
         <v>599</v>
       </c>
       <c r="D65">
-        <v>223</v>
+        <v>15.47</v>
       </c>
       <c r="E65" t="s">
         <v>637</v>
       </c>
       <c r="F65">
-        <v>219.4</v>
+        <v>16.27</v>
       </c>
       <c r="G65">
-        <v>-1.61</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -4751,16 +4771,16 @@
         <v>599</v>
       </c>
       <c r="D66">
-        <v>10.5</v>
+        <v>13.99</v>
       </c>
       <c r="E66" t="s">
         <v>637</v>
       </c>
       <c r="F66">
-        <v>13.28</v>
+        <v>19.65</v>
       </c>
       <c r="G66">
-        <v>26.48</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4774,16 +4794,16 @@
         <v>599</v>
       </c>
       <c r="D67">
-        <v>24.93</v>
+        <v>32</v>
       </c>
       <c r="E67" t="s">
         <v>637</v>
       </c>
       <c r="F67">
-        <v>26.44</v>
+        <v>33.95</v>
       </c>
       <c r="G67">
-        <v>6.06</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4797,16 +4817,16 @@
         <v>600</v>
       </c>
       <c r="D68">
-        <v>140</v>
+        <v>27.3</v>
       </c>
       <c r="E68" t="s">
         <v>639</v>
       </c>
       <c r="F68">
-        <v>144.31</v>
+        <v>26.65</v>
       </c>
       <c r="G68">
-        <v>3.08</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4820,16 +4840,16 @@
         <v>600</v>
       </c>
       <c r="D69">
-        <v>26.28</v>
+        <v>140</v>
       </c>
       <c r="E69" t="s">
         <v>640</v>
       </c>
       <c r="F69">
-        <v>26.85</v>
+        <v>144.31</v>
       </c>
       <c r="G69">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4843,16 +4863,16 @@
         <v>600</v>
       </c>
       <c r="D70">
-        <v>57.94</v>
+        <v>26.28</v>
       </c>
       <c r="E70" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F70">
-        <v>60.04</v>
+        <v>26.85</v>
       </c>
       <c r="G70">
-        <v>3.62</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -4866,16 +4886,16 @@
         <v>600</v>
       </c>
       <c r="D71">
-        <v>29.4</v>
+        <v>57.94</v>
       </c>
       <c r="E71" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F71">
-        <v>26.82</v>
+        <v>60.04</v>
       </c>
       <c r="G71">
-        <v>-8.779999999999999</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -4889,24 +4909,24 @@
         <v>600</v>
       </c>
       <c r="D72">
-        <v>27.3</v>
+        <v>29.4</v>
       </c>
       <c r="E72" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F72">
-        <v>26.65</v>
+        <v>26.82</v>
       </c>
       <c r="G72">
-        <v>-2.38</v>
+        <v>-8.779999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B73" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C73" t="s">
         <v>600</v>
@@ -4915,7 +4935,7 @@
         <v>32.52</v>
       </c>
       <c r="E73" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F73">
         <v>31.9</v>
@@ -4938,7 +4958,7 @@
         <v>2.15</v>
       </c>
       <c r="E74" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F74">
         <v>2.15</v>
@@ -4961,7 +4981,7 @@
         <v>37</v>
       </c>
       <c r="E75" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F75">
         <v>41.69</v>
@@ -4984,7 +5004,7 @@
         <v>22.81</v>
       </c>
       <c r="E76" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F76">
         <v>23.51</v>
@@ -5007,7 +5027,7 @@
         <v>4.75</v>
       </c>
       <c r="E77" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F77">
         <v>4.81</v>
@@ -5027,16 +5047,16 @@
         <v>601</v>
       </c>
       <c r="D78">
-        <v>56.3</v>
+        <v>80.27</v>
       </c>
       <c r="E78" t="s">
         <v>642</v>
       </c>
       <c r="F78">
-        <v>50.71</v>
+        <v>73.53</v>
       </c>
       <c r="G78">
-        <v>-9.93</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5050,200 +5070,200 @@
         <v>601</v>
       </c>
       <c r="D79">
-        <v>333</v>
+        <v>14.7</v>
       </c>
       <c r="E79" t="s">
         <v>643</v>
       </c>
       <c r="F79">
-        <v>331.9</v>
+        <v>13.65</v>
       </c>
       <c r="G79">
-        <v>-0.33</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C80" t="s">
         <v>601</v>
       </c>
       <c r="D80">
-        <v>35.62</v>
+        <v>294.01</v>
       </c>
       <c r="E80" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F80">
-        <v>31.82</v>
+        <v>354</v>
       </c>
       <c r="G80">
-        <v>-10.67</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B81" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C81" t="s">
         <v>601</v>
       </c>
       <c r="D81">
-        <v>18.55</v>
+        <v>41.92</v>
       </c>
       <c r="E81" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F81">
-        <v>12.52</v>
+        <v>35.76</v>
       </c>
       <c r="G81">
-        <v>-32.51</v>
+        <v>-14.69</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B82" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C82" t="s">
         <v>601</v>
       </c>
       <c r="D82">
-        <v>61.16</v>
+        <v>6.88</v>
       </c>
       <c r="E82" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F82">
-        <v>58.86</v>
+        <v>6.11</v>
       </c>
       <c r="G82">
-        <v>-3.76</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B83" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C83" t="s">
         <v>601</v>
       </c>
       <c r="D83">
-        <v>6.88</v>
+        <v>333</v>
       </c>
       <c r="E83" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F83">
-        <v>6.11</v>
+        <v>331.9</v>
       </c>
       <c r="G83">
-        <v>-11.19</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C84" t="s">
         <v>601</v>
       </c>
       <c r="D84">
-        <v>14.7</v>
+        <v>18.55</v>
       </c>
       <c r="E84" t="s">
         <v>644</v>
       </c>
       <c r="F84">
-        <v>13.65</v>
+        <v>12.52</v>
       </c>
       <c r="G84">
-        <v>-7.14</v>
+        <v>-32.51</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C85" t="s">
         <v>601</v>
       </c>
       <c r="D85">
-        <v>80.27</v>
+        <v>35.62</v>
       </c>
       <c r="E85" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F85">
-        <v>73.53</v>
+        <v>31.82</v>
       </c>
       <c r="G85">
-        <v>-8.4</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B86" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="C86" t="s">
         <v>601</v>
       </c>
       <c r="D86">
-        <v>41.92</v>
+        <v>61.16</v>
       </c>
       <c r="E86" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F86">
-        <v>35.76</v>
+        <v>58.86</v>
       </c>
       <c r="G86">
-        <v>-14.69</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B87" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="C87" t="s">
         <v>601</v>
       </c>
       <c r="D87">
-        <v>294.01</v>
+        <v>56.3</v>
       </c>
       <c r="E87" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F87">
-        <v>354</v>
+        <v>50.71</v>
       </c>
       <c r="G87">
-        <v>20.4</v>
+        <v>-9.93</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5441,16 +5461,16 @@
         <v>603</v>
       </c>
       <c r="D96">
-        <v>24.6</v>
+        <v>54.38</v>
       </c>
       <c r="E96" t="s">
         <v>652</v>
       </c>
       <c r="F96">
-        <v>24.97</v>
+        <v>54.25</v>
       </c>
       <c r="G96">
-        <v>1.5</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -5464,16 +5484,16 @@
         <v>603</v>
       </c>
       <c r="D97">
-        <v>84.98</v>
+        <v>27.88</v>
       </c>
       <c r="E97" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F97">
-        <v>83.27</v>
+        <v>28.49</v>
       </c>
       <c r="G97">
-        <v>-2.01</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -5487,16 +5507,16 @@
         <v>603</v>
       </c>
       <c r="D98">
-        <v>7.05</v>
+        <v>15.52</v>
       </c>
       <c r="E98" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F98">
-        <v>7.01</v>
+        <v>15.46</v>
       </c>
       <c r="G98">
-        <v>-0.57</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -5510,16 +5530,16 @@
         <v>603</v>
       </c>
       <c r="D99">
-        <v>15.52</v>
+        <v>14.45</v>
       </c>
       <c r="E99" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F99">
-        <v>15.46</v>
+        <v>14.48</v>
       </c>
       <c r="G99">
-        <v>-0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -5533,16 +5553,16 @@
         <v>603</v>
       </c>
       <c r="D100">
-        <v>14.45</v>
+        <v>84.98</v>
       </c>
       <c r="E100" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F100">
-        <v>14.48</v>
+        <v>83.27</v>
       </c>
       <c r="G100">
-        <v>0.21</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -5556,16 +5576,16 @@
         <v>603</v>
       </c>
       <c r="D101">
-        <v>27.88</v>
+        <v>24.6</v>
       </c>
       <c r="E101" t="s">
         <v>652</v>
       </c>
       <c r="F101">
-        <v>28.49</v>
+        <v>24.97</v>
       </c>
       <c r="G101">
-        <v>2.19</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -5579,16 +5599,16 @@
         <v>603</v>
       </c>
       <c r="D102">
-        <v>54.38</v>
+        <v>7.05</v>
       </c>
       <c r="E102" t="s">
         <v>652</v>
       </c>
       <c r="F102">
-        <v>54.25</v>
+        <v>7.01</v>
       </c>
       <c r="G102">
-        <v>-0.24</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -5602,16 +5622,16 @@
         <v>604</v>
       </c>
       <c r="D103">
-        <v>6.78</v>
+        <v>22.2</v>
       </c>
       <c r="E103" t="s">
         <v>647</v>
       </c>
       <c r="F103">
-        <v>6.54</v>
+        <v>23.35</v>
       </c>
       <c r="G103">
-        <v>-3.54</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -5625,16 +5645,16 @@
         <v>604</v>
       </c>
       <c r="D104">
-        <v>36.23</v>
+        <v>6.78</v>
       </c>
       <c r="E104" t="s">
         <v>647</v>
       </c>
       <c r="F104">
-        <v>45.02</v>
+        <v>6.54</v>
       </c>
       <c r="G104">
-        <v>24.26</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -5648,16 +5668,16 @@
         <v>604</v>
       </c>
       <c r="D105">
-        <v>47.33</v>
+        <v>36.23</v>
       </c>
       <c r="E105" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="F105">
-        <v>47.25</v>
+        <v>45.02</v>
       </c>
       <c r="G105">
-        <v>-0.17</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -5671,16 +5691,16 @@
         <v>604</v>
       </c>
       <c r="D106">
-        <v>28.8</v>
+        <v>47.33</v>
       </c>
       <c r="E106" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="F106">
-        <v>28.57</v>
+        <v>47.25</v>
       </c>
       <c r="G106">
-        <v>-0.8</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -5694,16 +5714,16 @@
         <v>604</v>
       </c>
       <c r="D107">
-        <v>16.1</v>
+        <v>28.8</v>
       </c>
       <c r="E107" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="F107">
-        <v>15.64</v>
+        <v>28.57</v>
       </c>
       <c r="G107">
-        <v>-2.86</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -5717,16 +5737,16 @@
         <v>604</v>
       </c>
       <c r="D108">
-        <v>22.2</v>
+        <v>16.1</v>
       </c>
       <c r="E108" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="F108">
-        <v>23.35</v>
+        <v>15.64</v>
       </c>
       <c r="G108">
-        <v>5.18</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -5777,10 +5797,10 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B111" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C111" t="s">
         <v>604</v>
@@ -5832,16 +5852,16 @@
         <v>605</v>
       </c>
       <c r="D113">
-        <v>71</v>
+        <v>3.92</v>
       </c>
       <c r="E113" t="s">
         <v>658</v>
       </c>
       <c r="F113">
-        <v>78.79000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="G113">
-        <v>10.97</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5855,16 +5875,16 @@
         <v>605</v>
       </c>
       <c r="D114">
-        <v>289</v>
+        <v>6.1</v>
       </c>
       <c r="E114" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F114">
-        <v>338</v>
+        <v>6.17</v>
       </c>
       <c r="G114">
-        <v>16.96</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5878,16 +5898,16 @@
         <v>605</v>
       </c>
       <c r="D115">
-        <v>4.84</v>
+        <v>23.3</v>
       </c>
       <c r="E115" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F115">
-        <v>4.41</v>
+        <v>23.32</v>
       </c>
       <c r="G115">
-        <v>-8.880000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5901,16 +5921,16 @@
         <v>605</v>
       </c>
       <c r="D116">
-        <v>145.59</v>
+        <v>27</v>
       </c>
       <c r="E116" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F116">
-        <v>159.19</v>
+        <v>26.73</v>
       </c>
       <c r="G116">
-        <v>9.34</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5924,16 +5944,16 @@
         <v>605</v>
       </c>
       <c r="D117">
-        <v>41.79</v>
+        <v>20</v>
       </c>
       <c r="E117" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F117">
-        <v>56.27</v>
+        <v>19.31</v>
       </c>
       <c r="G117">
-        <v>34.65</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5947,16 +5967,16 @@
         <v>605</v>
       </c>
       <c r="D118">
-        <v>27</v>
+        <v>145.59</v>
       </c>
       <c r="E118" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F118">
-        <v>26.73</v>
+        <v>159.19</v>
       </c>
       <c r="G118">
-        <v>-1</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5970,16 +5990,16 @@
         <v>605</v>
       </c>
       <c r="D119">
-        <v>6.1</v>
+        <v>71</v>
       </c>
       <c r="E119" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F119">
-        <v>6.17</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G119">
-        <v>1.15</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5993,16 +6013,16 @@
         <v>605</v>
       </c>
       <c r="D120">
-        <v>20</v>
+        <v>41.79</v>
       </c>
       <c r="E120" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F120">
-        <v>19.31</v>
+        <v>56.27</v>
       </c>
       <c r="G120">
-        <v>-3.45</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6016,16 +6036,16 @@
         <v>605</v>
       </c>
       <c r="D121">
-        <v>23.3</v>
+        <v>4.84</v>
       </c>
       <c r="E121" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F121">
-        <v>23.32</v>
+        <v>4.41</v>
       </c>
       <c r="G121">
-        <v>0.09</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6039,16 +6059,16 @@
         <v>605</v>
       </c>
       <c r="D122">
-        <v>3.92</v>
+        <v>289</v>
       </c>
       <c r="E122" t="s">
         <v>659</v>
       </c>
       <c r="F122">
-        <v>3.9</v>
+        <v>338</v>
       </c>
       <c r="G122">
-        <v>-0.51</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6062,16 +6082,16 @@
         <v>606</v>
       </c>
       <c r="D123">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="E123" t="s">
         <v>660</v>
       </c>
       <c r="F123">
-        <v>28.88</v>
+        <v>118.43</v>
       </c>
       <c r="G123">
-        <v>11.08</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6085,131 +6105,131 @@
         <v>606</v>
       </c>
       <c r="D124">
-        <v>53.9</v>
+        <v>5.08</v>
       </c>
       <c r="E124" t="s">
         <v>660</v>
       </c>
       <c r="F124">
-        <v>59.81</v>
+        <v>4.6</v>
       </c>
       <c r="G124">
-        <v>10.96</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="B125" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="C125" t="s">
         <v>606</v>
       </c>
       <c r="D125">
-        <v>127</v>
+        <v>28.94</v>
       </c>
       <c r="E125" t="s">
         <v>660</v>
       </c>
       <c r="F125">
-        <v>130.97</v>
+        <v>30.76</v>
       </c>
       <c r="G125">
-        <v>3.13</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B126" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C126" t="s">
         <v>606</v>
       </c>
       <c r="D126">
-        <v>38.2</v>
+        <v>17.95</v>
       </c>
       <c r="E126" t="s">
         <v>660</v>
       </c>
       <c r="F126">
-        <v>47</v>
+        <v>20.77</v>
       </c>
       <c r="G126">
-        <v>23.04</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C127" t="s">
         <v>606</v>
       </c>
       <c r="D127">
-        <v>16.73</v>
+        <v>7.01</v>
       </c>
       <c r="E127" t="s">
         <v>660</v>
       </c>
       <c r="F127">
-        <v>17.67</v>
+        <v>7.13</v>
       </c>
       <c r="G127">
-        <v>5.62</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B128" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C128" t="s">
         <v>606</v>
       </c>
       <c r="D128">
-        <v>17.95</v>
+        <v>38.2</v>
       </c>
       <c r="E128" t="s">
         <v>660</v>
       </c>
       <c r="F128">
-        <v>20.77</v>
+        <v>47</v>
       </c>
       <c r="G128">
-        <v>15.71</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="B129" t="s">
-        <v>442</v>
+        <v>381</v>
       </c>
       <c r="C129" t="s">
         <v>606</v>
       </c>
       <c r="D129">
-        <v>7.01</v>
+        <v>127</v>
       </c>
       <c r="E129" t="s">
         <v>660</v>
       </c>
       <c r="F129">
-        <v>7.13</v>
+        <v>130.97</v>
       </c>
       <c r="G129">
-        <v>1.71</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6223,16 +6243,16 @@
         <v>606</v>
       </c>
       <c r="D130">
-        <v>28.94</v>
+        <v>53.9</v>
       </c>
       <c r="E130" t="s">
         <v>660</v>
       </c>
       <c r="F130">
-        <v>30.76</v>
+        <v>59.81</v>
       </c>
       <c r="G130">
-        <v>6.29</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6246,16 +6266,16 @@
         <v>606</v>
       </c>
       <c r="D131">
-        <v>5.08</v>
+        <v>26</v>
       </c>
       <c r="E131" t="s">
         <v>660</v>
       </c>
       <c r="F131">
-        <v>4.6</v>
+        <v>28.88</v>
       </c>
       <c r="G131">
-        <v>-9.449999999999999</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6269,16 +6289,16 @@
         <v>606</v>
       </c>
       <c r="D132">
-        <v>113</v>
+        <v>16.73</v>
       </c>
       <c r="E132" t="s">
         <v>660</v>
       </c>
       <c r="F132">
-        <v>118.43</v>
+        <v>17.67</v>
       </c>
       <c r="G132">
-        <v>4.81</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -6292,16 +6312,16 @@
         <v>607</v>
       </c>
       <c r="D133">
-        <v>31.4</v>
+        <v>110</v>
       </c>
       <c r="E133" t="s">
         <v>661</v>
       </c>
       <c r="F133">
-        <v>28.23</v>
+        <v>105</v>
       </c>
       <c r="G133">
-        <v>-10.1</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -6315,16 +6335,16 @@
         <v>607</v>
       </c>
       <c r="D134">
-        <v>21.98</v>
+        <v>47.42</v>
       </c>
       <c r="E134" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F134">
-        <v>24.98</v>
+        <v>45.6</v>
       </c>
       <c r="G134">
-        <v>13.65</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -6338,108 +6358,108 @@
         <v>607</v>
       </c>
       <c r="D135">
-        <v>8.369999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="E135" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F135">
-        <v>8.4</v>
+        <v>11.17</v>
       </c>
       <c r="G135">
-        <v>0.36</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B136" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="C136" t="s">
         <v>607</v>
       </c>
       <c r="D136">
-        <v>106.8</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E136" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F136">
-        <v>110.11</v>
+        <v>61.4</v>
       </c>
       <c r="G136">
-        <v>3.1</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B137" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C137" t="s">
         <v>607</v>
       </c>
       <c r="D137">
-        <v>18.8</v>
+        <v>22.83</v>
       </c>
       <c r="E137" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F137">
-        <v>19.59</v>
+        <v>24.63</v>
       </c>
       <c r="G137">
-        <v>4.2</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B138" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C138" t="s">
         <v>607</v>
       </c>
       <c r="D138">
-        <v>22.83</v>
+        <v>18.8</v>
       </c>
       <c r="E138" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F138">
-        <v>24.63</v>
+        <v>19.59</v>
       </c>
       <c r="G138">
-        <v>7.88</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B139" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="C139" t="s">
         <v>607</v>
       </c>
       <c r="D139">
-        <v>65.73999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E139" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F139">
-        <v>61.4</v>
+        <v>8.4</v>
       </c>
       <c r="G139">
-        <v>-6.6</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -6453,16 +6473,16 @@
         <v>607</v>
       </c>
       <c r="D140">
-        <v>9.4</v>
+        <v>21.98</v>
       </c>
       <c r="E140" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F140">
-        <v>11.17</v>
+        <v>24.98</v>
       </c>
       <c r="G140">
-        <v>18.83</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -6476,16 +6496,16 @@
         <v>607</v>
       </c>
       <c r="D141">
-        <v>47.42</v>
+        <v>31.4</v>
       </c>
       <c r="E141" t="s">
         <v>662</v>
       </c>
       <c r="F141">
-        <v>45.6</v>
+        <v>28.23</v>
       </c>
       <c r="G141">
-        <v>-3.84</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -6499,223 +6519,223 @@
         <v>607</v>
       </c>
       <c r="D142">
-        <v>110</v>
+        <v>106.8</v>
       </c>
       <c r="E142" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F142">
-        <v>105</v>
+        <v>110.11</v>
       </c>
       <c r="G142">
-        <v>-4.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B143" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C143" t="s">
         <v>608</v>
       </c>
       <c r="D143">
-        <v>181.29</v>
+        <v>37.9</v>
       </c>
       <c r="E143" t="s">
         <v>663</v>
       </c>
       <c r="F143">
-        <v>191.66</v>
+        <v>43.45</v>
       </c>
       <c r="G143">
-        <v>5.72</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B144" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C144" t="s">
         <v>608</v>
       </c>
       <c r="D144">
-        <v>14.41</v>
+        <v>8.82</v>
       </c>
       <c r="E144" t="s">
         <v>663</v>
       </c>
       <c r="F144">
-        <v>17.22</v>
+        <v>8.27</v>
       </c>
       <c r="G144">
-        <v>19.5</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B145" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C145" t="s">
         <v>608</v>
       </c>
       <c r="D145">
-        <v>40.07</v>
+        <v>65.22</v>
       </c>
       <c r="E145" t="s">
         <v>663</v>
       </c>
       <c r="F145">
-        <v>45.14</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G145">
-        <v>12.65</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B146" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C146" t="s">
         <v>608</v>
       </c>
       <c r="D146">
-        <v>40.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E146" t="s">
         <v>663</v>
       </c>
       <c r="F146">
-        <v>47.29</v>
+        <v>95.16</v>
       </c>
       <c r="G146">
-        <v>16.19</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C147" t="s">
         <v>608</v>
       </c>
       <c r="D147">
-        <v>56.49</v>
+        <v>18.2</v>
       </c>
       <c r="E147" t="s">
         <v>663</v>
       </c>
       <c r="F147">
-        <v>77.11</v>
+        <v>17.9</v>
       </c>
       <c r="G147">
-        <v>36.5</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B148" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C148" t="s">
         <v>608</v>
       </c>
       <c r="D148">
-        <v>18.2</v>
+        <v>56.49</v>
       </c>
       <c r="E148" t="s">
         <v>663</v>
       </c>
       <c r="F148">
-        <v>17.9</v>
+        <v>77.11</v>
       </c>
       <c r="G148">
-        <v>-1.65</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B149" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C149" t="s">
         <v>608</v>
       </c>
       <c r="D149">
-        <v>95.09999999999999</v>
+        <v>40.07</v>
       </c>
       <c r="E149" t="s">
         <v>663</v>
       </c>
       <c r="F149">
-        <v>95.16</v>
+        <v>45.14</v>
       </c>
       <c r="G149">
-        <v>0.06</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B150" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C150" t="s">
         <v>608</v>
       </c>
       <c r="D150">
-        <v>65.22</v>
+        <v>14.41</v>
       </c>
       <c r="E150" t="s">
         <v>663</v>
       </c>
       <c r="F150">
-        <v>76.09999999999999</v>
+        <v>17.22</v>
       </c>
       <c r="G150">
-        <v>16.68</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B151" t="s">
-        <v>462</v>
+        <v>432</v>
       </c>
       <c r="C151" t="s">
         <v>608</v>
       </c>
       <c r="D151">
-        <v>8.82</v>
+        <v>181.29</v>
       </c>
       <c r="E151" t="s">
         <v>663</v>
       </c>
       <c r="F151">
-        <v>8.27</v>
+        <v>191.66</v>
       </c>
       <c r="G151">
-        <v>-6.24</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -6729,16 +6749,16 @@
         <v>608</v>
       </c>
       <c r="D152">
-        <v>37.9</v>
+        <v>40.7</v>
       </c>
       <c r="E152" t="s">
         <v>663</v>
       </c>
       <c r="F152">
-        <v>43.45</v>
+        <v>47.29</v>
       </c>
       <c r="G152">
-        <v>14.64</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -6752,93 +6772,93 @@
         <v>609</v>
       </c>
       <c r="D153">
-        <v>35.6</v>
+        <v>25</v>
       </c>
       <c r="E153" t="s">
         <v>664</v>
       </c>
       <c r="F153">
-        <v>36.29</v>
+        <v>30.35</v>
       </c>
       <c r="G153">
-        <v>1.94</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="B154" t="s">
-        <v>465</v>
+        <v>401</v>
       </c>
       <c r="C154" t="s">
         <v>609</v>
       </c>
       <c r="D154">
-        <v>115.38</v>
+        <v>37.87</v>
       </c>
       <c r="E154" t="s">
         <v>664</v>
       </c>
       <c r="F154">
-        <v>102.39</v>
+        <v>32.38</v>
       </c>
       <c r="G154">
-        <v>-11.26</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B155" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="C155" t="s">
         <v>609</v>
       </c>
       <c r="D155">
-        <v>14.19</v>
+        <v>3.65</v>
       </c>
       <c r="E155" t="s">
         <v>664</v>
       </c>
       <c r="F155">
-        <v>11.85</v>
+        <v>3.5</v>
       </c>
       <c r="G155">
-        <v>-16.49</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="B156" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C156" t="s">
         <v>609</v>
       </c>
       <c r="D156">
-        <v>60.01</v>
+        <v>14.19</v>
       </c>
       <c r="E156" t="s">
         <v>664</v>
       </c>
       <c r="F156">
-        <v>61.31</v>
+        <v>11.85</v>
       </c>
       <c r="G156">
-        <v>2.17</v>
+        <v>-16.49</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B157" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C157" t="s">
         <v>609</v>
@@ -6858,94 +6878,94 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B158" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C158" t="s">
         <v>609</v>
       </c>
       <c r="D158">
-        <v>5.06</v>
+        <v>35.6</v>
       </c>
       <c r="E158" t="s">
         <v>664</v>
       </c>
       <c r="F158">
-        <v>4.85</v>
+        <v>36.29</v>
       </c>
       <c r="G158">
-        <v>-4.15</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B159" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C159" t="s">
         <v>609</v>
       </c>
       <c r="D159">
-        <v>25</v>
+        <v>115.38</v>
       </c>
       <c r="E159" t="s">
         <v>664</v>
       </c>
       <c r="F159">
-        <v>30.35</v>
+        <v>102.39</v>
       </c>
       <c r="G159">
-        <v>21.4</v>
+        <v>-11.26</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B160" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C160" t="s">
         <v>609</v>
       </c>
       <c r="D160">
-        <v>3.65</v>
+        <v>5.06</v>
       </c>
       <c r="E160" t="s">
         <v>664</v>
       </c>
       <c r="F160">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="G160">
-        <v>-4.11</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="B161" t="s">
-        <v>398</v>
+        <v>470</v>
       </c>
       <c r="C161" t="s">
         <v>609</v>
       </c>
       <c r="D161">
-        <v>37.87</v>
+        <v>60.01</v>
       </c>
       <c r="E161" t="s">
         <v>664</v>
       </c>
       <c r="F161">
-        <v>32.38</v>
+        <v>61.31</v>
       </c>
       <c r="G161">
-        <v>-14.5</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7120,16 +7140,16 @@
         <v>611</v>
       </c>
       <c r="D169">
-        <v>17.63</v>
+        <v>66.28</v>
       </c>
       <c r="E169" t="s">
         <v>666</v>
       </c>
       <c r="F169">
-        <v>15.36</v>
+        <v>61.01</v>
       </c>
       <c r="G169">
-        <v>-12.88</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7143,16 +7163,16 @@
         <v>611</v>
       </c>
       <c r="D170">
-        <v>38.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="E170" t="s">
         <v>666</v>
       </c>
       <c r="F170">
-        <v>38.27</v>
+        <v>7.21</v>
       </c>
       <c r="G170">
-        <v>-0.6</v>
+        <v>-13.03</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7166,16 +7186,16 @@
         <v>611</v>
       </c>
       <c r="D171">
-        <v>114</v>
+        <v>2.47</v>
       </c>
       <c r="E171" t="s">
         <v>666</v>
       </c>
       <c r="F171">
-        <v>114.39</v>
+        <v>3.35</v>
       </c>
       <c r="G171">
-        <v>0.34</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7189,16 +7209,16 @@
         <v>611</v>
       </c>
       <c r="D172">
-        <v>30.77</v>
+        <v>8.43</v>
       </c>
       <c r="E172" t="s">
         <v>666</v>
       </c>
       <c r="F172">
-        <v>34.09</v>
+        <v>8.17</v>
       </c>
       <c r="G172">
-        <v>10.79</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7212,16 +7232,16 @@
         <v>611</v>
       </c>
       <c r="D173">
-        <v>41.29</v>
+        <v>5.72</v>
       </c>
       <c r="E173" t="s">
         <v>666</v>
       </c>
       <c r="F173">
-        <v>36.77</v>
+        <v>4.89</v>
       </c>
       <c r="G173">
-        <v>-10.95</v>
+        <v>-14.51</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7235,16 +7255,16 @@
         <v>611</v>
       </c>
       <c r="D174">
-        <v>8.43</v>
+        <v>38.5</v>
       </c>
       <c r="E174" t="s">
         <v>666</v>
       </c>
       <c r="F174">
-        <v>8.17</v>
+        <v>38.27</v>
       </c>
       <c r="G174">
-        <v>-3.08</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7258,16 +7278,16 @@
         <v>611</v>
       </c>
       <c r="D175">
-        <v>2.47</v>
+        <v>41.29</v>
       </c>
       <c r="E175" t="s">
         <v>666</v>
       </c>
       <c r="F175">
-        <v>3.35</v>
+        <v>36.77</v>
       </c>
       <c r="G175">
-        <v>35.63</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7281,16 +7301,16 @@
         <v>611</v>
       </c>
       <c r="D176">
-        <v>5.72</v>
+        <v>114</v>
       </c>
       <c r="E176" t="s">
         <v>666</v>
       </c>
       <c r="F176">
-        <v>4.89</v>
+        <v>114.39</v>
       </c>
       <c r="G176">
-        <v>-14.51</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7304,16 +7324,16 @@
         <v>611</v>
       </c>
       <c r="D177">
-        <v>8.289999999999999</v>
+        <v>17.63</v>
       </c>
       <c r="E177" t="s">
         <v>666</v>
       </c>
       <c r="F177">
-        <v>7.21</v>
+        <v>15.36</v>
       </c>
       <c r="G177">
-        <v>-13.03</v>
+        <v>-12.88</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7327,16 +7347,16 @@
         <v>611</v>
       </c>
       <c r="D178">
-        <v>66.28</v>
+        <v>30.77</v>
       </c>
       <c r="E178" t="s">
         <v>666</v>
       </c>
       <c r="F178">
-        <v>61.01</v>
+        <v>34.09</v>
       </c>
       <c r="G178">
-        <v>-7.95</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7350,16 +7370,16 @@
         <v>612</v>
       </c>
       <c r="D179">
-        <v>8.550000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="E179" t="s">
         <v>667</v>
       </c>
       <c r="F179">
-        <v>9</v>
+        <v>6.48</v>
       </c>
       <c r="G179">
-        <v>5.26</v>
+        <v>-11.84</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7373,177 +7393,177 @@
         <v>612</v>
       </c>
       <c r="D180">
-        <v>15.78</v>
+        <v>21.41</v>
       </c>
       <c r="E180" t="s">
         <v>668</v>
       </c>
       <c r="F180">
-        <v>15.97</v>
+        <v>16.91</v>
       </c>
       <c r="G180">
-        <v>1.2</v>
+        <v>-21.02</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="B181" t="s">
-        <v>490</v>
+        <v>445</v>
       </c>
       <c r="C181" t="s">
         <v>612</v>
       </c>
       <c r="D181">
-        <v>2.45</v>
+        <v>27.37</v>
       </c>
       <c r="E181" t="s">
         <v>669</v>
       </c>
       <c r="F181">
-        <v>2.36</v>
+        <v>27.15</v>
       </c>
       <c r="G181">
-        <v>-3.67</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B182" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C182" t="s">
         <v>612</v>
       </c>
       <c r="D182">
-        <v>11.7</v>
+        <v>50.33</v>
       </c>
       <c r="E182" t="s">
         <v>670</v>
       </c>
       <c r="F182">
-        <v>10.31</v>
+        <v>50.4</v>
       </c>
       <c r="G182">
-        <v>-11.88</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B183" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C183" t="s">
         <v>612</v>
       </c>
       <c r="D183">
-        <v>46.93</v>
+        <v>17</v>
       </c>
       <c r="E183" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F183">
-        <v>46.24</v>
+        <v>18.78</v>
       </c>
       <c r="G183">
-        <v>-1.47</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B184" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C184" t="s">
         <v>612</v>
       </c>
       <c r="D184">
-        <v>21.41</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E184" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F184">
-        <v>16.91</v>
+        <v>9</v>
       </c>
       <c r="G184">
-        <v>-21.02</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B185" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C185" t="s">
         <v>612</v>
       </c>
       <c r="D185">
-        <v>50.33</v>
+        <v>2.45</v>
       </c>
       <c r="E185" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F185">
-        <v>50.4</v>
+        <v>2.36</v>
       </c>
       <c r="G185">
-        <v>0.14</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B186" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C186" t="s">
         <v>612</v>
       </c>
       <c r="D186">
-        <v>17</v>
+        <v>15.78</v>
       </c>
       <c r="E186" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F186">
-        <v>18.78</v>
+        <v>15.97</v>
       </c>
       <c r="G186">
-        <v>10.47</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="B187" t="s">
-        <v>440</v>
+        <v>495</v>
       </c>
       <c r="C187" t="s">
         <v>612</v>
       </c>
       <c r="D187">
-        <v>27.37</v>
+        <v>11.7</v>
       </c>
       <c r="E187" t="s">
         <v>667</v>
       </c>
       <c r="F187">
-        <v>27.15</v>
+        <v>10.31</v>
       </c>
       <c r="G187">
-        <v>-0.8</v>
+        <v>-11.88</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7557,85 +7577,85 @@
         <v>612</v>
       </c>
       <c r="D188">
-        <v>7.35</v>
+        <v>46.93</v>
       </c>
       <c r="E188" t="s">
         <v>670</v>
       </c>
       <c r="F188">
-        <v>6.48</v>
+        <v>46.24</v>
       </c>
       <c r="G188">
-        <v>-11.84</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B189" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C189" t="s">
         <v>613</v>
       </c>
       <c r="D189">
-        <v>57.43</v>
+        <v>52.48</v>
       </c>
       <c r="E189" t="s">
         <v>672</v>
       </c>
       <c r="F189">
-        <v>66.40000000000001</v>
+        <v>50.93</v>
       </c>
       <c r="G189">
-        <v>15.62</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B190" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C190" t="s">
         <v>613</v>
       </c>
       <c r="D190">
-        <v>37.38</v>
+        <v>18.95</v>
       </c>
       <c r="E190" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F190">
-        <v>39.12</v>
+        <v>19.13</v>
       </c>
       <c r="G190">
-        <v>4.65</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>56</v>
+        <v>228</v>
       </c>
       <c r="B191" t="s">
-        <v>326</v>
+        <v>498</v>
       </c>
       <c r="C191" t="s">
         <v>613</v>
       </c>
       <c r="D191">
-        <v>43.8</v>
+        <v>12.8</v>
       </c>
       <c r="E191" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F191">
-        <v>43.36</v>
+        <v>12.81</v>
       </c>
       <c r="G191">
-        <v>-1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -7649,154 +7669,154 @@
         <v>613</v>
       </c>
       <c r="D192">
-        <v>44.15</v>
+        <v>62.85</v>
       </c>
       <c r="E192" t="s">
         <v>673</v>
       </c>
       <c r="F192">
-        <v>44.75</v>
+        <v>55.44</v>
       </c>
       <c r="G192">
-        <v>1.36</v>
+        <v>-11.79</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="B193" t="s">
-        <v>386</v>
+        <v>500</v>
       </c>
       <c r="C193" t="s">
         <v>613</v>
       </c>
       <c r="D193">
-        <v>35.11</v>
+        <v>1.94</v>
       </c>
       <c r="E193" t="s">
         <v>672</v>
       </c>
       <c r="F193">
-        <v>40.71</v>
+        <v>1.91</v>
       </c>
       <c r="G193">
-        <v>15.95</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B194" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C194" t="s">
         <v>613</v>
       </c>
       <c r="D194">
-        <v>12.8</v>
+        <v>57.43</v>
       </c>
       <c r="E194" t="s">
         <v>673</v>
       </c>
       <c r="F194">
-        <v>12.81</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G194">
-        <v>0.08</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B195" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C195" t="s">
         <v>613</v>
       </c>
       <c r="D195">
-        <v>1.94</v>
+        <v>44.15</v>
       </c>
       <c r="E195" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F195">
-        <v>1.91</v>
+        <v>44.75</v>
       </c>
       <c r="G195">
-        <v>-1.55</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>232</v>
+        <v>56</v>
       </c>
       <c r="B196" t="s">
-        <v>502</v>
+        <v>326</v>
       </c>
       <c r="C196" t="s">
         <v>613</v>
       </c>
       <c r="D196">
-        <v>62.85</v>
+        <v>43.8</v>
       </c>
       <c r="E196" t="s">
         <v>672</v>
       </c>
       <c r="F196">
-        <v>55.44</v>
+        <v>43.36</v>
       </c>
       <c r="G196">
-        <v>-11.79</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B197" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C197" t="s">
         <v>613</v>
       </c>
       <c r="D197">
-        <v>52.48</v>
+        <v>37.38</v>
       </c>
       <c r="E197" t="s">
         <v>673</v>
       </c>
       <c r="F197">
-        <v>50.93</v>
+        <v>39.12</v>
       </c>
       <c r="G197">
-        <v>-2.95</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>233</v>
+        <v>107</v>
       </c>
       <c r="B198" t="s">
-        <v>503</v>
+        <v>377</v>
       </c>
       <c r="C198" t="s">
         <v>613</v>
       </c>
       <c r="D198">
-        <v>18.95</v>
+        <v>35.11</v>
       </c>
       <c r="E198" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F198">
-        <v>19.13</v>
+        <v>40.71</v>
       </c>
       <c r="G198">
-        <v>0.95</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -7810,16 +7830,16 @@
         <v>614</v>
       </c>
       <c r="D199">
-        <v>59</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E199" t="s">
         <v>674</v>
       </c>
       <c r="F199">
-        <v>64.76000000000001</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="G199">
-        <v>9.76</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -7833,16 +7853,16 @@
         <v>614</v>
       </c>
       <c r="D200">
-        <v>16.51</v>
+        <v>19.9</v>
       </c>
       <c r="E200" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F200">
-        <v>17.32</v>
+        <v>19.08</v>
       </c>
       <c r="G200">
-        <v>4.91</v>
+        <v>-4.12</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -7856,16 +7876,16 @@
         <v>614</v>
       </c>
       <c r="D201">
-        <v>67.47</v>
+        <v>51</v>
       </c>
       <c r="E201" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F201">
-        <v>66.65000000000001</v>
+        <v>57.19</v>
       </c>
       <c r="G201">
-        <v>-1.22</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -7879,108 +7899,108 @@
         <v>614</v>
       </c>
       <c r="D202">
-        <v>24.22</v>
+        <v>99.92</v>
       </c>
       <c r="E202" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F202">
-        <v>25.26</v>
+        <v>112.71</v>
       </c>
       <c r="G202">
-        <v>4.29</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="B203" t="s">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="C203" t="s">
         <v>614</v>
       </c>
       <c r="D203">
-        <v>3.78</v>
+        <v>17.5</v>
       </c>
       <c r="E203" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F203">
-        <v>4.25</v>
+        <v>15.77</v>
       </c>
       <c r="G203">
-        <v>12.43</v>
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B204" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C204" t="s">
         <v>614</v>
       </c>
       <c r="D204">
-        <v>67.65000000000001</v>
+        <v>67.47</v>
       </c>
       <c r="E204" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F204">
-        <v>66.01000000000001</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="G204">
-        <v>-2.42</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B205" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C205" t="s">
         <v>614</v>
       </c>
       <c r="D205">
-        <v>19.9</v>
+        <v>16.51</v>
       </c>
       <c r="E205" t="s">
         <v>676</v>
       </c>
       <c r="F205">
-        <v>19.08</v>
+        <v>17.32</v>
       </c>
       <c r="G205">
-        <v>-4.12</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="B206" t="s">
-        <v>510</v>
+        <v>465</v>
       </c>
       <c r="C206" t="s">
         <v>614</v>
       </c>
       <c r="D206">
-        <v>99.92</v>
+        <v>3.78</v>
       </c>
       <c r="E206" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F206">
-        <v>112.71</v>
+        <v>4.25</v>
       </c>
       <c r="G206">
-        <v>12.8</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -7994,16 +8014,16 @@
         <v>614</v>
       </c>
       <c r="D207">
-        <v>17.5</v>
+        <v>24.22</v>
       </c>
       <c r="E207" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F207">
-        <v>15.77</v>
+        <v>25.26</v>
       </c>
       <c r="G207">
-        <v>-9.890000000000001</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8017,62 +8037,62 @@
         <v>614</v>
       </c>
       <c r="D208">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E208" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F208">
-        <v>57.19</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="G208">
-        <v>12.14</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="B209" t="s">
-        <v>513</v>
+        <v>449</v>
       </c>
       <c r="C209" t="s">
         <v>615</v>
       </c>
       <c r="D209">
-        <v>72.27</v>
+        <v>54.48</v>
       </c>
       <c r="E209" t="s">
         <v>677</v>
       </c>
       <c r="F209">
-        <v>71.89</v>
+        <v>50.89</v>
       </c>
       <c r="G209">
-        <v>-0.53</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="B210" t="s">
-        <v>439</v>
+        <v>513</v>
       </c>
       <c r="C210" t="s">
         <v>615</v>
       </c>
       <c r="D210">
-        <v>39.5</v>
+        <v>92.05</v>
       </c>
       <c r="E210" t="s">
         <v>677</v>
       </c>
       <c r="F210">
-        <v>41.43</v>
+        <v>100.71</v>
       </c>
       <c r="G210">
-        <v>4.89</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -8086,16 +8106,16 @@
         <v>615</v>
       </c>
       <c r="D211">
-        <v>85</v>
+        <v>11.42</v>
       </c>
       <c r="E211" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F211">
-        <v>72.3</v>
+        <v>11.01</v>
       </c>
       <c r="G211">
-        <v>-14.94</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -8109,131 +8129,131 @@
         <v>615</v>
       </c>
       <c r="D212">
-        <v>28.29</v>
+        <v>283.11</v>
       </c>
       <c r="E212" t="s">
         <v>677</v>
       </c>
       <c r="F212">
-        <v>27.71</v>
+        <v>289</v>
       </c>
       <c r="G212">
-        <v>-2.05</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="B213" t="s">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="C213" t="s">
         <v>615</v>
       </c>
       <c r="D213">
-        <v>27.59</v>
+        <v>38.39</v>
       </c>
       <c r="E213" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F213">
-        <v>28.41</v>
+        <v>39.68</v>
       </c>
       <c r="G213">
-        <v>2.97</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="B214" t="s">
-        <v>481</v>
+        <v>516</v>
       </c>
       <c r="C214" t="s">
         <v>615</v>
       </c>
       <c r="D214">
-        <v>38.39</v>
+        <v>85</v>
       </c>
       <c r="E214" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F214">
-        <v>39.68</v>
+        <v>72.3</v>
       </c>
       <c r="G214">
-        <v>3.36</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="B215" t="s">
-        <v>517</v>
+        <v>442</v>
       </c>
       <c r="C215" t="s">
         <v>615</v>
       </c>
       <c r="D215">
-        <v>11.42</v>
+        <v>39.5</v>
       </c>
       <c r="E215" t="s">
         <v>677</v>
       </c>
       <c r="F215">
-        <v>11.01</v>
+        <v>41.43</v>
       </c>
       <c r="G215">
-        <v>-3.59</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B216" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C216" t="s">
         <v>615</v>
       </c>
       <c r="D216">
-        <v>92.05</v>
+        <v>72.27</v>
       </c>
       <c r="E216" t="s">
         <v>677</v>
       </c>
       <c r="F216">
-        <v>100.71</v>
+        <v>71.89</v>
       </c>
       <c r="G216">
-        <v>9.41</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="B217" t="s">
-        <v>451</v>
+        <v>518</v>
       </c>
       <c r="C217" t="s">
         <v>615</v>
       </c>
       <c r="D217">
-        <v>54.48</v>
+        <v>27.59</v>
       </c>
       <c r="E217" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F217">
-        <v>50.89</v>
+        <v>28.41</v>
       </c>
       <c r="G217">
-        <v>-6.59</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -8247,16 +8267,16 @@
         <v>615</v>
       </c>
       <c r="D218">
-        <v>283.11</v>
+        <v>28.29</v>
       </c>
       <c r="E218" t="s">
         <v>677</v>
       </c>
       <c r="F218">
-        <v>289</v>
+        <v>27.71</v>
       </c>
       <c r="G218">
-        <v>2.08</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -8270,16 +8290,16 @@
         <v>616</v>
       </c>
       <c r="D219">
-        <v>37.25</v>
+        <v>13.3</v>
       </c>
       <c r="E219" t="s">
         <v>680</v>
       </c>
       <c r="F219">
-        <v>37.11</v>
+        <v>11.65</v>
       </c>
       <c r="G219">
-        <v>-0.38</v>
+        <v>-12.41</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -8293,16 +8313,16 @@
         <v>616</v>
       </c>
       <c r="D220">
-        <v>46</v>
+        <v>11.57</v>
       </c>
       <c r="E220" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F220">
-        <v>42.38</v>
+        <v>10.3</v>
       </c>
       <c r="G220">
-        <v>-7.87</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -8316,16 +8336,16 @@
         <v>616</v>
       </c>
       <c r="D221">
-        <v>81.34999999999999</v>
+        <v>5.87</v>
       </c>
       <c r="E221" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F221">
-        <v>77.02</v>
+        <v>5.85</v>
       </c>
       <c r="G221">
-        <v>-5.32</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -8339,16 +8359,16 @@
         <v>616</v>
       </c>
       <c r="D222">
-        <v>14.85</v>
+        <v>10.51</v>
       </c>
       <c r="E222" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F222">
-        <v>15.38</v>
+        <v>9.5</v>
       </c>
       <c r="G222">
-        <v>3.57</v>
+        <v>-9.609999999999999</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -8362,16 +8382,16 @@
         <v>616</v>
       </c>
       <c r="D223">
-        <v>10.52</v>
+        <v>9</v>
       </c>
       <c r="E223" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F223">
-        <v>8.66</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G223">
-        <v>-17.68</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -8385,16 +8405,16 @@
         <v>616</v>
       </c>
       <c r="D224">
-        <v>13.3</v>
+        <v>37.25</v>
       </c>
       <c r="E224" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F224">
-        <v>11.65</v>
+        <v>37.11</v>
       </c>
       <c r="G224">
-        <v>-12.41</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -8408,16 +8428,16 @@
         <v>616</v>
       </c>
       <c r="D225">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E225" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F225">
-        <v>8.380000000000001</v>
+        <v>42.38</v>
       </c>
       <c r="G225">
-        <v>-6.89</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -8431,16 +8451,16 @@
         <v>616</v>
       </c>
       <c r="D226">
-        <v>10.51</v>
+        <v>14.85</v>
       </c>
       <c r="E226" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F226">
-        <v>9.5</v>
+        <v>15.38</v>
       </c>
       <c r="G226">
-        <v>-9.609999999999999</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -8454,16 +8474,16 @@
         <v>616</v>
       </c>
       <c r="D227">
-        <v>5.87</v>
+        <v>10.52</v>
       </c>
       <c r="E227" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="F227">
-        <v>5.85</v>
+        <v>8.66</v>
       </c>
       <c r="G227">
-        <v>-0.34</v>
+        <v>-17.68</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -8477,16 +8497,16 @@
         <v>616</v>
       </c>
       <c r="D228">
-        <v>11.57</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="E228" t="s">
         <v>685</v>
       </c>
       <c r="F228">
-        <v>10.3</v>
+        <v>77.02</v>
       </c>
       <c r="G228">
-        <v>-10.98</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -8500,16 +8520,16 @@
         <v>617</v>
       </c>
       <c r="D229">
-        <v>92</v>
+        <v>5.4</v>
       </c>
       <c r="E229" t="s">
         <v>686</v>
       </c>
       <c r="F229">
-        <v>85</v>
+        <v>5.42</v>
       </c>
       <c r="G229">
-        <v>-7.61</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -8529,10 +8549,10 @@
         <v>687</v>
       </c>
       <c r="F230">
-        <v>33.87</v>
+        <v>36.11</v>
       </c>
       <c r="G230">
-        <v>-4.59</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -8546,16 +8566,16 @@
         <v>617</v>
       </c>
       <c r="D231">
-        <v>40.12</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E231" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F231">
-        <v>40.5</v>
+        <v>11.12</v>
       </c>
       <c r="G231">
-        <v>0.95</v>
+        <v>15.47</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -8569,16 +8589,16 @@
         <v>617</v>
       </c>
       <c r="D232">
-        <v>56.01</v>
+        <v>5.77</v>
       </c>
       <c r="E232" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F232">
-        <v>53.66</v>
+        <v>5.89</v>
       </c>
       <c r="G232">
-        <v>-4.2</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -8592,16 +8612,16 @@
         <v>617</v>
       </c>
       <c r="D233">
-        <v>5.77</v>
+        <v>56.01</v>
       </c>
       <c r="E233" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F233">
-        <v>5.89</v>
+        <v>53.66</v>
       </c>
       <c r="G233">
-        <v>2.08</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -8615,16 +8635,16 @@
         <v>617</v>
       </c>
       <c r="D234">
-        <v>9.630000000000001</v>
+        <v>35.5</v>
       </c>
       <c r="E234" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F234">
-        <v>11.12</v>
+        <v>33.87</v>
       </c>
       <c r="G234">
-        <v>15.47</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -8638,16 +8658,16 @@
         <v>617</v>
       </c>
       <c r="D235">
-        <v>35.5</v>
+        <v>92</v>
       </c>
       <c r="E235" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F235">
-        <v>36.11</v>
+        <v>85</v>
       </c>
       <c r="G235">
-        <v>1.72</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -8661,16 +8681,16 @@
         <v>617</v>
       </c>
       <c r="D236">
-        <v>5.4</v>
+        <v>40.12</v>
       </c>
       <c r="E236" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F236">
-        <v>5.42</v>
+        <v>40.5</v>
       </c>
       <c r="G236">
-        <v>0.37</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -8684,185 +8704,185 @@
         <v>618</v>
       </c>
       <c r="D237">
-        <v>25.95</v>
+        <v>11.31</v>
       </c>
       <c r="E237" t="s">
         <v>690</v>
       </c>
       <c r="F237">
-        <v>27.59</v>
+        <v>9.74</v>
       </c>
       <c r="G237">
-        <v>6.32</v>
+        <v>-13.88</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>206</v>
+        <v>269</v>
       </c>
       <c r="B238" t="s">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="C238" t="s">
         <v>618</v>
       </c>
       <c r="D238">
-        <v>19.56</v>
+        <v>98.52</v>
       </c>
       <c r="E238" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F238">
-        <v>18.54</v>
+        <v>92.31</v>
       </c>
       <c r="G238">
-        <v>-5.21</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B239" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C239" t="s">
         <v>618</v>
       </c>
       <c r="D239">
-        <v>18.37</v>
+        <v>7.95</v>
       </c>
       <c r="E239" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F239">
-        <v>20.45</v>
+        <v>6.13</v>
       </c>
       <c r="G239">
-        <v>11.32</v>
+        <v>-22.89</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B240" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C240" t="s">
         <v>618</v>
       </c>
       <c r="D240">
-        <v>53.58</v>
+        <v>6.12</v>
       </c>
       <c r="E240" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F240">
-        <v>52.65</v>
+        <v>6.48</v>
       </c>
       <c r="G240">
-        <v>-1.74</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B241" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C241" t="s">
         <v>618</v>
       </c>
       <c r="D241">
-        <v>6.12</v>
+        <v>18.37</v>
       </c>
       <c r="E241" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F241">
-        <v>6.48</v>
+        <v>19.04</v>
       </c>
       <c r="G241">
-        <v>5.88</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B242" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C242" t="s">
         <v>618</v>
       </c>
       <c r="D242">
-        <v>9.84</v>
+        <v>25.95</v>
       </c>
       <c r="E242" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F242">
-        <v>9.390000000000001</v>
+        <v>27.59</v>
       </c>
       <c r="G242">
-        <v>-4.57</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C243" t="s">
         <v>618</v>
       </c>
       <c r="D243">
-        <v>98.52</v>
+        <v>53.58</v>
       </c>
       <c r="E243" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F243">
-        <v>92.31</v>
+        <v>52.65</v>
       </c>
       <c r="G243">
-        <v>-6.3</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B244" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C244" t="s">
         <v>618</v>
       </c>
       <c r="D244">
-        <v>7.95</v>
+        <v>18.37</v>
       </c>
       <c r="E244" t="s">
         <v>693</v>
       </c>
       <c r="F244">
-        <v>6.13</v>
+        <v>20.45</v>
       </c>
       <c r="G244">
-        <v>-22.89</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B245" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C245" t="s">
         <v>618</v>
@@ -8871,7 +8891,7 @@
         <v>3.71</v>
       </c>
       <c r="E245" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F245">
         <v>3.84</v>
@@ -8882,25 +8902,25 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>276</v>
+        <v>206</v>
       </c>
       <c r="B246" t="s">
-        <v>546</v>
+        <v>476</v>
       </c>
       <c r="C246" t="s">
         <v>618</v>
       </c>
       <c r="D246">
-        <v>11.31</v>
+        <v>19.56</v>
       </c>
       <c r="E246" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F246">
-        <v>9.74</v>
+        <v>18.54</v>
       </c>
       <c r="G246">
-        <v>-13.88</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -8914,16 +8934,16 @@
         <v>618</v>
       </c>
       <c r="D247">
-        <v>18.37</v>
+        <v>9.84</v>
       </c>
       <c r="E247" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="F247">
-        <v>19.04</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G247">
-        <v>3.65</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -8937,16 +8957,16 @@
         <v>619</v>
       </c>
       <c r="D248">
-        <v>28.95</v>
+        <v>20.13</v>
       </c>
       <c r="E248" t="s">
         <v>695</v>
       </c>
       <c r="F248">
-        <v>31.66</v>
+        <v>20.42</v>
       </c>
       <c r="G248">
-        <v>9.359999999999999</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -8960,16 +8980,16 @@
         <v>619</v>
       </c>
       <c r="D249">
-        <v>12.98</v>
+        <v>2.53</v>
       </c>
       <c r="E249" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F249">
-        <v>12.48</v>
+        <v>2.52</v>
       </c>
       <c r="G249">
-        <v>-3.85</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -8983,16 +9003,16 @@
         <v>619</v>
       </c>
       <c r="D250">
-        <v>28.9</v>
+        <v>5.8</v>
       </c>
       <c r="E250" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F250">
-        <v>28</v>
+        <v>5.51</v>
       </c>
       <c r="G250">
-        <v>-3.11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -9006,16 +9026,16 @@
         <v>619</v>
       </c>
       <c r="D251">
-        <v>66.33</v>
+        <v>12.99</v>
       </c>
       <c r="E251" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F251">
-        <v>69</v>
+        <v>12.35</v>
       </c>
       <c r="G251">
-        <v>4.03</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -9029,16 +9049,16 @@
         <v>619</v>
       </c>
       <c r="D252">
-        <v>7.15</v>
+        <v>30.42</v>
       </c>
       <c r="E252" t="s">
         <v>695</v>
       </c>
       <c r="F252">
-        <v>7.06</v>
+        <v>31.31</v>
       </c>
       <c r="G252">
-        <v>-1.26</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -9052,16 +9072,16 @@
         <v>619</v>
       </c>
       <c r="D253">
-        <v>20.13</v>
+        <v>7.15</v>
       </c>
       <c r="E253" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F253">
-        <v>20.42</v>
+        <v>7.06</v>
       </c>
       <c r="G253">
-        <v>1.44</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -9075,16 +9095,16 @@
         <v>619</v>
       </c>
       <c r="D254">
-        <v>30.42</v>
+        <v>28.9</v>
       </c>
       <c r="E254" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F254">
-        <v>31.31</v>
+        <v>28</v>
       </c>
       <c r="G254">
-        <v>2.93</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -9098,16 +9118,16 @@
         <v>619</v>
       </c>
       <c r="D255">
-        <v>5.8</v>
+        <v>12.98</v>
       </c>
       <c r="E255" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F255">
-        <v>5.51</v>
+        <v>12.48</v>
       </c>
       <c r="G255">
-        <v>-5</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -9121,16 +9141,16 @@
         <v>619</v>
       </c>
       <c r="D256">
-        <v>2.53</v>
+        <v>28.95</v>
       </c>
       <c r="E256" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F256">
-        <v>2.52</v>
+        <v>31.66</v>
       </c>
       <c r="G256">
-        <v>-0.4</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -9144,16 +9164,16 @@
         <v>619</v>
       </c>
       <c r="D257">
-        <v>12.99</v>
+        <v>66.33</v>
       </c>
       <c r="E257" t="s">
         <v>695</v>
       </c>
       <c r="F257">
-        <v>12.35</v>
+        <v>69</v>
       </c>
       <c r="G257">
-        <v>-4.93</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -9167,16 +9187,16 @@
         <v>620</v>
       </c>
       <c r="D258">
-        <v>53.4</v>
+        <v>20.33</v>
       </c>
       <c r="E258" t="s">
         <v>699</v>
       </c>
       <c r="F258">
-        <v>59.38</v>
+        <v>20.96</v>
       </c>
       <c r="G258">
-        <v>11.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -9190,16 +9210,16 @@
         <v>620</v>
       </c>
       <c r="D259">
-        <v>8.83</v>
+        <v>22.21</v>
       </c>
       <c r="E259" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F259">
-        <v>8.779999999999999</v>
+        <v>22.99</v>
       </c>
       <c r="G259">
-        <v>-0.57</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -9213,85 +9233,85 @@
         <v>620</v>
       </c>
       <c r="D260">
-        <v>5.77</v>
+        <v>65</v>
       </c>
       <c r="E260" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F260">
-        <v>5.88</v>
+        <v>63.89</v>
       </c>
       <c r="G260">
-        <v>1.91</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="B261" t="s">
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="C261" t="s">
         <v>620</v>
       </c>
       <c r="D261">
-        <v>23.6</v>
+        <v>33.6</v>
       </c>
       <c r="E261" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F261">
-        <v>23.77</v>
+        <v>36.82</v>
       </c>
       <c r="G261">
-        <v>0.72</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B262" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C262" t="s">
         <v>620</v>
       </c>
       <c r="D262">
-        <v>22.54</v>
+        <v>19.3</v>
       </c>
       <c r="E262" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F262">
-        <v>24.82</v>
+        <v>19.19</v>
       </c>
       <c r="G262">
-        <v>10.12</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>292</v>
+        <v>233</v>
       </c>
       <c r="B263" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="C263" t="s">
         <v>620</v>
       </c>
       <c r="D263">
-        <v>20.33</v>
+        <v>23.6</v>
       </c>
       <c r="E263" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F263">
-        <v>20.96</v>
+        <v>23.77</v>
       </c>
       <c r="G263">
-        <v>3.1</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -9305,16 +9325,16 @@
         <v>620</v>
       </c>
       <c r="D264">
-        <v>33.6</v>
+        <v>22.54</v>
       </c>
       <c r="E264" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F264">
-        <v>36.82</v>
+        <v>24.82</v>
       </c>
       <c r="G264">
-        <v>9.58</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -9328,16 +9348,16 @@
         <v>620</v>
       </c>
       <c r="D265">
-        <v>65</v>
+        <v>8.83</v>
       </c>
       <c r="E265" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F265">
-        <v>63.89</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G265">
-        <v>-1.71</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -9351,16 +9371,16 @@
         <v>620</v>
       </c>
       <c r="D266">
-        <v>22.21</v>
+        <v>5.77</v>
       </c>
       <c r="E266" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F266">
-        <v>22.99</v>
+        <v>5.88</v>
       </c>
       <c r="G266">
-        <v>3.51</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -9374,16 +9394,16 @@
         <v>620</v>
       </c>
       <c r="D267">
-        <v>19.3</v>
+        <v>53.4</v>
       </c>
       <c r="E267" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F267">
-        <v>19.19</v>
+        <v>59.38</v>
       </c>
       <c r="G267">
-        <v>-0.57</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -9397,223 +9417,223 @@
         <v>621</v>
       </c>
       <c r="D268">
-        <v>6.87</v>
+        <v>21.59</v>
       </c>
       <c r="E268" t="s">
         <v>703</v>
       </c>
       <c r="F268">
-        <v>7.1</v>
+        <v>23.13</v>
       </c>
       <c r="G268">
-        <v>3.35</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>298</v>
+        <v>123</v>
       </c>
       <c r="B269" t="s">
-        <v>568</v>
+        <v>393</v>
       </c>
       <c r="C269" t="s">
         <v>621</v>
       </c>
       <c r="D269">
-        <v>104</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E269" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F269">
-        <v>100.61</v>
+        <v>86.3</v>
       </c>
       <c r="G269">
-        <v>-3.26</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="B270" t="s">
-        <v>504</v>
+        <v>568</v>
       </c>
       <c r="C270" t="s">
         <v>621</v>
       </c>
       <c r="D270">
-        <v>36.47</v>
+        <v>11.6</v>
       </c>
       <c r="E270" t="s">
         <v>703</v>
       </c>
       <c r="F270">
-        <v>36.13</v>
+        <v>11.89</v>
       </c>
       <c r="G270">
-        <v>-0.93</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="B271" t="s">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="C271" t="s">
         <v>621</v>
       </c>
       <c r="D271">
-        <v>128.8</v>
+        <v>206.01</v>
       </c>
       <c r="E271" t="s">
         <v>703</v>
       </c>
       <c r="F271">
-        <v>138.99</v>
+        <v>242.63</v>
       </c>
       <c r="G271">
-        <v>7.91</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B272" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C272" t="s">
         <v>621</v>
       </c>
       <c r="D272">
-        <v>28.03</v>
+        <v>20.66</v>
       </c>
       <c r="E272" t="s">
         <v>703</v>
       </c>
       <c r="F272">
-        <v>26.98</v>
+        <v>18.1</v>
       </c>
       <c r="G272">
-        <v>-3.75</v>
+        <v>-12.39</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B273" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C273" t="s">
         <v>621</v>
       </c>
       <c r="D273">
-        <v>21.59</v>
+        <v>128.8</v>
       </c>
       <c r="E273" t="s">
         <v>703</v>
       </c>
       <c r="F273">
-        <v>23.13</v>
+        <v>138.99</v>
       </c>
       <c r="G273">
-        <v>7.13</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="B274" t="s">
-        <v>572</v>
+        <v>512</v>
       </c>
       <c r="C274" t="s">
         <v>621</v>
       </c>
       <c r="D274">
-        <v>20.66</v>
+        <v>36.47</v>
       </c>
       <c r="E274" t="s">
         <v>703</v>
       </c>
       <c r="F274">
-        <v>18.1</v>
+        <v>36.13</v>
       </c>
       <c r="G274">
-        <v>-12.39</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="B275" t="s">
-        <v>519</v>
+        <v>571</v>
       </c>
       <c r="C275" t="s">
         <v>621</v>
       </c>
       <c r="D275">
-        <v>206.01</v>
+        <v>104</v>
       </c>
       <c r="E275" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F275">
-        <v>242.63</v>
+        <v>100.61</v>
       </c>
       <c r="G275">
-        <v>17.78</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B276" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C276" t="s">
         <v>621</v>
       </c>
       <c r="D276">
-        <v>11.6</v>
+        <v>6.87</v>
       </c>
       <c r="E276" t="s">
         <v>703</v>
       </c>
       <c r="F276">
-        <v>11.89</v>
+        <v>7.1</v>
       </c>
       <c r="G276">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="B277" t="s">
-        <v>393</v>
+        <v>573</v>
       </c>
       <c r="C277" t="s">
         <v>621</v>
       </c>
       <c r="D277">
-        <v>73.98999999999999</v>
+        <v>28.03</v>
       </c>
       <c r="E277" t="s">
         <v>703</v>
       </c>
       <c r="F277">
-        <v>86.3</v>
+        <v>26.98</v>
       </c>
       <c r="G277">
-        <v>16.64</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -9627,16 +9647,16 @@
         <v>622</v>
       </c>
       <c r="D278">
-        <v>233</v>
+        <v>246.4</v>
       </c>
       <c r="E278" t="s">
         <v>705</v>
       </c>
       <c r="F278">
-        <v>245.3</v>
+        <v>259.59</v>
       </c>
       <c r="G278">
-        <v>5.28</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -9650,177 +9670,177 @@
         <v>622</v>
       </c>
       <c r="D279">
-        <v>141.34</v>
+        <v>13.44</v>
       </c>
       <c r="E279" t="s">
         <v>705</v>
       </c>
       <c r="F279">
-        <v>133.73</v>
+        <v>13.27</v>
       </c>
       <c r="G279">
-        <v>-5.38</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>112</v>
+        <v>306</v>
       </c>
       <c r="B280" t="s">
-        <v>382</v>
+        <v>576</v>
       </c>
       <c r="C280" t="s">
         <v>622</v>
       </c>
       <c r="D280">
-        <v>107.92</v>
+        <v>5.12</v>
       </c>
       <c r="E280" t="s">
         <v>705</v>
       </c>
       <c r="F280">
-        <v>107.21</v>
+        <v>4.13</v>
       </c>
       <c r="G280">
-        <v>-0.66</v>
+        <v>-19.34</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B281" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C281" t="s">
         <v>622</v>
       </c>
       <c r="D281">
-        <v>15</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="E281" t="s">
         <v>705</v>
       </c>
       <c r="F281">
-        <v>10.69</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="G281">
-        <v>-28.73</v>
+        <v>-13.02</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B282" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C282" t="s">
         <v>622</v>
       </c>
       <c r="D282">
-        <v>5.55</v>
+        <v>6.39</v>
       </c>
       <c r="E282" t="s">
         <v>705</v>
       </c>
       <c r="F282">
-        <v>5.03</v>
+        <v>5.99</v>
       </c>
       <c r="G282">
-        <v>-9.369999999999999</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B283" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C283" t="s">
         <v>622</v>
       </c>
       <c r="D283">
-        <v>88.81999999999999</v>
+        <v>15</v>
       </c>
       <c r="E283" t="s">
         <v>705</v>
       </c>
       <c r="F283">
-        <v>77.26000000000001</v>
+        <v>10.69</v>
       </c>
       <c r="G283">
-        <v>-13.02</v>
+        <v>-28.73</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B284" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C284" t="s">
         <v>622</v>
       </c>
       <c r="D284">
-        <v>6.39</v>
+        <v>141.34</v>
       </c>
       <c r="E284" t="s">
         <v>705</v>
       </c>
       <c r="F284">
-        <v>5.99</v>
+        <v>133.73</v>
       </c>
       <c r="G284">
-        <v>-6.26</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B285" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C285" t="s">
         <v>622</v>
       </c>
       <c r="D285">
-        <v>5.12</v>
+        <v>233</v>
       </c>
       <c r="E285" t="s">
         <v>705</v>
       </c>
       <c r="F285">
-        <v>4.13</v>
+        <v>245.3</v>
       </c>
       <c r="G285">
-        <v>-19.34</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>311</v>
+        <v>111</v>
       </c>
       <c r="B286" t="s">
-        <v>581</v>
+        <v>381</v>
       </c>
       <c r="C286" t="s">
         <v>622</v>
       </c>
       <c r="D286">
-        <v>13.44</v>
+        <v>107.92</v>
       </c>
       <c r="E286" t="s">
         <v>705</v>
       </c>
       <c r="F286">
-        <v>13.27</v>
+        <v>107.21</v>
       </c>
       <c r="G286">
-        <v>-1.26</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -9834,16 +9854,16 @@
         <v>622</v>
       </c>
       <c r="D287">
-        <v>246.4</v>
+        <v>5.55</v>
       </c>
       <c r="E287" t="s">
         <v>705</v>
       </c>
       <c r="F287">
-        <v>259.59</v>
+        <v>5.03</v>
       </c>
       <c r="G287">
-        <v>5.35</v>
+        <v>-9.369999999999999</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -9871,79 +9891,79 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B289" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C289" t="s">
         <v>623</v>
       </c>
       <c r="D289">
-        <v>27.84</v>
+        <v>12.4</v>
       </c>
       <c r="E289" t="s">
         <v>706</v>
       </c>
       <c r="F289">
-        <v>27.5</v>
+        <v>11.98</v>
       </c>
       <c r="G289">
-        <v>-1.22</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B290" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C290" t="s">
         <v>623</v>
       </c>
       <c r="D290">
-        <v>4.15</v>
+        <v>27.84</v>
       </c>
       <c r="E290" t="s">
         <v>706</v>
       </c>
       <c r="F290">
-        <v>5.67</v>
+        <v>27.5</v>
       </c>
       <c r="G290">
-        <v>36.63</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B291" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C291" t="s">
         <v>623</v>
       </c>
       <c r="D291">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="E291" t="s">
         <v>706</v>
       </c>
       <c r="F291">
-        <v>12.81</v>
+        <v>11.98</v>
       </c>
       <c r="G291">
-        <v>5.87</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B292" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C292" t="s">
         <v>623</v>
@@ -9963,163 +9983,163 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B293" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C293" t="s">
         <v>623</v>
       </c>
       <c r="D293">
-        <v>12.35</v>
+        <v>4.87</v>
       </c>
       <c r="E293" t="s">
         <v>706</v>
       </c>
       <c r="F293">
-        <v>12.66</v>
+        <v>5.04</v>
       </c>
       <c r="G293">
-        <v>2.51</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B294" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C294" t="s">
         <v>623</v>
       </c>
       <c r="D294">
-        <v>3.53</v>
+        <v>12.35</v>
       </c>
       <c r="E294" t="s">
         <v>706</v>
       </c>
       <c r="F294">
-        <v>3.42</v>
+        <v>12.66</v>
       </c>
       <c r="G294">
-        <v>-3.12</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B295" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C295" t="s">
         <v>623</v>
       </c>
       <c r="D295">
-        <v>4.87</v>
+        <v>64.66</v>
       </c>
       <c r="E295" t="s">
         <v>706</v>
       </c>
       <c r="F295">
-        <v>5.04</v>
+        <v>61.77</v>
       </c>
       <c r="G295">
-        <v>3.49</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B296" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C296" t="s">
         <v>623</v>
       </c>
       <c r="D296">
-        <v>3.53</v>
+        <v>12.1</v>
       </c>
       <c r="E296" t="s">
         <v>706</v>
       </c>
       <c r="F296">
-        <v>3.42</v>
+        <v>12.81</v>
       </c>
       <c r="G296">
-        <v>-3.12</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B297" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C297" t="s">
         <v>623</v>
       </c>
       <c r="D297">
-        <v>12.35</v>
+        <v>4.15</v>
       </c>
       <c r="E297" t="s">
         <v>706</v>
       </c>
       <c r="F297">
-        <v>12.66</v>
+        <v>5.67</v>
       </c>
       <c r="G297">
-        <v>2.51</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B298" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C298" t="s">
         <v>623</v>
       </c>
       <c r="D298">
-        <v>12.4</v>
+        <v>27.84</v>
       </c>
       <c r="E298" t="s">
         <v>706</v>
       </c>
       <c r="F298">
-        <v>11.98</v>
+        <v>27.5</v>
       </c>
       <c r="G298">
-        <v>-3.39</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B299" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C299" t="s">
         <v>623</v>
       </c>
       <c r="D299">
-        <v>12.1</v>
+        <v>4.15</v>
       </c>
       <c r="E299" t="s">
         <v>706</v>
       </c>
       <c r="F299">
-        <v>12.81</v>
+        <v>5.67</v>
       </c>
       <c r="G299">
-        <v>5.87</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -10147,125 +10167,125 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B301" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C301" t="s">
         <v>623</v>
       </c>
       <c r="D301">
-        <v>64.66</v>
+        <v>3.53</v>
       </c>
       <c r="E301" t="s">
         <v>706</v>
       </c>
       <c r="F301">
-        <v>61.77</v>
+        <v>3.42</v>
       </c>
       <c r="G301">
-        <v>-4.47</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B302" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C302" t="s">
         <v>623</v>
       </c>
       <c r="D302">
-        <v>4.87</v>
+        <v>12.35</v>
       </c>
       <c r="E302" t="s">
         <v>706</v>
       </c>
       <c r="F302">
-        <v>5.04</v>
+        <v>12.66</v>
       </c>
       <c r="G302">
-        <v>3.49</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B303" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C303" t="s">
         <v>623</v>
       </c>
       <c r="D303">
-        <v>3.53</v>
+        <v>12.1</v>
       </c>
       <c r="E303" t="s">
         <v>706</v>
       </c>
       <c r="F303">
-        <v>3.42</v>
+        <v>12.81</v>
       </c>
       <c r="G303">
-        <v>-3.12</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B304" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C304" t="s">
         <v>623</v>
       </c>
       <c r="D304">
-        <v>12.35</v>
+        <v>27.84</v>
       </c>
       <c r="E304" t="s">
         <v>706</v>
       </c>
       <c r="F304">
-        <v>12.66</v>
+        <v>27.5</v>
       </c>
       <c r="G304">
-        <v>2.51</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B305" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C305" t="s">
         <v>623</v>
       </c>
       <c r="D305">
-        <v>64.66</v>
+        <v>4.15</v>
       </c>
       <c r="E305" t="s">
         <v>706</v>
       </c>
       <c r="F305">
-        <v>61.77</v>
+        <v>5.67</v>
       </c>
       <c r="G305">
-        <v>-4.47</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B306" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C306" t="s">
         <v>623</v>
@@ -10294,107 +10314,291 @@
         <v>623</v>
       </c>
       <c r="D307">
-        <v>4.15</v>
+        <v>64.66</v>
       </c>
       <c r="E307" t="s">
         <v>706</v>
       </c>
       <c r="F307">
-        <v>5.67</v>
+        <v>61.77</v>
       </c>
       <c r="G307">
-        <v>36.63</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B308" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C308" t="s">
         <v>623</v>
       </c>
       <c r="D308">
-        <v>27.84</v>
+        <v>12.35</v>
       </c>
       <c r="E308" t="s">
         <v>706</v>
       </c>
       <c r="F308">
-        <v>27.5</v>
+        <v>12.66</v>
       </c>
       <c r="G308">
-        <v>-1.22</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B309" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C309" t="s">
         <v>623</v>
       </c>
       <c r="D309">
-        <v>4.15</v>
+        <v>3.53</v>
       </c>
       <c r="E309" t="s">
         <v>706</v>
       </c>
       <c r="F309">
-        <v>5.67</v>
+        <v>3.42</v>
       </c>
       <c r="G309">
-        <v>36.63</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B310" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C310" t="s">
         <v>623</v>
       </c>
       <c r="D310">
-        <v>27.84</v>
+        <v>4.87</v>
       </c>
       <c r="E310" t="s">
         <v>706</v>
       </c>
       <c r="F310">
-        <v>27.5</v>
+        <v>5.04</v>
       </c>
       <c r="G310">
-        <v>-1.22</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B311" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C311" t="s">
         <v>623</v>
       </c>
       <c r="D311">
-        <v>4.87</v>
+        <v>27.84</v>
       </c>
       <c r="E311" t="s">
         <v>706</v>
       </c>
       <c r="F311">
+        <v>27.5</v>
+      </c>
+      <c r="G311">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" t="s">
+        <v>319</v>
+      </c>
+      <c r="B312" t="s">
+        <v>589</v>
+      </c>
+      <c r="C312" t="s">
+        <v>623</v>
+      </c>
+      <c r="D312">
+        <v>4.15</v>
+      </c>
+      <c r="E312" t="s">
+        <v>706</v>
+      </c>
+      <c r="F312">
+        <v>5.67</v>
+      </c>
+      <c r="G312">
+        <v>36.63</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" t="s">
+        <v>318</v>
+      </c>
+      <c r="B313" t="s">
+        <v>588</v>
+      </c>
+      <c r="C313" t="s">
+        <v>623</v>
+      </c>
+      <c r="D313">
+        <v>12.1</v>
+      </c>
+      <c r="E313" t="s">
+        <v>706</v>
+      </c>
+      <c r="F313">
+        <v>12.81</v>
+      </c>
+      <c r="G313">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" t="s">
+        <v>315</v>
+      </c>
+      <c r="B314" t="s">
+        <v>585</v>
+      </c>
+      <c r="C314" t="s">
+        <v>623</v>
+      </c>
+      <c r="D314">
+        <v>64.66</v>
+      </c>
+      <c r="E314" t="s">
+        <v>706</v>
+      </c>
+      <c r="F314">
+        <v>61.77</v>
+      </c>
+      <c r="G314">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" t="s">
+        <v>317</v>
+      </c>
+      <c r="B315" t="s">
+        <v>587</v>
+      </c>
+      <c r="C315" t="s">
+        <v>623</v>
+      </c>
+      <c r="D315">
+        <v>12.35</v>
+      </c>
+      <c r="E315" t="s">
+        <v>706</v>
+      </c>
+      <c r="F315">
+        <v>12.66</v>
+      </c>
+      <c r="G315">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" t="s">
+        <v>320</v>
+      </c>
+      <c r="B316" t="s">
+        <v>590</v>
+      </c>
+      <c r="C316" t="s">
+        <v>623</v>
+      </c>
+      <c r="D316">
+        <v>3.53</v>
+      </c>
+      <c r="E316" t="s">
+        <v>706</v>
+      </c>
+      <c r="F316">
+        <v>3.42</v>
+      </c>
+      <c r="G316">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" t="s">
+        <v>590</v>
+      </c>
+      <c r="C317" t="s">
+        <v>623</v>
+      </c>
+      <c r="D317">
+        <v>3.53</v>
+      </c>
+      <c r="E317" t="s">
+        <v>706</v>
+      </c>
+      <c r="F317">
+        <v>3.42</v>
+      </c>
+      <c r="G317">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" t="s">
+        <v>316</v>
+      </c>
+      <c r="B318" t="s">
+        <v>586</v>
+      </c>
+      <c r="C318" t="s">
+        <v>623</v>
+      </c>
+      <c r="D318">
+        <v>4.87</v>
+      </c>
+      <c r="E318" t="s">
+        <v>706</v>
+      </c>
+      <c r="F318">
         <v>5.04</v>
       </c>
-      <c r="G311">
+      <c r="G318">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" t="s">
+        <v>316</v>
+      </c>
+      <c r="B319" t="s">
+        <v>586</v>
+      </c>
+      <c r="C319" t="s">
+        <v>623</v>
+      </c>
+      <c r="D319">
+        <v>4.87</v>
+      </c>
+      <c r="E319" t="s">
+        <v>706</v>
+      </c>
+      <c r="F319">
+        <v>5.04</v>
+      </c>
+      <c r="G319">
         <v>3.49</v>
       </c>
     </row>
